--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.168</t>
+          <t>$1.169</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+39.1%</t>
+          <t>+40.0%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.131</t>
+          <t>$1.135</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1787,10 +1787,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.13806875</v>
+        <v>1.14308125</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.12975</v>
+        <v>1.14324375</v>
       </c>
       <c r="F13" s="32" t="n">
         <v>0.6522</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.7403</v>
+        <v>0.8205</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.7711</v>
+        <v>0.987</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1200</v>
+        <v>1330</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1250</v>
+        <v>1600</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="72" t="inlineStr">
         <is>
-          <t>▲ +26.3%</t>
+          <t>▲ +40.0%</t>
         </is>
       </c>
       <c r="K23" s="69" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.167846296296296</v>
+        <v>1.169331481481481</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.131401851851852</v>
+        <v>1.1354</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.7403</v>
+        <v>0.8205</v>
       </c>
       <c r="E24" s="72" t="inlineStr">
         <is>
-          <t>▲ +26.3%</t>
+          <t>▲ +40.0%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.7711</v>
+        <v>0.987</v>
       </c>
       <c r="H24" s="72" t="inlineStr">
         <is>
-          <t>▲ +4.2%</t>
+          <t>▲ +33.3%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1200</v>
+        <v>1330</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1250</v>
+        <v>1600</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -7650,23 +7650,23 @@
       </c>
       <c r="G11" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Nigeria</t>
+          <t xml:space="preserve">  7.  Botswana</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.7403</v>
+        <v>0.7792</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.7711</v>
-      </c>
-      <c r="K11" s="114" t="inlineStr">
-        <is>
-          <t>▲ +26.3%</t>
+        <v>0.7792</v>
+      </c>
+      <c r="K11" s="112" t="inlineStr">
+        <is>
+          <t>▼ -31.8%</t>
         </is>
       </c>
     </row>
@@ -7694,23 +7694,23 @@
       </c>
       <c r="G12" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Botswana</t>
+          <t xml:space="preserve">  8.  Nigeria</t>
         </is>
       </c>
       <c r="H12" s="106" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I12" s="107" t="n">
-        <v>0.7792</v>
+        <v>0.8205</v>
       </c>
       <c r="J12" s="108" t="n">
-        <v>0.7792</v>
-      </c>
-      <c r="K12" s="112" t="inlineStr">
-        <is>
-          <t>▼ -31.8%</t>
+        <v>0.987</v>
+      </c>
+      <c r="K12" s="114" t="inlineStr">
+        <is>
+          <t>▲ +40.0%</t>
         </is>
       </c>
     </row>
@@ -7850,38 +7850,38 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>1.15</v>
+        <v>0.5861</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.6</v>
+        <v>0.8205</v>
       </c>
       <c r="F19" s="72" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +40.0%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.45</v>
+        <v>0.2344</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
@@ -7891,53 +7891,53 @@
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>0.8398</v>
+        <v>1.6</v>
       </c>
       <c r="F20" s="72" t="inlineStr">
         <is>
-          <t>▲ +30.3%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.1951</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>0.5861</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>0.7403</v>
+        <v>0.8398</v>
       </c>
       <c r="F21" s="72" t="inlineStr">
         <is>
-          <t>▲ +26.3%</t>
+          <t>▲ +30.3%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.1542</v>
+        <v>0.1951</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -9045,10 +9045,10 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.13806875</v>
+        <v>1.14308125</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.12975</v>
+        <v>1.14324375</v>
       </c>
       <c r="E14" s="131" t="n">
         <v>0.6522</v>
@@ -9521,20 +9521,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.7403</v>
+        <v>0.8205</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.7711</v>
+        <v>0.987</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1200</v>
+        <v>1330</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1250</v>
+        <v>1600</v>
       </c>
       <c r="G28" s="72" t="inlineStr">
         <is>
-          <t>▲ +26.3%</t>
+          <t>▲ +40.0%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1768,7 +1768,7 @@
         <v>0.6327166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.60015</v>
+        <v>0.6001500000000001</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -8772,7 +8772,7 @@
         <v>0.6327166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.60015</v>
+        <v>0.6001500000000001</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1073,6 +1073,9 @@
     <xf numFmtId="164" fontId="19" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1090,9 +1093,6 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-03-30</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-03-31</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.169</t>
+          <t>$1.172</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+40.0%</t>
+          <t>+56.5%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.135</t>
+          <t>$1.136</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1768,7 +1768,7 @@
         <v>0.6327166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6001500000000001</v>
+        <v>0.6112333333333333</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,16 +1787,16 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.14308125</v>
+        <v>1.12671875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.14324375</v>
+        <v>1.11750625</v>
       </c>
       <c r="F13" s="32" t="n">
         <v>0.6522</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>1.5232</v>
+        <v>1.6391</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1831,10 +1831,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.419066666666667</v>
+        <v>1.430346666666666</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.354446666666667</v>
+        <v>1.358573333333333</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.6602</v>
@@ -1853,16 +1853,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.114822222222222</v>
+        <v>1.141366666666667</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.061933333333333</v>
+        <v>1.094111111111111</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>2.17</v>
+        <v>2.1204</v>
       </c>
     </row>
     <row r="18" ht="10" customHeight="1"/>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D21" s="45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-03-30</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-03-31</t>
         </is>
       </c>
     </row>
@@ -2252,13 +2252,13 @@
         <v>1.0474</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="G8" s="58" t="n">
         <v>630</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
@@ -2350,23 +2350,23 @@
         </is>
       </c>
       <c r="E11" s="66" t="n">
-        <v>1.3576</v>
+        <v>1.1341</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>1.3742</v>
+        <v>1.1589</v>
       </c>
       <c r="G11" s="67" t="n">
-        <v>820</v>
+        <v>685</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>830</v>
+        <v>700</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
       </c>
-      <c r="J11" s="72" t="inlineStr">
-        <is>
-          <t>▲ +10.7%</t>
+      <c r="J11" s="70" t="inlineStr">
+        <is>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="K11" s="69" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.8205</v>
+        <v>0.6663</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.987</v>
+        <v>0.6663</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1330</v>
+        <v>1080</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1600</v>
+        <v>1080</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="72" t="inlineStr">
         <is>
-          <t>▲ +40.0%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="K23" s="69" t="inlineStr">
@@ -2961,23 +2961,23 @@
         </is>
       </c>
       <c r="E24" s="57" t="n">
-        <v>1.5232</v>
+        <v>1.6391</v>
       </c>
       <c r="F24" s="57" t="n">
-        <v>1.1258</v>
+        <v>1.25</v>
       </c>
       <c r="G24" s="58" t="n">
-        <v>920</v>
+        <v>990</v>
       </c>
       <c r="H24" s="58" t="n">
-        <v>680</v>
+        <v>755</v>
       </c>
       <c r="I24" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J24" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J24" s="72" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="K24" s="61" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="K30" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -3680,28 +3680,28 @@
         </is>
       </c>
       <c r="E41" s="66" t="n">
-        <v>0.8398</v>
+        <v>1.009</v>
       </c>
       <c r="F41" s="66" t="n">
-        <v>0.8884</v>
+        <v>1.046</v>
       </c>
       <c r="G41" s="67" t="n">
         <v>132.18</v>
       </c>
       <c r="H41" s="67" t="n">
-        <v>139.84</v>
+        <v>137.03</v>
       </c>
       <c r="I41" s="68" t="n">
-        <v>157.4</v>
+        <v>131</v>
       </c>
       <c r="J41" s="72" t="inlineStr">
         <is>
-          <t>▲ +30.3%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="K41" s="69" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -3918,13 +3918,13 @@
         <v>1.3595</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.3315</v>
+        <v>1.2358</v>
       </c>
       <c r="G46" s="58" t="n">
         <v>1989</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>1948</v>
+        <v>1808</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="K49" s="69" t="inlineStr">
         <is>
-          <t>🔴 Low</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -4486,28 +4486,28 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.1401</v>
+        <v>1.4286</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.0121</v>
+        <v>1.4286</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>20.75</v>
+        <v>26</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>18.42</v>
+        <v>26</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="70" t="inlineStr">
-        <is>
-          <t>▼ -7.5%</t>
+      <c r="J59" s="72" t="inlineStr">
+        <is>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="K59" s="69" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -4580,28 +4580,28 @@
         </is>
       </c>
       <c r="E61" s="66" t="n">
-        <v>2.17</v>
+        <v>2.1204</v>
       </c>
       <c r="F61" s="66" t="n">
-        <v>2.05</v>
+        <v>1.9231</v>
       </c>
       <c r="G61" s="67" t="n">
-        <v>56.42</v>
+        <v>55.13</v>
       </c>
       <c r="H61" s="67" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="I61" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="J61" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J61" s="70" t="inlineStr">
+        <is>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="K61" s="69" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.169331481481481</v>
+        <v>1.172040740740741</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.1354</v>
+        <v>1.135514814814815</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-03-30</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -4987,18 +4987,18 @@
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="H9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0474</v>
+      </c>
+      <c r="H9" s="72" t="inlineStr">
+        <is>
+          <t>▲ +6.8%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
         <v>630</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="K9" s="69" t="inlineStr">
         <is>
@@ -5073,29 +5073,29 @@
         <v>1.2262</v>
       </c>
       <c r="D12" s="91" t="n">
-        <v>1.3576</v>
-      </c>
-      <c r="E12" s="72" t="inlineStr">
-        <is>
-          <t>▲ +10.7%</t>
+        <v>1.1341</v>
+      </c>
+      <c r="E12" s="70" t="inlineStr">
+        <is>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="F12" s="90" t="n">
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>1.3742</v>
-      </c>
-      <c r="H12" s="72" t="inlineStr">
-        <is>
-          <t>▲ +9.1%</t>
+        <v>1.1589</v>
+      </c>
+      <c r="H12" s="70" t="inlineStr">
+        <is>
+          <t>▼ -8.0%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
-        <v>820</v>
+        <v>685</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>830</v>
+        <v>700</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.8205</v>
+        <v>0.6663</v>
       </c>
       <c r="E24" s="72" t="inlineStr">
         <is>
-          <t>▲ +40.0%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="H24" s="72" t="inlineStr">
-        <is>
-          <t>▲ +33.3%</t>
+        <v>0.6663</v>
+      </c>
+      <c r="H24" s="70" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1330</v>
+        <v>1080</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1600</v>
+        <v>1080</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -5658,29 +5658,29 @@
         <v>1.5244</v>
       </c>
       <c r="D25" s="89" t="n">
-        <v>1.5232</v>
-      </c>
-      <c r="E25" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.6391</v>
+      </c>
+      <c r="E25" s="72" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="F25" s="90" t="n">
         <v>1.1268</v>
       </c>
       <c r="G25" s="89" t="n">
-        <v>1.1258</v>
-      </c>
-      <c r="H25" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.25</v>
+      </c>
+      <c r="H25" s="72" t="inlineStr">
+        <is>
+          <t>▲ +10.9%</t>
         </is>
       </c>
       <c r="I25" s="67" t="n">
-        <v>920</v>
+        <v>990</v>
       </c>
       <c r="J25" s="67" t="n">
-        <v>680</v>
+        <v>755</v>
       </c>
       <c r="K25" s="69" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="K31" s="69" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -6347,33 +6347,33 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="D42" s="91" t="n">
-        <v>0.8398</v>
+        <v>1.009</v>
       </c>
       <c r="E42" s="72" t="inlineStr">
         <is>
-          <t>▲ +30.3%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="F42" s="90" t="n">
         <v>0.6288</v>
       </c>
       <c r="G42" s="91" t="n">
-        <v>0.8884</v>
+        <v>1.046</v>
       </c>
       <c r="H42" s="72" t="inlineStr">
         <is>
-          <t>▲ +41.3%</t>
+          <t>▲ +66.3%</t>
         </is>
       </c>
       <c r="I42" s="58" t="n">
         <v>132.18</v>
       </c>
       <c r="J42" s="58" t="n">
-        <v>139.84</v>
+        <v>137.03</v>
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -6583,18 +6583,18 @@
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.3315</v>
+        <v>1.2358</v>
       </c>
       <c r="H47" s="70" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -7.9%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
         <v>1989</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>1948</v>
+        <v>1808</v>
       </c>
       <c r="K47" s="69" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
-          <t>🔴 Low</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -7119,33 +7119,33 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.1401</v>
-      </c>
-      <c r="E60" s="70" t="inlineStr">
-        <is>
-          <t>▼ -7.5%</t>
+        <v>1.4286</v>
+      </c>
+      <c r="E60" s="72" t="inlineStr">
+        <is>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.0121</v>
-      </c>
-      <c r="H60" s="70" t="inlineStr">
-        <is>
-          <t>▼ -21.4%</t>
+        <v>1.4286</v>
+      </c>
+      <c r="H60" s="72" t="inlineStr">
+        <is>
+          <t>▲ +10.9%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>20.75</v>
+        <v>26</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>18.42</v>
+        <v>26</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -7209,33 +7209,33 @@
         <v>2.17</v>
       </c>
       <c r="D62" s="91" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E62" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2.1204</v>
+      </c>
+      <c r="E62" s="70" t="inlineStr">
+        <is>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="F62" s="90" t="n">
         <v>2.05</v>
       </c>
       <c r="G62" s="91" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H62" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.9231</v>
+      </c>
+      <c r="H62" s="70" t="inlineStr">
+        <is>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="I62" s="58" t="n">
-        <v>56.42</v>
+        <v>55.13</v>
       </c>
       <c r="J62" s="58" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="K62" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7418,14 +7418,14 @@
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2.17</v>
+        <v>2.1204</v>
       </c>
       <c r="D6" s="105" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E6" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.9231</v>
+      </c>
+      <c r="E6" s="106" t="inlineStr">
+        <is>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
@@ -7433,15 +7433,15 @@
           <t xml:space="preserve">  2.  Angola</t>
         </is>
       </c>
-      <c r="H6" s="106" t="inlineStr">
+      <c r="H6" s="107" t="inlineStr">
         <is>
           <t>Southern Africa</t>
         </is>
       </c>
-      <c r="I6" s="107" t="n">
+      <c r="I6" s="108" t="n">
         <v>0.3272</v>
       </c>
-      <c r="J6" s="108" t="n">
+      <c r="J6" s="109" t="n">
         <v>0.2181</v>
       </c>
       <c r="K6" s="99" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="109" t="inlineStr">
+      <c r="A8" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  CAR</t>
         </is>
@@ -7516,20 +7516,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="110" t="inlineStr">
+      <c r="G8" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  Egypt</t>
         </is>
       </c>
-      <c r="H8" s="106" t="inlineStr">
+      <c r="H8" s="107" t="inlineStr">
         <is>
           <t>North Africa</t>
         </is>
       </c>
-      <c r="I8" s="107" t="n">
+      <c r="I8" s="108" t="n">
         <v>0.4771</v>
       </c>
-      <c r="J8" s="108" t="n">
+      <c r="J8" s="109" t="n">
         <v>0.4076</v>
       </c>
       <c r="K8" s="99" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="111" t="inlineStr">
+      <c r="A9" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  5.  Comoros</t>
         </is>
@@ -7555,7 +7555,7 @@
       <c r="D9" s="98" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E9" s="112" t="inlineStr">
+      <c r="E9" s="106" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
@@ -7576,102 +7576,102 @@
       <c r="J9" s="102" t="n">
         <v>0.7223000000000001</v>
       </c>
-      <c r="K9" s="112" t="inlineStr">
+      <c r="K9" s="106" t="inlineStr">
         <is>
           <t>▼ -28.6%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Somalia</t>
+      <c r="A10" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Senegal</t>
         </is>
       </c>
       <c r="B10" s="103" t="inlineStr">
         <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="104" t="n">
+        <v>1.6391</v>
+      </c>
+      <c r="D10" s="105" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E10" s="114" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
+        </is>
+      </c>
+      <c r="G10" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  South Sudan</t>
+        </is>
+      </c>
+      <c r="H10" s="107" t="inlineStr">
+        <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n">
+      <c r="I10" s="108" t="n">
+        <v>0.6602</v>
+      </c>
+      <c r="J10" s="109" t="n">
+        <v>0.6602</v>
+      </c>
+      <c r="K10" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Somalia</t>
+        </is>
+      </c>
+      <c r="B11" s="96" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C11" s="97" t="n">
         <v>1.6</v>
       </c>
-      <c r="D10" s="105" t="n">
+      <c r="D11" s="98" t="n">
         <v>1.4</v>
       </c>
-      <c r="E10" s="114" t="inlineStr">
+      <c r="E11" s="114" t="inlineStr">
         <is>
           <t>▲ +39.1%</t>
         </is>
       </c>
-      <c r="G10" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  South Sudan</t>
-        </is>
-      </c>
-      <c r="H10" s="106" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="I10" s="107" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="J10" s="108" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="K10" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Senegal</t>
-        </is>
-      </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="G11" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Nigeria</t>
+        </is>
+      </c>
+      <c r="H11" s="100" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C11" s="97" t="n">
-        <v>1.5232</v>
-      </c>
-      <c r="D11" s="98" t="n">
-        <v>1.1258</v>
-      </c>
-      <c r="E11" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Botswana</t>
-        </is>
-      </c>
-      <c r="H11" s="100" t="inlineStr">
-        <is>
-          <t>Southern Africa</t>
-        </is>
-      </c>
       <c r="I11" s="101" t="n">
-        <v>0.7792</v>
+        <v>0.6663</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.7792</v>
-      </c>
-      <c r="K11" s="112" t="inlineStr">
-        <is>
-          <t>▼ -31.8%</t>
+        <v>0.6663</v>
+      </c>
+      <c r="K11" s="114" t="inlineStr">
+        <is>
+          <t>▲ +13.7%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="109" t="inlineStr">
+      <c r="A12" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  8.  Mali</t>
         </is>
@@ -7692,48 +7692,48 @@
           <t>▲ +12.9%</t>
         </is>
       </c>
-      <c r="G12" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Nigeria</t>
-        </is>
-      </c>
-      <c r="H12" s="106" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="I12" s="107" t="n">
-        <v>0.8205</v>
-      </c>
-      <c r="J12" s="108" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="K12" s="114" t="inlineStr">
-        <is>
-          <t>▲ +40.0%</t>
+      <c r="G12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Botswana</t>
+        </is>
+      </c>
+      <c r="H12" s="107" t="inlineStr">
+        <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
+      <c r="I12" s="108" t="n">
+        <v>0.7792</v>
+      </c>
+      <c r="J12" s="109" t="n">
+        <v>0.7792</v>
+      </c>
+      <c r="K12" s="106" t="inlineStr">
+        <is>
+          <t>▼ -31.8%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Seychelles</t>
+      <c r="A13" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  South Africa</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.4261</v>
+        <v>1.4286</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.4163</v>
+        <v>1.4286</v>
       </c>
       <c r="E13" s="114" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="G13" s="113" t="inlineStr">
@@ -7759,41 +7759,41 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Sierra Leone</t>
+      <c r="A14" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Seychelles</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.4222</v>
+        <v>1.4261</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.5556</v>
-      </c>
-      <c r="E14" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="110" t="inlineStr">
+        <v>1.4163</v>
+      </c>
+      <c r="E14" s="114" t="inlineStr">
+        <is>
+          <t>▲ +1.1%</t>
+        </is>
+      </c>
+      <c r="G14" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Tunisia</t>
         </is>
       </c>
-      <c r="H14" s="106" t="inlineStr">
+      <c r="H14" s="107" t="inlineStr">
         <is>
           <t>North Africa</t>
         </is>
       </c>
-      <c r="I14" s="107" t="n">
+      <c r="I14" s="108" t="n">
         <v>0.8377</v>
       </c>
-      <c r="J14" s="108" t="n">
+      <c r="J14" s="109" t="n">
         <v>0.7318</v>
       </c>
       <c r="K14" s="99" t="inlineStr">
@@ -7850,32 +7850,32 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.5861</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>0.8205</v>
+        <v>1.009</v>
       </c>
       <c r="F19" s="72" t="inlineStr">
         <is>
-          <t>▲ +40.0%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.2344</v>
+        <v>0.3643</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -7912,32 +7912,32 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>1.2332</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>0.8398</v>
+        <v>1.4286</v>
       </c>
       <c r="F21" s="72" t="inlineStr">
         <is>
-          <t>▲ +30.3%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.1951</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -7974,7 +7974,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
@@ -7984,28 +7984,28 @@
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.2831</v>
+        <v>0.5861</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.4487</v>
+        <v>0.6663</v>
       </c>
       <c r="F23" s="72" t="inlineStr">
         <is>
-          <t>▲ +12.9%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.1656</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
@@ -8019,24 +8019,24 @@
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2831</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.3576</v>
+        <v>1.4487</v>
       </c>
       <c r="F24" s="72" t="inlineStr">
         <is>
-          <t>▲ +10.7%</t>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.1314</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
@@ -8046,214 +8046,214 @@
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.5244</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.1301</v>
+        <v>1.6391</v>
       </c>
       <c r="F25" s="72" t="inlineStr">
         <is>
-          <t>▲ +3.9%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.0419</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.0882</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.3699</v>
+        <v>1.1301</v>
       </c>
       <c r="F26" s="72" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +3.9%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.022</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3479</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.3699</v>
       </c>
       <c r="F27" s="72" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.31</v>
+        <v>1.3681</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.3261</v>
+        <v>1.3873</v>
       </c>
       <c r="F28" s="72" t="inlineStr">
         <is>
-          <t>▲ +1.2%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.0161</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.31</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.4261</v>
+        <v>1.3261</v>
       </c>
       <c r="F29" s="72" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +1.2%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.0161</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.4106</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.0582</v>
+        <v>1.4261</v>
       </c>
       <c r="F30" s="72" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.1%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.0555</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.0568</v>
-      </c>
-      <c r="F31" s="70" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G31" s="119" t="n">
-        <v>-0.0048</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F31" s="72" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G31" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
@@ -8263,28 +8263,28 @@
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.0616</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.3595</v>
+        <v>1.0568</v>
       </c>
       <c r="F32" s="70" t="inlineStr">
         <is>
-          <t>▼ -0.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G32" s="119" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0048</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,28 +8294,28 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.3691</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.3661</v>
+        <v>1.3595</v>
       </c>
       <c r="F33" s="70" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="G33" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.009599999999999999</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,28 +8325,28 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.0641</v>
+        <v>2.17</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.025</v>
+        <v>2.1204</v>
       </c>
       <c r="F34" s="70" t="inlineStr">
         <is>
-          <t>▼ -3.7%</t>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G34" s="119" t="n">
-        <v>-0.0391</v>
+        <v>-0.0496</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
@@ -8356,28 +8356,28 @@
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.784</v>
+        <v>1.3986</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.6851</v>
+        <v>1.3661</v>
       </c>
       <c r="F35" s="70" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G35" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
@@ -8387,90 +8387,90 @@
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.0641</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>0.9677</v>
+        <v>1.025</v>
       </c>
       <c r="F36" s="70" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -3.7%</t>
         </is>
       </c>
       <c r="G36" s="119" t="n">
-        <v>-0.0639</v>
+        <v>-0.0391</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.784</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.1401</v>
+        <v>1.6851</v>
       </c>
       <c r="F37" s="70" t="inlineStr">
         <is>
-          <t>▼ -7.5%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G37" s="119" t="n">
-        <v>-0.0931</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.0316</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>0.9851</v>
+        <v>0.9677</v>
       </c>
       <c r="F38" s="70" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0639</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
@@ -8484,55 +8484,55 @@
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.2262</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.1258</v>
+        <v>1.1341</v>
       </c>
       <c r="F39" s="70" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.0921</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.0671</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.0606</v>
+        <v>0.9851</v>
       </c>
       <c r="F40" s="70" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
@@ -8546,55 +8546,55 @@
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2212</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.1755</v>
+        <v>1.1258</v>
       </c>
       <c r="F41" s="70" t="inlineStr">
         <is>
-          <t>▼ -11.5%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.1534</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.1939</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.0538</v>
+        <v>1.0606</v>
       </c>
       <c r="F42" s="70" t="inlineStr">
         <is>
-          <t>▼ -17.4%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.2224</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
@@ -8608,55 +8608,55 @@
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.3587</v>
+        <v>1.3289</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.1043</v>
+        <v>1.1755</v>
       </c>
       <c r="F43" s="70" t="inlineStr">
         <is>
-          <t>▼ -18.7%</t>
+          <t>▼ -11.5%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.2544</v>
+        <v>-0.1534</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>0.914</v>
+        <v>1.2762</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>0.6522</v>
+        <v>1.0538</v>
       </c>
       <c r="F44" s="70" t="inlineStr">
         <is>
-          <t>▼ -28.6%</t>
+          <t>▼ -17.4%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.2618</v>
+        <v>-0.2224</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
@@ -8666,52 +8666,114 @@
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3587</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.8959</v>
+        <v>1.1043</v>
       </c>
       <c r="F45" s="70" t="inlineStr">
         <is>
-          <t>▼ -30.5%</t>
+          <t>▼ -18.7%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.3927</v>
+        <v>-0.2544</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="C46" s="118" t="inlineStr">
+        <is>
+          <t>GHS</t>
+        </is>
+      </c>
+      <c r="D46" s="88" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="E46" s="89" t="n">
+        <v>0.6522</v>
+      </c>
+      <c r="F46" s="70" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
+        </is>
+      </c>
+      <c r="G46" s="119" t="n">
+        <v>-0.2618</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="53" t="inlineStr">
+        <is>
+          <t>Cabo Verde</t>
+        </is>
+      </c>
+      <c r="B47" s="54" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="C47" s="116" t="inlineStr">
+        <is>
+          <t>CVE</t>
+        </is>
+      </c>
+      <c r="D47" s="88" t="n">
+        <v>1.2886</v>
+      </c>
+      <c r="E47" s="91" t="n">
+        <v>0.8959</v>
+      </c>
+      <c r="F47" s="70" t="inlineStr">
+        <is>
+          <t>▼ -30.5%</t>
+        </is>
+      </c>
+      <c r="G47" s="119" t="n">
+        <v>-0.3927</v>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="62" t="inlineStr">
+        <is>
           <t>Botswana</t>
         </is>
       </c>
-      <c r="B46" s="63" t="inlineStr">
+      <c r="B48" s="63" t="inlineStr">
         <is>
           <t>Southern Africa</t>
         </is>
       </c>
-      <c r="C46" s="118" t="inlineStr">
+      <c r="C48" s="118" t="inlineStr">
         <is>
           <t>BWP</t>
         </is>
       </c>
-      <c r="D46" s="88" t="n">
+      <c r="D48" s="88" t="n">
         <v>1.1425</v>
       </c>
-      <c r="E46" s="89" t="n">
+      <c r="E48" s="89" t="n">
         <v>0.7792</v>
       </c>
-      <c r="F46" s="70" t="inlineStr">
+      <c r="F48" s="70" t="inlineStr">
         <is>
           <t>▼ -31.8%</t>
         </is>
       </c>
-      <c r="G46" s="119" t="n">
+      <c r="G48" s="119" t="n">
         <v>-0.3633</v>
       </c>
     </row>
@@ -8772,7 +8834,7 @@
         <v>0.6327166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6001500000000001</v>
+        <v>0.6112333333333333</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -8976,13 +9038,13 @@
         <v>1.0474</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="E10" s="58" t="n">
         <v>630</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
@@ -9045,16 +9107,16 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.14308125</v>
+        <v>1.12671875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.14324375</v>
+        <v>1.11750625</v>
       </c>
       <c r="E14" s="131" t="n">
         <v>0.6522</v>
       </c>
       <c r="F14" s="132" t="n">
-        <v>1.5232</v>
+        <v>1.6391</v>
       </c>
       <c r="G14" s="129" t="n"/>
       <c r="H14" s="129" t="n"/>
@@ -9113,20 +9175,20 @@
         </is>
       </c>
       <c r="C16" s="57" t="n">
-        <v>1.3576</v>
+        <v>1.1341</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>1.3742</v>
+        <v>1.1589</v>
       </c>
       <c r="E16" s="58" t="n">
-        <v>820</v>
+        <v>685</v>
       </c>
       <c r="F16" s="58" t="n">
-        <v>830</v>
-      </c>
-      <c r="G16" s="72" t="inlineStr">
-        <is>
-          <t>▲ +10.7%</t>
+        <v>700</v>
+      </c>
+      <c r="G16" s="70" t="inlineStr">
+        <is>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="H16" s="61" t="inlineStr">
@@ -9521,20 +9583,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.8205</v>
+        <v>0.6663</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.987</v>
+        <v>0.6663</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1330</v>
+        <v>1080</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1600</v>
+        <v>1080</v>
       </c>
       <c r="G28" s="72" t="inlineStr">
         <is>
-          <t>▲ +40.0%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9555,20 +9617,20 @@
         </is>
       </c>
       <c r="C29" s="66" t="n">
-        <v>1.5232</v>
+        <v>1.6391</v>
       </c>
       <c r="D29" s="66" t="n">
-        <v>1.1258</v>
+        <v>1.25</v>
       </c>
       <c r="E29" s="67" t="n">
-        <v>920</v>
+        <v>990</v>
       </c>
       <c r="F29" s="67" t="n">
-        <v>680</v>
-      </c>
-      <c r="G29" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>755</v>
+      </c>
+      <c r="G29" s="72" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="H29" s="69" t="inlineStr">
@@ -9815,7 +9877,7 @@
       </c>
       <c r="H38" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -10005,10 +10067,10 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.419066666666667</v>
+        <v>1.430346666666666</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.354446666666667</v>
+        <v>1.358573333333333</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>0.6602</v>
@@ -10209,25 +10271,25 @@
         </is>
       </c>
       <c r="C52" s="57" t="n">
-        <v>0.8398</v>
+        <v>1.009</v>
       </c>
       <c r="D52" s="57" t="n">
-        <v>0.8884</v>
+        <v>1.046</v>
       </c>
       <c r="E52" s="58" t="n">
         <v>132.18</v>
       </c>
       <c r="F52" s="58" t="n">
-        <v>139.84</v>
+        <v>137.03</v>
       </c>
       <c r="G52" s="72" t="inlineStr">
         <is>
-          <t>▲ +30.3%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="H52" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -10382,13 +10444,13 @@
         <v>1.3595</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.3315</v>
+        <v>1.2358</v>
       </c>
       <c r="E57" s="67" t="n">
         <v>1989</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>1948</v>
+        <v>1808</v>
       </c>
       <c r="G57" s="70" t="inlineStr">
         <is>
@@ -10499,7 +10561,7 @@
       </c>
       <c r="H60" s="61" t="inlineStr">
         <is>
-          <t>🔴 Low</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -10587,16 +10649,16 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.114822222222222</v>
+        <v>1.141366666666667</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.061933333333333</v>
+        <v>1.094111111111111</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
       </c>
       <c r="F65" s="153" t="n">
-        <v>2.17</v>
+        <v>2.1204</v>
       </c>
       <c r="G65" s="150" t="n"/>
       <c r="H65" s="150" t="n"/>
@@ -10859,25 +10921,25 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.1401</v>
+        <v>1.4286</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.0121</v>
+        <v>1.4286</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>20.75</v>
+        <v>26</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>18.42</v>
-      </c>
-      <c r="G73" s="70" t="inlineStr">
-        <is>
-          <t>▼ -7.5%</t>
+        <v>26</v>
+      </c>
+      <c r="G73" s="72" t="inlineStr">
+        <is>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -10927,25 +10989,25 @@
         </is>
       </c>
       <c r="C75" s="57" t="n">
-        <v>2.17</v>
+        <v>2.1204</v>
       </c>
       <c r="D75" s="57" t="n">
-        <v>2.05</v>
+        <v>1.9231</v>
       </c>
       <c r="E75" s="58" t="n">
-        <v>56.42</v>
+        <v>55.13</v>
       </c>
       <c r="F75" s="58" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="G75" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>50</v>
+      </c>
+      <c r="G75" s="70" t="inlineStr">
+        <is>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="H75" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -284,14 +284,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00065F46"/>
-      <sz val="9"/>
+      <color rgb="00991B1B"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
-      <sz val="10"/>
+      <color rgb="00065F46"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -966,17 +966,17 @@
     <xf numFmtId="4" fontId="39" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1097,7 +1097,7 @@
     <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1106,7 +1106,7 @@
     <xf numFmtId="0" fontId="53" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="45" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1137,11 +1137,11 @@
     <xf numFmtId="0" fontId="54" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="44" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="45" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="58" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-03-31</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-01</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.172</t>
+          <t>$1.215</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+56.5%</t>
+          <t>+90.0%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.136</t>
+          <t>$1.174</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6327166666666667</v>
+        <v>0.6536</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6112333333333333</v>
+        <v>0.5869166666666668</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.0538</v>
+        <v>1.3779</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.12671875</v>
+        <v>1.16508125</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.11750625</v>
+        <v>1.1378375</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6522</v>
+        <v>0.5861</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.430346666666666</v>
+        <v>1.488813333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.358573333333333</v>
+        <v>1.425326666666667</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.6602</v>
+        <v>1.009</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.141366666666667</v>
+        <v>1.220277777777778</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.094111111111111</v>
+        <v>1.192455555555555</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-03-31</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2108,26 +2108,26 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.4771</v>
+        <v>0.2783</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.4076</v>
+        <v>0.2783</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>20.5</v>
+        <v>14</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
-      <c r="J5" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="69" t="inlineStr">
+      <c r="J5" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.7%</t>
+        </is>
+      </c>
+      <c r="K5" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -2202,26 +2202,26 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.0538</v>
+        <v>1.3779</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.2223</v>
+        <v>1.2722</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>10.57</v>
+        <v>13.82</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>12.26</v>
+        <v>12.76</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
-      <c r="J7" s="70" t="inlineStr">
-        <is>
-          <t>▼ -17.4%</t>
-        </is>
-      </c>
-      <c r="K7" s="69" t="inlineStr">
+      <c r="J7" s="71" t="inlineStr">
+        <is>
+          <t>▲ +8.0%</t>
+        </is>
+      </c>
+      <c r="K7" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -2252,13 +2252,13 @@
         <v>1.0474</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="G8" s="58" t="n">
         <v>630</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
@@ -2315,14 +2315,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="69" t="inlineStr">
+      <c r="K9" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="71" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸  WEST AFRICA</t>
         </is>
@@ -2350,26 +2350,26 @@
         </is>
       </c>
       <c r="E11" s="66" t="n">
-        <v>1.1341</v>
+        <v>1.1507</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>1.1589</v>
+        <v>1.1921</v>
       </c>
       <c r="G11" s="67" t="n">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
       </c>
-      <c r="J11" s="70" t="inlineStr">
-        <is>
-          <t>▼ -7.5%</t>
-        </is>
-      </c>
-      <c r="K11" s="69" t="inlineStr">
+      <c r="J11" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.2%</t>
+        </is>
+      </c>
+      <c r="K11" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -2444,26 +2444,26 @@
         </is>
       </c>
       <c r="E13" s="66" t="n">
-        <v>0.8959</v>
+        <v>1.1719</v>
       </c>
       <c r="F13" s="66" t="n">
-        <v>0.8959</v>
+        <v>0.9846</v>
       </c>
       <c r="G13" s="67" t="n">
-        <v>99</v>
+        <v>129.5</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>99</v>
+        <v>108.8</v>
       </c>
       <c r="I13" s="68" t="n">
         <v>110.5</v>
       </c>
-      <c r="J13" s="70" t="inlineStr">
-        <is>
-          <t>▼ -30.5%</t>
-        </is>
-      </c>
-      <c r="K13" s="69" t="inlineStr">
+      <c r="J13" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.1%</t>
+        </is>
+      </c>
+      <c r="K13" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -2491,23 +2491,23 @@
         </is>
       </c>
       <c r="E14" s="57" t="n">
-        <v>1.1301</v>
+        <v>1.0253</v>
       </c>
       <c r="F14" s="57" t="n">
-        <v>1.1726</v>
+        <v>1.0253</v>
       </c>
       <c r="G14" s="58" t="n">
-        <v>82.5</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="H14" s="58" t="n">
-        <v>85.59999999999999</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="I14" s="59" t="n">
         <v>73</v>
       </c>
-      <c r="J14" s="72" t="inlineStr">
-        <is>
-          <t>▲ +3.9%</t>
+      <c r="J14" s="69" t="inlineStr">
+        <is>
+          <t>▼ -5.8%</t>
         </is>
       </c>
       <c r="K14" s="61" t="inlineStr">
@@ -2538,26 +2538,26 @@
         </is>
       </c>
       <c r="E15" s="66" t="n">
-        <v>0.6522</v>
+        <v>0.8471</v>
       </c>
       <c r="F15" s="66" t="n">
-        <v>0.7223000000000001</v>
+        <v>1.0892</v>
       </c>
       <c r="G15" s="67" t="n">
-        <v>10.24</v>
+        <v>13.3</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>11.34</v>
+        <v>17.1</v>
       </c>
       <c r="I15" s="68" t="n">
         <v>15.7</v>
       </c>
-      <c r="J15" s="70" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
-        </is>
-      </c>
-      <c r="K15" s="69" t="inlineStr">
+      <c r="J15" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
+        </is>
+      </c>
+      <c r="K15" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -2599,7 +2599,7 @@
       <c r="I16" s="59" t="n">
         <v>8650</v>
       </c>
-      <c r="J16" s="72" t="inlineStr">
+      <c r="J16" s="71" t="inlineStr">
         <is>
           <t>▲ +1.4%</t>
         </is>
@@ -2646,12 +2646,12 @@
       <c r="I17" s="68" t="n">
         <v>604</v>
       </c>
-      <c r="J17" s="70" t="inlineStr">
+      <c r="J17" s="69" t="inlineStr">
         <is>
           <t>▼ -11.5%</t>
         </is>
       </c>
-      <c r="K17" s="69" t="inlineStr">
+      <c r="K17" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -2679,23 +2679,23 @@
         </is>
       </c>
       <c r="E18" s="57" t="n">
-        <v>1.1043</v>
+        <v>1.4156</v>
       </c>
       <c r="F18" s="57" t="n">
-        <v>1.1043</v>
+        <v>1.1838</v>
       </c>
       <c r="G18" s="58" t="n">
-        <v>667</v>
+        <v>855</v>
       </c>
       <c r="H18" s="58" t="n">
-        <v>667</v>
+        <v>715</v>
       </c>
       <c r="I18" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J18" s="70" t="inlineStr">
-        <is>
-          <t>▼ -18.7%</t>
+      <c r="J18" s="71" t="inlineStr">
+        <is>
+          <t>▲ +4.2%</t>
         </is>
       </c>
       <c r="K18" s="61" t="inlineStr">
@@ -2745,7 +2745,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K19" s="69" t="inlineStr">
+      <c r="K19" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -2787,7 +2787,7 @@
       <c r="I20" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J20" s="72" t="inlineStr">
+      <c r="J20" s="71" t="inlineStr">
         <is>
           <t>▲ +12.9%</t>
         </is>
@@ -2839,7 +2839,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K21" s="69" t="inlineStr">
+      <c r="K21" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -2914,26 +2914,26 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.5861</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.5706</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1080</v>
+        <v>950</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1080</v>
+        <v>925</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
-      <c r="J23" s="72" t="inlineStr">
-        <is>
-          <t>▲ +13.7%</t>
-        </is>
-      </c>
-      <c r="K23" s="69" t="inlineStr">
+      <c r="J23" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -2975,7 +2975,7 @@
       <c r="I24" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J24" s="72" t="inlineStr">
+      <c r="J24" s="71" t="inlineStr">
         <is>
           <t>▲ +7.5%</t>
         </is>
@@ -3027,7 +3027,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K25" s="69" t="inlineStr">
+      <c r="K25" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -3069,7 +3069,7 @@
       <c r="I26" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J26" s="70" t="inlineStr">
+      <c r="J26" s="69" t="inlineStr">
         <is>
           <t>▼ -7.8%</t>
         </is>
@@ -3175,7 +3175,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K29" s="69" t="inlineStr">
+      <c r="K29" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -3269,7 +3269,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K31" s="69" t="inlineStr">
+      <c r="K31" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -3363,7 +3363,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K33" s="69" t="inlineStr">
+      <c r="K33" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -3405,7 +3405,7 @@
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="70" t="inlineStr">
+      <c r="J34" s="69" t="inlineStr">
         <is>
           <t>▼ -7.7%</t>
         </is>
@@ -3457,7 +3457,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K35" s="69" t="inlineStr">
+      <c r="K35" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -3506,12 +3506,12 @@
       <c r="I37" s="68" t="n">
         <v>2920</v>
       </c>
-      <c r="J37" s="72" t="inlineStr">
+      <c r="J37" s="71" t="inlineStr">
         <is>
           <t>▲ +1.6%</t>
         </is>
       </c>
-      <c r="K37" s="69" t="inlineStr">
+      <c r="K37" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -3553,7 +3553,7 @@
       <c r="I38" s="59" t="n">
         <v>451</v>
       </c>
-      <c r="J38" s="70" t="inlineStr">
+      <c r="J38" s="69" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
@@ -3605,7 +3605,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K39" s="69" t="inlineStr">
+      <c r="K39" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -3694,12 +3694,12 @@
       <c r="I41" s="68" t="n">
         <v>131</v>
       </c>
-      <c r="J41" s="72" t="inlineStr">
+      <c r="J41" s="71" t="inlineStr">
         <is>
           <t>▲ +56.5%</t>
         </is>
       </c>
-      <c r="K41" s="69" t="inlineStr">
+      <c r="K41" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -3741,7 +3741,7 @@
       <c r="I42" s="59" t="n">
         <v>130.5</v>
       </c>
-      <c r="J42" s="70" t="inlineStr">
+      <c r="J42" s="69" t="inlineStr">
         <is>
           <t>▼ -2.3%</t>
         </is>
@@ -3788,12 +3788,12 @@
       <c r="I43" s="68" t="n">
         <v>4620</v>
       </c>
-      <c r="J43" s="70" t="inlineStr">
+      <c r="J43" s="69" t="inlineStr">
         <is>
           <t>▼ -11.2%</t>
         </is>
       </c>
-      <c r="K43" s="69" t="inlineStr">
+      <c r="K43" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -3887,7 +3887,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K45" s="69" t="inlineStr">
+      <c r="K45" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -3915,23 +3915,23 @@
         </is>
       </c>
       <c r="E46" s="57" t="n">
-        <v>1.3595</v>
+        <v>1.2057</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.2358</v>
+        <v>1.1511</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>1989</v>
+        <v>1764</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>1808</v>
+        <v>1684</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
       </c>
-      <c r="J46" s="70" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+      <c r="J46" s="69" t="inlineStr">
+        <is>
+          <t>▼ -11.9%</t>
         </is>
       </c>
       <c r="K46" s="61" t="inlineStr">
@@ -3965,23 +3965,23 @@
         <v>1.4261</v>
       </c>
       <c r="F47" s="66" t="n">
-        <v>1.4163</v>
+        <v>1.4269</v>
       </c>
       <c r="G47" s="67" t="n">
         <v>20.18</v>
       </c>
       <c r="H47" s="67" t="n">
-        <v>20.04</v>
+        <v>20.19</v>
       </c>
       <c r="I47" s="68" t="n">
         <v>14.15</v>
       </c>
-      <c r="J47" s="72" t="inlineStr">
+      <c r="J47" s="71" t="inlineStr">
         <is>
           <t>▲ +1.1%</t>
         </is>
       </c>
-      <c r="K47" s="69" t="inlineStr">
+      <c r="K47" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -4023,7 +4023,7 @@
       <c r="I48" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="72" t="inlineStr">
+      <c r="J48" s="71" t="inlineStr">
         <is>
           <t>▲ +39.1%</t>
         </is>
@@ -4056,26 +4056,26 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K49" s="69" t="inlineStr">
+      <c r="J49" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
+        </is>
+      </c>
+      <c r="K49" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -4103,23 +4103,23 @@
         </is>
       </c>
       <c r="E50" s="57" t="n">
-        <v>1.0568</v>
+        <v>1.4096</v>
       </c>
       <c r="F50" s="57" t="n">
-        <v>1.0568</v>
+        <v>1.4096</v>
       </c>
       <c r="G50" s="58" t="n">
-        <v>2864</v>
+        <v>3820</v>
       </c>
       <c r="H50" s="58" t="n">
-        <v>2864</v>
+        <v>3820</v>
       </c>
       <c r="I50" s="59" t="n">
         <v>2710</v>
       </c>
-      <c r="J50" s="70" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
+      <c r="J50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="K50" s="61" t="inlineStr">
@@ -4150,26 +4150,26 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.3819</v>
+        <v>1.4657</v>
       </c>
       <c r="F51" s="66" t="n">
-        <v>1.3093</v>
+        <v>1.4377</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>4950</v>
+        <v>5250</v>
       </c>
       <c r="H51" s="67" t="n">
-        <v>4690</v>
+        <v>5150</v>
       </c>
       <c r="I51" s="68" t="n">
         <v>3582</v>
       </c>
-      <c r="J51" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K51" s="69" t="inlineStr">
+      <c r="J51" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
+        </is>
+      </c>
+      <c r="K51" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -4223,7 +4223,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K53" s="69" t="inlineStr">
+      <c r="K53" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>0.7792</v>
+        <v>1.1425</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>0.7792</v>
+        <v>1.2024</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>10.55</v>
+        <v>15.47</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>10.55</v>
+        <v>16.28</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
-      <c r="J54" s="70" t="inlineStr">
-        <is>
-          <t>▼ -31.8%</t>
+      <c r="J54" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4298,26 +4298,26 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>1.2399</v>
+        <v>1.0485</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>1.2399</v>
+        <v>1.0701</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>23</v>
+        <v>19.45</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>23</v>
+        <v>19.85</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
-      <c r="J55" s="72" t="inlineStr">
-        <is>
-          <t>▲ +15.6%</t>
-        </is>
-      </c>
-      <c r="K55" s="69" t="inlineStr">
+      <c r="J55" s="69" t="inlineStr">
+        <is>
+          <t>▼ -2.2%</t>
+        </is>
+      </c>
+      <c r="K55" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -4345,23 +4345,23 @@
         </is>
       </c>
       <c r="E56" s="57" t="n">
-        <v>0.9677</v>
+        <v>1.2129</v>
       </c>
       <c r="F56" s="57" t="n">
-        <v>1.0458</v>
+        <v>1.1482</v>
       </c>
       <c r="G56" s="58" t="n">
-        <v>17.95</v>
+        <v>22.5</v>
       </c>
       <c r="H56" s="58" t="n">
-        <v>19.4</v>
+        <v>21.3</v>
       </c>
       <c r="I56" s="59" t="n">
         <v>18.55</v>
       </c>
-      <c r="J56" s="70" t="inlineStr">
-        <is>
-          <t>▼ -6.2%</t>
+      <c r="J56" s="71" t="inlineStr">
+        <is>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="K56" s="61" t="inlineStr">
@@ -4392,26 +4392,26 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>1.3261</v>
+        <v>1.3037</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>1.248</v>
+        <v>1.2462</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>85</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>80</v>
+        <v>79.88</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="J57" s="72" t="inlineStr">
-        <is>
-          <t>▲ +1.2%</t>
-        </is>
-      </c>
-      <c r="K57" s="69" t="inlineStr">
+      <c r="J57" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
+        </is>
+      </c>
+      <c r="K57" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -4439,28 +4439,28 @@
         </is>
       </c>
       <c r="E58" s="57" t="n">
-        <v>1.0582</v>
+        <v>1.4555</v>
       </c>
       <c r="F58" s="57" t="n">
-        <v>1.0636</v>
+        <v>1.4555</v>
       </c>
       <c r="G58" s="58" t="n">
-        <v>19.63</v>
+        <v>27</v>
       </c>
       <c r="H58" s="58" t="n">
-        <v>19.73</v>
+        <v>27</v>
       </c>
       <c r="I58" s="59" t="n">
         <v>18.55</v>
       </c>
-      <c r="J58" s="72" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
+      <c r="J58" s="71" t="inlineStr">
+        <is>
+          <t>▲ +37.9%</t>
         </is>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -4486,26 +4486,26 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.4286</v>
+        <v>1.3736</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.4286</v>
+        <v>1.3736</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="72" t="inlineStr">
-        <is>
-          <t>▲ +15.8%</t>
-        </is>
-      </c>
-      <c r="K59" s="69" t="inlineStr">
+      <c r="J59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
+        </is>
+      </c>
+      <c r="K59" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -4533,23 +4533,23 @@
         </is>
       </c>
       <c r="E60" s="57" t="n">
-        <v>1.025</v>
+        <v>0.9982</v>
       </c>
       <c r="F60" s="57" t="n">
-        <v>0.9006999999999999</v>
+        <v>1.0949</v>
       </c>
       <c r="G60" s="58" t="n">
-        <v>27.88</v>
+        <v>27.15</v>
       </c>
       <c r="H60" s="58" t="n">
-        <v>24.5</v>
+        <v>29.78</v>
       </c>
       <c r="I60" s="59" t="n">
         <v>27.2</v>
       </c>
-      <c r="J60" s="70" t="inlineStr">
-        <is>
-          <t>▼ -3.7%</t>
+      <c r="J60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="K60" s="61" t="inlineStr">
@@ -4594,12 +4594,12 @@
       <c r="I61" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="J61" s="70" t="inlineStr">
+      <c r="J61" s="69" t="inlineStr">
         <is>
           <t>▼ -2.3%</t>
         </is>
       </c>
-      <c r="K61" s="69" t="inlineStr">
+      <c r="K61" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.172040740740741</v>
+        <v>1.21512037037037</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.135514814814815</v>
+        <v>1.17377037037037</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-03-31</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-01</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       <c r="J5" s="67" t="n">
         <v>31</v>
       </c>
-      <c r="K5" s="69" t="inlineStr">
+      <c r="K5" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.4771</v>
-      </c>
-      <c r="E6" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2783</v>
+      </c>
+      <c r="E6" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.7%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.4076</v>
-      </c>
-      <c r="H6" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2783</v>
+      </c>
+      <c r="H6" s="69" t="inlineStr">
+        <is>
+          <t>▼ -31.7%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>20.5</v>
+        <v>14</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
       <c r="J7" s="67" t="n">
         <v>0.135</v>
       </c>
-      <c r="K7" s="69" t="inlineStr">
+      <c r="K7" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.0538</v>
-      </c>
-      <c r="E8" s="70" t="inlineStr">
-        <is>
-          <t>▼ -17.4%</t>
+        <v>1.3779</v>
+      </c>
+      <c r="E8" s="71" t="inlineStr">
+        <is>
+          <t>▲ +8.0%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.2223</v>
-      </c>
-      <c r="H8" s="72" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+        <v>1.2722</v>
+      </c>
+      <c r="H8" s="71" t="inlineStr">
+        <is>
+          <t>▲ +10.9%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>10.57</v>
+        <v>13.82</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>12.26</v>
+        <v>12.76</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -4987,20 +4987,20 @@
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.0474</v>
-      </c>
-      <c r="H9" s="72" t="inlineStr">
-        <is>
-          <t>▲ +6.8%</t>
+        <v>0.9809</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
         <v>630</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>630</v>
-      </c>
-      <c r="K9" s="69" t="inlineStr">
+        <v>590</v>
+      </c>
+      <c r="K9" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -5052,7 +5052,7 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="71" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▸  WEST AFRICA</t>
         </is>
@@ -5073,29 +5073,29 @@
         <v>1.2262</v>
       </c>
       <c r="D12" s="91" t="n">
-        <v>1.1341</v>
-      </c>
-      <c r="E12" s="70" t="inlineStr">
-        <is>
-          <t>▼ -7.5%</t>
+        <v>1.1507</v>
+      </c>
+      <c r="E12" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="F12" s="90" t="n">
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>1.1589</v>
-      </c>
-      <c r="H12" s="70" t="inlineStr">
-        <is>
-          <t>▼ -8.0%</t>
+        <v>1.1921</v>
+      </c>
+      <c r="H12" s="69" t="inlineStr">
+        <is>
+          <t>▼ -5.3%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
       <c r="J13" s="67" t="n">
         <v>724</v>
       </c>
-      <c r="K13" s="69" t="inlineStr">
+      <c r="K13" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -5163,29 +5163,29 @@
         <v>1.2886</v>
       </c>
       <c r="D14" s="91" t="n">
-        <v>0.8959</v>
-      </c>
-      <c r="E14" s="70" t="inlineStr">
-        <is>
-          <t>▼ -30.5%</t>
+        <v>1.1719</v>
+      </c>
+      <c r="E14" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.1%</t>
         </is>
       </c>
       <c r="F14" s="90" t="n">
         <v>1.0826</v>
       </c>
       <c r="G14" s="91" t="n">
-        <v>0.8959</v>
-      </c>
-      <c r="H14" s="70" t="inlineStr">
-        <is>
-          <t>▼ -17.2%</t>
+        <v>0.9846</v>
+      </c>
+      <c r="H14" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.1%</t>
         </is>
       </c>
       <c r="I14" s="58" t="n">
-        <v>99</v>
+        <v>129.5</v>
       </c>
       <c r="J14" s="58" t="n">
-        <v>99</v>
+        <v>108.8</v>
       </c>
       <c r="K14" s="61" t="inlineStr">
         <is>
@@ -5208,31 +5208,31 @@
         <v>1.0882</v>
       </c>
       <c r="D15" s="89" t="n">
-        <v>1.1301</v>
-      </c>
-      <c r="E15" s="72" t="inlineStr">
-        <is>
-          <t>▲ +3.9%</t>
+        <v>1.0253</v>
+      </c>
+      <c r="E15" s="69" t="inlineStr">
+        <is>
+          <t>▼ -5.8%</t>
         </is>
       </c>
       <c r="F15" s="90" t="n">
         <v>0.9559</v>
       </c>
       <c r="G15" s="89" t="n">
-        <v>1.1726</v>
-      </c>
-      <c r="H15" s="72" t="inlineStr">
-        <is>
-          <t>▲ +22.7%</t>
+        <v>1.0253</v>
+      </c>
+      <c r="H15" s="71" t="inlineStr">
+        <is>
+          <t>▲ +7.3%</t>
         </is>
       </c>
       <c r="I15" s="67" t="n">
-        <v>82.5</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="J15" s="67" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="K15" s="69" t="inlineStr">
+        <v>74.84999999999999</v>
+      </c>
+      <c r="K15" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -5253,29 +5253,29 @@
         <v>0.914</v>
       </c>
       <c r="D16" s="91" t="n">
-        <v>0.6522</v>
-      </c>
-      <c r="E16" s="70" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>0.8471</v>
+      </c>
+      <c r="E16" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="F16" s="90" t="n">
         <v>0.914</v>
       </c>
       <c r="G16" s="91" t="n">
-        <v>0.7223000000000001</v>
-      </c>
-      <c r="H16" s="70" t="inlineStr">
-        <is>
-          <t>▼ -21.0%</t>
+        <v>1.0892</v>
+      </c>
+      <c r="H16" s="71" t="inlineStr">
+        <is>
+          <t>▲ +19.2%</t>
         </is>
       </c>
       <c r="I16" s="58" t="n">
-        <v>10.24</v>
+        <v>13.3</v>
       </c>
       <c r="J16" s="58" t="n">
-        <v>11.34</v>
+        <v>17.1</v>
       </c>
       <c r="K16" s="61" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
       <c r="D17" s="89" t="n">
         <v>1.3873</v>
       </c>
-      <c r="E17" s="72" t="inlineStr">
+      <c r="E17" s="71" t="inlineStr">
         <is>
           <t>▲ +1.4%</t>
         </is>
@@ -5311,7 +5311,7 @@
       <c r="G17" s="89" t="n">
         <v>1.3873</v>
       </c>
-      <c r="H17" s="72" t="inlineStr">
+      <c r="H17" s="71" t="inlineStr">
         <is>
           <t>▲ +3.5%</t>
         </is>
@@ -5322,7 +5322,7 @@
       <c r="J17" s="67" t="n">
         <v>12000</v>
       </c>
-      <c r="K17" s="69" t="inlineStr">
+      <c r="K17" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -5345,7 +5345,7 @@
       <c r="D18" s="91" t="n">
         <v>1.1755</v>
       </c>
-      <c r="E18" s="70" t="inlineStr">
+      <c r="E18" s="69" t="inlineStr">
         <is>
           <t>▼ -11.5%</t>
         </is>
@@ -5356,7 +5356,7 @@
       <c r="G18" s="91" t="n">
         <v>1.0232</v>
       </c>
-      <c r="H18" s="70" t="inlineStr">
+      <c r="H18" s="69" t="inlineStr">
         <is>
           <t>▼ -19.4%</t>
         </is>
@@ -5388,31 +5388,31 @@
         <v>1.3587</v>
       </c>
       <c r="D19" s="89" t="n">
-        <v>1.1043</v>
-      </c>
-      <c r="E19" s="70" t="inlineStr">
-        <is>
-          <t>▼ -18.7%</t>
+        <v>1.4156</v>
+      </c>
+      <c r="E19" s="71" t="inlineStr">
+        <is>
+          <t>▲ +4.2%</t>
         </is>
       </c>
       <c r="F19" s="90" t="n">
         <v>1.1185</v>
       </c>
       <c r="G19" s="89" t="n">
-        <v>1.1043</v>
-      </c>
-      <c r="H19" s="70" t="inlineStr">
-        <is>
-          <t>▼ -1.3%</t>
+        <v>1.1838</v>
+      </c>
+      <c r="H19" s="71" t="inlineStr">
+        <is>
+          <t>▲ +5.8%</t>
         </is>
       </c>
       <c r="I19" s="67" t="n">
-        <v>667</v>
+        <v>855</v>
       </c>
       <c r="J19" s="67" t="n">
-        <v>667</v>
-      </c>
-      <c r="K19" s="69" t="inlineStr">
+        <v>715</v>
+      </c>
+      <c r="K19" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -5480,7 +5480,7 @@
       <c r="D21" s="89" t="n">
         <v>1.4487</v>
       </c>
-      <c r="E21" s="72" t="inlineStr">
+      <c r="E21" s="71" t="inlineStr">
         <is>
           <t>▲ +12.9%</t>
         </is>
@@ -5491,7 +5491,7 @@
       <c r="G21" s="89" t="n">
         <v>1.5563</v>
       </c>
-      <c r="H21" s="72" t="inlineStr">
+      <c r="H21" s="71" t="inlineStr">
         <is>
           <t>▲ +29.7%</t>
         </is>
@@ -5502,7 +5502,7 @@
       <c r="J21" s="67" t="n">
         <v>940</v>
       </c>
-      <c r="K21" s="69" t="inlineStr">
+      <c r="K21" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -5592,7 +5592,7 @@
       <c r="J23" s="67" t="n">
         <v>618</v>
       </c>
-      <c r="K23" s="69" t="inlineStr">
+      <c r="K23" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="E24" s="72" t="inlineStr">
-        <is>
-          <t>▲ +13.7%</t>
+        <v>0.5861</v>
+      </c>
+      <c r="E24" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="H24" s="70" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>0.5706</v>
+      </c>
+      <c r="H24" s="69" t="inlineStr">
+        <is>
+          <t>▼ -22.9%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1080</v>
+        <v>950</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1080</v>
+        <v>925</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
       <c r="D25" s="89" t="n">
         <v>1.6391</v>
       </c>
-      <c r="E25" s="72" t="inlineStr">
+      <c r="E25" s="71" t="inlineStr">
         <is>
           <t>▲ +7.5%</t>
         </is>
@@ -5671,7 +5671,7 @@
       <c r="G25" s="89" t="n">
         <v>1.25</v>
       </c>
-      <c r="H25" s="72" t="inlineStr">
+      <c r="H25" s="71" t="inlineStr">
         <is>
           <t>▲ +10.9%</t>
         </is>
@@ -5682,7 +5682,7 @@
       <c r="J25" s="67" t="n">
         <v>755</v>
       </c>
-      <c r="K25" s="69" t="inlineStr">
+      <c r="K25" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -5750,7 +5750,7 @@
       <c r="D27" s="89" t="n">
         <v>1.1258</v>
       </c>
-      <c r="E27" s="70" t="inlineStr">
+      <c r="E27" s="69" t="inlineStr">
         <is>
           <t>▼ -7.8%</t>
         </is>
@@ -5761,7 +5761,7 @@
       <c r="G27" s="89" t="n">
         <v>1.1507</v>
       </c>
-      <c r="H27" s="70" t="inlineStr">
+      <c r="H27" s="69" t="inlineStr">
         <is>
           <t>▼ -2.6%</t>
         </is>
@@ -5772,7 +5772,7 @@
       <c r="J27" s="67" t="n">
         <v>695</v>
       </c>
-      <c r="K27" s="69" t="inlineStr">
+      <c r="K27" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -5824,7 +5824,7 @@
       <c r="J29" s="67" t="n">
         <v>1300</v>
       </c>
-      <c r="K29" s="69" t="inlineStr">
+      <c r="K29" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -5914,7 +5914,7 @@
       <c r="J31" s="67" t="n">
         <v>665</v>
       </c>
-      <c r="K31" s="69" t="inlineStr">
+      <c r="K31" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -6004,7 +6004,7 @@
       <c r="J33" s="67" t="n">
         <v>630</v>
       </c>
-      <c r="K33" s="69" t="inlineStr">
+      <c r="K33" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -6072,7 +6072,7 @@
       <c r="D35" s="89" t="n">
         <v>0.9851</v>
       </c>
-      <c r="E35" s="70" t="inlineStr">
+      <c r="E35" s="69" t="inlineStr">
         <is>
           <t>▼ -7.7%</t>
         </is>
@@ -6083,7 +6083,7 @@
       <c r="G35" s="89" t="n">
         <v>0.9685</v>
       </c>
-      <c r="H35" s="72" t="inlineStr">
+      <c r="H35" s="71" t="inlineStr">
         <is>
           <t>▲ +1.5%</t>
         </is>
@@ -6094,7 +6094,7 @@
       <c r="J35" s="67" t="n">
         <v>585</v>
       </c>
-      <c r="K35" s="69" t="inlineStr">
+      <c r="K35" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -6169,7 +6169,7 @@
       <c r="D38" s="91" t="n">
         <v>1.3699</v>
       </c>
-      <c r="E38" s="72" t="inlineStr">
+      <c r="E38" s="71" t="inlineStr">
         <is>
           <t>▲ +1.6%</t>
         </is>
@@ -6180,7 +6180,7 @@
       <c r="G38" s="91" t="n">
         <v>1.3442</v>
       </c>
-      <c r="H38" s="72" t="inlineStr">
+      <c r="H38" s="71" t="inlineStr">
         <is>
           <t>▲ +4.4%</t>
         </is>
@@ -6214,7 +6214,7 @@
       <c r="D39" s="89" t="n">
         <v>1.6851</v>
       </c>
-      <c r="E39" s="70" t="inlineStr">
+      <c r="E39" s="69" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
@@ -6225,7 +6225,7 @@
       <c r="G39" s="89" t="n">
         <v>1.5078</v>
       </c>
-      <c r="H39" s="70" t="inlineStr">
+      <c r="H39" s="69" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
@@ -6236,7 +6236,7 @@
       <c r="J39" s="67" t="n">
         <v>680</v>
       </c>
-      <c r="K39" s="69" t="inlineStr">
+      <c r="K39" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -6326,7 +6326,7 @@
       <c r="J41" s="67" t="n">
         <v>26</v>
       </c>
-      <c r="K41" s="69" t="inlineStr">
+      <c r="K41" s="70" t="inlineStr">
         <is>
           <t>🔴 Low</t>
         </is>
@@ -6349,7 +6349,7 @@
       <c r="D42" s="91" t="n">
         <v>1.009</v>
       </c>
-      <c r="E42" s="72" t="inlineStr">
+      <c r="E42" s="71" t="inlineStr">
         <is>
           <t>▲ +56.5%</t>
         </is>
@@ -6360,7 +6360,7 @@
       <c r="G42" s="91" t="n">
         <v>1.046</v>
       </c>
-      <c r="H42" s="72" t="inlineStr">
+      <c r="H42" s="71" t="inlineStr">
         <is>
           <t>▲ +66.3%</t>
         </is>
@@ -6394,7 +6394,7 @@
       <c r="D43" s="89" t="n">
         <v>1.3661</v>
       </c>
-      <c r="E43" s="70" t="inlineStr">
+      <c r="E43" s="69" t="inlineStr">
         <is>
           <t>▼ -2.3%</t>
         </is>
@@ -6405,7 +6405,7 @@
       <c r="G43" s="89" t="n">
         <v>1.2762</v>
       </c>
-      <c r="H43" s="70" t="inlineStr">
+      <c r="H43" s="69" t="inlineStr">
         <is>
           <t>▼ -2.3%</t>
         </is>
@@ -6416,7 +6416,7 @@
       <c r="J43" s="67" t="n">
         <v>166.54</v>
       </c>
-      <c r="K43" s="69" t="inlineStr">
+      <c r="K43" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -6439,7 +6439,7 @@
       <c r="D44" s="91" t="n">
         <v>1.0606</v>
       </c>
-      <c r="E44" s="70" t="inlineStr">
+      <c r="E44" s="69" t="inlineStr">
         <is>
           <t>▼ -11.2%</t>
         </is>
@@ -6450,7 +6450,7 @@
       <c r="G44" s="91" t="n">
         <v>1.0087</v>
       </c>
-      <c r="H44" s="70" t="inlineStr">
+      <c r="H44" s="69" t="inlineStr">
         <is>
           <t>▼ -9.9%</t>
         </is>
@@ -6506,7 +6506,7 @@
       <c r="J45" s="67" t="n">
         <v>4945</v>
       </c>
-      <c r="K45" s="69" t="inlineStr">
+      <c r="K45" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -6572,31 +6572,31 @@
         <v>1.3691</v>
       </c>
       <c r="D47" s="89" t="n">
-        <v>1.3595</v>
-      </c>
-      <c r="E47" s="70" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+        <v>1.2057</v>
+      </c>
+      <c r="E47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -11.9%</t>
         </is>
       </c>
       <c r="F47" s="90" t="n">
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.2358</v>
-      </c>
-      <c r="H47" s="70" t="inlineStr">
-        <is>
-          <t>▼ -7.9%</t>
+        <v>1.1511</v>
+      </c>
+      <c r="H47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -14.2%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
-        <v>1989</v>
+        <v>1764</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>1808</v>
-      </c>
-      <c r="K47" s="69" t="inlineStr">
+        <v>1684</v>
+      </c>
+      <c r="K47" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -6619,7 +6619,7 @@
       <c r="D48" s="91" t="n">
         <v>1.4261</v>
       </c>
-      <c r="E48" s="72" t="inlineStr">
+      <c r="E48" s="71" t="inlineStr">
         <is>
           <t>▲ +1.1%</t>
         </is>
@@ -6628,18 +6628,18 @@
         <v>1.33</v>
       </c>
       <c r="G48" s="91" t="n">
-        <v>1.4163</v>
-      </c>
-      <c r="H48" s="72" t="inlineStr">
-        <is>
-          <t>▲ +6.5%</t>
+        <v>1.4269</v>
+      </c>
+      <c r="H48" s="71" t="inlineStr">
+        <is>
+          <t>▲ +7.3%</t>
         </is>
       </c>
       <c r="I48" s="58" t="n">
         <v>20.18</v>
       </c>
       <c r="J48" s="58" t="n">
-        <v>20.04</v>
+        <v>20.19</v>
       </c>
       <c r="K48" s="61" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
       <c r="D49" s="89" t="n">
         <v>1.6</v>
       </c>
-      <c r="E49" s="72" t="inlineStr">
+      <c r="E49" s="71" t="inlineStr">
         <is>
           <t>▲ +39.1%</t>
         </is>
@@ -6675,7 +6675,7 @@
       <c r="G49" s="89" t="n">
         <v>1.4</v>
       </c>
-      <c r="H49" s="72" t="inlineStr">
+      <c r="H49" s="71" t="inlineStr">
         <is>
           <t>▲ +33.3%</t>
         </is>
@@ -6686,7 +6686,7 @@
       <c r="J49" s="67" t="n">
         <v>1.4</v>
       </c>
-      <c r="K49" s="69" t="inlineStr">
+      <c r="K49" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="E50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="E50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="H50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="H50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -6752,31 +6752,31 @@
         <v>1.0616</v>
       </c>
       <c r="D51" s="89" t="n">
-        <v>1.0568</v>
-      </c>
-      <c r="E51" s="70" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
+        <v>1.4096</v>
+      </c>
+      <c r="E51" s="71" t="inlineStr">
+        <is>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="F51" s="90" t="n">
         <v>1.021</v>
       </c>
       <c r="G51" s="89" t="n">
-        <v>1.0568</v>
-      </c>
-      <c r="H51" s="72" t="inlineStr">
-        <is>
-          <t>▲ +3.5%</t>
+        <v>1.4096</v>
+      </c>
+      <c r="H51" s="71" t="inlineStr">
+        <is>
+          <t>▲ +38.1%</t>
         </is>
       </c>
       <c r="I51" s="67" t="n">
-        <v>2864</v>
+        <v>3820</v>
       </c>
       <c r="J51" s="67" t="n">
-        <v>2864</v>
-      </c>
-      <c r="K51" s="69" t="inlineStr">
+        <v>3820</v>
+      </c>
+      <c r="K51" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -6797,29 +6797,29 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.3819</v>
-      </c>
-      <c r="E52" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.4657</v>
+      </c>
+      <c r="E52" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
         <v>1.2741</v>
       </c>
       <c r="G52" s="91" t="n">
-        <v>1.3093</v>
-      </c>
-      <c r="H52" s="72" t="inlineStr">
-        <is>
-          <t>▲ +2.8%</t>
+        <v>1.4377</v>
+      </c>
+      <c r="H52" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.8%</t>
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>4950</v>
+        <v>5250</v>
       </c>
       <c r="J52" s="58" t="n">
-        <v>4690</v>
+        <v>5150</v>
       </c>
       <c r="K52" s="61" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
       <c r="G54" s="91" t="n">
         <v>0.2181</v>
       </c>
-      <c r="H54" s="70" t="inlineStr">
+      <c r="H54" s="69" t="inlineStr">
         <is>
           <t>▼ -50.0%</t>
         </is>
@@ -6894,31 +6894,31 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>0.7792</v>
-      </c>
-      <c r="E55" s="70" t="inlineStr">
-        <is>
-          <t>▼ -31.8%</t>
+        <v>1.1425</v>
+      </c>
+      <c r="E55" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>0.7792</v>
-      </c>
-      <c r="H55" s="70" t="inlineStr">
-        <is>
-          <t>▼ -35.2%</t>
+        <v>1.2024</v>
+      </c>
+      <c r="H55" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>10.55</v>
+        <v>15.47</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="K55" s="69" t="inlineStr">
+        <v>16.28</v>
+      </c>
+      <c r="K55" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>1.2399</v>
-      </c>
-      <c r="E56" s="72" t="inlineStr">
-        <is>
-          <t>▲ +15.6%</t>
+        <v>1.0485</v>
+      </c>
+      <c r="E56" s="69" t="inlineStr">
+        <is>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>1.2399</v>
-      </c>
-      <c r="H56" s="72" t="inlineStr">
-        <is>
-          <t>▲ +8.1%</t>
+        <v>1.0701</v>
+      </c>
+      <c r="H56" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>23</v>
+        <v>19.45</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>23</v>
+        <v>19.85</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -6984,31 +6984,31 @@
         <v>1.0316</v>
       </c>
       <c r="D57" s="89" t="n">
-        <v>0.9677</v>
-      </c>
-      <c r="E57" s="70" t="inlineStr">
-        <is>
-          <t>▼ -6.2%</t>
+        <v>1.2129</v>
+      </c>
+      <c r="E57" s="71" t="inlineStr">
+        <is>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="F57" s="90" t="n">
         <v>1.1149</v>
       </c>
       <c r="G57" s="89" t="n">
-        <v>1.0458</v>
-      </c>
-      <c r="H57" s="70" t="inlineStr">
-        <is>
-          <t>▼ -6.2%</t>
+        <v>1.1482</v>
+      </c>
+      <c r="H57" s="71" t="inlineStr">
+        <is>
+          <t>▲ +3.0%</t>
         </is>
       </c>
       <c r="I57" s="67" t="n">
-        <v>17.95</v>
+        <v>22.5</v>
       </c>
       <c r="J57" s="67" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="K57" s="69" t="inlineStr">
+        <v>21.3</v>
+      </c>
+      <c r="K57" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>1.3261</v>
-      </c>
-      <c r="E58" s="72" t="inlineStr">
-        <is>
-          <t>▲ +1.2%</t>
+        <v>1.3037</v>
+      </c>
+      <c r="E58" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>1.248</v>
-      </c>
-      <c r="H58" s="70" t="inlineStr">
-        <is>
-          <t>▼ -0.1%</t>
+        <v>1.2462</v>
+      </c>
+      <c r="H58" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.3%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>85</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>80</v>
+        <v>79.88</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7074,33 +7074,33 @@
         <v>1.0555</v>
       </c>
       <c r="D59" s="89" t="n">
-        <v>1.0582</v>
-      </c>
-      <c r="E59" s="72" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
+        <v>1.4555</v>
+      </c>
+      <c r="E59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +37.9%</t>
         </is>
       </c>
       <c r="F59" s="90" t="n">
         <v>1.0582</v>
       </c>
       <c r="G59" s="89" t="n">
-        <v>1.0636</v>
-      </c>
-      <c r="H59" s="72" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+        <v>1.4555</v>
+      </c>
+      <c r="H59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +37.5%</t>
         </is>
       </c>
       <c r="I59" s="67" t="n">
-        <v>19.63</v>
+        <v>27</v>
       </c>
       <c r="J59" s="67" t="n">
-        <v>19.73</v>
-      </c>
-      <c r="K59" s="69" t="inlineStr">
-        <is>
-          <t>🟢 High</t>
+        <v>27</v>
+      </c>
+      <c r="K59" s="70" t="inlineStr">
+        <is>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.4286</v>
-      </c>
-      <c r="E60" s="72" t="inlineStr">
-        <is>
-          <t>▲ +15.8%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="E60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.4286</v>
-      </c>
-      <c r="H60" s="72" t="inlineStr">
-        <is>
-          <t>▲ +10.9%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="H60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7164,31 +7164,31 @@
         <v>1.0641</v>
       </c>
       <c r="D61" s="89" t="n">
-        <v>1.025</v>
-      </c>
-      <c r="E61" s="70" t="inlineStr">
-        <is>
-          <t>▼ -3.7%</t>
+        <v>0.9982</v>
+      </c>
+      <c r="E61" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="F61" s="90" t="n">
         <v>0.9351</v>
       </c>
       <c r="G61" s="89" t="n">
-        <v>0.9006999999999999</v>
-      </c>
-      <c r="H61" s="70" t="inlineStr">
-        <is>
-          <t>▼ -3.7%</t>
+        <v>1.0949</v>
+      </c>
+      <c r="H61" s="71" t="inlineStr">
+        <is>
+          <t>▲ +17.1%</t>
         </is>
       </c>
       <c r="I61" s="67" t="n">
-        <v>27.88</v>
+        <v>27.15</v>
       </c>
       <c r="J61" s="67" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="K61" s="69" t="inlineStr">
+        <v>29.78</v>
+      </c>
+      <c r="K61" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -7211,7 +7211,7 @@
       <c r="D62" s="91" t="n">
         <v>2.1204</v>
       </c>
-      <c r="E62" s="70" t="inlineStr">
+      <c r="E62" s="69" t="inlineStr">
         <is>
           <t>▼ -2.3%</t>
         </is>
@@ -7222,7 +7222,7 @@
       <c r="G62" s="91" t="n">
         <v>1.9231</v>
       </c>
-      <c r="H62" s="70" t="inlineStr">
+      <c r="H62" s="69" t="inlineStr">
         <is>
           <t>▼ -6.2%</t>
         </is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7430,23 +7430,23 @@
       </c>
       <c r="G6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Angola</t>
+          <t xml:space="preserve">  2.  Egypt</t>
         </is>
       </c>
       <c r="H6" s="107" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I6" s="108" t="n">
-        <v>0.3272</v>
+        <v>0.2783</v>
       </c>
       <c r="J6" s="109" t="n">
-        <v>0.2181</v>
-      </c>
-      <c r="K6" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2783</v>
+      </c>
+      <c r="K6" s="106" t="inlineStr">
+        <is>
+          <t>▼ -41.7%</t>
         </is>
       </c>
     </row>
@@ -7474,19 +7474,19 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Algeria</t>
+          <t xml:space="preserve">  3.  Angola</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.3494</v>
+        <v>0.3272</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2305</v>
+        <v>0.2181</v>
       </c>
       <c r="K7" s="99" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="G8" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  Egypt</t>
+          <t xml:space="preserve">  4.  Algeria</t>
         </is>
       </c>
       <c r="H8" s="107" t="inlineStr">
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.4771</v>
+        <v>0.3494</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.4076</v>
+        <v>0.2305</v>
       </c>
       <c r="K8" s="99" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="G9" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Ghana</t>
+          <t xml:space="preserve">  5.  Nigeria</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
@@ -7571,14 +7571,14 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6522</v>
+        <v>0.5861</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.7223000000000001</v>
-      </c>
-      <c r="K9" s="106" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>0.5706</v>
+      </c>
+      <c r="K9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7606,19 +7606,19 @@
       </c>
       <c r="G10" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  South Sudan</t>
+          <t xml:space="preserve">  6.  Niger</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.6602</v>
+        <v>0.8262</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>0.6602</v>
+        <v>1.0232</v>
       </c>
       <c r="K10" s="99" t="inlineStr">
         <is>
@@ -7650,74 +7650,74 @@
       </c>
       <c r="G11" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Nigeria</t>
+          <t xml:space="preserve">  7.  Tunisia</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.6663</v>
+        <v>0.8377</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="K11" s="114" t="inlineStr">
-        <is>
-          <t>▲ +13.7%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K11" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Mali</t>
+          <t xml:space="preserve">  8.  Uganda</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
         <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C12" s="104" t="n">
+        <v>1.4657</v>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>1.4377</v>
+      </c>
+      <c r="E12" s="114" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
+        </is>
+      </c>
+      <c r="G12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Ghana</t>
+        </is>
+      </c>
+      <c r="H12" s="107" t="inlineStr">
+        <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C12" s="104" t="n">
-        <v>1.4487</v>
-      </c>
-      <c r="D12" s="105" t="n">
-        <v>1.5563</v>
-      </c>
-      <c r="E12" s="114" t="inlineStr">
-        <is>
-          <t>▲ +12.9%</t>
-        </is>
-      </c>
-      <c r="G12" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Botswana</t>
-        </is>
-      </c>
-      <c r="H12" s="107" t="inlineStr">
-        <is>
-          <t>Southern Africa</t>
-        </is>
-      </c>
       <c r="I12" s="108" t="n">
-        <v>0.7792</v>
+        <v>0.8471</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.7792</v>
+        <v>1.0892</v>
       </c>
       <c r="K12" s="106" t="inlineStr">
         <is>
-          <t>▼ -31.8%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  South Africa</t>
+          <t xml:space="preserve">  9.  Namibia</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
@@ -7726,19 +7726,19 @@
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.4286</v>
+        <v>1.4555</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.4286</v>
+        <v>1.4555</v>
       </c>
       <c r="E13" s="114" t="inlineStr">
         <is>
-          <t>▲ +15.8%</t>
+          <t>▲ +37.9%</t>
         </is>
       </c>
       <c r="G13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Niger</t>
+          <t xml:space="preserve">  9.  Liberia</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
@@ -7747,10 +7747,10 @@
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8262</v>
+        <v>0.8608</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>1.0232</v>
+        <v>0.9124</v>
       </c>
       <c r="K13" s="99" t="inlineStr">
         <is>
@@ -7761,40 +7761,40 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Seychelles</t>
+          <t xml:space="preserve">  10.  Mali</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.4261</v>
+        <v>1.4487</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.4163</v>
+        <v>1.5563</v>
       </c>
       <c r="E14" s="114" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="G14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Tunisia</t>
+          <t xml:space="preserve">  10.  Equatorial Guinea</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.8377</v>
+        <v>0.9106</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.7318</v>
+        <v>0.8609</v>
       </c>
       <c r="K14" s="99" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,28 +7860,28 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.009</v>
-      </c>
-      <c r="F19" s="72" t="inlineStr">
-        <is>
-          <t>▲ +56.5%</t>
+        <v>1.2544</v>
+      </c>
+      <c r="F19" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.3643</v>
+        <v>0.5942</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
@@ -7891,59 +7891,59 @@
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>1.15</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F20" s="72" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
+        <v>1.009</v>
+      </c>
+      <c r="F20" s="71" t="inlineStr">
+        <is>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.45</v>
+        <v>0.3643</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.15</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.4286</v>
-      </c>
-      <c r="F21" s="72" t="inlineStr">
-        <is>
-          <t>▲ +15.8%</t>
+        <v>1.6</v>
+      </c>
+      <c r="F21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.1954</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
@@ -7953,90 +7953,90 @@
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.0555</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.2399</v>
-      </c>
-      <c r="F22" s="72" t="inlineStr">
-        <is>
-          <t>▲ +15.6%</t>
+        <v>1.4555</v>
+      </c>
+      <c r="F22" s="71" t="inlineStr">
+        <is>
+          <t>▲ +37.9%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.1677</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0616</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="F23" s="72" t="inlineStr">
-        <is>
-          <t>▲ +13.7%</t>
+        <v>1.4096</v>
+      </c>
+      <c r="F23" s="71" t="inlineStr">
+        <is>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.2831</v>
+        <v>1.0316</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.4487</v>
-      </c>
-      <c r="F24" s="72" t="inlineStr">
-        <is>
-          <t>▲ +12.9%</t>
+        <v>1.2129</v>
+      </c>
+      <c r="F24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.1656</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
@@ -8050,86 +8050,86 @@
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.2831</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.6391</v>
-      </c>
-      <c r="F25" s="72" t="inlineStr">
-        <is>
-          <t>▲ +7.5%</t>
+        <v>1.4487</v>
+      </c>
+      <c r="F25" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.2332</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.1301</v>
-      </c>
-      <c r="F26" s="72" t="inlineStr">
-        <is>
-          <t>▲ +3.9%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="F26" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.0419</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.2762</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.3699</v>
-      </c>
-      <c r="F27" s="72" t="inlineStr">
-        <is>
-          <t>▲ +1.6%</t>
+        <v>1.3779</v>
+      </c>
+      <c r="F27" s="71" t="inlineStr">
+        <is>
+          <t>▲ +8.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.022</v>
+        <v>0.1017</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
@@ -8139,152 +8139,152 @@
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.5244</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.3873</v>
-      </c>
-      <c r="F28" s="72" t="inlineStr">
-        <is>
-          <t>▲ +1.4%</t>
+        <v>1.6391</v>
+      </c>
+      <c r="F28" s="71" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.31</v>
+        <v>1.3819</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.3261</v>
-      </c>
-      <c r="F29" s="72" t="inlineStr">
-        <is>
-          <t>▲ +1.2%</t>
+        <v>1.4657</v>
+      </c>
+      <c r="F29" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.0161</v>
+        <v>0.0838</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3587</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.4261</v>
-      </c>
-      <c r="F30" s="72" t="inlineStr">
-        <is>
-          <t>▲ +1.1%</t>
+        <v>1.4156</v>
+      </c>
+      <c r="F30" s="71" t="inlineStr">
+        <is>
+          <t>▲ +4.2%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.0569</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3479</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.0582</v>
-      </c>
-      <c r="F31" s="72" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
+        <v>1.3699</v>
+      </c>
+      <c r="F31" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.3681</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.0568</v>
-      </c>
-      <c r="F32" s="70" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G32" s="119" t="n">
-        <v>-0.0048</v>
+        <v>1.3873</v>
+      </c>
+      <c r="F32" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.4%</t>
+        </is>
+      </c>
+      <c r="G32" s="117" t="n">
+        <v>0.0192</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,28 +8294,28 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.4106</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.3595</v>
-      </c>
-      <c r="F33" s="70" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
-        </is>
-      </c>
-      <c r="G33" s="119" t="n">
-        <v>-0.009599999999999999</v>
+        <v>1.4261</v>
+      </c>
+      <c r="F33" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.1%</t>
+        </is>
+      </c>
+      <c r="G33" s="117" t="n">
+        <v>0.0155</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,59 +8325,59 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>2.17</v>
+        <v>1.31</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>2.1204</v>
-      </c>
-      <c r="F34" s="70" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
+        <v>1.3037</v>
+      </c>
+      <c r="F34" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G34" s="119" t="n">
-        <v>-0.0496</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.0722</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.3661</v>
-      </c>
-      <c r="F35" s="70" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
+        <v>1.0485</v>
+      </c>
+      <c r="F35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="G35" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
@@ -8387,28 +8387,28 @@
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.0641</v>
+        <v>2.17</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.025</v>
-      </c>
-      <c r="F36" s="70" t="inlineStr">
-        <is>
-          <t>▼ -3.7%</t>
+        <v>2.1204</v>
+      </c>
+      <c r="F36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G36" s="119" t="n">
-        <v>-0.0391</v>
+        <v>-0.0496</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,59 +8418,59 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.784</v>
+        <v>1.3986</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.6851</v>
-      </c>
-      <c r="F37" s="70" t="inlineStr">
-        <is>
-          <t>▼ -5.5%</t>
+        <v>1.3661</v>
+      </c>
+      <c r="F37" s="69" t="inlineStr">
+        <is>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G37" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.784</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>0.9677</v>
-      </c>
-      <c r="F38" s="70" t="inlineStr">
-        <is>
-          <t>▼ -6.2%</t>
+        <v>1.6851</v>
+      </c>
+      <c r="F38" s="69" t="inlineStr">
+        <is>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0639</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
@@ -8480,183 +8480,183 @@
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.0882</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.1341</v>
-      </c>
-      <c r="F39" s="70" t="inlineStr">
-        <is>
-          <t>▼ -7.5%</t>
+        <v>1.0253</v>
+      </c>
+      <c r="F39" s="69" t="inlineStr">
+        <is>
+          <t>▼ -5.8%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0921</v>
+        <v>-0.0629</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.2262</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="F40" s="70" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>1.1507</v>
+      </c>
+      <c r="F40" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0755</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0641</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.1258</v>
-      </c>
-      <c r="F41" s="70" t="inlineStr">
-        <is>
-          <t>▼ -7.8%</t>
+        <v>0.9982</v>
+      </c>
+      <c r="F41" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.1939</v>
+        <v>0.914</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.0606</v>
-      </c>
-      <c r="F42" s="70" t="inlineStr">
-        <is>
-          <t>▼ -11.2%</t>
+        <v>0.8471</v>
+      </c>
+      <c r="F42" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.0671</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.1755</v>
-      </c>
-      <c r="F43" s="70" t="inlineStr">
-        <is>
-          <t>▼ -11.5%</t>
+        <v>0.9851</v>
+      </c>
+      <c r="F43" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.1534</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.2212</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.0538</v>
-      </c>
-      <c r="F44" s="70" t="inlineStr">
-        <is>
-          <t>▼ -17.4%</t>
+        <v>1.1258</v>
+      </c>
+      <c r="F44" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.2224</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
@@ -8666,59 +8666,59 @@
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.3587</v>
+        <v>1.2886</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>1.1043</v>
-      </c>
-      <c r="F45" s="70" t="inlineStr">
-        <is>
-          <t>▼ -18.7%</t>
+        <v>1.1719</v>
+      </c>
+      <c r="F45" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.1%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.2544</v>
+        <v>-0.1167</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>0.914</v>
+        <v>1.1939</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.6522</v>
-      </c>
-      <c r="F46" s="70" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>1.0606</v>
+      </c>
+      <c r="F46" s="69" t="inlineStr">
+        <is>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.2618</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
@@ -8728,53 +8728,84 @@
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3289</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.8959</v>
-      </c>
-      <c r="F47" s="70" t="inlineStr">
-        <is>
-          <t>▼ -30.5%</t>
+        <v>1.1755</v>
+      </c>
+      <c r="F47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -11.5%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.3927</v>
+        <v>-0.1534</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.3691</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>0.7792</v>
-      </c>
-      <c r="F48" s="70" t="inlineStr">
-        <is>
-          <t>▼ -31.8%</t>
+        <v>1.2057</v>
+      </c>
+      <c r="F48" s="69" t="inlineStr">
+        <is>
+          <t>▼ -11.9%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.3633</v>
+        <v>-0.1634</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="53" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B49" s="54" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="C49" s="116" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="D49" s="88" t="n">
+        <v>0.4771</v>
+      </c>
+      <c r="E49" s="91" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="F49" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.7%</t>
+        </is>
+      </c>
+      <c r="G49" s="119" t="n">
+        <v>-0.1988</v>
       </c>
     </row>
   </sheetData>
@@ -8831,16 +8862,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6327166666666667</v>
+        <v>0.6536</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6112333333333333</v>
+        <v>0.5869166666666668</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.0538</v>
+        <v>1.3779</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -8933,23 +8964,23 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.4771</v>
+        <v>0.2783</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.4076</v>
+        <v>0.2783</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G7" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="69" t="inlineStr">
+        <v>14</v>
+      </c>
+      <c r="G7" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.7%</t>
+        </is>
+      </c>
+      <c r="H7" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -9001,23 +9032,23 @@
         </is>
       </c>
       <c r="C9" s="66" t="n">
-        <v>1.0538</v>
+        <v>1.3779</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.2223</v>
+        <v>1.2722</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>10.57</v>
+        <v>13.82</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>12.26</v>
-      </c>
-      <c r="G9" s="70" t="inlineStr">
-        <is>
-          <t>▼ -17.4%</t>
-        </is>
-      </c>
-      <c r="H9" s="69" t="inlineStr">
+        <v>12.76</v>
+      </c>
+      <c r="G9" s="71" t="inlineStr">
+        <is>
+          <t>▲ +8.0%</t>
+        </is>
+      </c>
+      <c r="H9" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -9038,13 +9069,13 @@
         <v>1.0474</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="E10" s="58" t="n">
         <v>630</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
@@ -9085,7 +9116,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="69" t="inlineStr">
+      <c r="H11" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -9107,13 +9138,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.12671875</v>
+        <v>1.16508125</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.11750625</v>
+        <v>1.1378375</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6522</v>
+        <v>0.5861</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9175,20 +9206,20 @@
         </is>
       </c>
       <c r="C16" s="57" t="n">
-        <v>1.1341</v>
+        <v>1.1507</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>1.1589</v>
+        <v>1.1921</v>
       </c>
       <c r="E16" s="58" t="n">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="F16" s="58" t="n">
-        <v>700</v>
-      </c>
-      <c r="G16" s="70" t="inlineStr">
-        <is>
-          <t>▼ -7.5%</t>
+        <v>720</v>
+      </c>
+      <c r="G16" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="H16" s="61" t="inlineStr">
@@ -9225,7 +9256,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="69" t="inlineStr">
+      <c r="H17" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -9243,20 +9274,20 @@
         </is>
       </c>
       <c r="C18" s="57" t="n">
-        <v>0.8959</v>
+        <v>1.1719</v>
       </c>
       <c r="D18" s="57" t="n">
-        <v>0.8959</v>
+        <v>0.9846</v>
       </c>
       <c r="E18" s="58" t="n">
-        <v>99</v>
+        <v>129.5</v>
       </c>
       <c r="F18" s="58" t="n">
-        <v>99</v>
-      </c>
-      <c r="G18" s="70" t="inlineStr">
-        <is>
-          <t>▼ -30.5%</t>
+        <v>108.8</v>
+      </c>
+      <c r="G18" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.1%</t>
         </is>
       </c>
       <c r="H18" s="61" t="inlineStr">
@@ -9277,23 +9308,23 @@
         </is>
       </c>
       <c r="C19" s="66" t="n">
-        <v>1.1301</v>
+        <v>1.0253</v>
       </c>
       <c r="D19" s="66" t="n">
-        <v>1.1726</v>
+        <v>1.0253</v>
       </c>
       <c r="E19" s="67" t="n">
-        <v>82.5</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F19" s="67" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="G19" s="72" t="inlineStr">
-        <is>
-          <t>▲ +3.9%</t>
-        </is>
-      </c>
-      <c r="H19" s="69" t="inlineStr">
+        <v>74.84999999999999</v>
+      </c>
+      <c r="G19" s="69" t="inlineStr">
+        <is>
+          <t>▼ -5.8%</t>
+        </is>
+      </c>
+      <c r="H19" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -9311,20 +9342,20 @@
         </is>
       </c>
       <c r="C20" s="57" t="n">
-        <v>0.6522</v>
+        <v>0.8471</v>
       </c>
       <c r="D20" s="57" t="n">
-        <v>0.7223000000000001</v>
+        <v>1.0892</v>
       </c>
       <c r="E20" s="58" t="n">
-        <v>10.24</v>
+        <v>13.3</v>
       </c>
       <c r="F20" s="58" t="n">
-        <v>11.34</v>
-      </c>
-      <c r="G20" s="70" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>17.1</v>
+      </c>
+      <c r="G20" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="H20" s="61" t="inlineStr">
@@ -9356,12 +9387,12 @@
       <c r="F21" s="67" t="n">
         <v>12000</v>
       </c>
-      <c r="G21" s="72" t="inlineStr">
+      <c r="G21" s="71" t="inlineStr">
         <is>
           <t>▲ +1.4%</t>
         </is>
       </c>
-      <c r="H21" s="69" t="inlineStr">
+      <c r="H21" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -9390,7 +9421,7 @@
       <c r="F22" s="58" t="n">
         <v>618</v>
       </c>
-      <c r="G22" s="70" t="inlineStr">
+      <c r="G22" s="69" t="inlineStr">
         <is>
           <t>▼ -11.5%</t>
         </is>
@@ -9413,23 +9444,23 @@
         </is>
       </c>
       <c r="C23" s="66" t="n">
-        <v>1.1043</v>
+        <v>1.4156</v>
       </c>
       <c r="D23" s="66" t="n">
-        <v>1.1043</v>
+        <v>1.1838</v>
       </c>
       <c r="E23" s="67" t="n">
-        <v>667</v>
+        <v>855</v>
       </c>
       <c r="F23" s="67" t="n">
-        <v>667</v>
-      </c>
-      <c r="G23" s="70" t="inlineStr">
-        <is>
-          <t>▼ -18.7%</t>
-        </is>
-      </c>
-      <c r="H23" s="69" t="inlineStr">
+        <v>715</v>
+      </c>
+      <c r="G23" s="71" t="inlineStr">
+        <is>
+          <t>▲ +4.2%</t>
+        </is>
+      </c>
+      <c r="H23" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -9492,12 +9523,12 @@
       <c r="F25" s="67" t="n">
         <v>940</v>
       </c>
-      <c r="G25" s="72" t="inlineStr">
+      <c r="G25" s="71" t="inlineStr">
         <is>
           <t>▲ +12.9%</t>
         </is>
       </c>
-      <c r="H25" s="69" t="inlineStr">
+      <c r="H25" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -9565,7 +9596,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H27" s="69" t="inlineStr">
+      <c r="H27" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -9583,20 +9614,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.5861</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.5706</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1080</v>
+        <v>950</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1080</v>
-      </c>
-      <c r="G28" s="72" t="inlineStr">
-        <is>
-          <t>▲ +13.7%</t>
+        <v>925</v>
+      </c>
+      <c r="G28" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9628,12 +9659,12 @@
       <c r="F29" s="67" t="n">
         <v>755</v>
       </c>
-      <c r="G29" s="72" t="inlineStr">
+      <c r="G29" s="71" t="inlineStr">
         <is>
           <t>▲ +7.5%</t>
         </is>
       </c>
-      <c r="H29" s="69" t="inlineStr">
+      <c r="H29" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -9696,12 +9727,12 @@
       <c r="F31" s="67" t="n">
         <v>695</v>
       </c>
-      <c r="G31" s="70" t="inlineStr">
+      <c r="G31" s="69" t="inlineStr">
         <is>
           <t>▼ -7.8%</t>
         </is>
       </c>
-      <c r="H31" s="69" t="inlineStr">
+      <c r="H31" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -9841,7 +9872,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H37" s="69" t="inlineStr">
+      <c r="H37" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -9909,7 +9940,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H39" s="69" t="inlineStr">
+      <c r="H39" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -9977,7 +10008,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H41" s="69" t="inlineStr">
+      <c r="H41" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -10006,7 +10037,7 @@
       <c r="F42" s="58" t="n">
         <v>585</v>
       </c>
-      <c r="G42" s="70" t="inlineStr">
+      <c r="G42" s="69" t="inlineStr">
         <is>
           <t>▼ -7.7%</t>
         </is>
@@ -10045,7 +10076,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H43" s="69" t="inlineStr">
+      <c r="H43" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -10067,13 +10098,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.430346666666666</v>
+        <v>1.488813333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.358573333333333</v>
+        <v>1.425326666666667</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.6602</v>
+        <v>1.009</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10146,7 +10177,7 @@
       <c r="F48" s="58" t="n">
         <v>3925</v>
       </c>
-      <c r="G48" s="72" t="inlineStr">
+      <c r="G48" s="71" t="inlineStr">
         <is>
           <t>▲ +1.6%</t>
         </is>
@@ -10180,12 +10211,12 @@
       <c r="F49" s="67" t="n">
         <v>680</v>
       </c>
-      <c r="G49" s="70" t="inlineStr">
+      <c r="G49" s="69" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
       </c>
-      <c r="H49" s="69" t="inlineStr">
+      <c r="H49" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -10253,7 +10284,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H51" s="69" t="inlineStr">
+      <c r="H51" s="70" t="inlineStr">
         <is>
           <t>🔴 Low</t>
         </is>
@@ -10282,7 +10313,7 @@
       <c r="F52" s="58" t="n">
         <v>137.03</v>
       </c>
-      <c r="G52" s="72" t="inlineStr">
+      <c r="G52" s="71" t="inlineStr">
         <is>
           <t>▲ +56.5%</t>
         </is>
@@ -10316,12 +10347,12 @@
       <c r="F53" s="67" t="n">
         <v>166.54</v>
       </c>
-      <c r="G53" s="70" t="inlineStr">
+      <c r="G53" s="69" t="inlineStr">
         <is>
           <t>▼ -2.3%</t>
         </is>
       </c>
-      <c r="H53" s="69" t="inlineStr">
+      <c r="H53" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -10350,7 +10381,7 @@
       <c r="F54" s="58" t="n">
         <v>4660</v>
       </c>
-      <c r="G54" s="70" t="inlineStr">
+      <c r="G54" s="69" t="inlineStr">
         <is>
           <t>▼ -11.2%</t>
         </is>
@@ -10389,7 +10420,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H55" s="69" t="inlineStr">
+      <c r="H55" s="70" t="inlineStr">
         <is>
           <t>🟢 High</t>
         </is>
@@ -10441,23 +10472,23 @@
         </is>
       </c>
       <c r="C57" s="66" t="n">
-        <v>1.3595</v>
+        <v>1.2057</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.2358</v>
+        <v>1.1511</v>
       </c>
       <c r="E57" s="67" t="n">
-        <v>1989</v>
+        <v>1764</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>1808</v>
-      </c>
-      <c r="G57" s="70" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
-        </is>
-      </c>
-      <c r="H57" s="69" t="inlineStr">
+        <v>1684</v>
+      </c>
+      <c r="G57" s="69" t="inlineStr">
+        <is>
+          <t>▼ -11.9%</t>
+        </is>
+      </c>
+      <c r="H57" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -10478,15 +10509,15 @@
         <v>1.4261</v>
       </c>
       <c r="D58" s="57" t="n">
-        <v>1.4163</v>
+        <v>1.4269</v>
       </c>
       <c r="E58" s="58" t="n">
         <v>20.18</v>
       </c>
       <c r="F58" s="58" t="n">
-        <v>20.04</v>
-      </c>
-      <c r="G58" s="72" t="inlineStr">
+        <v>20.19</v>
+      </c>
+      <c r="G58" s="71" t="inlineStr">
         <is>
           <t>▲ +1.1%</t>
         </is>
@@ -10520,12 +10551,12 @@
       <c r="F59" s="67" t="n">
         <v>1.4</v>
       </c>
-      <c r="G59" s="72" t="inlineStr">
+      <c r="G59" s="71" t="inlineStr">
         <is>
           <t>▲ +39.1%</t>
         </is>
       </c>
-      <c r="H59" s="69" t="inlineStr">
+      <c r="H59" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -10543,20 +10574,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G60" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5700</v>
+      </c>
+      <c r="G60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">
@@ -10577,23 +10608,23 @@
         </is>
       </c>
       <c r="C61" s="66" t="n">
-        <v>1.0568</v>
+        <v>1.4096</v>
       </c>
       <c r="D61" s="66" t="n">
-        <v>1.0568</v>
+        <v>1.4096</v>
       </c>
       <c r="E61" s="67" t="n">
-        <v>2864</v>
+        <v>3820</v>
       </c>
       <c r="F61" s="67" t="n">
-        <v>2864</v>
-      </c>
-      <c r="G61" s="70" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="H61" s="69" t="inlineStr">
+        <v>3820</v>
+      </c>
+      <c r="G61" s="71" t="inlineStr">
+        <is>
+          <t>▲ +32.8%</t>
+        </is>
+      </c>
+      <c r="H61" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -10611,20 +10642,20 @@
         </is>
       </c>
       <c r="C62" s="57" t="n">
-        <v>1.3819</v>
+        <v>1.4657</v>
       </c>
       <c r="D62" s="57" t="n">
-        <v>1.3093</v>
+        <v>1.4377</v>
       </c>
       <c r="E62" s="58" t="n">
-        <v>4950</v>
+        <v>5250</v>
       </c>
       <c r="F62" s="58" t="n">
-        <v>4690</v>
-      </c>
-      <c r="G62" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5150</v>
+      </c>
+      <c r="G62" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="H62" s="61" t="inlineStr">
@@ -10649,10 +10680,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.141366666666667</v>
+        <v>1.220277777777778</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.094111111111111</v>
+        <v>1.192455555555555</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10751,23 +10782,23 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>0.7792</v>
+        <v>1.1425</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>0.7792</v>
+        <v>1.2024</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>10.55</v>
+        <v>15.47</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="G68" s="70" t="inlineStr">
-        <is>
-          <t>▼ -31.8%</t>
-        </is>
-      </c>
-      <c r="H68" s="69" t="inlineStr">
+        <v>16.28</v>
+      </c>
+      <c r="G68" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -10785,20 +10816,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>1.2399</v>
+        <v>1.0485</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>1.2399</v>
+        <v>1.0701</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>23</v>
+        <v>19.45</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>23</v>
-      </c>
-      <c r="G69" s="72" t="inlineStr">
-        <is>
-          <t>▲ +15.6%</t>
+        <v>19.85</v>
+      </c>
+      <c r="G69" s="69" t="inlineStr">
+        <is>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">
@@ -10819,23 +10850,23 @@
         </is>
       </c>
       <c r="C70" s="66" t="n">
-        <v>0.9677</v>
+        <v>1.2129</v>
       </c>
       <c r="D70" s="66" t="n">
-        <v>1.0458</v>
+        <v>1.1482</v>
       </c>
       <c r="E70" s="67" t="n">
-        <v>17.95</v>
+        <v>22.5</v>
       </c>
       <c r="F70" s="67" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="G70" s="70" t="inlineStr">
-        <is>
-          <t>▼ -6.2%</t>
-        </is>
-      </c>
-      <c r="H70" s="69" t="inlineStr">
+        <v>21.3</v>
+      </c>
+      <c r="G70" s="71" t="inlineStr">
+        <is>
+          <t>▲ +17.6%</t>
+        </is>
+      </c>
+      <c r="H70" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -10853,20 +10884,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>1.3261</v>
+        <v>1.3037</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>1.248</v>
+        <v>1.2462</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>85</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>80</v>
-      </c>
-      <c r="G71" s="72" t="inlineStr">
-        <is>
-          <t>▲ +1.2%</t>
+        <v>79.88</v>
+      </c>
+      <c r="G71" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">
@@ -10887,25 +10918,25 @@
         </is>
       </c>
       <c r="C72" s="66" t="n">
-        <v>1.0582</v>
+        <v>1.4555</v>
       </c>
       <c r="D72" s="66" t="n">
-        <v>1.0636</v>
+        <v>1.4555</v>
       </c>
       <c r="E72" s="67" t="n">
-        <v>19.63</v>
+        <v>27</v>
       </c>
       <c r="F72" s="67" t="n">
-        <v>19.73</v>
-      </c>
-      <c r="G72" s="72" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
-        </is>
-      </c>
-      <c r="H72" s="69" t="inlineStr">
-        <is>
-          <t>🟢 High</t>
+        <v>27</v>
+      </c>
+      <c r="G72" s="71" t="inlineStr">
+        <is>
+          <t>▲ +37.9%</t>
+        </is>
+      </c>
+      <c r="H72" s="70" t="inlineStr">
+        <is>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -10921,20 +10952,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.4286</v>
+        <v>1.3736</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.4286</v>
+        <v>1.3736</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>26</v>
-      </c>
-      <c r="G73" s="72" t="inlineStr">
-        <is>
-          <t>▲ +15.8%</t>
+        <v>25</v>
+      </c>
+      <c r="G73" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">
@@ -10955,23 +10986,23 @@
         </is>
       </c>
       <c r="C74" s="66" t="n">
-        <v>1.025</v>
+        <v>0.9982</v>
       </c>
       <c r="D74" s="66" t="n">
-        <v>0.9006999999999999</v>
+        <v>1.0949</v>
       </c>
       <c r="E74" s="67" t="n">
-        <v>27.88</v>
+        <v>27.15</v>
       </c>
       <c r="F74" s="67" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="G74" s="70" t="inlineStr">
-        <is>
-          <t>▼ -3.7%</t>
-        </is>
-      </c>
-      <c r="H74" s="69" t="inlineStr">
+        <v>29.78</v>
+      </c>
+      <c r="G74" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.2%</t>
+        </is>
+      </c>
+      <c r="H74" s="70" t="inlineStr">
         <is>
           <t>🟡 Medium</t>
         </is>
@@ -11000,7 +11031,7 @@
       <c r="F75" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="G75" s="70" t="inlineStr">
+      <c r="G75" s="69" t="inlineStr">
         <is>
           <t>▼ -2.3%</t>
         </is>

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1073,18 +1073,21 @@
     <xf numFmtId="164" fontId="19" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1096,9 +1099,6 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-01</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-03</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.215</t>
+          <t>$1.220</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.174</t>
+          <t>$1.181</t>
         </is>
       </c>
     </row>
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6536</v>
+        <v>0.6636000000000001</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.5869166666666668</v>
+        <v>0.6140166666666667</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.3779</v>
+        <v>1.4447</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.16508125</v>
+        <v>1.175625</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.1378375</v>
+        <v>1.15045</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.5861</v>
+        <v>0.6663</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2173625</v>
+        <v>1.2275</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1930875</v>
+        <v>1.191225</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.488813333333333</v>
+        <v>1.504273333333334</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.425326666666667</v>
+        <v>1.44424</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>1.009</v>
+        <v>1.0606</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,16 +1853,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.220277777777778</v>
+        <v>1.189444444444445</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.192455555555555</v>
+        <v>1.162866666666667</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>2.1204</v>
+        <v>2.1808</v>
       </c>
     </row>
     <row r="18" ht="10" customHeight="1"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-01</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.338</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.2684</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.7%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.3779</v>
+        <v>1.4447</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.2722</v>
+        <v>1.4447</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>13.82</v>
+        <v>14.49</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>12.76</v>
+        <v>14.49</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.0%</t>
+          <t>▲ +13.2%</t>
         </is>
       </c>
       <c r="K7" s="70" t="inlineStr">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="F8" s="57" t="n">
         <v>0.9809</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="H8" s="58" t="n">
         <v>590</v>
@@ -2263,9 +2263,9 @@
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J8" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2350,23 +2350,23 @@
         </is>
       </c>
       <c r="E11" s="66" t="n">
-        <v>1.1507</v>
+        <v>1.1258</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>1.1921</v>
+        <v>1.1589</v>
       </c>
       <c r="G11" s="67" t="n">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
       </c>
       <c r="J11" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="K11" s="70" t="inlineStr">
@@ -2444,23 +2444,23 @@
         </is>
       </c>
       <c r="E13" s="66" t="n">
-        <v>1.1719</v>
+        <v>1.0635</v>
       </c>
       <c r="F13" s="66" t="n">
-        <v>0.9846</v>
+        <v>1.0635</v>
       </c>
       <c r="G13" s="67" t="n">
-        <v>129.5</v>
+        <v>117.52</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>108.8</v>
+        <v>117.52</v>
       </c>
       <c r="I13" s="68" t="n">
         <v>110.5</v>
       </c>
       <c r="J13" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.1%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="K13" s="70" t="inlineStr">
@@ -2491,23 +2491,23 @@
         </is>
       </c>
       <c r="E14" s="57" t="n">
-        <v>1.0253</v>
+        <v>1.1301</v>
       </c>
       <c r="F14" s="57" t="n">
-        <v>1.0253</v>
+        <v>1.1589</v>
       </c>
       <c r="G14" s="58" t="n">
-        <v>74.84999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H14" s="58" t="n">
-        <v>74.84999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I14" s="59" t="n">
         <v>73</v>
       </c>
-      <c r="J14" s="69" t="inlineStr">
-        <is>
-          <t>▼ -5.8%</t>
+      <c r="J14" s="71" t="inlineStr">
+        <is>
+          <t>▲ +3.9%</t>
         </is>
       </c>
       <c r="K14" s="61" t="inlineStr">
@@ -2538,23 +2538,23 @@
         </is>
       </c>
       <c r="E15" s="66" t="n">
-        <v>0.8471</v>
+        <v>0.9675</v>
       </c>
       <c r="F15" s="66" t="n">
-        <v>1.0892</v>
+        <v>1.1369</v>
       </c>
       <c r="G15" s="67" t="n">
-        <v>13.3</v>
+        <v>15.19</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>17.1</v>
+        <v>17.85</v>
       </c>
       <c r="I15" s="68" t="n">
         <v>15.7</v>
       </c>
-      <c r="J15" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+      <c r="J15" s="71" t="inlineStr">
+        <is>
+          <t>▲ +5.8%</t>
         </is>
       </c>
       <c r="K15" s="70" t="inlineStr">
@@ -2632,23 +2632,23 @@
         </is>
       </c>
       <c r="E17" s="66" t="n">
-        <v>1.1755</v>
+        <v>1.3377</v>
       </c>
       <c r="F17" s="66" t="n">
-        <v>1.0232</v>
+        <v>1.2583</v>
       </c>
       <c r="G17" s="67" t="n">
-        <v>710</v>
+        <v>808</v>
       </c>
       <c r="H17" s="67" t="n">
-        <v>618</v>
+        <v>760</v>
       </c>
       <c r="I17" s="68" t="n">
         <v>604</v>
       </c>
-      <c r="J17" s="69" t="inlineStr">
-        <is>
-          <t>▼ -11.5%</t>
+      <c r="J17" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.7%</t>
         </is>
       </c>
       <c r="K17" s="70" t="inlineStr">
@@ -2773,23 +2773,23 @@
         </is>
       </c>
       <c r="E20" s="57" t="n">
-        <v>1.4487</v>
+        <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.5563</v>
+        <v>1.2003</v>
       </c>
       <c r="G20" s="58" t="n">
-        <v>875</v>
+        <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>940</v>
+        <v>725</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J20" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.9%</t>
+      <c r="J20" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K20" s="61" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.5861</v>
+        <v>0.6663</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.5706</v>
+        <v>0.6663</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>950</v>
+        <v>1080</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>925</v>
+        <v>1080</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
-      <c r="J23" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J23" s="71" t="inlineStr">
+        <is>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+      <c r="J34" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -3680,23 +3680,23 @@
         </is>
       </c>
       <c r="E41" s="66" t="n">
-        <v>1.009</v>
+        <v>1.0871</v>
       </c>
       <c r="F41" s="66" t="n">
-        <v>1.046</v>
+        <v>1.245</v>
       </c>
       <c r="G41" s="67" t="n">
-        <v>132.18</v>
+        <v>142.41</v>
       </c>
       <c r="H41" s="67" t="n">
-        <v>137.03</v>
+        <v>163.09</v>
       </c>
       <c r="I41" s="68" t="n">
         <v>131</v>
       </c>
       <c r="J41" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="K41" s="70" t="inlineStr">
@@ -3915,23 +3915,23 @@
         </is>
       </c>
       <c r="E46" s="57" t="n">
-        <v>1.2057</v>
+        <v>1.3595</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.1511</v>
+        <v>1.2358</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>1764</v>
+        <v>1989</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>1684</v>
+        <v>1808</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
       </c>
       <c r="J46" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.9%</t>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="K46" s="61" t="inlineStr">
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>1.1425</v>
+        <v>1.7725</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>1.2024</v>
+        <v>1.9202</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>15.47</v>
+        <v>24</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>16.28</v>
+        <v>26</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
-      <c r="J54" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J54" s="71" t="inlineStr">
+        <is>
+          <t>▲ +55.1%</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
       <c r="J55" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="K55" s="70" t="inlineStr">
@@ -4439,28 +4439,28 @@
         </is>
       </c>
       <c r="E58" s="57" t="n">
-        <v>1.4555</v>
+        <v>1.0582</v>
       </c>
       <c r="F58" s="57" t="n">
-        <v>1.4555</v>
+        <v>1.0636</v>
       </c>
       <c r="G58" s="58" t="n">
-        <v>27</v>
+        <v>19.63</v>
       </c>
       <c r="H58" s="58" t="n">
-        <v>27</v>
+        <v>19.73</v>
       </c>
       <c r="I58" s="59" t="n">
         <v>18.55</v>
       </c>
       <c r="J58" s="71" t="inlineStr">
         <is>
-          <t>▲ +37.9%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.3736</v>
+        <v>0.989</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.3736</v>
+        <v>0.989</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+      <c r="J59" s="69" t="inlineStr">
+        <is>
+          <t>▼ -19.8%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4580,13 +4580,13 @@
         </is>
       </c>
       <c r="E61" s="66" t="n">
-        <v>2.1204</v>
+        <v>2.1808</v>
       </c>
       <c r="F61" s="66" t="n">
         <v>1.9231</v>
       </c>
       <c r="G61" s="67" t="n">
-        <v>55.13</v>
+        <v>56.7</v>
       </c>
       <c r="H61" s="67" t="n">
         <v>50</v>
@@ -4594,9 +4594,9 @@
       <c r="I61" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="J61" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
+      <c r="J61" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="K61" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.21512037037037</v>
+        <v>1.220012962962962</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.17377037037037</v>
+        <v>1.180564814814815</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-01</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-03</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.2783</v>
+        <v>0.338</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.7%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2783</v>
+        <v>0.2684</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -31.7%</t>
+          <t>▼ -34.1%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.3779</v>
+        <v>1.4447</v>
       </c>
       <c r="E8" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.0%</t>
+          <t>▲ +13.2%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.2722</v>
+        <v>1.4447</v>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>▲ +10.9%</t>
+          <t>▲ +26.0%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>13.82</v>
+        <v>14.49</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>12.76</v>
+        <v>14.49</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -4976,11 +4976,11 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.0474</v>
-      </c>
-      <c r="E9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9809</v>
+      </c>
+      <c r="E9" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="J9" s="67" t="n">
         <v>590</v>
@@ -5073,29 +5073,29 @@
         <v>1.2262</v>
       </c>
       <c r="D12" s="91" t="n">
-        <v>1.1507</v>
+        <v>1.1258</v>
       </c>
       <c r="E12" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="F12" s="90" t="n">
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>1.1921</v>
+        <v>1.1589</v>
       </c>
       <c r="H12" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.3%</t>
+          <t>▼ -8.0%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -5163,29 +5163,29 @@
         <v>1.2886</v>
       </c>
       <c r="D14" s="91" t="n">
-        <v>1.1719</v>
+        <v>1.0635</v>
       </c>
       <c r="E14" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.1%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="F14" s="90" t="n">
         <v>1.0826</v>
       </c>
       <c r="G14" s="91" t="n">
-        <v>0.9846</v>
+        <v>1.0635</v>
       </c>
       <c r="H14" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.1%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="I14" s="58" t="n">
-        <v>129.5</v>
+        <v>117.52</v>
       </c>
       <c r="J14" s="58" t="n">
-        <v>108.8</v>
+        <v>117.52</v>
       </c>
       <c r="K14" s="61" t="inlineStr">
         <is>
@@ -5208,29 +5208,29 @@
         <v>1.0882</v>
       </c>
       <c r="D15" s="89" t="n">
-        <v>1.0253</v>
-      </c>
-      <c r="E15" s="69" t="inlineStr">
-        <is>
-          <t>▼ -5.8%</t>
+        <v>1.1301</v>
+      </c>
+      <c r="E15" s="71" t="inlineStr">
+        <is>
+          <t>▲ +3.9%</t>
         </is>
       </c>
       <c r="F15" s="90" t="n">
         <v>0.9559</v>
       </c>
       <c r="G15" s="89" t="n">
-        <v>1.0253</v>
+        <v>1.1589</v>
       </c>
       <c r="H15" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.3%</t>
+          <t>▲ +21.2%</t>
         </is>
       </c>
       <c r="I15" s="67" t="n">
-        <v>74.84999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="J15" s="67" t="n">
-        <v>74.84999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K15" s="70" t="inlineStr">
         <is>
@@ -5253,29 +5253,29 @@
         <v>0.914</v>
       </c>
       <c r="D16" s="91" t="n">
-        <v>0.8471</v>
-      </c>
-      <c r="E16" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>0.9675</v>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>▲ +5.8%</t>
         </is>
       </c>
       <c r="F16" s="90" t="n">
         <v>0.914</v>
       </c>
       <c r="G16" s="91" t="n">
-        <v>1.0892</v>
+        <v>1.1369</v>
       </c>
       <c r="H16" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.2%</t>
+          <t>▲ +24.4%</t>
         </is>
       </c>
       <c r="I16" s="58" t="n">
-        <v>13.3</v>
+        <v>15.19</v>
       </c>
       <c r="J16" s="58" t="n">
-        <v>17.1</v>
+        <v>17.85</v>
       </c>
       <c r="K16" s="61" t="inlineStr">
         <is>
@@ -5343,29 +5343,29 @@
         <v>1.3289</v>
       </c>
       <c r="D18" s="91" t="n">
-        <v>1.1755</v>
-      </c>
-      <c r="E18" s="69" t="inlineStr">
-        <is>
-          <t>▼ -11.5%</t>
+        <v>1.3377</v>
+      </c>
+      <c r="E18" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.7%</t>
         </is>
       </c>
       <c r="F18" s="90" t="n">
         <v>1.2693</v>
       </c>
       <c r="G18" s="91" t="n">
-        <v>1.0232</v>
+        <v>1.2583</v>
       </c>
       <c r="H18" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.4%</t>
+          <t>▼ -0.9%</t>
         </is>
       </c>
       <c r="I18" s="58" t="n">
-        <v>710</v>
+        <v>808</v>
       </c>
       <c r="J18" s="58" t="n">
-        <v>618</v>
+        <v>760</v>
       </c>
       <c r="K18" s="61" t="inlineStr">
         <is>
@@ -5478,29 +5478,29 @@
         <v>1.2831</v>
       </c>
       <c r="D21" s="89" t="n">
-        <v>1.4487</v>
-      </c>
-      <c r="E21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.9%</t>
+        <v>1.2831</v>
+      </c>
+      <c r="E21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="90" t="n">
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.5563</v>
-      </c>
-      <c r="H21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +29.7%</t>
+        <v>1.2003</v>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
-        <v>875</v>
+        <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>940</v>
+        <v>725</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.5861</v>
-      </c>
-      <c r="E24" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.6663</v>
+      </c>
+      <c r="E24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.5706</v>
+        <v>0.6663</v>
       </c>
       <c r="H24" s="69" t="inlineStr">
         <is>
-          <t>▼ -22.9%</t>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>950</v>
+        <v>1080</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>925</v>
+        <v>1080</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="E35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>1.0662</v>
+      </c>
+      <c r="E35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9685</v>
-      </c>
-      <c r="H35" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.5%</t>
+        <v>0.9536</v>
+      </c>
+      <c r="H35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6347,29 +6347,29 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="D42" s="91" t="n">
-        <v>1.009</v>
+        <v>1.0871</v>
       </c>
       <c r="E42" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="F42" s="90" t="n">
         <v>0.6288</v>
       </c>
       <c r="G42" s="91" t="n">
-        <v>1.046</v>
+        <v>1.245</v>
       </c>
       <c r="H42" s="71" t="inlineStr">
         <is>
-          <t>▲ +66.3%</t>
+          <t>▲ +98.0%</t>
         </is>
       </c>
       <c r="I42" s="58" t="n">
-        <v>132.18</v>
+        <v>142.41</v>
       </c>
       <c r="J42" s="58" t="n">
-        <v>137.03</v>
+        <v>163.09</v>
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
@@ -6572,29 +6572,29 @@
         <v>1.3691</v>
       </c>
       <c r="D47" s="89" t="n">
-        <v>1.2057</v>
+        <v>1.3595</v>
       </c>
       <c r="E47" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.9%</t>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="F47" s="90" t="n">
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.1511</v>
+        <v>1.2358</v>
       </c>
       <c r="H47" s="69" t="inlineStr">
         <is>
-          <t>▼ -14.2%</t>
+          <t>▼ -7.9%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
-        <v>1764</v>
+        <v>1989</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>1684</v>
+        <v>1808</v>
       </c>
       <c r="K47" s="70" t="inlineStr">
         <is>
@@ -6894,29 +6894,29 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>1.1425</v>
-      </c>
-      <c r="E55" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.7725</v>
+      </c>
+      <c r="E55" s="71" t="inlineStr">
+        <is>
+          <t>▲ +55.1%</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>1.2024</v>
-      </c>
-      <c r="H55" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.9202</v>
+      </c>
+      <c r="H55" s="71" t="inlineStr">
+        <is>
+          <t>▲ +59.7%</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>15.47</v>
+        <v>24</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>16.28</v>
+        <v>26</v>
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="H56" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -24.8%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -7074,33 +7074,33 @@
         <v>1.0555</v>
       </c>
       <c r="D59" s="89" t="n">
-        <v>1.4555</v>
+        <v>1.0582</v>
       </c>
       <c r="E59" s="71" t="inlineStr">
         <is>
-          <t>▲ +37.9%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="F59" s="90" t="n">
         <v>1.0582</v>
       </c>
       <c r="G59" s="89" t="n">
-        <v>1.4555</v>
+        <v>1.0636</v>
       </c>
       <c r="H59" s="71" t="inlineStr">
         <is>
-          <t>▲ +37.5%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="I59" s="67" t="n">
-        <v>27</v>
+        <v>19.63</v>
       </c>
       <c r="J59" s="67" t="n">
-        <v>27</v>
+        <v>19.73</v>
       </c>
       <c r="K59" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="E60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>0.989</v>
+      </c>
+      <c r="E60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -19.8%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="H60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+        <v>0.989</v>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -23.2%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7209,11 +7209,11 @@
         <v>2.17</v>
       </c>
       <c r="D62" s="91" t="n">
-        <v>2.1204</v>
-      </c>
-      <c r="E62" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
+        <v>2.1808</v>
+      </c>
+      <c r="E62" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="F62" s="90" t="n">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="I62" s="58" t="n">
-        <v>55.13</v>
+        <v>56.7</v>
       </c>
       <c r="J62" s="58" t="n">
         <v>50</v>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7418,35 +7418,35 @@
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2.1204</v>
+        <v>2.1808</v>
       </c>
       <c r="D6" s="105" t="n">
         <v>1.9231</v>
       </c>
       <c r="E6" s="106" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Egypt</t>
+          <t xml:space="preserve">  2.  Angola</t>
         </is>
       </c>
       <c r="H6" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I6" s="108" t="n">
-        <v>0.2783</v>
+        <v>0.3272</v>
       </c>
       <c r="J6" s="109" t="n">
-        <v>0.2783</v>
-      </c>
-      <c r="K6" s="106" t="inlineStr">
-        <is>
-          <t>▼ -41.7%</t>
+        <v>0.2181</v>
+      </c>
+      <c r="K6" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7474,49 +7474,49 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Angola</t>
+          <t xml:space="preserve">  3.  Egypt</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
         <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="I7" s="101" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="J7" s="102" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="K7" s="110" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Botswana</t>
+        </is>
+      </c>
+      <c r="B8" s="103" t="inlineStr">
+        <is>
           <t>Southern Africa</t>
         </is>
       </c>
-      <c r="I7" s="101" t="n">
-        <v>0.3272</v>
-      </c>
-      <c r="J7" s="102" t="n">
-        <v>0.2181</v>
-      </c>
-      <c r="K7" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  CAR</t>
-        </is>
-      </c>
-      <c r="B8" s="103" t="inlineStr">
-        <is>
-          <t>Central Africa</t>
-        </is>
-      </c>
       <c r="C8" s="104" t="n">
-        <v>1.7384</v>
+        <v>1.7725</v>
       </c>
       <c r="D8" s="105" t="n">
-        <v>2.1523</v>
-      </c>
-      <c r="E8" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="111" t="inlineStr">
+        <v>1.9202</v>
+      </c>
+      <c r="E8" s="106" t="inlineStr">
+        <is>
+          <t>▲ +55.1%</t>
+        </is>
+      </c>
+      <c r="G8" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  Algeria</t>
         </is>
@@ -7539,72 +7539,72 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Comoros</t>
+      <c r="A9" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  CAR</t>
         </is>
       </c>
       <c r="B9" s="96" t="inlineStr">
         <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="C9" s="97" t="n">
+        <v>1.7384</v>
+      </c>
+      <c r="D9" s="98" t="n">
+        <v>2.1523</v>
+      </c>
+      <c r="E9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Nigeria</t>
+        </is>
+      </c>
+      <c r="H9" s="100" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="I9" s="101" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="J9" s="102" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="K9" s="106" t="inlineStr">
+        <is>
+          <t>▲ +13.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Comoros</t>
+        </is>
+      </c>
+      <c r="B10" s="103" t="inlineStr">
+        <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C9" s="97" t="n">
+      <c r="C10" s="104" t="n">
         <v>1.6851</v>
       </c>
-      <c r="D9" s="98" t="n">
+      <c r="D10" s="105" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E9" s="106" t="inlineStr">
+      <c r="E10" s="110" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
       </c>
-      <c r="G9" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Nigeria</t>
-        </is>
-      </c>
-      <c r="H9" s="100" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="I9" s="101" t="n">
-        <v>0.5861</v>
-      </c>
-      <c r="J9" s="102" t="n">
-        <v>0.5706</v>
-      </c>
-      <c r="K9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Senegal</t>
-        </is>
-      </c>
-      <c r="B10" s="103" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="C10" s="104" t="n">
-        <v>1.6391</v>
-      </c>
-      <c r="D10" s="105" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E10" s="114" t="inlineStr">
-        <is>
-          <t>▲ +7.5%</t>
-        </is>
-      </c>
-      <c r="G10" s="111" t="inlineStr">
+      <c r="G10" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  Niger</t>
         </is>
@@ -7627,28 +7627,28 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Somalia</t>
+      <c r="A11" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Senegal</t>
         </is>
       </c>
       <c r="B11" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C11" s="97" t="n">
-        <v>1.6</v>
+        <v>1.6391</v>
       </c>
       <c r="D11" s="98" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E11" s="114" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
-        </is>
-      </c>
-      <c r="G11" s="113" t="inlineStr">
+        <v>1.25</v>
+      </c>
+      <c r="E11" s="106" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
+        </is>
+      </c>
+      <c r="G11" s="114" t="inlineStr">
         <is>
           <t xml:space="preserve">  7.  Tunisia</t>
         </is>
@@ -7671,9 +7671,9 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Uganda</t>
+      <c r="A12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Somalia</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
@@ -7682,105 +7682,105 @@
         </is>
       </c>
       <c r="C12" s="104" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E12" s="106" t="inlineStr">
+        <is>
+          <t>▲ +39.1%</t>
+        </is>
+      </c>
+      <c r="G12" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Liberia</t>
+        </is>
+      </c>
+      <c r="H12" s="107" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="I12" s="108" t="n">
+        <v>0.8608</v>
+      </c>
+      <c r="J12" s="109" t="n">
+        <v>0.9124</v>
+      </c>
+      <c r="K12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Uganda</t>
+        </is>
+      </c>
+      <c r="B13" s="96" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C13" s="97" t="n">
         <v>1.4657</v>
       </c>
-      <c r="D12" s="105" t="n">
+      <c r="D13" s="98" t="n">
         <v>1.4377</v>
       </c>
-      <c r="E12" s="114" t="inlineStr">
+      <c r="E13" s="106" t="inlineStr">
         <is>
           <t>▲ +6.1%</t>
         </is>
       </c>
-      <c r="G12" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Ghana</t>
-        </is>
-      </c>
-      <c r="H12" s="107" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="I12" s="108" t="n">
-        <v>0.8471</v>
-      </c>
-      <c r="J12" s="109" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K12" s="106" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Namibia</t>
-        </is>
-      </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="G13" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Eswatini</t>
+        </is>
+      </c>
+      <c r="H13" s="100" t="inlineStr">
         <is>
           <t>Southern Africa</t>
         </is>
       </c>
-      <c r="C13" s="97" t="n">
-        <v>1.4555</v>
-      </c>
-      <c r="D13" s="98" t="n">
-        <v>1.4555</v>
-      </c>
-      <c r="E13" s="114" t="inlineStr">
-        <is>
-          <t>▲ +37.9%</t>
-        </is>
-      </c>
-      <c r="G13" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Liberia</t>
-        </is>
-      </c>
-      <c r="H13" s="100" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
       <c r="I13" s="101" t="n">
-        <v>0.8608</v>
+        <v>0.8625</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.9124</v>
-      </c>
-      <c r="K13" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8625</v>
+      </c>
+      <c r="K13" s="110" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Mali</t>
+      <c r="A14" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Morocco</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.4487</v>
+        <v>1.4447</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.5563</v>
-      </c>
-      <c r="E14" s="114" t="inlineStr">
-        <is>
-          <t>▲ +12.9%</t>
-        </is>
-      </c>
-      <c r="G14" s="111" t="inlineStr">
+        <v>1.4447</v>
+      </c>
+      <c r="E14" s="106" t="inlineStr">
+        <is>
+          <t>▲ +13.2%</t>
+        </is>
+      </c>
+      <c r="G14" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Equatorial Guinea</t>
         </is>
@@ -7898,77 +7898,77 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.009</v>
+        <v>1.0871</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.3643</v>
+        <v>0.4424</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.15</v>
+        <v>1.1425</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.6</v>
+        <v>1.7725</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +55.1%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.15</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.4555</v>
+        <v>1.6</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +37.9%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -8036,7 +8036,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
@@ -8046,146 +8046,146 @@
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.2831</v>
+        <v>0.5861</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.4487</v>
+        <v>0.6663</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.9%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1656</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.2762</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.3736</v>
+        <v>1.4447</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +13.2%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.1685</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.5244</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.3779</v>
+        <v>1.6391</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.0%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1017</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3819</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.6391</v>
+        <v>1.4657</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.0838</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.3819</v>
+        <v>0.914</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.4657</v>
+        <v>0.9675</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +5.8%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.0838</v>
+        <v>0.0535</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -8222,156 +8222,156 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.0882</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.3699</v>
+        <v>1.1301</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +3.9%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.022</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3479</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.3873</v>
+        <v>1.3699</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3681</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.4261</v>
+        <v>1.3873</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.31</v>
+        <v>1.4106</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F34" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G34" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.4261</v>
+      </c>
+      <c r="F34" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.1%</t>
+        </is>
+      </c>
+      <c r="G34" s="117" t="n">
+        <v>0.0155</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.3289</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.0485</v>
-      </c>
-      <c r="F35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.2%</t>
-        </is>
-      </c>
-      <c r="G35" s="119" t="n">
-        <v>-0.0237</v>
+        <v>1.3377</v>
+      </c>
+      <c r="F35" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.7%</t>
+        </is>
+      </c>
+      <c r="G35" s="117" t="n">
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -8394,232 +8394,232 @@
         <v>2.17</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>2.1204</v>
-      </c>
-      <c r="F36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
-        </is>
-      </c>
-      <c r="G36" s="119" t="n">
-        <v>-0.0496</v>
+        <v>2.1808</v>
+      </c>
+      <c r="F36" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
+        </is>
+      </c>
+      <c r="G36" s="117" t="n">
+        <v>0.0108</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.0555</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3661</v>
-      </c>
-      <c r="F37" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
-        </is>
-      </c>
-      <c r="G37" s="119" t="n">
-        <v>-0.0325</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F37" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G37" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.784</v>
+        <v>1.31</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.6851</v>
+        <v>1.3037</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.3691</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.0253</v>
+        <v>1.3595</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.8%</t>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0629</v>
+        <v>-0.009599999999999999</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.3986</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.1507</v>
+        <v>1.3661</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0755</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.784</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>0.9982</v>
+        <v>1.6851</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>0.914</v>
+        <v>1.0641</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>0.8471</v>
+        <v>0.9982</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.0474</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>0.9851</v>
+        <v>0.9809</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -8656,7 +8656,7 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
@@ -8666,22 +8666,22 @@
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.2262</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>1.1719</v>
+        <v>1.1258</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.1%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.1167</v>
+        <v>-0.1004</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -8718,7 +8718,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
@@ -8728,84 +8728,115 @@
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2886</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.1755</v>
+        <v>1.0635</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.5%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.1534</v>
+        <v>-0.2251</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.0722</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.2057</v>
+        <v>0.8625</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.9%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1634</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B49" s="54" t="inlineStr">
+        <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
+      <c r="C49" s="116" t="inlineStr">
+        <is>
+          <t>ZAR</t>
+        </is>
+      </c>
+      <c r="D49" s="88" t="n">
+        <v>1.2332</v>
+      </c>
+      <c r="E49" s="91" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="F49" s="69" t="inlineStr">
+        <is>
+          <t>▼ -19.8%</t>
+        </is>
+      </c>
+      <c r="G49" s="119" t="n">
+        <v>-0.2442</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="62" t="inlineStr">
+        <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B49" s="54" t="inlineStr">
+      <c r="B50" s="63" t="inlineStr">
         <is>
           <t>North Africa</t>
         </is>
       </c>
-      <c r="C49" s="116" t="inlineStr">
+      <c r="C50" s="118" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
       </c>
-      <c r="D49" s="88" t="n">
+      <c r="D50" s="88" t="n">
         <v>0.4771</v>
       </c>
-      <c r="E49" s="91" t="n">
-        <v>0.2783</v>
-      </c>
-      <c r="F49" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.7%</t>
-        </is>
-      </c>
-      <c r="G49" s="119" t="n">
-        <v>-0.1988</v>
+      <c r="E50" s="89" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="F50" s="69" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
+        </is>
+      </c>
+      <c r="G50" s="119" t="n">
+        <v>-0.1391</v>
       </c>
     </row>
   </sheetData>
@@ -8862,16 +8893,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6536</v>
+        <v>0.6636000000000001</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.5869166666666668</v>
+        <v>0.6140166666666667</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.3779</v>
+        <v>1.4447</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -8964,20 +8995,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.338</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.2684</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.7%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9032,20 +9063,20 @@
         </is>
       </c>
       <c r="C9" s="66" t="n">
-        <v>1.3779</v>
+        <v>1.4447</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.2722</v>
+        <v>1.4447</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>13.82</v>
+        <v>14.49</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>12.76</v>
+        <v>14.49</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.0%</t>
+          <t>▲ +13.2%</t>
         </is>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -9066,20 +9097,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="D10" s="57" t="n">
         <v>0.9809</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="F10" s="58" t="n">
         <v>590</v>
       </c>
-      <c r="G10" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G10" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9138,13 +9169,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.16508125</v>
+        <v>1.175625</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.1378375</v>
+        <v>1.15045</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.5861</v>
+        <v>0.6663</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9206,20 +9237,20 @@
         </is>
       </c>
       <c r="C16" s="57" t="n">
-        <v>1.1507</v>
+        <v>1.1258</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>1.1921</v>
+        <v>1.1589</v>
       </c>
       <c r="E16" s="58" t="n">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="F16" s="58" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="G16" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="H16" s="61" t="inlineStr">
@@ -9274,20 +9305,20 @@
         </is>
       </c>
       <c r="C18" s="57" t="n">
-        <v>1.1719</v>
+        <v>1.0635</v>
       </c>
       <c r="D18" s="57" t="n">
-        <v>0.9846</v>
+        <v>1.0635</v>
       </c>
       <c r="E18" s="58" t="n">
-        <v>129.5</v>
+        <v>117.52</v>
       </c>
       <c r="F18" s="58" t="n">
-        <v>108.8</v>
+        <v>117.52</v>
       </c>
       <c r="G18" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.1%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="H18" s="61" t="inlineStr">
@@ -9308,20 +9339,20 @@
         </is>
       </c>
       <c r="C19" s="66" t="n">
-        <v>1.0253</v>
+        <v>1.1301</v>
       </c>
       <c r="D19" s="66" t="n">
-        <v>1.0253</v>
+        <v>1.1589</v>
       </c>
       <c r="E19" s="67" t="n">
-        <v>74.84999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="F19" s="67" t="n">
-        <v>74.84999999999999</v>
-      </c>
-      <c r="G19" s="69" t="inlineStr">
-        <is>
-          <t>▼ -5.8%</t>
+        <v>84.59999999999999</v>
+      </c>
+      <c r="G19" s="71" t="inlineStr">
+        <is>
+          <t>▲ +3.9%</t>
         </is>
       </c>
       <c r="H19" s="70" t="inlineStr">
@@ -9342,20 +9373,20 @@
         </is>
       </c>
       <c r="C20" s="57" t="n">
-        <v>0.8471</v>
+        <v>0.9675</v>
       </c>
       <c r="D20" s="57" t="n">
-        <v>1.0892</v>
+        <v>1.1369</v>
       </c>
       <c r="E20" s="58" t="n">
-        <v>13.3</v>
+        <v>15.19</v>
       </c>
       <c r="F20" s="58" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="G20" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>17.85</v>
+      </c>
+      <c r="G20" s="71" t="inlineStr">
+        <is>
+          <t>▲ +5.8%</t>
         </is>
       </c>
       <c r="H20" s="61" t="inlineStr">
@@ -9410,20 +9441,20 @@
         </is>
       </c>
       <c r="C22" s="57" t="n">
-        <v>1.1755</v>
+        <v>1.3377</v>
       </c>
       <c r="D22" s="57" t="n">
-        <v>1.0232</v>
+        <v>1.2583</v>
       </c>
       <c r="E22" s="58" t="n">
-        <v>710</v>
+        <v>808</v>
       </c>
       <c r="F22" s="58" t="n">
-        <v>618</v>
-      </c>
-      <c r="G22" s="69" t="inlineStr">
-        <is>
-          <t>▼ -11.5%</t>
+        <v>760</v>
+      </c>
+      <c r="G22" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.7%</t>
         </is>
       </c>
       <c r="H22" s="61" t="inlineStr">
@@ -9512,20 +9543,20 @@
         </is>
       </c>
       <c r="C25" s="66" t="n">
-        <v>1.4487</v>
+        <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.5563</v>
+        <v>1.2003</v>
       </c>
       <c r="E25" s="67" t="n">
-        <v>875</v>
+        <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>940</v>
-      </c>
-      <c r="G25" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.9%</t>
+        <v>725</v>
+      </c>
+      <c r="G25" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="70" t="inlineStr">
@@ -9614,20 +9645,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.5861</v>
+        <v>0.6663</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.5706</v>
+        <v>0.6663</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>950</v>
+        <v>1080</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>925</v>
-      </c>
-      <c r="G28" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1080</v>
+      </c>
+      <c r="G28" s="71" t="inlineStr">
+        <is>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9754,10 +9785,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2173625</v>
+        <v>1.2275</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1930875</v>
+        <v>1.191225</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10026,20 +10057,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>585</v>
-      </c>
-      <c r="G42" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>576</v>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10098,13 +10129,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.488813333333333</v>
+        <v>1.504273333333334</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.425326666666667</v>
+        <v>1.44424</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>1.009</v>
+        <v>1.0606</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10302,20 +10333,20 @@
         </is>
       </c>
       <c r="C52" s="57" t="n">
-        <v>1.009</v>
+        <v>1.0871</v>
       </c>
       <c r="D52" s="57" t="n">
-        <v>1.046</v>
+        <v>1.245</v>
       </c>
       <c r="E52" s="58" t="n">
-        <v>132.18</v>
+        <v>142.41</v>
       </c>
       <c r="F52" s="58" t="n">
-        <v>137.03</v>
+        <v>163.09</v>
       </c>
       <c r="G52" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="H52" s="61" t="inlineStr">
@@ -10472,20 +10503,20 @@
         </is>
       </c>
       <c r="C57" s="66" t="n">
-        <v>1.2057</v>
+        <v>1.3595</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.1511</v>
+        <v>1.2358</v>
       </c>
       <c r="E57" s="67" t="n">
-        <v>1764</v>
+        <v>1989</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>1684</v>
+        <v>1808</v>
       </c>
       <c r="G57" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.9%</t>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="H57" s="70" t="inlineStr">
@@ -10680,16 +10711,16 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.220277777777778</v>
+        <v>1.189444444444445</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.192455555555555</v>
+        <v>1.162866666666667</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
       </c>
       <c r="F65" s="153" t="n">
-        <v>2.1204</v>
+        <v>2.1808</v>
       </c>
       <c r="G65" s="150" t="n"/>
       <c r="H65" s="150" t="n"/>
@@ -10782,20 +10813,20 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>1.1425</v>
+        <v>1.7725</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>1.2024</v>
+        <v>1.9202</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>15.47</v>
+        <v>24</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="G68" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>26</v>
+      </c>
+      <c r="G68" s="71" t="inlineStr">
+        <is>
+          <t>▲ +55.1%</t>
         </is>
       </c>
       <c r="H68" s="70" t="inlineStr">
@@ -10816,20 +10847,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="G69" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">
@@ -10918,25 +10949,25 @@
         </is>
       </c>
       <c r="C72" s="66" t="n">
-        <v>1.4555</v>
+        <v>1.0582</v>
       </c>
       <c r="D72" s="66" t="n">
-        <v>1.4555</v>
+        <v>1.0636</v>
       </c>
       <c r="E72" s="67" t="n">
-        <v>27</v>
+        <v>19.63</v>
       </c>
       <c r="F72" s="67" t="n">
-        <v>27</v>
+        <v>19.73</v>
       </c>
       <c r="G72" s="71" t="inlineStr">
         <is>
-          <t>▲ +37.9%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="H72" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -10952,20 +10983,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.3736</v>
+        <v>0.989</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.3736</v>
+        <v>0.989</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>25</v>
-      </c>
-      <c r="G73" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>18</v>
+      </c>
+      <c r="G73" s="69" t="inlineStr">
+        <is>
+          <t>▼ -19.8%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">
@@ -11020,20 +11051,20 @@
         </is>
       </c>
       <c r="C75" s="57" t="n">
-        <v>2.1204</v>
+        <v>2.1808</v>
       </c>
       <c r="D75" s="57" t="n">
         <v>1.9231</v>
       </c>
       <c r="E75" s="58" t="n">
-        <v>55.13</v>
+        <v>56.7</v>
       </c>
       <c r="F75" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="G75" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
+      <c r="G75" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="H75" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-03</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-04</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.220</t>
+          <t>$1.215</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.181</t>
+          <t>$1.158</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
         <v>0.6636000000000001</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6140166666666667</v>
+        <v>0.5394</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.175625</v>
+        <v>1.1833</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.15045</v>
+        <v>1.11475625</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2275</v>
+        <v>1.17085</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.191225</v>
+        <v>1.1611125</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,10 +1831,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.504273333333334</v>
+        <v>1.518586666666667</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.44424</v>
+        <v>1.462333333333333</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>1.0606</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.189444444444445</v>
+        <v>1.174733333333333</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.162866666666667</v>
+        <v>1.139955555555556</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-03</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-04</t>
         </is>
       </c>
     </row>
@@ -2205,13 +2205,13 @@
         <v>1.4447</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.4447</v>
+        <v>0.997</v>
       </c>
       <c r="G7" s="67" t="n">
         <v>14.49</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>14.49</v>
+        <v>10</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
@@ -2491,23 +2491,23 @@
         </is>
       </c>
       <c r="E14" s="57" t="n">
-        <v>1.1301</v>
+        <v>1.3875</v>
       </c>
       <c r="F14" s="57" t="n">
-        <v>1.1589</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="G14" s="58" t="n">
-        <v>82.5</v>
+        <v>101.29</v>
       </c>
       <c r="H14" s="58" t="n">
-        <v>84.59999999999999</v>
+        <v>47.43</v>
       </c>
       <c r="I14" s="59" t="n">
         <v>73</v>
       </c>
       <c r="J14" s="71" t="inlineStr">
         <is>
-          <t>▲ +3.9%</t>
+          <t>▲ +27.5%</t>
         </is>
       </c>
       <c r="K14" s="61" t="inlineStr">
@@ -2538,23 +2538,23 @@
         </is>
       </c>
       <c r="E15" s="66" t="n">
-        <v>0.9675</v>
+        <v>0.8471</v>
       </c>
       <c r="F15" s="66" t="n">
-        <v>1.1369</v>
+        <v>1.0892</v>
       </c>
       <c r="G15" s="67" t="n">
-        <v>15.19</v>
+        <v>13.3</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>17.85</v>
+        <v>17.1</v>
       </c>
       <c r="I15" s="68" t="n">
         <v>15.7</v>
       </c>
-      <c r="J15" s="71" t="inlineStr">
-        <is>
-          <t>▲ +5.8%</t>
+      <c r="J15" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="K15" s="70" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J34" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>1.3023</v>
+        <v>0.9302</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>1.186</v>
+        <v>0.9302</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -3915,23 +3915,23 @@
         </is>
       </c>
       <c r="E46" s="57" t="n">
-        <v>1.3595</v>
+        <v>1.5742</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.2358</v>
+        <v>1.5072</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>1989</v>
+        <v>2303</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>1808</v>
+        <v>2205</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
       </c>
-      <c r="J46" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+      <c r="J46" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="K46" s="61" t="inlineStr">
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>1.7725</v>
+        <v>1.2555</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>1.9202</v>
+        <v>1.3294</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
       <c r="J54" s="71" t="inlineStr">
         <is>
-          <t>▲ +55.1%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>0.989</v>
+        <v>1.3736</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>0.989</v>
+        <v>1.3736</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="69" t="inlineStr">
-        <is>
-          <t>▼ -19.8%</t>
+      <c r="J59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.220012962962962</v>
+        <v>1.215418518518518</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.180564814814815</v>
+        <v>1.158444444444444</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-03</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-04</t>
         </is>
       </c>
     </row>
@@ -4942,18 +4942,18 @@
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.4447</v>
-      </c>
-      <c r="H8" s="71" t="inlineStr">
-        <is>
-          <t>▲ +26.0%</t>
+        <v>0.997</v>
+      </c>
+      <c r="H8" s="69" t="inlineStr">
+        <is>
+          <t>▼ -13.1%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
         <v>14.49</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>14.49</v>
+        <v>10</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -5208,29 +5208,29 @@
         <v>1.0882</v>
       </c>
       <c r="D15" s="89" t="n">
-        <v>1.1301</v>
+        <v>1.3875</v>
       </c>
       <c r="E15" s="71" t="inlineStr">
         <is>
-          <t>▲ +3.9%</t>
+          <t>▲ +27.5%</t>
         </is>
       </c>
       <c r="F15" s="90" t="n">
         <v>0.9559</v>
       </c>
       <c r="G15" s="89" t="n">
-        <v>1.1589</v>
-      </c>
-      <c r="H15" s="71" t="inlineStr">
-        <is>
-          <t>▲ +21.2%</t>
+        <v>0.6497000000000001</v>
+      </c>
+      <c r="H15" s="69" t="inlineStr">
+        <is>
+          <t>▼ -32.0%</t>
         </is>
       </c>
       <c r="I15" s="67" t="n">
-        <v>82.5</v>
+        <v>101.29</v>
       </c>
       <c r="J15" s="67" t="n">
-        <v>84.59999999999999</v>
+        <v>47.43</v>
       </c>
       <c r="K15" s="70" t="inlineStr">
         <is>
@@ -5253,29 +5253,29 @@
         <v>0.914</v>
       </c>
       <c r="D16" s="91" t="n">
-        <v>0.9675</v>
-      </c>
-      <c r="E16" s="71" t="inlineStr">
-        <is>
-          <t>▲ +5.8%</t>
+        <v>0.8471</v>
+      </c>
+      <c r="E16" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="F16" s="90" t="n">
         <v>0.914</v>
       </c>
       <c r="G16" s="91" t="n">
-        <v>1.1369</v>
+        <v>1.0892</v>
       </c>
       <c r="H16" s="71" t="inlineStr">
         <is>
-          <t>▲ +24.4%</t>
+          <t>▲ +19.2%</t>
         </is>
       </c>
       <c r="I16" s="58" t="n">
-        <v>15.19</v>
+        <v>13.3</v>
       </c>
       <c r="J16" s="58" t="n">
-        <v>17.85</v>
+        <v>17.1</v>
       </c>
       <c r="K16" s="61" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="H24" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.0%</t>
+          <t>▼ -11.9%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>1.0662</v>
-      </c>
-      <c r="E35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9851</v>
+      </c>
+      <c r="E35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9536</v>
-      </c>
-      <c r="H35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9685</v>
+      </c>
+      <c r="H35" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.5%</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>1.3023</v>
-      </c>
-      <c r="E36" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9302</v>
+      </c>
+      <c r="E36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>1.186</v>
-      </c>
-      <c r="H36" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9302</v>
+      </c>
+      <c r="H36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -21.6%</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -6572,29 +6572,29 @@
         <v>1.3691</v>
       </c>
       <c r="D47" s="89" t="n">
-        <v>1.3595</v>
-      </c>
-      <c r="E47" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+        <v>1.5742</v>
+      </c>
+      <c r="E47" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="F47" s="90" t="n">
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.2358</v>
-      </c>
-      <c r="H47" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.9%</t>
+        <v>1.5072</v>
+      </c>
+      <c r="H47" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.3%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
-        <v>1989</v>
+        <v>2303</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>1808</v>
+        <v>2205</v>
       </c>
       <c r="K47" s="70" t="inlineStr">
         <is>
@@ -6894,29 +6894,29 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>1.7725</v>
+        <v>1.2555</v>
       </c>
       <c r="E55" s="71" t="inlineStr">
         <is>
-          <t>▲ +55.1%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>1.9202</v>
+        <v>1.3294</v>
       </c>
       <c r="H55" s="71" t="inlineStr">
         <is>
-          <t>▲ +59.7%</t>
+          <t>▲ +10.6%</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="E60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -19.8%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="E60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="H60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -23.2%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="H60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7497,23 +7497,23 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  Botswana</t>
+          <t xml:space="preserve">  4.  CAR</t>
         </is>
       </c>
       <c r="B8" s="103" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C8" s="104" t="n">
-        <v>1.7725</v>
+        <v>1.7384</v>
       </c>
       <c r="D8" s="105" t="n">
-        <v>1.9202</v>
-      </c>
-      <c r="E8" s="106" t="inlineStr">
-        <is>
-          <t>▲ +55.1%</t>
+        <v>2.1523</v>
+      </c>
+      <c r="E8" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="112" t="inlineStr">
@@ -7541,23 +7541,23 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  CAR</t>
+          <t xml:space="preserve">  5.  Comoros</t>
         </is>
       </c>
       <c r="B9" s="96" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C9" s="97" t="n">
-        <v>1.7384</v>
+        <v>1.6851</v>
       </c>
       <c r="D9" s="98" t="n">
-        <v>2.1523</v>
-      </c>
-      <c r="E9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.5078</v>
+      </c>
+      <c r="E9" s="110" t="inlineStr">
+        <is>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G9" s="114" t="inlineStr">
@@ -7571,37 +7571,37 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="K9" s="106" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Comoros</t>
+          <t xml:space="preserve">  6.  Senegal</t>
         </is>
       </c>
       <c r="B10" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C10" s="104" t="n">
-        <v>1.6851</v>
+        <v>1.6391</v>
       </c>
       <c r="D10" s="105" t="n">
-        <v>1.5078</v>
-      </c>
-      <c r="E10" s="110" t="inlineStr">
-        <is>
-          <t>▼ -5.5%</t>
+        <v>1.25</v>
+      </c>
+      <c r="E10" s="106" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G10" s="112" t="inlineStr">
@@ -7629,23 +7629,23 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Senegal</t>
+          <t xml:space="preserve">  7.  Somalia</t>
         </is>
       </c>
       <c r="B11" s="96" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C11" s="97" t="n">
-        <v>1.6391</v>
+        <v>1.6</v>
       </c>
       <c r="D11" s="98" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="E11" s="106" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G11" s="114" t="inlineStr">
@@ -7673,7 +7673,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Somalia</t>
+          <t xml:space="preserve">  8.  Rwanda</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
@@ -7682,19 +7682,19 @@
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.6</v>
+        <v>1.5742</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.4</v>
+        <v>1.5072</v>
       </c>
       <c r="E12" s="106" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G12" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Liberia</t>
+          <t xml:space="preserve">  8.  Ghana</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
@@ -7703,14 +7703,14 @@
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8608</v>
+        <v>0.8471</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.9124</v>
-      </c>
-      <c r="K12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0892</v>
+      </c>
+      <c r="K12" s="110" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
@@ -7738,23 +7738,23 @@
       </c>
       <c r="G13" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Eswatini</t>
+          <t xml:space="preserve">  9.  Liberia</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8625</v>
+        <v>0.8608</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="K13" s="110" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+        <v>0.9124</v>
+      </c>
+      <c r="K13" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
         <v>1.4447</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.4447</v>
+        <v>0.997</v>
       </c>
       <c r="E14" s="106" t="inlineStr">
         <is>
@@ -7782,23 +7782,23 @@
       </c>
       <c r="G14" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Equatorial Guinea</t>
+          <t xml:space="preserve">  10.  Eswatini</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.9106</v>
+        <v>0.8625</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8609</v>
-      </c>
-      <c r="K14" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8625</v>
+      </c>
+      <c r="K14" s="110" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
@@ -7912,38 +7912,38 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.15</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.7725</v>
+        <v>1.6</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +55.1%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
@@ -7953,53 +7953,53 @@
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.15</v>
+        <v>1.0616</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.6</v>
+        <v>1.4096</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.45</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.0882</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.4096</v>
+        <v>1.3875</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +27.5%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.348</v>
+        <v>0.2993</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -8036,32 +8036,32 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.3691</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>0.6663</v>
+        <v>1.5742</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -8098,100 +8098,100 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.2332</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.3736</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.3819</v>
+        <v>0.5861</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.4657</v>
+        <v>0.6521</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.0838</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>0.914</v>
+        <v>1.1425</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>0.9675</v>
+        <v>1.2555</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.8%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.0535</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
@@ -8205,210 +8205,210 @@
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.3587</v>
+        <v>1.5244</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.4156</v>
+        <v>1.6391</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +4.2%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.0569</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.3819</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.1301</v>
+        <v>1.4657</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +3.9%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.0419</v>
+        <v>0.0838</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3587</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.3699</v>
+        <v>1.4156</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +4.2%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.022</v>
+        <v>0.0569</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3479</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.3699</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3681</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4261</v>
+        <v>1.3873</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.4106</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.3377</v>
+        <v>1.4261</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.7%</t>
+          <t>▲ +1.1%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>2.17</v>
+        <v>1.3289</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>2.1808</v>
+        <v>1.3377</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.5%</t>
+          <t>▲ +0.7%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0108</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,28 +8418,28 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.0555</v>
+        <v>2.17</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.0582</v>
+        <v>2.1808</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
@@ -8449,53 +8449,53 @@
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0555</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F38" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G38" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F38" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G38" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.31</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3595</v>
+        <v>1.3037</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -8625,7 +8625,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
@@ -8635,90 +8635,90 @@
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.2212</v>
+        <v>0.914</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.1258</v>
+        <v>0.8471</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.0671</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>1.1258</v>
+        <v>0.9851</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.1004</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2212</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>1.0606</v>
+        <v>1.1258</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
@@ -8728,114 +8728,176 @@
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.2262</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.0635</v>
+        <v>1.1258</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.2251</v>
+        <v>-0.1004</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.1939</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>0.8625</v>
+        <v>1.0606</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.2886</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>0.989</v>
+        <v>1.0635</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.8%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.2442</v>
+        <v>-0.2251</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
+          <t>Eswatini</t>
+        </is>
+      </c>
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
+      <c r="C50" s="118" t="inlineStr">
+        <is>
+          <t>SZL</t>
+        </is>
+      </c>
+      <c r="D50" s="88" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="E50" s="89" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="F50" s="69" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
+        </is>
+      </c>
+      <c r="G50" s="119" t="n">
+        <v>-0.2097</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="53" t="inlineStr">
+        <is>
+          <t>Sao Tome</t>
+        </is>
+      </c>
+      <c r="B51" s="54" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="C51" s="116" t="inlineStr">
+        <is>
+          <t>STN</t>
+        </is>
+      </c>
+      <c r="D51" s="88" t="n">
+        <v>1.3023</v>
+      </c>
+      <c r="E51" s="91" t="n">
+        <v>0.9302</v>
+      </c>
+      <c r="F51" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
+        </is>
+      </c>
+      <c r="G51" s="119" t="n">
+        <v>-0.3721</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="62" t="inlineStr">
+        <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B50" s="63" t="inlineStr">
+      <c r="B52" s="63" t="inlineStr">
         <is>
           <t>North Africa</t>
         </is>
       </c>
-      <c r="C50" s="118" t="inlineStr">
+      <c r="C52" s="118" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
       </c>
-      <c r="D50" s="88" t="n">
+      <c r="D52" s="88" t="n">
         <v>0.4771</v>
       </c>
-      <c r="E50" s="89" t="n">
+      <c r="E52" s="89" t="n">
         <v>0.338</v>
       </c>
-      <c r="F50" s="69" t="inlineStr">
+      <c r="F52" s="69" t="inlineStr">
         <is>
           <t>▼ -29.2%</t>
         </is>
       </c>
-      <c r="G50" s="119" t="n">
+      <c r="G52" s="119" t="n">
         <v>-0.1391</v>
       </c>
     </row>
@@ -8896,7 +8958,7 @@
         <v>0.6636000000000001</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6140166666666667</v>
+        <v>0.5394</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9066,13 +9128,13 @@
         <v>1.4447</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.4447</v>
+        <v>0.997</v>
       </c>
       <c r="E9" s="67" t="n">
         <v>14.49</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>14.49</v>
+        <v>10</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
@@ -9169,13 +9231,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.175625</v>
+        <v>1.1833</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.15045</v>
+        <v>1.11475625</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9339,20 +9401,20 @@
         </is>
       </c>
       <c r="C19" s="66" t="n">
-        <v>1.1301</v>
+        <v>1.3875</v>
       </c>
       <c r="D19" s="66" t="n">
-        <v>1.1589</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="E19" s="67" t="n">
-        <v>82.5</v>
+        <v>101.29</v>
       </c>
       <c r="F19" s="67" t="n">
-        <v>84.59999999999999</v>
+        <v>47.43</v>
       </c>
       <c r="G19" s="71" t="inlineStr">
         <is>
-          <t>▲ +3.9%</t>
+          <t>▲ +27.5%</t>
         </is>
       </c>
       <c r="H19" s="70" t="inlineStr">
@@ -9373,20 +9435,20 @@
         </is>
       </c>
       <c r="C20" s="57" t="n">
-        <v>0.9675</v>
+        <v>0.8471</v>
       </c>
       <c r="D20" s="57" t="n">
-        <v>1.1369</v>
+        <v>1.0892</v>
       </c>
       <c r="E20" s="58" t="n">
-        <v>15.19</v>
+        <v>13.3</v>
       </c>
       <c r="F20" s="58" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="G20" s="71" t="inlineStr">
-        <is>
-          <t>▲ +5.8%</t>
+        <v>17.1</v>
+      </c>
+      <c r="G20" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="H20" s="61" t="inlineStr">
@@ -9645,20 +9707,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9785,10 +9847,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2275</v>
+        <v>1.17085</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.191225</v>
+        <v>1.1611125</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10057,20 +10119,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>576</v>
-      </c>
-      <c r="G42" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>585</v>
+      </c>
+      <c r="G42" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10091,20 +10153,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>1.3023</v>
+        <v>0.9302</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>1.186</v>
+        <v>0.9302</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G43" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>20</v>
+      </c>
+      <c r="G43" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">
@@ -10129,10 +10191,10 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.504273333333334</v>
+        <v>1.518586666666667</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.44424</v>
+        <v>1.462333333333333</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>1.0606</v>
@@ -10503,20 +10565,20 @@
         </is>
       </c>
       <c r="C57" s="66" t="n">
-        <v>1.3595</v>
+        <v>1.5742</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.2358</v>
+        <v>1.5072</v>
       </c>
       <c r="E57" s="67" t="n">
-        <v>1989</v>
+        <v>2303</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>1808</v>
-      </c>
-      <c r="G57" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+        <v>2205</v>
+      </c>
+      <c r="G57" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="H57" s="70" t="inlineStr">
@@ -10711,10 +10773,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.189444444444445</v>
+        <v>1.174733333333333</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.162866666666667</v>
+        <v>1.139955555555556</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10813,20 +10875,20 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>1.7725</v>
+        <v>1.2555</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>1.9202</v>
+        <v>1.3294</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G68" s="71" t="inlineStr">
         <is>
-          <t>▲ +55.1%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="H68" s="70" t="inlineStr">
@@ -10983,20 +11045,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>0.989</v>
+        <v>1.3736</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>0.989</v>
+        <v>1.3736</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>18</v>
-      </c>
-      <c r="G73" s="69" t="inlineStr">
-        <is>
-          <t>▼ -19.8%</t>
+        <v>25</v>
+      </c>
+      <c r="G73" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-04</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-05</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.215</t>
+          <t>$1.206</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+90.0%</t>
+          <t>+68.6%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.158</t>
+          <t>$1.176</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1768,7 +1768,7 @@
         <v>0.6636000000000001</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.5394</v>
+        <v>0.6140166666666667</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.1833</v>
+        <v>1.17518125</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.11475625</v>
+        <v>1.11665</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6521</v>
+        <v>0.6663</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.17085</v>
+        <v>1.2173625</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1611125</v>
+        <v>1.1930875</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.518586666666667</v>
+        <v>1.476433333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.462333333333333</v>
+        <v>1.41832</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>1.0606</v>
+        <v>0.5942</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.174733333333333</v>
+        <v>1.162577777777778</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.139955555555556</v>
+        <v>1.236877777777778</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-04</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-05</t>
         </is>
       </c>
     </row>
@@ -2205,13 +2205,13 @@
         <v>1.4447</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>0.997</v>
+        <v>1.4447</v>
       </c>
       <c r="G7" s="67" t="n">
         <v>14.49</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>10</v>
+        <v>14.49</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
@@ -2491,23 +2491,23 @@
         </is>
       </c>
       <c r="E14" s="57" t="n">
-        <v>1.3875</v>
+        <v>1.3014</v>
       </c>
       <c r="F14" s="57" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6493</v>
       </c>
       <c r="G14" s="58" t="n">
-        <v>101.29</v>
+        <v>95</v>
       </c>
       <c r="H14" s="58" t="n">
-        <v>47.43</v>
+        <v>47.4</v>
       </c>
       <c r="I14" s="59" t="n">
         <v>73</v>
       </c>
       <c r="J14" s="71" t="inlineStr">
         <is>
-          <t>▲ +27.5%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="K14" s="61" t="inlineStr">
@@ -2679,23 +2679,23 @@
         </is>
       </c>
       <c r="E18" s="57" t="n">
-        <v>1.4156</v>
+        <v>1.3576</v>
       </c>
       <c r="F18" s="57" t="n">
-        <v>1.1838</v>
+        <v>1.1175</v>
       </c>
       <c r="G18" s="58" t="n">
-        <v>855</v>
+        <v>820</v>
       </c>
       <c r="H18" s="58" t="n">
-        <v>715</v>
+        <v>675</v>
       </c>
       <c r="I18" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J18" s="71" t="inlineStr">
-        <is>
-          <t>▲ +4.2%</t>
+      <c r="J18" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K18" s="61" t="inlineStr">
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.6663</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.6663</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1057</v>
+        <v>1080</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1057</v>
+        <v>1080</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.3023</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.186</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+      <c r="J35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>1.2544</v>
+        <v>0.5942</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>1.2544</v>
+        <v>0.5942</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+      <c r="J49" s="69" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.4657</v>
+        <v>1.4936</v>
       </c>
       <c r="F51" s="66" t="n">
         <v>1.4377</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>5250</v>
+        <v>5350</v>
       </c>
       <c r="H51" s="67" t="n">
         <v>5150</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="J51" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +8.1%</t>
         </is>
       </c>
       <c r="K51" s="70" t="inlineStr">
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>1.2555</v>
+        <v>0.9601</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>1.3294</v>
+        <v>1.9941</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
-      <c r="J54" s="71" t="inlineStr">
-        <is>
-          <t>▲ +9.9%</t>
+      <c r="J54" s="69" t="inlineStr">
+        <is>
+          <t>▼ -16.0%</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
       <c r="J55" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="K55" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.215418518518518</v>
+        <v>1.206168518518518</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.158444444444444</v>
+        <v>1.175961111111111</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-04</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-05</t>
         </is>
       </c>
     </row>
@@ -4942,18 +4942,18 @@
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="H8" s="69" t="inlineStr">
-        <is>
-          <t>▼ -13.1%</t>
+        <v>1.4447</v>
+      </c>
+      <c r="H8" s="71" t="inlineStr">
+        <is>
+          <t>▲ +26.0%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
         <v>14.49</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>10</v>
+        <v>14.49</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -5208,29 +5208,29 @@
         <v>1.0882</v>
       </c>
       <c r="D15" s="89" t="n">
-        <v>1.3875</v>
+        <v>1.3014</v>
       </c>
       <c r="E15" s="71" t="inlineStr">
         <is>
-          <t>▲ +27.5%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="F15" s="90" t="n">
         <v>0.9559</v>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6493</v>
       </c>
       <c r="H15" s="69" t="inlineStr">
         <is>
-          <t>▼ -32.0%</t>
+          <t>▼ -32.1%</t>
         </is>
       </c>
       <c r="I15" s="67" t="n">
-        <v>101.29</v>
+        <v>95</v>
       </c>
       <c r="J15" s="67" t="n">
-        <v>47.43</v>
+        <v>47.4</v>
       </c>
       <c r="K15" s="70" t="inlineStr">
         <is>
@@ -5388,29 +5388,29 @@
         <v>1.3587</v>
       </c>
       <c r="D19" s="89" t="n">
-        <v>1.4156</v>
-      </c>
-      <c r="E19" s="71" t="inlineStr">
-        <is>
-          <t>▲ +4.2%</t>
+        <v>1.3576</v>
+      </c>
+      <c r="E19" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="90" t="n">
         <v>1.1185</v>
       </c>
       <c r="G19" s="89" t="n">
-        <v>1.1838</v>
-      </c>
-      <c r="H19" s="71" t="inlineStr">
-        <is>
-          <t>▲ +5.8%</t>
+        <v>1.1175</v>
+      </c>
+      <c r="H19" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I19" s="67" t="n">
-        <v>855</v>
+        <v>820</v>
       </c>
       <c r="J19" s="67" t="n">
-        <v>715</v>
+        <v>675</v>
       </c>
       <c r="K19" s="70" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2003</v>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2831</v>
+      </c>
+      <c r="H21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6521</v>
+        <v>0.6663</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6521</v>
+        <v>0.6663</v>
       </c>
       <c r="H24" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.9%</t>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1057</v>
+        <v>1080</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1057</v>
+        <v>1080</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="E36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>1.3023</v>
+      </c>
+      <c r="E36" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="H36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -21.6%</t>
+        <v>1.186</v>
+      </c>
+      <c r="H36" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>1.2544</v>
-      </c>
-      <c r="E50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>0.5942</v>
+      </c>
+      <c r="E50" s="69" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>1.2544</v>
-      </c>
-      <c r="H50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>0.5942</v>
+      </c>
+      <c r="H50" s="69" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -6797,11 +6797,11 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.4657</v>
+        <v>1.4936</v>
       </c>
       <c r="E52" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +8.1%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>5250</v>
+        <v>5350</v>
       </c>
       <c r="J52" s="58" t="n">
         <v>5150</v>
@@ -6894,29 +6894,29 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>1.2555</v>
-      </c>
-      <c r="E55" s="71" t="inlineStr">
-        <is>
-          <t>▲ +9.9%</t>
+        <v>0.9601</v>
+      </c>
+      <c r="E55" s="69" t="inlineStr">
+        <is>
+          <t>▼ -16.0%</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>1.3294</v>
+        <v>1.9941</v>
       </c>
       <c r="H55" s="71" t="inlineStr">
         <is>
-          <t>▲ +10.6%</t>
+          <t>▲ +65.8%</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="H56" s="69" t="inlineStr">
         <is>
-          <t>▼ -24.8%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7562,23 +7562,23 @@
       </c>
       <c r="G9" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Nigeria</t>
+          <t xml:space="preserve">  5.  South Sudan</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6521</v>
+        <v>0.5942</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="K9" s="106" t="inlineStr">
-        <is>
-          <t>▲ +11.3%</t>
+        <v>0.5942</v>
+      </c>
+      <c r="K9" s="110" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G10" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Niger</t>
+          <t xml:space="preserve">  6.  Nigeria</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
@@ -7615,14 +7615,14 @@
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.8262</v>
+        <v>0.6663</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K10" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.6663</v>
+      </c>
+      <c r="K10" s="106" t="inlineStr">
+        <is>
+          <t>▲ +13.7%</t>
         </is>
       </c>
     </row>
@@ -7650,19 +7650,19 @@
       </c>
       <c r="G11" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Tunisia</t>
+          <t xml:space="preserve">  7.  Niger</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8377</v>
+        <v>0.8262</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.7318</v>
+        <v>1.0232</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7694,23 +7694,23 @@
       </c>
       <c r="G12" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Ghana</t>
+          <t xml:space="preserve">  8.  Tunisia</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8471</v>
+        <v>0.8377</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K12" s="110" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7726,19 +7726,19 @@
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.4657</v>
+        <v>1.4936</v>
       </c>
       <c r="D13" s="98" t="n">
         <v>1.4377</v>
       </c>
       <c r="E13" s="106" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +8.1%</t>
         </is>
       </c>
       <c r="G13" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Liberia</t>
+          <t xml:space="preserve">  9.  Ghana</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
@@ -7747,14 +7747,14 @@
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8608</v>
+        <v>0.8471</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.9124</v>
-      </c>
-      <c r="K13" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0892</v>
+      </c>
+      <c r="K13" s="110" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
         <v>1.4447</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>0.997</v>
+        <v>1.4447</v>
       </c>
       <c r="E14" s="106" t="inlineStr">
         <is>
@@ -7782,23 +7782,23 @@
       </c>
       <c r="G14" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Eswatini</t>
+          <t xml:space="preserve">  10.  Liberia</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.8625</v>
+        <v>0.8608</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="K14" s="110" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+        <v>0.9124</v>
+      </c>
+      <c r="K14" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,28 +7860,28 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6602</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.2544</v>
+        <v>1.0871</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.5942</v>
+        <v>0.4424</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
@@ -7891,28 +7891,28 @@
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.0871</v>
+        <v>1.6</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.4424</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
@@ -7922,146 +7922,146 @@
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.15</v>
+        <v>1.0616</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.6</v>
+        <v>1.4096</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.45</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.0882</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.4096</v>
+        <v>1.3014</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.348</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0316</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.3875</v>
+        <v>1.2129</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +27.5%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.2993</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.3691</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.2129</v>
+        <v>1.5742</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.3691</v>
+        <v>0.5861</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.5742</v>
+        <v>0.6663</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -8129,286 +8129,286 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.3819</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.6521</v>
+        <v>1.4936</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +8.1%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.066</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.5244</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.2555</v>
+        <v>1.6391</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3479</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.6391</v>
+        <v>1.3699</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.3681</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.4657</v>
+        <v>1.3873</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.0838</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3587</v>
+        <v>1.4106</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.4156</v>
+        <v>1.4261</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +4.2%</t>
+          <t>▲ +1.1%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.0569</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3289</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.3699</v>
+        <v>1.3377</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +0.7%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.022</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.3681</v>
+        <v>2.17</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.3873</v>
+        <v>2.1808</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.0555</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.4261</v>
+        <v>1.0582</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.31</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3377</v>
-      </c>
-      <c r="F36" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.7%</t>
-        </is>
-      </c>
-      <c r="G36" s="117" t="n">
-        <v>0.008800000000000001</v>
+        <v>1.3037</v>
+      </c>
+      <c r="F36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
+        </is>
+      </c>
+      <c r="G36" s="119" t="n">
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,214 +8418,214 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>2.17</v>
+        <v>1.0722</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>2.1808</v>
-      </c>
-      <c r="F37" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
-        </is>
-      </c>
-      <c r="G37" s="117" t="n">
-        <v>0.0108</v>
+        <v>1.0485</v>
+      </c>
+      <c r="F37" s="69" t="inlineStr">
+        <is>
+          <t>▼ -2.2%</t>
+        </is>
+      </c>
+      <c r="G37" s="119" t="n">
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3986</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.0582</v>
-      </c>
-      <c r="F38" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
-        </is>
-      </c>
-      <c r="G38" s="117" t="n">
-        <v>0.0027</v>
+        <v>1.3661</v>
+      </c>
+      <c r="F38" s="69" t="inlineStr">
+        <is>
+          <t>▼ -2.3%</t>
+        </is>
+      </c>
+      <c r="G38" s="119" t="n">
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.31</v>
+        <v>1.784</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3037</v>
+        <v>1.6851</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0063</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.0641</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3661</v>
+        <v>0.9982</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.784</v>
+        <v>1.0474</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.6851</v>
+        <v>0.9809</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.0641</v>
+        <v>0.914</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>0.9982</v>
+        <v>0.8471</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.0474</v>
+        <v>1.0671</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>0.9809</v>
+        <v>0.9851</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.3%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0665</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
@@ -8635,146 +8635,146 @@
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>0.914</v>
+        <v>1.2212</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>0.8471</v>
+        <v>1.1258</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.2262</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.9851</v>
+        <v>1.1258</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.1004</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.2212</v>
+        <v>0.6602</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>1.1258</v>
+        <v>0.5942</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.066</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.1939</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.1258</v>
+        <v>1.0606</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.1004</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.1425</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.0606</v>
+        <v>0.9601</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -16.0%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.1824</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -8811,93 +8811,31 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.0722</v>
+        <v>0.4771</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>0.8625</v>
+        <v>0.338</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.2097</v>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="53" t="inlineStr">
-        <is>
-          <t>Sao Tome</t>
-        </is>
-      </c>
-      <c r="B51" s="54" t="inlineStr">
-        <is>
-          <t>Central Africa</t>
-        </is>
-      </c>
-      <c r="C51" s="116" t="inlineStr">
-        <is>
-          <t>STN</t>
-        </is>
-      </c>
-      <c r="D51" s="88" t="n">
-        <v>1.3023</v>
-      </c>
-      <c r="E51" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="F51" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
-        </is>
-      </c>
-      <c r="G51" s="119" t="n">
-        <v>-0.3721</v>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="62" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B52" s="63" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="C52" s="118" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="D52" s="88" t="n">
-        <v>0.4771</v>
-      </c>
-      <c r="E52" s="89" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="F52" s="69" t="inlineStr">
-        <is>
-          <t>▼ -29.2%</t>
-        </is>
-      </c>
-      <c r="G52" s="119" t="n">
         <v>-0.1391</v>
       </c>
     </row>
@@ -8958,7 +8896,7 @@
         <v>0.6636000000000001</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.5394</v>
+        <v>0.6140166666666667</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9128,13 +9066,13 @@
         <v>1.4447</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>0.997</v>
+        <v>1.4447</v>
       </c>
       <c r="E9" s="67" t="n">
         <v>14.49</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>10</v>
+        <v>14.49</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
@@ -9231,13 +9169,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.1833</v>
+        <v>1.17518125</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.11475625</v>
+        <v>1.11665</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6521</v>
+        <v>0.6663</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9401,20 +9339,20 @@
         </is>
       </c>
       <c r="C19" s="66" t="n">
-        <v>1.3875</v>
+        <v>1.3014</v>
       </c>
       <c r="D19" s="66" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6493</v>
       </c>
       <c r="E19" s="67" t="n">
-        <v>101.29</v>
+        <v>95</v>
       </c>
       <c r="F19" s="67" t="n">
-        <v>47.43</v>
+        <v>47.4</v>
       </c>
       <c r="G19" s="71" t="inlineStr">
         <is>
-          <t>▲ +27.5%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="H19" s="70" t="inlineStr">
@@ -9537,20 +9475,20 @@
         </is>
       </c>
       <c r="C23" s="66" t="n">
-        <v>1.4156</v>
+        <v>1.3576</v>
       </c>
       <c r="D23" s="66" t="n">
-        <v>1.1838</v>
+        <v>1.1175</v>
       </c>
       <c r="E23" s="67" t="n">
-        <v>855</v>
+        <v>820</v>
       </c>
       <c r="F23" s="67" t="n">
-        <v>715</v>
-      </c>
-      <c r="G23" s="71" t="inlineStr">
-        <is>
-          <t>▲ +4.2%</t>
+        <v>675</v>
+      </c>
+      <c r="G23" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="70" t="inlineStr">
@@ -9608,13 +9546,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9707,20 +9645,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6521</v>
+        <v>0.6663</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6521</v>
+        <v>0.6663</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1057</v>
+        <v>1080</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1057</v>
+        <v>1080</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9847,10 +9785,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.17085</v>
+        <v>1.2173625</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1611125</v>
+        <v>1.1930875</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10153,20 +10091,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.3023</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.186</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>20</v>
-      </c>
-      <c r="G43" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>25.5</v>
+      </c>
+      <c r="G43" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">
@@ -10191,13 +10129,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.518586666666667</v>
+        <v>1.476433333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.462333333333333</v>
+        <v>1.41832</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>1.0606</v>
+        <v>0.5942</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10667,20 +10605,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>1.2544</v>
+        <v>0.5942</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>1.2544</v>
+        <v>0.5942</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>2700</v>
+      </c>
+      <c r="G60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">
@@ -10735,20 +10673,20 @@
         </is>
       </c>
       <c r="C62" s="57" t="n">
-        <v>1.4657</v>
+        <v>1.4936</v>
       </c>
       <c r="D62" s="57" t="n">
         <v>1.4377</v>
       </c>
       <c r="E62" s="58" t="n">
-        <v>5250</v>
+        <v>5350</v>
       </c>
       <c r="F62" s="58" t="n">
         <v>5150</v>
       </c>
       <c r="G62" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +8.1%</t>
         </is>
       </c>
       <c r="H62" s="61" t="inlineStr">
@@ -10773,10 +10711,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.174733333333333</v>
+        <v>1.162577777777778</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.139955555555556</v>
+        <v>1.236877777777778</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10875,20 +10813,20 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>1.2555</v>
+        <v>0.9601</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>1.3294</v>
+        <v>1.9941</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>18</v>
-      </c>
-      <c r="G68" s="71" t="inlineStr">
-        <is>
-          <t>▲ +9.9%</t>
+        <v>27</v>
+      </c>
+      <c r="G68" s="69" t="inlineStr">
+        <is>
+          <t>▼ -16.0%</t>
         </is>
       </c>
       <c r="H68" s="70" t="inlineStr">
@@ -10909,20 +10847,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="G69" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1085,14 +1085,14 @@
     <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-05</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-06</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.206</t>
+          <t>$1.223</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+68.6%</t>
+          <t>+90.0%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.176</t>
+          <t>$1.169</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6636000000000001</v>
+        <v>0.69125</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6140166666666667</v>
+        <v>0.6333833333333333</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.17518125</v>
+        <v>1.195475</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.11665</v>
+        <v>1.1290625</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6663</v>
+        <v>0.8262</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2173625</v>
+        <v>1.2275</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1930875</v>
+        <v>1.191225</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.476433333333333</v>
+        <v>1.520446666666667</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.41832</v>
+        <v>1.462333333333333</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.5942</v>
+        <v>1.0606</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.162577777777778</v>
+        <v>1.125655555555556</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.236877777777778</v>
+        <v>1.090877777777778</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-05</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.338</v>
+        <v>0.4374</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.3181</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -8.3%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+      <c r="J8" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2350,23 +2350,23 @@
         </is>
       </c>
       <c r="E11" s="66" t="n">
-        <v>1.1258</v>
+        <v>1.1507</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>1.1589</v>
+        <v>1.1921</v>
       </c>
       <c r="G11" s="67" t="n">
-        <v>680</v>
+        <v>695</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
       </c>
       <c r="J11" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="K11" s="70" t="inlineStr">
@@ -2726,23 +2726,23 @@
         </is>
       </c>
       <c r="E19" s="66" t="n">
-        <v>0.8608</v>
+        <v>0.9639</v>
       </c>
       <c r="F19" s="66" t="n">
-        <v>0.9124</v>
+        <v>0.9639</v>
       </c>
       <c r="G19" s="67" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="I19" s="68" t="n">
         <v>194</v>
       </c>
-      <c r="J19" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J19" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="K19" s="70" t="inlineStr">
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.863</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.863</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1080</v>
+        <v>1399</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1080</v>
+        <v>1399</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+      <c r="J34" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>0.5942</v>
+        <v>1.2544</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>0.5942</v>
+        <v>1.2544</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+      <c r="J49" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>0.9601</v>
+        <v>1.2555</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>1.9941</v>
+        <v>1.3294</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
-      <c r="J54" s="69" t="inlineStr">
-        <is>
-          <t>▼ -16.0%</t>
+      <c r="J54" s="71" t="inlineStr">
+        <is>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
       <c r="J55" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="K55" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.3736</v>
+        <v>0.9319</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.3736</v>
+        <v>0.9319</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>25</v>
+        <v>16.96</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>25</v>
+        <v>16.96</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+      <c r="J59" s="69" t="inlineStr">
+        <is>
+          <t>▼ -24.4%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.206168518518518</v>
+        <v>1.222827777777777</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.175961111111111</v>
+        <v>1.169407407407407</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-05</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-06</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.338</v>
+        <v>0.4374</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -8.3%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2684</v>
+        <v>0.3181</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -34.1%</t>
+          <t>▼ -22.0%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="E9" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+        <v>1.0474</v>
+      </c>
+      <c r="E9" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="H9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0474</v>
+      </c>
+      <c r="H9" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.8%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5073,29 +5073,29 @@
         <v>1.2262</v>
       </c>
       <c r="D12" s="91" t="n">
-        <v>1.1258</v>
+        <v>1.1507</v>
       </c>
       <c r="E12" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="F12" s="90" t="n">
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>1.1589</v>
+        <v>1.1921</v>
       </c>
       <c r="H12" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.0%</t>
+          <t>▼ -5.3%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
-        <v>680</v>
+        <v>695</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -5433,29 +5433,29 @@
         <v>0.8608</v>
       </c>
       <c r="D20" s="91" t="n">
-        <v>0.8608</v>
-      </c>
-      <c r="E20" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9639</v>
+      </c>
+      <c r="E20" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="F20" s="90" t="n">
         <v>0.9124</v>
       </c>
       <c r="G20" s="91" t="n">
-        <v>0.9124</v>
-      </c>
-      <c r="H20" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9639</v>
+      </c>
+      <c r="H20" s="71" t="inlineStr">
+        <is>
+          <t>▲ +5.6%</t>
         </is>
       </c>
       <c r="I20" s="58" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="J20" s="58" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="K20" s="61" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2831</v>
-      </c>
-      <c r="H21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.9%</t>
+        <v>1.2003</v>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6663</v>
+        <v>0.863</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="H24" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>0.863</v>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +16.6%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1080</v>
+        <v>1399</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1080</v>
+        <v>1399</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="E35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>1.0662</v>
+      </c>
+      <c r="E35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9685</v>
-      </c>
-      <c r="H35" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.5%</t>
+        <v>0.9536</v>
+      </c>
+      <c r="H35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>0.5942</v>
-      </c>
-      <c r="E50" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>1.2544</v>
+      </c>
+      <c r="E50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>0.5942</v>
-      </c>
-      <c r="H50" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>1.2544</v>
+      </c>
+      <c r="H50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -6894,29 +6894,29 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>0.9601</v>
-      </c>
-      <c r="E55" s="69" t="inlineStr">
-        <is>
-          <t>▼ -16.0%</t>
+        <v>1.2555</v>
+      </c>
+      <c r="E55" s="71" t="inlineStr">
+        <is>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>1.9941</v>
+        <v>1.3294</v>
       </c>
       <c r="H55" s="71" t="inlineStr">
         <is>
-          <t>▲ +65.8%</t>
+          <t>▲ +10.6%</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="H56" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -24.8%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="E60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>0.9319</v>
+      </c>
+      <c r="E60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -24.4%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="H60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+        <v>0.9319</v>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -27.7%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>25</v>
+        <v>16.96</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>25</v>
+        <v>16.96</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Egypt</t>
+          <t xml:space="preserve">  3.  Algeria</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
@@ -7483,19 +7483,19 @@
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.338</v>
+        <v>0.3494</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2684</v>
-      </c>
-      <c r="K7" s="110" t="inlineStr">
-        <is>
-          <t>▼ -29.2%</t>
+        <v>0.2305</v>
+      </c>
+      <c r="K7" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="111" t="inlineStr">
+      <c r="A8" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  CAR</t>
         </is>
@@ -7516,9 +7516,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Algeria</t>
+      <c r="G8" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Egypt</t>
         </is>
       </c>
       <c r="H8" s="107" t="inlineStr">
@@ -7527,14 +7527,14 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.3494</v>
+        <v>0.4374</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K8" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.3181</v>
+      </c>
+      <c r="K8" s="112" t="inlineStr">
+        <is>
+          <t>▼ -8.3%</t>
         </is>
       </c>
     </row>
@@ -7555,35 +7555,35 @@
       <c r="D9" s="98" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E9" s="110" t="inlineStr">
+      <c r="E9" s="112" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G9" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  South Sudan</t>
+          <t xml:space="preserve">  5.  Niger</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.5942</v>
+        <v>0.8262</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.5942</v>
-      </c>
-      <c r="K9" s="110" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>1.0232</v>
+      </c>
+      <c r="K9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="111" t="inlineStr">
+      <c r="A10" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  Senegal</t>
         </is>
@@ -7604,25 +7604,25 @@
           <t>▲ +7.5%</t>
         </is>
       </c>
-      <c r="G10" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Nigeria</t>
+      <c r="G10" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Tunisia</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.6663</v>
+        <v>0.8377</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="K10" s="106" t="inlineStr">
-        <is>
-          <t>▲ +13.7%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K10" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="G11" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Niger</t>
+          <t xml:space="preserve">  7.  Ghana</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
@@ -7659,19 +7659,19 @@
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8262</v>
+        <v>0.8471</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K11" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0892</v>
+      </c>
+      <c r="K11" s="112" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="111" t="inlineStr">
+      <c r="A12" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  8.  Rwanda</t>
         </is>
@@ -7692,25 +7692,25 @@
           <t>▲ +15.0%</t>
         </is>
       </c>
-      <c r="G12" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Tunisia</t>
+      <c r="G12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Eswatini</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8377</v>
+        <v>0.8625</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.7318</v>
-      </c>
-      <c r="K12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8625</v>
+      </c>
+      <c r="K12" s="112" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G13" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Ghana</t>
+          <t xml:space="preserve">  9.  Nigeria</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
@@ -7747,19 +7747,19 @@
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8471</v>
+        <v>0.863</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K13" s="110" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>0.863</v>
+      </c>
+      <c r="K13" s="106" t="inlineStr">
+        <is>
+          <t>▲ +47.2%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="111" t="inlineStr">
+      <c r="A14" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Morocco</t>
         </is>
@@ -7780,21 +7780,21 @@
           <t>▲ +13.2%</t>
         </is>
       </c>
-      <c r="G14" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Liberia</t>
+      <c r="G14" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Equatorial Guinea</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.8608</v>
+        <v>0.9106</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.9124</v>
+        <v>0.8609</v>
       </c>
       <c r="K14" s="99" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,28 +7860,28 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.0871</v>
+        <v>1.2544</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.4424</v>
+        <v>0.5942</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
@@ -7891,307 +7891,307 @@
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>1.15</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.6</v>
+        <v>1.0871</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.45</v>
+        <v>0.4424</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.0616</v>
+        <v>0.5861</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.4096</v>
+        <v>0.863</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.348</v>
+        <v>0.2769</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.15</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.3014</v>
+        <v>1.6</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.0616</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.2129</v>
+        <v>1.4096</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.0882</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.5742</v>
+        <v>1.3014</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0316</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>0.6663</v>
+        <v>1.2129</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.3691</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.4447</v>
+        <v>1.5742</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.2%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1685</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.2762</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.3736</v>
+        <v>1.4447</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +13.2%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.1685</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.3819</v>
+        <v>0.8608</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.4936</v>
+        <v>0.9639</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.1%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1117</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.1425</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.2555</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
@@ -8201,28 +8201,28 @@
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3819</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.3699</v>
+        <v>1.4936</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +8.1%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.022</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
@@ -8232,28 +8232,28 @@
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.5244</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.6391</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
@@ -8263,28 +8263,28 @@
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3479</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.4261</v>
+        <v>1.3699</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,90 +8294,90 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.3681</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.3377</v>
+        <v>1.3873</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.7%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>2.17</v>
+        <v>1.4106</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>2.1808</v>
+        <v>1.4261</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.5%</t>
+          <t>▲ +1.1%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0108</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3289</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.0582</v>
+        <v>1.3377</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +0.7%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
@@ -8387,28 +8387,28 @@
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.31</v>
+        <v>2.17</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G36" s="119" t="n">
-        <v>-0.0063</v>
+        <v>2.1808</v>
+      </c>
+      <c r="F36" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
+        </is>
+      </c>
+      <c r="G36" s="117" t="n">
+        <v>0.0108</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,59 +8418,59 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.0555</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.0485</v>
-      </c>
-      <c r="F37" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.2%</t>
-        </is>
-      </c>
-      <c r="G37" s="119" t="n">
-        <v>-0.0237</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F37" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G37" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.31</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3661</v>
+        <v>1.3037</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
@@ -8480,146 +8480,146 @@
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.784</v>
+        <v>1.3986</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.6851</v>
+        <v>1.3661</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.784</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>0.9982</v>
+        <v>1.6851</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.0474</v>
+        <v>1.2262</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>0.9809</v>
+        <v>1.1507</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.3%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0665</v>
+        <v>-0.0755</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>0.914</v>
+        <v>1.0641</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>0.8471</v>
+        <v>0.9982</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.0671</v>
+        <v>0.914</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>0.9851</v>
+        <v>0.8471</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -8656,38 +8656,38 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.2262</v>
+        <v>0.4771</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>1.1258</v>
+        <v>0.4374</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -8.3%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.1004</v>
+        <v>-0.0397</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
@@ -8697,59 +8697,59 @@
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>0.6602</v>
+        <v>1.1939</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.5942</v>
+        <v>1.0606</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.0%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.066</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2886</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.0606</v>
+        <v>1.0635</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.2251</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
@@ -8759,84 +8759,53 @@
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.0722</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>0.9601</v>
+        <v>0.8625</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -16.0%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1824</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.2332</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.0635</v>
+        <v>0.9319</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -24.4%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.2251</v>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="62" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B50" s="63" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="C50" s="118" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="D50" s="88" t="n">
-        <v>0.4771</v>
-      </c>
-      <c r="E50" s="89" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="F50" s="69" t="inlineStr">
-        <is>
-          <t>▼ -29.2%</t>
-        </is>
-      </c>
-      <c r="G50" s="119" t="n">
-        <v>-0.1391</v>
+        <v>-0.3013</v>
       </c>
     </row>
   </sheetData>
@@ -8893,10 +8862,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6636000000000001</v>
+        <v>0.69125</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6140166666666667</v>
+        <v>0.6333833333333333</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -8995,20 +8964,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.338</v>
+        <v>0.4374</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.3181</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -8.3%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9097,20 +9066,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>590</v>
-      </c>
-      <c r="G10" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+        <v>630</v>
+      </c>
+      <c r="G10" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9169,13 +9138,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.17518125</v>
+        <v>1.195475</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.11665</v>
+        <v>1.1290625</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6663</v>
+        <v>0.8262</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9237,20 +9206,20 @@
         </is>
       </c>
       <c r="C16" s="57" t="n">
-        <v>1.1258</v>
+        <v>1.1507</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>1.1589</v>
+        <v>1.1921</v>
       </c>
       <c r="E16" s="58" t="n">
-        <v>680</v>
+        <v>695</v>
       </c>
       <c r="F16" s="58" t="n">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="G16" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="H16" s="61" t="inlineStr">
@@ -9509,20 +9478,20 @@
         </is>
       </c>
       <c r="C24" s="57" t="n">
-        <v>0.8608</v>
+        <v>0.9639</v>
       </c>
       <c r="D24" s="57" t="n">
-        <v>0.9124</v>
+        <v>0.9639</v>
       </c>
       <c r="E24" s="58" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F24" s="58" t="n">
-        <v>177</v>
-      </c>
-      <c r="G24" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>187</v>
+      </c>
+      <c r="G24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="H24" s="61" t="inlineStr">
@@ -9546,13 +9515,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9645,20 +9614,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.863</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.863</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1080</v>
+        <v>1399</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1080</v>
+        <v>1399</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9785,10 +9754,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2173625</v>
+        <v>1.2275</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1930875</v>
+        <v>1.191225</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10057,20 +10026,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>585</v>
-      </c>
-      <c r="G42" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>576</v>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10129,13 +10098,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.476433333333333</v>
+        <v>1.520446666666667</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.41832</v>
+        <v>1.462333333333333</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.5942</v>
+        <v>1.0606</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10605,20 +10574,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>0.5942</v>
+        <v>1.2544</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>0.5942</v>
+        <v>1.2544</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>2700</v>
-      </c>
-      <c r="G60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>5700</v>
+      </c>
+      <c r="G60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">
@@ -10711,10 +10680,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.162577777777778</v>
+        <v>1.125655555555556</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.236877777777778</v>
+        <v>1.090877777777778</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10813,20 +10782,20 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>0.9601</v>
+        <v>1.2555</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>1.9941</v>
+        <v>1.3294</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>27</v>
-      </c>
-      <c r="G68" s="69" t="inlineStr">
-        <is>
-          <t>▼ -16.0%</t>
+        <v>18</v>
+      </c>
+      <c r="G68" s="71" t="inlineStr">
+        <is>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="H68" s="70" t="inlineStr">
@@ -10847,20 +10816,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="G69" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">
@@ -10983,20 +10952,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.3736</v>
+        <v>0.9319</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.3736</v>
+        <v>0.9319</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>25</v>
+        <v>16.96</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>25</v>
-      </c>
-      <c r="G73" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>16.96</v>
+      </c>
+      <c r="G73" s="69" t="inlineStr">
+        <is>
+          <t>▼ -24.4%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1085,14 +1085,14 @@
     <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-06</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-07</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.223</t>
+          <t>$1.228</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.169</t>
+          <t>$1.184</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.69125</v>
+        <v>0.6746833333333334</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6333833333333333</v>
+        <v>0.6251000000000001</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.195475</v>
+        <v>1.192575</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.1290625</v>
+        <v>1.15371875</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.8262</v>
+        <v>0.7835</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.125655555555556</v>
+        <v>1.174733333333333</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.090877777777778</v>
+        <v>1.139955555555556</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-06</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-07</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.4374</v>
+        <v>0.338</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.3181</v>
+        <v>0.2684</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.3%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.863</v>
+        <v>0.7835</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.863</v>
+        <v>1.0009</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1399</v>
+        <v>1270</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1399</v>
+        <v>1622.5</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +33.7%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3055,23 +3055,23 @@
         </is>
       </c>
       <c r="E26" s="57" t="n">
-        <v>1.1258</v>
+        <v>1.1589</v>
       </c>
       <c r="F26" s="57" t="n">
-        <v>1.1507</v>
+        <v>1.4073</v>
       </c>
       <c r="G26" s="58" t="n">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="H26" s="58" t="n">
-        <v>695</v>
+        <v>850</v>
       </c>
       <c r="I26" s="59" t="n">
         <v>604</v>
       </c>
       <c r="J26" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -5.1%</t>
         </is>
       </c>
       <c r="K26" s="61" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>0.9319</v>
+        <v>1.3736</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>0.9319</v>
+        <v>1.3736</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>16.96</v>
+        <v>25</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>16.96</v>
+        <v>25</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="69" t="inlineStr">
-        <is>
-          <t>▼ -24.4%</t>
+      <c r="J59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.222827777777777</v>
+        <v>1.228307407407407</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.169407407407407</v>
+        <v>1.183972222222222</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-06</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-07</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.4374</v>
+        <v>0.338</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.3%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.3181</v>
+        <v>0.2684</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -22.0%</t>
+          <t>▼ -34.1%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.863</v>
+        <v>0.7835</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +33.7%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.863</v>
+        <v>1.0009</v>
       </c>
       <c r="H24" s="71" t="inlineStr">
         <is>
-          <t>▲ +16.6%</t>
+          <t>▲ +35.2%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1399</v>
+        <v>1270</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1399</v>
+        <v>1622.5</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -5748,29 +5748,29 @@
         <v>1.2212</v>
       </c>
       <c r="D27" s="89" t="n">
-        <v>1.1258</v>
+        <v>1.1589</v>
       </c>
       <c r="E27" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -5.1%</t>
         </is>
       </c>
       <c r="F27" s="90" t="n">
         <v>1.1814</v>
       </c>
       <c r="G27" s="89" t="n">
-        <v>1.1507</v>
-      </c>
-      <c r="H27" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.6%</t>
+        <v>1.4073</v>
+      </c>
+      <c r="H27" s="71" t="inlineStr">
+        <is>
+          <t>▲ +19.1%</t>
         </is>
       </c>
       <c r="I27" s="67" t="n">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="J27" s="67" t="n">
-        <v>695</v>
+        <v>850</v>
       </c>
       <c r="K27" s="70" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>0.9319</v>
-      </c>
-      <c r="E60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -24.4%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="E60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>0.9319</v>
-      </c>
-      <c r="H60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -27.7%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="H60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>16.96</v>
+        <v>25</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>16.96</v>
+        <v>25</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Algeria</t>
+          <t xml:space="preserve">  3.  Egypt</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
@@ -7483,19 +7483,19 @@
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.3494</v>
+        <v>0.338</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K7" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2684</v>
+      </c>
+      <c r="K7" s="110" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="110" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  CAR</t>
         </is>
@@ -7516,9 +7516,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Egypt</t>
+      <c r="G8" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Algeria</t>
         </is>
       </c>
       <c r="H8" s="107" t="inlineStr">
@@ -7527,14 +7527,14 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.4374</v>
+        <v>0.3494</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.3181</v>
-      </c>
-      <c r="K8" s="112" t="inlineStr">
-        <is>
-          <t>▼ -8.3%</t>
+        <v>0.2305</v>
+      </c>
+      <c r="K8" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7555,14 +7555,14 @@
       <c r="D9" s="98" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E9" s="112" t="inlineStr">
+      <c r="E9" s="110" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G9" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Niger</t>
+          <t xml:space="preserve">  5.  Nigeria</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
@@ -7571,19 +7571,19 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.8262</v>
+        <v>0.7835</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0009</v>
+      </c>
+      <c r="K9" s="106" t="inlineStr">
+        <is>
+          <t>▲ +33.7%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="110" t="inlineStr">
+      <c r="A10" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  Senegal</t>
         </is>
@@ -7604,21 +7604,21 @@
           <t>▲ +7.5%</t>
         </is>
       </c>
-      <c r="G10" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Tunisia</t>
+      <c r="G10" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Niger</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.8377</v>
+        <v>0.8262</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>0.7318</v>
+        <v>1.0232</v>
       </c>
       <c r="K10" s="99" t="inlineStr">
         <is>
@@ -7650,28 +7650,28 @@
       </c>
       <c r="G11" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Ghana</t>
+          <t xml:space="preserve">  7.  Tunisia</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8471</v>
+        <v>0.8377</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K11" s="112" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K11" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="110" t="inlineStr">
+      <c r="A12" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  8.  Rwanda</t>
         </is>
@@ -7692,25 +7692,25 @@
           <t>▲ +15.0%</t>
         </is>
       </c>
-      <c r="G12" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Eswatini</t>
+      <c r="G12" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Ghana</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8625</v>
+        <v>0.8471</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="K12" s="112" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+        <v>1.0892</v>
+      </c>
+      <c r="K12" s="110" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
@@ -7738,28 +7738,28 @@
       </c>
       <c r="G13" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Nigeria</t>
+          <t xml:space="preserve">  9.  Eswatini</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.863</v>
+        <v>0.8625</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="K13" s="106" t="inlineStr">
-        <is>
-          <t>▲ +47.2%</t>
+        <v>0.8625</v>
+      </c>
+      <c r="K13" s="110" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="110" t="inlineStr">
+      <c r="A14" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Morocco</t>
         </is>
@@ -7780,7 +7780,7 @@
           <t>▲ +13.2%</t>
         </is>
       </c>
-      <c r="G14" s="111" t="inlineStr">
+      <c r="G14" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Equatorial Guinea</t>
         </is>
@@ -7912,63 +7912,63 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.15</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>0.863</v>
+        <v>1.6</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.2769</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.15</v>
+        <v>0.5861</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.6</v>
+        <v>0.7835</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +33.7%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.45</v>
+        <v>0.1974</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -8160,7 +8160,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,245 +8170,245 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.2332</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.2555</v>
+        <v>1.3736</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.1425</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.4936</v>
+        <v>1.2555</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.1%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1117</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3819</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.4936</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +8.1%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.5244</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.3699</v>
+        <v>1.6391</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.022</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3479</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.3699</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3681</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4261</v>
+        <v>1.3873</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.4106</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.3377</v>
+        <v>1.4261</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.7%</t>
+          <t>▲ +1.1%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>2.17</v>
+        <v>1.3289</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>2.1808</v>
+        <v>1.3377</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.5%</t>
+          <t>▲ +0.7%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0108</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,28 +8418,28 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.0555</v>
+        <v>2.17</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.0582</v>
+        <v>2.1808</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
@@ -8449,59 +8449,59 @@
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0555</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F38" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G38" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F38" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G38" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.31</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3661</v>
+        <v>1.3037</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
@@ -8511,28 +8511,28 @@
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.784</v>
+        <v>1.3986</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.6851</v>
+        <v>1.3661</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
@@ -8546,55 +8546,55 @@
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2212</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.1507</v>
+        <v>1.1589</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.1%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0755</v>
+        <v>-0.0623</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.784</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>0.9982</v>
+        <v>1.6851</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
@@ -8604,84 +8604,84 @@
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>0.914</v>
+        <v>1.2262</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>0.8471</v>
+        <v>1.1507</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0755</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0641</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.1258</v>
+        <v>0.9982</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>0.4771</v>
+        <v>0.914</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.4374</v>
+        <v>0.8471</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.3%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0397</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -8780,32 +8780,32 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2332</v>
+        <v>0.4771</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>0.9319</v>
+        <v>0.338</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -24.4%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.3013</v>
+        <v>-0.1391</v>
       </c>
     </row>
   </sheetData>
@@ -8862,10 +8862,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.69125</v>
+        <v>0.6746833333333334</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6333833333333333</v>
+        <v>0.6251000000000001</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -8964,20 +8964,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.4374</v>
+        <v>0.338</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.3181</v>
+        <v>0.2684</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.3%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9138,13 +9138,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.195475</v>
+        <v>1.192575</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.1290625</v>
+        <v>1.15371875</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.8262</v>
+        <v>0.7835</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9614,20 +9614,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.863</v>
+        <v>0.7835</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.863</v>
+        <v>1.0009</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1399</v>
+        <v>1270</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1399</v>
+        <v>1622.5</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +33.7%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9716,20 +9716,20 @@
         </is>
       </c>
       <c r="C31" s="66" t="n">
-        <v>1.1258</v>
+        <v>1.1589</v>
       </c>
       <c r="D31" s="66" t="n">
-        <v>1.1507</v>
+        <v>1.4073</v>
       </c>
       <c r="E31" s="67" t="n">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="F31" s="67" t="n">
-        <v>695</v>
+        <v>850</v>
       </c>
       <c r="G31" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -5.1%</t>
         </is>
       </c>
       <c r="H31" s="70" t="inlineStr">
@@ -10680,10 +10680,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.125655555555556</v>
+        <v>1.174733333333333</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.090877777777778</v>
+        <v>1.139955555555556</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10952,20 +10952,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>0.9319</v>
+        <v>1.3736</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>0.9319</v>
+        <v>1.3736</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>16.96</v>
+        <v>25</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="G73" s="69" t="inlineStr">
-        <is>
-          <t>▼ -24.4%</t>
+        <v>25</v>
+      </c>
+      <c r="G73" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-07</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-08</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.228</t>
+          <t>$1.224</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+90.0%</t>
+          <t>+68.6%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.184</t>
+          <t>$1.185</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6746833333333334</v>
+        <v>0.63915</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6251000000000001</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,16 +1787,16 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.192575</v>
+        <v>1.25105625</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.15371875</v>
+        <v>1.1836625</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.7835</v>
+        <v>0.6663</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>1.6391</v>
+        <v>2.2222</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2275</v>
+        <v>1.2173625</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.191225</v>
+        <v>1.1930875</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.520446666666667</v>
+        <v>1.480833333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.462333333333333</v>
+        <v>1.42272</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>1.0606</v>
+        <v>0.6602</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,16 +1853,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.174733333333333</v>
+        <v>1.143388888888889</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.139955555555556</v>
+        <v>1.172866666666667</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>2.1808</v>
+        <v>1.4771</v>
       </c>
     </row>
     <row r="18" ht="10" customHeight="1"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-07</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-08</t>
         </is>
       </c>
     </row>
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.338</v>
+        <v>0.2734</v>
       </c>
       <c r="F5" s="66" t="n">
         <v>0.2684</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>17</v>
+        <v>13.75</v>
       </c>
       <c r="H5" s="67" t="n">
         <v>13.5</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -42.7%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.2%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="K7" s="70" t="inlineStr">
@@ -2538,23 +2538,23 @@
         </is>
       </c>
       <c r="E15" s="66" t="n">
-        <v>0.8471</v>
+        <v>0.9675</v>
       </c>
       <c r="F15" s="66" t="n">
-        <v>1.0892</v>
+        <v>1.1369</v>
       </c>
       <c r="G15" s="67" t="n">
-        <v>13.3</v>
+        <v>15.19</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>17.1</v>
+        <v>17.85</v>
       </c>
       <c r="I15" s="68" t="n">
         <v>15.7</v>
       </c>
-      <c r="J15" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+      <c r="J15" s="71" t="inlineStr">
+        <is>
+          <t>▲ +5.8%</t>
         </is>
       </c>
       <c r="K15" s="70" t="inlineStr">
@@ -2773,23 +2773,23 @@
         </is>
       </c>
       <c r="E20" s="57" t="n">
-        <v>1.2831</v>
+        <v>1.4487</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2003</v>
+        <v>1.5563</v>
       </c>
       <c r="G20" s="58" t="n">
-        <v>775</v>
+        <v>875</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>725</v>
+        <v>940</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J20" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J20" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="K20" s="61" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.7835</v>
+        <v>0.6663</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>1.0009</v>
+        <v>0.6663</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1270</v>
+        <v>1080</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1622.5</v>
+        <v>1080</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +33.7%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3008,28 +3008,28 @@
         </is>
       </c>
       <c r="E25" s="66" t="n">
-        <v>1.4222</v>
+        <v>2.2222</v>
       </c>
       <c r="F25" s="66" t="n">
-        <v>1.5556</v>
+        <v>2.2222</v>
       </c>
       <c r="G25" s="67" t="n">
-        <v>32000</v>
+        <v>50000</v>
       </c>
       <c r="H25" s="67" t="n">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="I25" s="68" t="n">
         <v>22500</v>
       </c>
-      <c r="J25" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J25" s="71" t="inlineStr">
+        <is>
+          <t>▲ +56.2%</t>
         </is>
       </c>
       <c r="K25" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -3055,23 +3055,23 @@
         </is>
       </c>
       <c r="E26" s="57" t="n">
-        <v>1.1589</v>
+        <v>1.1258</v>
       </c>
       <c r="F26" s="57" t="n">
-        <v>1.4073</v>
+        <v>1.1507</v>
       </c>
       <c r="G26" s="58" t="n">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="H26" s="58" t="n">
-        <v>850</v>
+        <v>695</v>
       </c>
       <c r="I26" s="59" t="n">
         <v>604</v>
       </c>
       <c r="J26" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.1%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="K26" s="61" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J34" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="K44" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+      <c r="J49" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>1.2555</v>
+        <v>1.4771</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>1.3294</v>
+        <v>1.8501</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>18</v>
+        <v>25.05</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
       <c r="J54" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +29.3%</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
       <c r="J55" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="K55" s="70" t="inlineStr">
@@ -4439,28 +4439,28 @@
         </is>
       </c>
       <c r="E58" s="57" t="n">
-        <v>1.0582</v>
+        <v>1.2739</v>
       </c>
       <c r="F58" s="57" t="n">
-        <v>1.0636</v>
+        <v>1.2792</v>
       </c>
       <c r="G58" s="58" t="n">
-        <v>19.63</v>
+        <v>23.63</v>
       </c>
       <c r="H58" s="58" t="n">
-        <v>19.73</v>
+        <v>23.73</v>
       </c>
       <c r="I58" s="59" t="n">
         <v>18.55</v>
       </c>
       <c r="J58" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +20.7%</t>
         </is>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -4580,23 +4580,23 @@
         </is>
       </c>
       <c r="E61" s="66" t="n">
-        <v>2.1808</v>
+        <v>1.2754</v>
       </c>
       <c r="F61" s="66" t="n">
-        <v>1.9231</v>
+        <v>1.2754</v>
       </c>
       <c r="G61" s="67" t="n">
-        <v>56.7</v>
+        <v>33.16</v>
       </c>
       <c r="H61" s="67" t="n">
-        <v>50</v>
+        <v>33.16</v>
       </c>
       <c r="I61" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="J61" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+      <c r="J61" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.2%</t>
         </is>
       </c>
       <c r="K61" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.228307407407407</v>
+        <v>1.223957407407407</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.183972222222222</v>
+        <v>1.18485</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-07</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-08</t>
         </is>
       </c>
     </row>
@@ -4841,11 +4841,11 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.338</v>
+        <v>0.2734</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -42.7%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>17</v>
+        <v>13.75</v>
       </c>
       <c r="J6" s="58" t="n">
         <v>13.5</v>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="E8" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.2%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>▲ +26.0%</t>
+          <t>▲ +13.0%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -5253,29 +5253,29 @@
         <v>0.914</v>
       </c>
       <c r="D16" s="91" t="n">
-        <v>0.8471</v>
-      </c>
-      <c r="E16" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>0.9675</v>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>▲ +5.8%</t>
         </is>
       </c>
       <c r="F16" s="90" t="n">
         <v>0.914</v>
       </c>
       <c r="G16" s="91" t="n">
-        <v>1.0892</v>
+        <v>1.1369</v>
       </c>
       <c r="H16" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.2%</t>
+          <t>▲ +24.4%</t>
         </is>
       </c>
       <c r="I16" s="58" t="n">
-        <v>13.3</v>
+        <v>15.19</v>
       </c>
       <c r="J16" s="58" t="n">
-        <v>17.1</v>
+        <v>17.85</v>
       </c>
       <c r="K16" s="61" t="inlineStr">
         <is>
@@ -5478,29 +5478,29 @@
         <v>1.2831</v>
       </c>
       <c r="D21" s="89" t="n">
-        <v>1.2831</v>
-      </c>
-      <c r="E21" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.4487</v>
+      </c>
+      <c r="E21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="F21" s="90" t="n">
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2003</v>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.5563</v>
+      </c>
+      <c r="H21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +29.7%</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
-        <v>775</v>
+        <v>875</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>725</v>
+        <v>940</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.7835</v>
+        <v>0.6663</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +33.7%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>1.0009</v>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>▲ +35.2%</t>
+        <v>0.6663</v>
+      </c>
+      <c r="H24" s="69" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1270</v>
+        <v>1080</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1622.5</v>
+        <v>1080</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -5703,33 +5703,33 @@
         <v>1.4222</v>
       </c>
       <c r="D26" s="91" t="n">
-        <v>1.4222</v>
-      </c>
-      <c r="E26" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2.2222</v>
+      </c>
+      <c r="E26" s="71" t="inlineStr">
+        <is>
+          <t>▲ +56.2%</t>
         </is>
       </c>
       <c r="F26" s="90" t="n">
         <v>1.5556</v>
       </c>
       <c r="G26" s="91" t="n">
-        <v>1.5556</v>
-      </c>
-      <c r="H26" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2.2222</v>
+      </c>
+      <c r="H26" s="71" t="inlineStr">
+        <is>
+          <t>▲ +42.9%</t>
         </is>
       </c>
       <c r="I26" s="58" t="n">
-        <v>32000</v>
+        <v>50000</v>
       </c>
       <c r="J26" s="58" t="n">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="K26" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -5748,29 +5748,29 @@
         <v>1.2212</v>
       </c>
       <c r="D27" s="89" t="n">
-        <v>1.1589</v>
+        <v>1.1258</v>
       </c>
       <c r="E27" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.1%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="F27" s="90" t="n">
         <v>1.1814</v>
       </c>
       <c r="G27" s="89" t="n">
-        <v>1.4073</v>
-      </c>
-      <c r="H27" s="71" t="inlineStr">
-        <is>
-          <t>▲ +19.1%</t>
+        <v>1.1507</v>
+      </c>
+      <c r="H27" s="69" t="inlineStr">
+        <is>
+          <t>▼ -2.6%</t>
         </is>
       </c>
       <c r="I27" s="67" t="n">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="J27" s="67" t="n">
-        <v>850</v>
+        <v>695</v>
       </c>
       <c r="K27" s="70" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>1.0662</v>
-      </c>
-      <c r="E35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9851</v>
+      </c>
+      <c r="E35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9536</v>
-      </c>
-      <c r="H35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9685</v>
+      </c>
+      <c r="H35" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.5%</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="K45" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>1.2544</v>
-      </c>
-      <c r="E50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="E50" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>1.2544</v>
-      </c>
-      <c r="H50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="H50" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -6894,29 +6894,29 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>1.2555</v>
+        <v>1.4771</v>
       </c>
       <c r="E55" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +29.3%</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>1.3294</v>
+        <v>1.8501</v>
       </c>
       <c r="H55" s="71" t="inlineStr">
         <is>
-          <t>▲ +10.6%</t>
+          <t>▲ +53.9%</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>18</v>
+        <v>25.05</v>
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="H56" s="69" t="inlineStr">
         <is>
-          <t>▼ -24.8%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -7074,33 +7074,33 @@
         <v>1.0555</v>
       </c>
       <c r="D59" s="89" t="n">
-        <v>1.0582</v>
+        <v>1.2739</v>
       </c>
       <c r="E59" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +20.7%</t>
         </is>
       </c>
       <c r="F59" s="90" t="n">
         <v>1.0582</v>
       </c>
       <c r="G59" s="89" t="n">
-        <v>1.0636</v>
+        <v>1.2792</v>
       </c>
       <c r="H59" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.5%</t>
+          <t>▲ +20.9%</t>
         </is>
       </c>
       <c r="I59" s="67" t="n">
-        <v>19.63</v>
+        <v>23.63</v>
       </c>
       <c r="J59" s="67" t="n">
-        <v>19.73</v>
+        <v>23.73</v>
       </c>
       <c r="K59" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -7209,29 +7209,29 @@
         <v>2.17</v>
       </c>
       <c r="D62" s="91" t="n">
-        <v>2.1808</v>
-      </c>
-      <c r="E62" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+        <v>1.2754</v>
+      </c>
+      <c r="E62" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.2%</t>
         </is>
       </c>
       <c r="F62" s="90" t="n">
         <v>2.05</v>
       </c>
       <c r="G62" s="91" t="n">
-        <v>1.9231</v>
+        <v>1.2754</v>
       </c>
       <c r="H62" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -37.8%</t>
         </is>
       </c>
       <c r="I62" s="58" t="n">
-        <v>56.7</v>
+        <v>33.16</v>
       </c>
       <c r="J62" s="58" t="n">
-        <v>50</v>
+        <v>33.16</v>
       </c>
       <c r="K62" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7409,44 +7409,44 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Zimbabwe</t>
+          <t xml:space="preserve">  2.  Sierra Leone</t>
         </is>
       </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2.1808</v>
+        <v>2.2222</v>
       </c>
       <c r="D6" s="105" t="n">
-        <v>1.9231</v>
+        <v>2.2222</v>
       </c>
       <c r="E6" s="106" t="inlineStr">
         <is>
-          <t>▲ +0.5%</t>
+          <t>▲ +56.2%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Angola</t>
+          <t xml:space="preserve">  2.  Egypt</t>
         </is>
       </c>
       <c r="H6" s="107" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I6" s="108" t="n">
-        <v>0.3272</v>
+        <v>0.2734</v>
       </c>
       <c r="J6" s="109" t="n">
-        <v>0.2181</v>
-      </c>
-      <c r="K6" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2684</v>
+      </c>
+      <c r="K6" s="110" t="inlineStr">
+        <is>
+          <t>▼ -42.7%</t>
         </is>
       </c>
     </row>
@@ -7474,23 +7474,23 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Egypt</t>
+          <t xml:space="preserve">  3.  Angola</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.338</v>
+        <v>0.3272</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2684</v>
-      </c>
-      <c r="K7" s="110" t="inlineStr">
-        <is>
-          <t>▼ -29.2%</t>
+        <v>0.2181</v>
+      </c>
+      <c r="K7" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7562,23 +7562,23 @@
       </c>
       <c r="G9" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Nigeria</t>
+          <t xml:space="preserve">  5.  South Sudan</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.7835</v>
+        <v>0.6602</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>1.0009</v>
-      </c>
-      <c r="K9" s="106" t="inlineStr">
-        <is>
-          <t>▲ +33.7%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="K9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G10" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Niger</t>
+          <t xml:space="preserve">  6.  Nigeria</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
@@ -7615,14 +7615,14 @@
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.8262</v>
+        <v>0.6663</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K10" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.6663</v>
+      </c>
+      <c r="K10" s="106" t="inlineStr">
+        <is>
+          <t>▲ +13.7%</t>
         </is>
       </c>
     </row>
@@ -7650,19 +7650,19 @@
       </c>
       <c r="G11" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Tunisia</t>
+          <t xml:space="preserve">  7.  Niger</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8377</v>
+        <v>0.8262</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.7318</v>
+        <v>1.0232</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7694,23 +7694,23 @@
       </c>
       <c r="G12" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Ghana</t>
+          <t xml:space="preserve">  8.  Tunisia</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8471</v>
+        <v>0.8377</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K12" s="110" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7738,67 +7738,67 @@
       </c>
       <c r="G13" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Eswatini</t>
+          <t xml:space="preserve">  9.  Equatorial Guinea</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8625</v>
+        <v>0.9106</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="K13" s="110" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+        <v>0.8609</v>
+      </c>
+      <c r="K13" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Morocco</t>
+          <t xml:space="preserve">  10.  Botswana</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.4447</v>
+        <v>1.4771</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.4447</v>
+        <v>1.8501</v>
       </c>
       <c r="E14" s="106" t="inlineStr">
         <is>
-          <t>▲ +13.2%</t>
+          <t>▲ +29.3%</t>
         </is>
       </c>
       <c r="G14" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Equatorial Guinea</t>
+          <t xml:space="preserve">  10.  Liberia</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.9106</v>
+        <v>0.9639</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8609</v>
-      </c>
-      <c r="K14" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9639</v>
+      </c>
+      <c r="K14" s="106" t="inlineStr">
+        <is>
+          <t>▲ +12.0%</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,53 +7860,53 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6602</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.2544</v>
+        <v>1.0871</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.5942</v>
+        <v>0.4424</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>1.4222</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.0871</v>
+        <v>2.2222</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +56.2%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.4424</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -7943,193 +7943,193 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0616</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>0.7835</v>
+        <v>1.4096</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +33.7%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.1974</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.1425</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.4096</v>
+        <v>1.4771</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +29.3%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.348</v>
+        <v>0.3346</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0555</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.3014</v>
+        <v>1.2739</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +20.7%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.2184</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.0882</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.2129</v>
+        <v>1.3014</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.0316</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.5742</v>
+        <v>1.2129</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.3691</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.4447</v>
+        <v>1.5742</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.2%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1685</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
@@ -8139,183 +8139,183 @@
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.8608</v>
+        <v>0.5861</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.9639</v>
+        <v>0.6663</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.2831</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.3736</v>
+        <v>1.4487</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.1425</v>
+        <v>0.8608</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.2555</v>
+        <v>0.9639</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.2332</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.4936</v>
+        <v>1.3736</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.1%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1117</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3819</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.6391</v>
+        <v>1.4936</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +8.1%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.5244</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.3699</v>
+        <v>1.6391</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.022</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,28 +8325,28 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.3681</v>
+        <v>0.914</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.3873</v>
+        <v>0.9675</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +5.8%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0535</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
@@ -8356,214 +8356,214 @@
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3479</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.4261</v>
+        <v>1.3699</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2762</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3377</v>
+        <v>1.2961</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.7%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>2.17</v>
+        <v>1.3681</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>2.1808</v>
+        <v>1.3873</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.5%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0108</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.4106</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.0582</v>
+        <v>1.4261</v>
       </c>
       <c r="F38" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.1%</t>
         </is>
       </c>
       <c r="G38" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.31</v>
+        <v>1.3289</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F39" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G39" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.3377</v>
+      </c>
+      <c r="F39" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.7%</t>
+        </is>
+      </c>
+      <c r="G39" s="117" t="n">
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.31</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3661</v>
+        <v>1.3037</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0722</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.1589</v>
+        <v>1.0485</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.1%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0623</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
@@ -8573,76 +8573,76 @@
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.784</v>
+        <v>1.3986</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.6851</v>
+        <v>1.3661</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.784</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.1507</v>
+        <v>1.6851</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0755</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.2262</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>0.9982</v>
+        <v>1.1507</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
@@ -8650,75 +8650,75 @@
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0755</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>0.914</v>
+        <v>1.0641</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.8471</v>
+        <v>0.9982</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.0671</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>1.0606</v>
+        <v>0.9851</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
@@ -8728,84 +8728,146 @@
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.2212</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.0635</v>
+        <v>1.1258</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.2251</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.1939</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>0.8625</v>
+        <v>1.0606</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
+          <t>Cabo Verde</t>
+        </is>
+      </c>
+      <c r="B49" s="54" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="C49" s="116" t="inlineStr">
+        <is>
+          <t>CVE</t>
+        </is>
+      </c>
+      <c r="D49" s="88" t="n">
+        <v>1.2886</v>
+      </c>
+      <c r="E49" s="91" t="n">
+        <v>1.0635</v>
+      </c>
+      <c r="F49" s="69" t="inlineStr">
+        <is>
+          <t>▼ -17.5%</t>
+        </is>
+      </c>
+      <c r="G49" s="119" t="n">
+        <v>-0.2251</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="62" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
+      <c r="C50" s="118" t="inlineStr">
+        <is>
+          <t>ZWG</t>
+        </is>
+      </c>
+      <c r="D50" s="88" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E50" s="89" t="n">
+        <v>1.2754</v>
+      </c>
+      <c r="F50" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.2%</t>
+        </is>
+      </c>
+      <c r="G50" s="119" t="n">
+        <v>-0.8946</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="53" t="inlineStr">
+        <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B49" s="54" t="inlineStr">
+      <c r="B51" s="54" t="inlineStr">
         <is>
           <t>North Africa</t>
         </is>
       </c>
-      <c r="C49" s="116" t="inlineStr">
+      <c r="C51" s="116" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
       </c>
-      <c r="D49" s="88" t="n">
+      <c r="D51" s="88" t="n">
         <v>0.4771</v>
       </c>
-      <c r="E49" s="91" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="F49" s="69" t="inlineStr">
-        <is>
-          <t>▼ -29.2%</t>
-        </is>
-      </c>
-      <c r="G49" s="119" t="n">
-        <v>-0.1391</v>
+      <c r="E51" s="91" t="n">
+        <v>0.2734</v>
+      </c>
+      <c r="F51" s="69" t="inlineStr">
+        <is>
+          <t>▼ -42.7%</t>
+        </is>
+      </c>
+      <c r="G51" s="119" t="n">
+        <v>-0.2037</v>
       </c>
     </row>
   </sheetData>
@@ -8862,16 +8924,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6746833333333334</v>
+        <v>0.63915</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6251000000000001</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -8964,20 +9026,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.338</v>
+        <v>0.2734</v>
       </c>
       <c r="D7" s="66" t="n">
         <v>0.2684</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>17</v>
+        <v>13.75</v>
       </c>
       <c r="F7" s="67" t="n">
         <v>13.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -42.7%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9032,20 +9094,20 @@
         </is>
       </c>
       <c r="C9" s="66" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.2%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -9138,16 +9200,16 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.192575</v>
+        <v>1.25105625</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.15371875</v>
+        <v>1.1836625</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.7835</v>
+        <v>0.6663</v>
       </c>
       <c r="F14" s="132" t="n">
-        <v>1.6391</v>
+        <v>2.2222</v>
       </c>
       <c r="G14" s="129" t="n"/>
       <c r="H14" s="129" t="n"/>
@@ -9342,20 +9404,20 @@
         </is>
       </c>
       <c r="C20" s="57" t="n">
-        <v>0.8471</v>
+        <v>0.9675</v>
       </c>
       <c r="D20" s="57" t="n">
-        <v>1.0892</v>
+        <v>1.1369</v>
       </c>
       <c r="E20" s="58" t="n">
-        <v>13.3</v>
+        <v>15.19</v>
       </c>
       <c r="F20" s="58" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="G20" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>17.85</v>
+      </c>
+      <c r="G20" s="71" t="inlineStr">
+        <is>
+          <t>▲ +5.8%</t>
         </is>
       </c>
       <c r="H20" s="61" t="inlineStr">
@@ -9512,20 +9574,20 @@
         </is>
       </c>
       <c r="C25" s="66" t="n">
-        <v>1.2831</v>
+        <v>1.4487</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2003</v>
+        <v>1.5563</v>
       </c>
       <c r="E25" s="67" t="n">
-        <v>775</v>
+        <v>875</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>725</v>
-      </c>
-      <c r="G25" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>940</v>
+      </c>
+      <c r="G25" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="H25" s="70" t="inlineStr">
@@ -9614,20 +9676,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.7835</v>
+        <v>0.6663</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>1.0009</v>
+        <v>0.6663</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1270</v>
+        <v>1080</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1622.5</v>
+        <v>1080</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +33.7%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9682,25 +9744,25 @@
         </is>
       </c>
       <c r="C30" s="57" t="n">
-        <v>1.4222</v>
+        <v>2.2222</v>
       </c>
       <c r="D30" s="57" t="n">
-        <v>1.5556</v>
+        <v>2.2222</v>
       </c>
       <c r="E30" s="58" t="n">
-        <v>32000</v>
+        <v>50000</v>
       </c>
       <c r="F30" s="58" t="n">
-        <v>35000</v>
-      </c>
-      <c r="G30" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>50000</v>
+      </c>
+      <c r="G30" s="71" t="inlineStr">
+        <is>
+          <t>▲ +56.2%</t>
         </is>
       </c>
       <c r="H30" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -9716,20 +9778,20 @@
         </is>
       </c>
       <c r="C31" s="66" t="n">
-        <v>1.1589</v>
+        <v>1.1258</v>
       </c>
       <c r="D31" s="66" t="n">
-        <v>1.4073</v>
+        <v>1.1507</v>
       </c>
       <c r="E31" s="67" t="n">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="F31" s="67" t="n">
-        <v>850</v>
+        <v>695</v>
       </c>
       <c r="G31" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.1%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="H31" s="70" t="inlineStr">
@@ -9754,10 +9816,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2275</v>
+        <v>1.2173625</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.191225</v>
+        <v>1.1930875</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10026,20 +10088,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>576</v>
-      </c>
-      <c r="G42" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>585</v>
+      </c>
+      <c r="G42" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10098,13 +10160,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.520446666666667</v>
+        <v>1.480833333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.462333333333333</v>
+        <v>1.42272</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>1.0606</v>
+        <v>0.6602</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10422,7 +10484,7 @@
       </c>
       <c r="H55" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -10574,20 +10636,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>3000</v>
+      </c>
+      <c r="G60" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">
@@ -10680,16 +10742,16 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.174733333333333</v>
+        <v>1.143388888888889</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.139955555555556</v>
+        <v>1.172866666666667</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
       </c>
       <c r="F65" s="153" t="n">
-        <v>2.1808</v>
+        <v>1.4771</v>
       </c>
       <c r="G65" s="150" t="n"/>
       <c r="H65" s="150" t="n"/>
@@ -10782,20 +10844,20 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>1.2555</v>
+        <v>1.4771</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>1.3294</v>
+        <v>1.8501</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>18</v>
+        <v>25.05</v>
       </c>
       <c r="G68" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +29.3%</t>
         </is>
       </c>
       <c r="H68" s="70" t="inlineStr">
@@ -10816,20 +10878,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="G69" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">
@@ -10918,25 +10980,25 @@
         </is>
       </c>
       <c r="C72" s="66" t="n">
-        <v>1.0582</v>
+        <v>1.2739</v>
       </c>
       <c r="D72" s="66" t="n">
-        <v>1.0636</v>
+        <v>1.2792</v>
       </c>
       <c r="E72" s="67" t="n">
-        <v>19.63</v>
+        <v>23.63</v>
       </c>
       <c r="F72" s="67" t="n">
-        <v>19.73</v>
+        <v>23.73</v>
       </c>
       <c r="G72" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +20.7%</t>
         </is>
       </c>
       <c r="H72" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -11020,20 +11082,20 @@
         </is>
       </c>
       <c r="C75" s="57" t="n">
-        <v>2.1808</v>
+        <v>1.2754</v>
       </c>
       <c r="D75" s="57" t="n">
-        <v>1.9231</v>
+        <v>1.2754</v>
       </c>
       <c r="E75" s="58" t="n">
-        <v>56.7</v>
+        <v>33.16</v>
       </c>
       <c r="F75" s="58" t="n">
-        <v>50</v>
-      </c>
-      <c r="G75" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+        <v>33.16</v>
+      </c>
+      <c r="G75" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.2%</t>
         </is>
       </c>
       <c r="H75" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-08</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-10</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.224</t>
+          <t>$1.237</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+68.6%</t>
+          <t>+90.0%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.63915</v>
+        <v>0.6746833333333334</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.6251000000000001</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.2961</v>
+        <v>1.4447</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.25105625</v>
+        <v>1.24264375</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.1836625</v>
+        <v>1.17979375</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>2.2222</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.480833333333333</v>
+        <v>1.519326666666667</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.42272</v>
+        <v>1.46122</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.6602</v>
+        <v>1.0606</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,16 +1853,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.143388888888889</v>
+        <v>1.146044444444445</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.172866666666667</v>
+        <v>1.100455555555556</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>1.4771</v>
+        <v>2.1808</v>
       </c>
     </row>
     <row r="18" ht="10" customHeight="1"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-08</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-10</t>
         </is>
       </c>
     </row>
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.2734</v>
+        <v>0.338</v>
       </c>
       <c r="F5" s="66" t="n">
         <v>0.2684</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>13.75</v>
+        <v>17</v>
       </c>
       <c r="H5" s="67" t="n">
         <v>13.5</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -42.7%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.2961</v>
+        <v>1.4447</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.2961</v>
+        <v>1.4447</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>13</v>
+        <v>14.49</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>13</v>
+        <v>14.49</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +13.2%</t>
         </is>
       </c>
       <c r="K7" s="70" t="inlineStr">
@@ -2538,23 +2538,23 @@
         </is>
       </c>
       <c r="E15" s="66" t="n">
-        <v>0.9675</v>
+        <v>0.8471</v>
       </c>
       <c r="F15" s="66" t="n">
-        <v>1.1369</v>
+        <v>1.0892</v>
       </c>
       <c r="G15" s="67" t="n">
-        <v>15.19</v>
+        <v>13.3</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>17.85</v>
+        <v>17.1</v>
       </c>
       <c r="I15" s="68" t="n">
         <v>15.7</v>
       </c>
-      <c r="J15" s="71" t="inlineStr">
-        <is>
-          <t>▲ +5.8%</t>
+      <c r="J15" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="K15" s="70" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="K44" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J49" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4150,23 +4150,23 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.4936</v>
+        <v>1.4768</v>
       </c>
       <c r="F51" s="66" t="n">
-        <v>1.4377</v>
+        <v>1.421</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>5350</v>
+        <v>5290</v>
       </c>
       <c r="H51" s="67" t="n">
-        <v>5150</v>
+        <v>5090</v>
       </c>
       <c r="I51" s="68" t="n">
         <v>3582</v>
       </c>
       <c r="J51" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.1%</t>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="K51" s="70" t="inlineStr">
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>1.4771</v>
+        <v>1.2555</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>1.8501</v>
+        <v>1.3294</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>25.05</v>
+        <v>18</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
       <c r="J54" s="71" t="inlineStr">
         <is>
-          <t>▲ +29.3%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
       <c r="J55" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="K55" s="70" t="inlineStr">
@@ -4439,28 +4439,28 @@
         </is>
       </c>
       <c r="E58" s="57" t="n">
-        <v>1.2739</v>
+        <v>1.0582</v>
       </c>
       <c r="F58" s="57" t="n">
-        <v>1.2792</v>
+        <v>1.0636</v>
       </c>
       <c r="G58" s="58" t="n">
-        <v>23.63</v>
+        <v>19.63</v>
       </c>
       <c r="H58" s="58" t="n">
-        <v>23.73</v>
+        <v>19.73</v>
       </c>
       <c r="I58" s="59" t="n">
         <v>18.55</v>
       </c>
       <c r="J58" s="71" t="inlineStr">
         <is>
-          <t>▲ +20.7%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.1154</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.0181</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>25</v>
+        <v>18.53</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+      <c r="J59" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4580,23 +4580,23 @@
         </is>
       </c>
       <c r="E61" s="66" t="n">
-        <v>1.2754</v>
+        <v>2.1808</v>
       </c>
       <c r="F61" s="66" t="n">
-        <v>1.2754</v>
+        <v>1.9231</v>
       </c>
       <c r="G61" s="67" t="n">
-        <v>33.16</v>
+        <v>56.7</v>
       </c>
       <c r="H61" s="67" t="n">
-        <v>33.16</v>
+        <v>50</v>
       </c>
       <c r="I61" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="J61" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.2%</t>
+      <c r="J61" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="K61" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.223957407407407</v>
+        <v>1.236548148148148</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.18485</v>
+        <v>1.185081481481481</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-08</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-10</t>
         </is>
       </c>
     </row>
@@ -4841,11 +4841,11 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.2734</v>
+        <v>0.338</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -42.7%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>13.75</v>
+        <v>17</v>
       </c>
       <c r="J6" s="58" t="n">
         <v>13.5</v>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.2961</v>
+        <v>1.4447</v>
       </c>
       <c r="E8" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +13.2%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.2961</v>
+        <v>1.4447</v>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.0%</t>
+          <t>▲ +26.0%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>13</v>
+        <v>14.49</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>13</v>
+        <v>14.49</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -5253,29 +5253,29 @@
         <v>0.914</v>
       </c>
       <c r="D16" s="91" t="n">
-        <v>0.9675</v>
-      </c>
-      <c r="E16" s="71" t="inlineStr">
-        <is>
-          <t>▲ +5.8%</t>
+        <v>0.8471</v>
+      </c>
+      <c r="E16" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="F16" s="90" t="n">
         <v>0.914</v>
       </c>
       <c r="G16" s="91" t="n">
-        <v>1.1369</v>
+        <v>1.0892</v>
       </c>
       <c r="H16" s="71" t="inlineStr">
         <is>
-          <t>▲ +24.4%</t>
+          <t>▲ +19.2%</t>
         </is>
       </c>
       <c r="I16" s="58" t="n">
-        <v>15.19</v>
+        <v>13.3</v>
       </c>
       <c r="J16" s="58" t="n">
-        <v>17.85</v>
+        <v>17.1</v>
       </c>
       <c r="K16" s="61" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="H24" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.0%</t>
+          <t>▼ -11.9%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="K45" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="E50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="E50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="H50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="H50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -6797,29 +6797,29 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.4936</v>
+        <v>1.4768</v>
       </c>
       <c r="E52" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.1%</t>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
         <v>1.2741</v>
       </c>
       <c r="G52" s="91" t="n">
-        <v>1.4377</v>
+        <v>1.421</v>
       </c>
       <c r="H52" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.8%</t>
+          <t>▲ +11.5%</t>
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>5350</v>
+        <v>5290</v>
       </c>
       <c r="J52" s="58" t="n">
-        <v>5150</v>
+        <v>5090</v>
       </c>
       <c r="K52" s="61" t="inlineStr">
         <is>
@@ -6894,29 +6894,29 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>1.4771</v>
+        <v>1.2555</v>
       </c>
       <c r="E55" s="71" t="inlineStr">
         <is>
-          <t>▲ +29.3%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>1.8501</v>
+        <v>1.3294</v>
       </c>
       <c r="H55" s="71" t="inlineStr">
         <is>
-          <t>▲ +53.9%</t>
+          <t>▲ +10.6%</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>25.05</v>
+        <v>18</v>
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="H56" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -24.8%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -7074,33 +7074,33 @@
         <v>1.0555</v>
       </c>
       <c r="D59" s="89" t="n">
-        <v>1.2739</v>
+        <v>1.0582</v>
       </c>
       <c r="E59" s="71" t="inlineStr">
         <is>
-          <t>▲ +20.7%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="F59" s="90" t="n">
         <v>1.0582</v>
       </c>
       <c r="G59" s="89" t="n">
-        <v>1.2792</v>
+        <v>1.0636</v>
       </c>
       <c r="H59" s="71" t="inlineStr">
         <is>
-          <t>▲ +20.9%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="I59" s="67" t="n">
-        <v>23.63</v>
+        <v>19.63</v>
       </c>
       <c r="J59" s="67" t="n">
-        <v>23.73</v>
+        <v>19.73</v>
       </c>
       <c r="K59" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="E60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>1.1154</v>
+      </c>
+      <c r="E60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="H60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+        <v>1.0181</v>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -21.0%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>25</v>
+        <v>18.53</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7209,29 +7209,29 @@
         <v>2.17</v>
       </c>
       <c r="D62" s="91" t="n">
-        <v>1.2754</v>
-      </c>
-      <c r="E62" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.2%</t>
+        <v>2.1808</v>
+      </c>
+      <c r="E62" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="F62" s="90" t="n">
         <v>2.05</v>
       </c>
       <c r="G62" s="91" t="n">
-        <v>1.2754</v>
+        <v>1.9231</v>
       </c>
       <c r="H62" s="69" t="inlineStr">
         <is>
-          <t>▼ -37.8%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="I62" s="58" t="n">
-        <v>33.16</v>
+        <v>56.7</v>
       </c>
       <c r="J62" s="58" t="n">
-        <v>33.16</v>
+        <v>50</v>
       </c>
       <c r="K62" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7430,86 +7430,86 @@
       </c>
       <c r="G6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Egypt</t>
+          <t xml:space="preserve">  2.  Angola</t>
         </is>
       </c>
       <c r="H6" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I6" s="108" t="n">
-        <v>0.2734</v>
+        <v>0.3272</v>
       </c>
       <c r="J6" s="109" t="n">
-        <v>0.2684</v>
-      </c>
-      <c r="K6" s="110" t="inlineStr">
-        <is>
-          <t>▼ -42.7%</t>
+        <v>0.2181</v>
+      </c>
+      <c r="K6" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Eritrea</t>
+          <t xml:space="preserve">  3.  Zimbabwe</t>
         </is>
       </c>
       <c r="B7" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C7" s="97" t="n">
-        <v>2</v>
+        <v>2.1808</v>
       </c>
       <c r="D7" s="98" t="n">
-        <v>1.7333</v>
-      </c>
-      <c r="E7" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.9231</v>
+      </c>
+      <c r="E7" s="106" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Angola</t>
+          <t xml:space="preserve">  3.  Egypt</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.3272</v>
+        <v>0.338</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2181</v>
-      </c>
-      <c r="K7" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2684</v>
+      </c>
+      <c r="K7" s="110" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  CAR</t>
+          <t xml:space="preserve">  4.  Eritrea</t>
         </is>
       </c>
       <c r="B8" s="103" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C8" s="104" t="n">
-        <v>1.7384</v>
+        <v>2</v>
       </c>
       <c r="D8" s="105" t="n">
-        <v>2.1523</v>
+        <v>1.7333</v>
       </c>
       <c r="E8" s="99" t="inlineStr">
         <is>
@@ -7541,128 +7541,128 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Comoros</t>
+          <t xml:space="preserve">  5.  CAR</t>
         </is>
       </c>
       <c r="B9" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C9" s="97" t="n">
-        <v>1.6851</v>
+        <v>1.7384</v>
       </c>
       <c r="D9" s="98" t="n">
-        <v>1.5078</v>
-      </c>
-      <c r="E9" s="110" t="inlineStr">
-        <is>
-          <t>▼ -5.5%</t>
+        <v>2.1523</v>
+      </c>
+      <c r="E9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  South Sudan</t>
+          <t xml:space="preserve">  5.  Nigeria</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6602</v>
+        <v>0.6521</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="K9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.6521</v>
+      </c>
+      <c r="K9" s="106" t="inlineStr">
+        <is>
+          <t>▲ +11.3%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Senegal</t>
+          <t xml:space="preserve">  6.  Comoros</t>
         </is>
       </c>
       <c r="B10" s="103" t="inlineStr">
         <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="104" t="n">
+        <v>1.6851</v>
+      </c>
+      <c r="D10" s="105" t="n">
+        <v>1.5078</v>
+      </c>
+      <c r="E10" s="110" t="inlineStr">
+        <is>
+          <t>▼ -5.5%</t>
+        </is>
+      </c>
+      <c r="G10" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Niger</t>
+        </is>
+      </c>
+      <c r="H10" s="107" t="inlineStr">
+        <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n">
-        <v>1.6391</v>
-      </c>
-      <c r="D10" s="105" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E10" s="106" t="inlineStr">
-        <is>
-          <t>▲ +7.5%</t>
-        </is>
-      </c>
-      <c r="G10" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Nigeria</t>
-        </is>
-      </c>
-      <c r="H10" s="107" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
       <c r="I10" s="108" t="n">
-        <v>0.6663</v>
+        <v>0.8262</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="K10" s="106" t="inlineStr">
-        <is>
-          <t>▲ +13.7%</t>
+        <v>1.0232</v>
+      </c>
+      <c r="K10" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Somalia</t>
+          <t xml:space="preserve">  7.  Senegal</t>
         </is>
       </c>
       <c r="B11" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C11" s="97" t="n">
-        <v>1.6</v>
+        <v>1.6391</v>
       </c>
       <c r="D11" s="98" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="E11" s="106" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G11" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Niger</t>
+          <t xml:space="preserve">  7.  Tunisia</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8262</v>
+        <v>0.8377</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>1.0232</v>
+        <v>0.7318</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Rwanda</t>
+          <t xml:space="preserve">  8.  Somalia</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
@@ -7682,42 +7682,42 @@
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.5742</v>
+        <v>1.6</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.5072</v>
+        <v>1.4</v>
       </c>
       <c r="E12" s="106" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G12" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Tunisia</t>
+          <t xml:space="preserve">  8.  Ghana</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8377</v>
+        <v>0.8471</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.7318</v>
-      </c>
-      <c r="K12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0892</v>
+      </c>
+      <c r="K12" s="110" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Uganda</t>
+          <t xml:space="preserve">  9.  Rwanda</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
@@ -7726,79 +7726,79 @@
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.4936</v>
+        <v>1.5742</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.4377</v>
+        <v>1.5072</v>
       </c>
       <c r="E13" s="106" t="inlineStr">
         <is>
-          <t>▲ +8.1%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G13" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Equatorial Guinea</t>
+          <t xml:space="preserve">  9.  Eswatini</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.9106</v>
+        <v>0.8625</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.8609</v>
-      </c>
-      <c r="K13" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8625</v>
+      </c>
+      <c r="K13" s="110" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Botswana</t>
+          <t xml:space="preserve">  10.  Uganda</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.4771</v>
+        <v>1.4768</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.8501</v>
+        <v>1.421</v>
       </c>
       <c r="E14" s="106" t="inlineStr">
         <is>
-          <t>▲ +29.3%</t>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="G14" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Liberia</t>
+          <t xml:space="preserve">  10.  Equatorial Guinea</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.9639</v>
+        <v>0.9106</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.9639</v>
-      </c>
-      <c r="K14" s="106" t="inlineStr">
-        <is>
-          <t>▲ +12.0%</t>
+        <v>0.8609</v>
+      </c>
+      <c r="K14" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,90 +7860,90 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.0871</v>
+        <v>1.2544</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.4424</v>
+        <v>0.5942</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>1.4222</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>2.2222</v>
+        <v>1.0871</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.2%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.8</v>
+        <v>0.4424</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.15</v>
+        <v>1.4222</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.6</v>
+        <v>2.2222</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +56.2%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
@@ -7953,183 +7953,183 @@
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.15</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.4096</v>
+        <v>1.6</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.348</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.0616</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.4771</v>
+        <v>1.4096</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +29.3%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.3346</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.0882</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.2739</v>
+        <v>1.3014</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +20.7%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2184</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0316</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.3014</v>
+        <v>1.2129</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.3691</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.2129</v>
+        <v>1.5742</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.2762</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.5742</v>
+        <v>1.4447</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +13.2%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1685</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
@@ -8139,28 +8139,28 @@
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.2831</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.6663</v>
+        <v>1.4487</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,28 +8170,28 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.2831</v>
+        <v>0.8608</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.4487</v>
+        <v>0.9639</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.9%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1656</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
@@ -8201,28 +8201,28 @@
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>0.8608</v>
+        <v>0.5861</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>0.9639</v>
+        <v>0.6521</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
@@ -8232,183 +8232,183 @@
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.1425</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.3736</v>
+        <v>1.2555</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.5244</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.4936</v>
+        <v>1.6391</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.1%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1117</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3819</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.4768</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>0.914</v>
+        <v>1.3479</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>0.9675</v>
+        <v>1.3699</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.8%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0535</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3681</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.3699</v>
+        <v>1.3873</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.022</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.4106</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.2961</v>
+        <v>1.4261</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +1.1%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0199</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,84 +8418,84 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3289</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.3377</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +0.7%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.4106</v>
+        <v>2.17</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.4261</v>
+        <v>2.1808</v>
       </c>
       <c r="F38" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G38" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.0555</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3377</v>
+        <v>1.0582</v>
       </c>
       <c r="F39" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.7%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="G39" s="117" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -8532,38 +8532,38 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.3986</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.0485</v>
+        <v>1.3661</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0237</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
@@ -8573,76 +8573,76 @@
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.784</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.3661</v>
+        <v>1.6851</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.784</v>
+        <v>1.2262</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.6851</v>
+        <v>1.1507</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0755</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.0641</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.1507</v>
+        <v>0.9982</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
@@ -8650,38 +8650,38 @@
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0755</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.0641</v>
+        <v>0.914</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.9982</v>
+        <v>0.8471</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -8749,125 +8749,156 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2332</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.0606</v>
+        <v>1.1154</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.1178</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.1939</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.0635</v>
+        <v>1.0606</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.2251</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>2.17</v>
+        <v>1.2886</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.2754</v>
+        <v>1.0635</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.2%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.8946</v>
+        <v>-0.2251</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
+          <t>Eswatini</t>
+        </is>
+      </c>
+      <c r="B51" s="54" t="inlineStr">
+        <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
+      <c r="C51" s="116" t="inlineStr">
+        <is>
+          <t>SZL</t>
+        </is>
+      </c>
+      <c r="D51" s="88" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="E51" s="91" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="F51" s="69" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
+        </is>
+      </c>
+      <c r="G51" s="119" t="n">
+        <v>-0.2097</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="62" t="inlineStr">
+        <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B51" s="54" t="inlineStr">
+      <c r="B52" s="63" t="inlineStr">
         <is>
           <t>North Africa</t>
         </is>
       </c>
-      <c r="C51" s="116" t="inlineStr">
+      <c r="C52" s="118" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
       </c>
-      <c r="D51" s="88" t="n">
+      <c r="D52" s="88" t="n">
         <v>0.4771</v>
       </c>
-      <c r="E51" s="91" t="n">
-        <v>0.2734</v>
-      </c>
-      <c r="F51" s="69" t="inlineStr">
-        <is>
-          <t>▼ -42.7%</t>
-        </is>
-      </c>
-      <c r="G51" s="119" t="n">
-        <v>-0.2037</v>
+      <c r="E52" s="89" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="F52" s="69" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
+        </is>
+      </c>
+      <c r="G52" s="119" t="n">
+        <v>-0.1391</v>
       </c>
     </row>
   </sheetData>
@@ -8924,16 +8955,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.63915</v>
+        <v>0.6746833333333334</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.6251000000000001</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.2961</v>
+        <v>1.4447</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9026,20 +9057,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.2734</v>
+        <v>0.338</v>
       </c>
       <c r="D7" s="66" t="n">
         <v>0.2684</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>13.75</v>
+        <v>17</v>
       </c>
       <c r="F7" s="67" t="n">
         <v>13.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -42.7%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9094,20 +9125,20 @@
         </is>
       </c>
       <c r="C9" s="66" t="n">
-        <v>1.2961</v>
+        <v>1.4447</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.2961</v>
+        <v>1.4447</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>13</v>
+        <v>14.49</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>13</v>
+        <v>14.49</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +13.2%</t>
         </is>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -9200,13 +9231,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.25105625</v>
+        <v>1.24264375</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.1836625</v>
+        <v>1.17979375</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>2.2222</v>
@@ -9404,20 +9435,20 @@
         </is>
       </c>
       <c r="C20" s="57" t="n">
-        <v>0.9675</v>
+        <v>0.8471</v>
       </c>
       <c r="D20" s="57" t="n">
-        <v>1.1369</v>
+        <v>1.0892</v>
       </c>
       <c r="E20" s="58" t="n">
-        <v>15.19</v>
+        <v>13.3</v>
       </c>
       <c r="F20" s="58" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="G20" s="71" t="inlineStr">
-        <is>
-          <t>▲ +5.8%</t>
+        <v>17.1</v>
+      </c>
+      <c r="G20" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="H20" s="61" t="inlineStr">
@@ -9676,20 +9707,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.6521</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1080</v>
+        <v>1057</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -10160,13 +10191,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.480833333333333</v>
+        <v>1.519326666666667</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.42272</v>
+        <v>1.46122</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.6602</v>
+        <v>1.0606</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10484,7 +10515,7 @@
       </c>
       <c r="H55" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -10636,20 +10667,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G60" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5700</v>
+      </c>
+      <c r="G60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">
@@ -10704,20 +10735,20 @@
         </is>
       </c>
       <c r="C62" s="57" t="n">
-        <v>1.4936</v>
+        <v>1.4768</v>
       </c>
       <c r="D62" s="57" t="n">
-        <v>1.4377</v>
+        <v>1.421</v>
       </c>
       <c r="E62" s="58" t="n">
-        <v>5350</v>
+        <v>5290</v>
       </c>
       <c r="F62" s="58" t="n">
-        <v>5150</v>
+        <v>5090</v>
       </c>
       <c r="G62" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.1%</t>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="H62" s="61" t="inlineStr">
@@ -10742,16 +10773,16 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.143388888888889</v>
+        <v>1.146044444444445</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.172866666666667</v>
+        <v>1.100455555555556</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
       </c>
       <c r="F65" s="153" t="n">
-        <v>1.4771</v>
+        <v>2.1808</v>
       </c>
       <c r="G65" s="150" t="n"/>
       <c r="H65" s="150" t="n"/>
@@ -10844,20 +10875,20 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>1.4771</v>
+        <v>1.2555</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>1.8501</v>
+        <v>1.3294</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>25.05</v>
+        <v>18</v>
       </c>
       <c r="G68" s="71" t="inlineStr">
         <is>
-          <t>▲ +29.3%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="H68" s="70" t="inlineStr">
@@ -10878,20 +10909,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="G69" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">
@@ -10980,25 +11011,25 @@
         </is>
       </c>
       <c r="C72" s="66" t="n">
-        <v>1.2739</v>
+        <v>1.0582</v>
       </c>
       <c r="D72" s="66" t="n">
-        <v>1.2792</v>
+        <v>1.0636</v>
       </c>
       <c r="E72" s="67" t="n">
-        <v>23.63</v>
+        <v>19.63</v>
       </c>
       <c r="F72" s="67" t="n">
-        <v>23.73</v>
+        <v>19.73</v>
       </c>
       <c r="G72" s="71" t="inlineStr">
         <is>
-          <t>▲ +20.7%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="H72" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -11014,20 +11045,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.1154</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.0181</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>25</v>
-      </c>
-      <c r="G73" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>18.53</v>
+      </c>
+      <c r="G73" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">
@@ -11082,20 +11113,20 @@
         </is>
       </c>
       <c r="C75" s="57" t="n">
-        <v>1.2754</v>
+        <v>2.1808</v>
       </c>
       <c r="D75" s="57" t="n">
-        <v>1.2754</v>
+        <v>1.9231</v>
       </c>
       <c r="E75" s="58" t="n">
-        <v>33.16</v>
+        <v>56.7</v>
       </c>
       <c r="F75" s="58" t="n">
-        <v>33.16</v>
-      </c>
-      <c r="G75" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.2%</t>
+        <v>50</v>
+      </c>
+      <c r="G75" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="H75" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-10</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-11</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.237</t>
+          <t>$1.209</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.185</t>
+          <t>$1.189</t>
         </is>
       </c>
     </row>
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6746833333333334</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6251000000000001</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,16 +1787,16 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.24264375</v>
+        <v>1.18256875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.17979375</v>
+        <v>1.1628875</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6521</v>
+        <v>0.3806</v>
       </c>
       <c r="G13" s="33" t="n">
-        <v>2.2222</v>
+        <v>1.6391</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.519326666666667</v>
+        <v>1.457393333333334</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.46122</v>
+        <v>1.43092</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>1.0606</v>
+        <v>0.7887</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.146044444444445</v>
+        <v>1.207566666666667</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.100455555555556</v>
+        <v>1.222011111111111</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-10</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-11</t>
         </is>
       </c>
     </row>
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.2%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="K7" s="70" t="inlineStr">
@@ -2632,23 +2632,23 @@
         </is>
       </c>
       <c r="E17" s="66" t="n">
-        <v>1.3377</v>
+        <v>1.3146</v>
       </c>
       <c r="F17" s="66" t="n">
-        <v>1.2583</v>
+        <v>1.1589</v>
       </c>
       <c r="G17" s="67" t="n">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="H17" s="67" t="n">
-        <v>760</v>
+        <v>700</v>
       </c>
       <c r="I17" s="68" t="n">
         <v>604</v>
       </c>
-      <c r="J17" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.7%</t>
+      <c r="J17" s="69" t="inlineStr">
+        <is>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="K17" s="70" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.3806</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.9254</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1057</v>
+        <v>617</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1057</v>
+        <v>1500</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
-      <c r="J23" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.3%</t>
+      <c r="J23" s="69" t="inlineStr">
+        <is>
+          <t>▼ -35.1%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3008,23 +3008,23 @@
         </is>
       </c>
       <c r="E25" s="66" t="n">
-        <v>2.2222</v>
+        <v>1.5556</v>
       </c>
       <c r="F25" s="66" t="n">
-        <v>2.2222</v>
+        <v>1.7778</v>
       </c>
       <c r="G25" s="67" t="n">
-        <v>50000</v>
+        <v>35000</v>
       </c>
       <c r="H25" s="67" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="I25" s="68" t="n">
         <v>22500</v>
       </c>
       <c r="J25" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.2%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="K25" s="70" t="inlineStr">
@@ -3492,13 +3492,13 @@
         </is>
       </c>
       <c r="E37" s="66" t="n">
-        <v>1.3699</v>
+        <v>0.7887</v>
       </c>
       <c r="F37" s="66" t="n">
         <v>1.3442</v>
       </c>
       <c r="G37" s="67" t="n">
-        <v>4000</v>
+        <v>2303</v>
       </c>
       <c r="H37" s="67" t="n">
         <v>3925</v>
@@ -3506,9 +3506,9 @@
       <c r="I37" s="68" t="n">
         <v>2920</v>
       </c>
-      <c r="J37" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.6%</t>
+      <c r="J37" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
         </is>
       </c>
       <c r="K37" s="70" t="inlineStr">
@@ -3774,23 +3774,23 @@
         </is>
       </c>
       <c r="E43" s="66" t="n">
-        <v>1.0606</v>
+        <v>1.0416</v>
       </c>
       <c r="F43" s="66" t="n">
-        <v>1.0087</v>
+        <v>1.0416</v>
       </c>
       <c r="G43" s="67" t="n">
-        <v>4900</v>
+        <v>4812</v>
       </c>
       <c r="H43" s="67" t="n">
-        <v>4660</v>
+        <v>4812</v>
       </c>
       <c r="I43" s="68" t="n">
         <v>4620</v>
       </c>
       <c r="J43" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -12.8%</t>
         </is>
       </c>
       <c r="K43" s="70" t="inlineStr">
@@ -3915,23 +3915,23 @@
         </is>
       </c>
       <c r="E46" s="57" t="n">
-        <v>1.5742</v>
+        <v>1.2454</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.5072</v>
+        <v>1.0198</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>2303</v>
+        <v>1822</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>2205</v>
+        <v>1492</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
       </c>
-      <c r="J46" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+      <c r="J46" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.0%</t>
         </is>
       </c>
       <c r="K46" s="61" t="inlineStr">
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>1.2555</v>
+        <v>1.551</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>1.3294</v>
+        <v>2.0679</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
       <c r="J54" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +35.8%</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.1154</v>
+        <v>1.3736</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.0181</v>
+        <v>1.3736</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>18.53</v>
+        <v>25</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+      <c r="J59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.236548148148148</v>
+        <v>1.209046296296296</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.185081481481481</v>
+        <v>1.189162962962963</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-10</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-11</t>
         </is>
       </c>
     </row>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="E8" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.2%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>▲ +26.0%</t>
+          <t>▲ +13.0%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -5343,29 +5343,29 @@
         <v>1.3289</v>
       </c>
       <c r="D18" s="91" t="n">
-        <v>1.3377</v>
-      </c>
-      <c r="E18" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.7%</t>
+        <v>1.3146</v>
+      </c>
+      <c r="E18" s="69" t="inlineStr">
+        <is>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="F18" s="90" t="n">
         <v>1.2693</v>
       </c>
       <c r="G18" s="91" t="n">
-        <v>1.2583</v>
+        <v>1.1589</v>
       </c>
       <c r="H18" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.9%</t>
+          <t>▼ -8.7%</t>
         </is>
       </c>
       <c r="I18" s="58" t="n">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="J18" s="58" t="n">
-        <v>760</v>
+        <v>700</v>
       </c>
       <c r="K18" s="61" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="E24" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.3%</t>
+        <v>0.3806</v>
+      </c>
+      <c r="E24" s="69" t="inlineStr">
+        <is>
+          <t>▼ -35.1%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="H24" s="69" t="inlineStr">
-        <is>
-          <t>▼ -11.9%</t>
+        <v>0.9254</v>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +25.0%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1057</v>
+        <v>617</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1057</v>
+        <v>1500</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -5703,29 +5703,29 @@
         <v>1.4222</v>
       </c>
       <c r="D26" s="91" t="n">
-        <v>2.2222</v>
+        <v>1.5556</v>
       </c>
       <c r="E26" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.2%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="F26" s="90" t="n">
         <v>1.5556</v>
       </c>
       <c r="G26" s="91" t="n">
-        <v>2.2222</v>
+        <v>1.7778</v>
       </c>
       <c r="H26" s="71" t="inlineStr">
         <is>
-          <t>▲ +42.9%</t>
+          <t>▲ +14.3%</t>
         </is>
       </c>
       <c r="I26" s="58" t="n">
-        <v>50000</v>
+        <v>35000</v>
       </c>
       <c r="J26" s="58" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="K26" s="61" t="inlineStr">
         <is>
@@ -6167,11 +6167,11 @@
         <v>1.3479</v>
       </c>
       <c r="D38" s="91" t="n">
-        <v>1.3699</v>
-      </c>
-      <c r="E38" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.6%</t>
+        <v>0.7887</v>
+      </c>
+      <c r="E38" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
         </is>
       </c>
       <c r="F38" s="90" t="n">
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="I38" s="58" t="n">
-        <v>4000</v>
+        <v>2303</v>
       </c>
       <c r="J38" s="58" t="n">
         <v>3925</v>
@@ -6437,29 +6437,29 @@
         <v>1.1939</v>
       </c>
       <c r="D44" s="91" t="n">
-        <v>1.0606</v>
+        <v>1.0416</v>
       </c>
       <c r="E44" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -12.8%</t>
         </is>
       </c>
       <c r="F44" s="90" t="n">
         <v>1.1199</v>
       </c>
       <c r="G44" s="91" t="n">
-        <v>1.0087</v>
+        <v>1.0416</v>
       </c>
       <c r="H44" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.9%</t>
+          <t>▼ -7.0%</t>
         </is>
       </c>
       <c r="I44" s="58" t="n">
-        <v>4900</v>
+        <v>4812</v>
       </c>
       <c r="J44" s="58" t="n">
-        <v>4660</v>
+        <v>4812</v>
       </c>
       <c r="K44" s="61" t="inlineStr">
         <is>
@@ -6572,29 +6572,29 @@
         <v>1.3691</v>
       </c>
       <c r="D47" s="89" t="n">
-        <v>1.5742</v>
-      </c>
-      <c r="E47" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+        <v>1.2454</v>
+      </c>
+      <c r="E47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.0%</t>
         </is>
       </c>
       <c r="F47" s="90" t="n">
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="H47" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.3%</t>
+        <v>1.0198</v>
+      </c>
+      <c r="H47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -24.0%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
-        <v>2303</v>
+        <v>1822</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>2205</v>
+        <v>1492</v>
       </c>
       <c r="K47" s="70" t="inlineStr">
         <is>
@@ -6894,29 +6894,29 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>1.2555</v>
+        <v>1.551</v>
       </c>
       <c r="E55" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +35.8%</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>1.3294</v>
+        <v>2.0679</v>
       </c>
       <c r="H55" s="71" t="inlineStr">
         <is>
-          <t>▲ +10.6%</t>
+          <t>▲ +72.0%</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.1154</v>
-      </c>
-      <c r="E60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="E60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.0181</v>
-      </c>
-      <c r="H60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -21.0%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="H60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>18.53</v>
+        <v>25</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7409,23 +7409,23 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Sierra Leone</t>
+          <t xml:space="preserve">  2.  Zimbabwe</t>
         </is>
       </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2.2222</v>
+        <v>2.1808</v>
       </c>
       <c r="D6" s="105" t="n">
-        <v>2.2222</v>
+        <v>1.9231</v>
       </c>
       <c r="E6" s="106" t="inlineStr">
         <is>
-          <t>▲ +56.2%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
@@ -7453,23 +7453,23 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Zimbabwe</t>
+          <t xml:space="preserve">  3.  Eritrea</t>
         </is>
       </c>
       <c r="B7" s="96" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C7" s="97" t="n">
-        <v>2.1808</v>
+        <v>2</v>
       </c>
       <c r="D7" s="98" t="n">
-        <v>1.9231</v>
-      </c>
-      <c r="E7" s="106" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+        <v>1.7333</v>
+      </c>
+      <c r="E7" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="95" t="inlineStr">
@@ -7497,19 +7497,19 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  Eritrea</t>
+          <t xml:space="preserve">  4.  CAR</t>
         </is>
       </c>
       <c r="B8" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C8" s="104" t="n">
-        <v>2</v>
+        <v>1.7384</v>
       </c>
       <c r="D8" s="105" t="n">
-        <v>1.7333</v>
+        <v>2.1523</v>
       </c>
       <c r="E8" s="99" t="inlineStr">
         <is>
@@ -7541,23 +7541,23 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  CAR</t>
+          <t xml:space="preserve">  5.  Comoros</t>
         </is>
       </c>
       <c r="B9" s="96" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C9" s="97" t="n">
-        <v>1.7384</v>
+        <v>1.6851</v>
       </c>
       <c r="D9" s="98" t="n">
-        <v>2.1523</v>
-      </c>
-      <c r="E9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.5078</v>
+      </c>
+      <c r="E9" s="110" t="inlineStr">
+        <is>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G9" s="114" t="inlineStr">
@@ -7571,98 +7571,98 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6521</v>
+        <v>0.3806</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="K9" s="106" t="inlineStr">
-        <is>
-          <t>▲ +11.3%</t>
+        <v>0.9254</v>
+      </c>
+      <c r="K9" s="110" t="inlineStr">
+        <is>
+          <t>▼ -35.1%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Comoros</t>
+          <t xml:space="preserve">  6.  Senegal</t>
         </is>
       </c>
       <c r="B10" s="103" t="inlineStr">
         <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="104" t="n">
+        <v>1.6391</v>
+      </c>
+      <c r="D10" s="105" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E10" s="106" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
+        </is>
+      </c>
+      <c r="G10" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Burundi</t>
+        </is>
+      </c>
+      <c r="H10" s="107" t="inlineStr">
+        <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n">
-        <v>1.6851</v>
-      </c>
-      <c r="D10" s="105" t="n">
-        <v>1.5078</v>
-      </c>
-      <c r="E10" s="110" t="inlineStr">
-        <is>
-          <t>▼ -5.5%</t>
-        </is>
-      </c>
-      <c r="G10" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Niger</t>
-        </is>
-      </c>
-      <c r="H10" s="107" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
       <c r="I10" s="108" t="n">
-        <v>0.8262</v>
+        <v>0.7887</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K10" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.3442</v>
+      </c>
+      <c r="K10" s="110" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Senegal</t>
+          <t xml:space="preserve">  7.  Somalia</t>
         </is>
       </c>
       <c r="B11" s="96" t="inlineStr">
         <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C11" s="97" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D11" s="98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E11" s="106" t="inlineStr">
+        <is>
+          <t>▲ +39.1%</t>
+        </is>
+      </c>
+      <c r="G11" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Niger</t>
+        </is>
+      </c>
+      <c r="H11" s="100" t="inlineStr">
+        <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C11" s="97" t="n">
-        <v>1.6391</v>
-      </c>
-      <c r="D11" s="98" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E11" s="106" t="inlineStr">
-        <is>
-          <t>▲ +7.5%</t>
-        </is>
-      </c>
-      <c r="G11" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Tunisia</t>
-        </is>
-      </c>
-      <c r="H11" s="100" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
       <c r="I11" s="101" t="n">
-        <v>0.8377</v>
+        <v>0.8262</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.7318</v>
+        <v>1.0232</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7673,88 +7673,88 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Somalia</t>
+          <t xml:space="preserve">  8.  Sierra Leone</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.6</v>
+        <v>1.5556</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.4</v>
+        <v>1.7778</v>
       </c>
       <c r="E12" s="106" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G12" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Ghana</t>
+          <t xml:space="preserve">  8.  Tunisia</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8471</v>
+        <v>0.8377</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K12" s="110" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Rwanda</t>
+          <t xml:space="preserve">  9.  Botswana</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5742</v>
+        <v>1.551</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.5072</v>
+        <v>2.0679</v>
       </c>
       <c r="E13" s="106" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +35.8%</t>
         </is>
       </c>
       <c r="G13" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Eswatini</t>
+          <t xml:space="preserve">  9.  Ghana</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8625</v>
+        <v>0.8471</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.8625</v>
+        <v>1.0892</v>
       </c>
       <c r="K13" s="110" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
@@ -7782,23 +7782,23 @@
       </c>
       <c r="G14" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Equatorial Guinea</t>
+          <t xml:space="preserve">  10.  Eswatini</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.9106</v>
+        <v>0.8625</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8609</v>
-      </c>
-      <c r="K14" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8625</v>
+      </c>
+      <c r="K14" s="110" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
@@ -7912,63 +7912,63 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.15</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>2.2222</v>
+        <v>1.6</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.2%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.15</v>
+        <v>1.1425</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.6</v>
+        <v>1.551</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +35.8%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.45</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -8067,100 +8067,100 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.2831</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.5742</v>
+        <v>1.4487</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.2762</v>
+        <v>0.8608</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.4447</v>
+        <v>0.9639</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.2%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1685</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.2831</v>
+        <v>1.2332</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.4487</v>
+        <v>1.3736</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.9%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1656</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,28 +8170,28 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.4222</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.5556</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
@@ -8201,121 +8201,121 @@
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.5244</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>0.6521</v>
+        <v>1.6391</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.066</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.3819</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.2555</v>
+        <v>1.4768</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.113</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.2762</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.6391</v>
+        <v>1.2961</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.3681</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.4768</v>
+        <v>1.3873</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.9%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0949</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,276 +8325,276 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.4106</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.3699</v>
+        <v>1.4261</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +1.1%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.022</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3681</v>
+        <v>2.17</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.3873</v>
+        <v>2.1808</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.0555</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.4261</v>
+        <v>1.0582</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.31</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3377</v>
-      </c>
-      <c r="F37" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.7%</t>
-        </is>
-      </c>
-      <c r="G37" s="117" t="n">
-        <v>0.008800000000000001</v>
+        <v>1.3037</v>
+      </c>
+      <c r="F37" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
+        </is>
+      </c>
+      <c r="G37" s="119" t="n">
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>2.17</v>
+        <v>1.3289</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>2.1808</v>
-      </c>
-      <c r="F38" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
-        </is>
-      </c>
-      <c r="G38" s="117" t="n">
-        <v>0.0108</v>
+        <v>1.3146</v>
+      </c>
+      <c r="F38" s="69" t="inlineStr">
+        <is>
+          <t>▼ -1.1%</t>
+        </is>
+      </c>
+      <c r="G38" s="119" t="n">
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3986</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.0582</v>
-      </c>
-      <c r="F39" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
-        </is>
-      </c>
-      <c r="G39" s="117" t="n">
-        <v>0.0027</v>
+        <v>1.3661</v>
+      </c>
+      <c r="F39" s="69" t="inlineStr">
+        <is>
+          <t>▼ -2.3%</t>
+        </is>
+      </c>
+      <c r="G39" s="119" t="n">
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.31</v>
+        <v>1.784</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3037</v>
+        <v>1.6851</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0063</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.2262</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.3661</v>
+        <v>1.1507</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0755</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.784</v>
+        <v>1.0641</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.6851</v>
+        <v>0.9982</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
@@ -8604,59 +8604,59 @@
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.2262</v>
+        <v>0.914</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.1507</v>
+        <v>0.8471</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0755</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.0671</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>0.9982</v>
+        <v>0.9851</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
@@ -8666,239 +8666,239 @@
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>0.914</v>
+        <v>1.2212</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.8471</v>
+        <v>1.1258</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.3691</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.9851</v>
+        <v>1.2454</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -9.0%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.1237</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.1939</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.1258</v>
+        <v>1.0416</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -12.8%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.1523</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.2886</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.1154</v>
+        <v>1.0635</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.6%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1178</v>
+        <v>-0.2251</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.0722</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.0606</v>
+        <v>0.8625</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.2886</v>
+        <v>0.4771</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.0635</v>
+        <v>0.338</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.2251</v>
+        <v>-0.1391</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.0722</v>
+        <v>0.5861</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.8625</v>
+        <v>0.3806</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -35.1%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.2055</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.3479</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.338</v>
+        <v>0.7887</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -41.5%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.1391</v>
+        <v>-0.5592</v>
       </c>
     </row>
   </sheetData>
@@ -8955,16 +8955,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6746833333333334</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6251000000000001</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9125,20 +9125,20 @@
         </is>
       </c>
       <c r="C9" s="66" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.4447</v>
+        <v>1.2961</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>14.49</v>
+        <v>13</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.2%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -9231,16 +9231,16 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.24264375</v>
+        <v>1.18256875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.17979375</v>
+        <v>1.1628875</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6521</v>
+        <v>0.3806</v>
       </c>
       <c r="F14" s="132" t="n">
-        <v>2.2222</v>
+        <v>1.6391</v>
       </c>
       <c r="G14" s="129" t="n"/>
       <c r="H14" s="129" t="n"/>
@@ -9503,20 +9503,20 @@
         </is>
       </c>
       <c r="C22" s="57" t="n">
-        <v>1.3377</v>
+        <v>1.3146</v>
       </c>
       <c r="D22" s="57" t="n">
-        <v>1.2583</v>
+        <v>1.1589</v>
       </c>
       <c r="E22" s="58" t="n">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="F22" s="58" t="n">
-        <v>760</v>
-      </c>
-      <c r="G22" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.7%</t>
+        <v>700</v>
+      </c>
+      <c r="G22" s="69" t="inlineStr">
+        <is>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="H22" s="61" t="inlineStr">
@@ -9707,20 +9707,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6521</v>
+        <v>0.3806</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6521</v>
+        <v>0.9254</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1057</v>
+        <v>617</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1057</v>
-      </c>
-      <c r="G28" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.3%</t>
+        <v>1500</v>
+      </c>
+      <c r="G28" s="69" t="inlineStr">
+        <is>
+          <t>▼ -35.1%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9775,20 +9775,20 @@
         </is>
       </c>
       <c r="C30" s="57" t="n">
-        <v>2.2222</v>
+        <v>1.5556</v>
       </c>
       <c r="D30" s="57" t="n">
-        <v>2.2222</v>
+        <v>1.7778</v>
       </c>
       <c r="E30" s="58" t="n">
-        <v>50000</v>
+        <v>35000</v>
       </c>
       <c r="F30" s="58" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="G30" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.2%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="H30" s="61" t="inlineStr">
@@ -10191,13 +10191,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.519326666666667</v>
+        <v>1.457393333333334</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.46122</v>
+        <v>1.43092</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>1.0606</v>
+        <v>0.7887</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10259,20 +10259,20 @@
         </is>
       </c>
       <c r="C48" s="57" t="n">
-        <v>1.3699</v>
+        <v>0.7887</v>
       </c>
       <c r="D48" s="57" t="n">
         <v>1.3442</v>
       </c>
       <c r="E48" s="58" t="n">
-        <v>4000</v>
+        <v>2303</v>
       </c>
       <c r="F48" s="58" t="n">
         <v>3925</v>
       </c>
-      <c r="G48" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.6%</t>
+      <c r="G48" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
         </is>
       </c>
       <c r="H48" s="61" t="inlineStr">
@@ -10463,20 +10463,20 @@
         </is>
       </c>
       <c r="C54" s="57" t="n">
-        <v>1.0606</v>
+        <v>1.0416</v>
       </c>
       <c r="D54" s="57" t="n">
-        <v>1.0087</v>
+        <v>1.0416</v>
       </c>
       <c r="E54" s="58" t="n">
-        <v>4900</v>
+        <v>4812</v>
       </c>
       <c r="F54" s="58" t="n">
-        <v>4660</v>
+        <v>4812</v>
       </c>
       <c r="G54" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -12.8%</t>
         </is>
       </c>
       <c r="H54" s="61" t="inlineStr">
@@ -10565,20 +10565,20 @@
         </is>
       </c>
       <c r="C57" s="66" t="n">
-        <v>1.5742</v>
+        <v>1.2454</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.5072</v>
+        <v>1.0198</v>
       </c>
       <c r="E57" s="67" t="n">
-        <v>2303</v>
+        <v>1822</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>2205</v>
-      </c>
-      <c r="G57" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+        <v>1492</v>
+      </c>
+      <c r="G57" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.0%</t>
         </is>
       </c>
       <c r="H57" s="70" t="inlineStr">
@@ -10773,10 +10773,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.146044444444445</v>
+        <v>1.207566666666667</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.100455555555556</v>
+        <v>1.222011111111111</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10875,20 +10875,20 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>1.2555</v>
+        <v>1.551</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>1.3294</v>
+        <v>2.0679</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G68" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +35.8%</t>
         </is>
       </c>
       <c r="H68" s="70" t="inlineStr">
@@ -11045,20 +11045,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.1154</v>
+        <v>1.3736</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.0181</v>
+        <v>1.3736</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="G73" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+        <v>25</v>
+      </c>
+      <c r="G73" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-11</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-12</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.209</t>
+          <t>$1.187</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+90.0%</t>
+          <t>+68.6%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.189</t>
+          <t>$1.153</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.18256875</v>
+        <v>1.2074</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.1628875</v>
+        <v>1.15324375</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.3806</v>
+        <v>0.7779</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2173625</v>
+        <v>1.17085</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1930875</v>
+        <v>1.1611125</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.457393333333334</v>
+        <v>1.440966666666667</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.43092</v>
+        <v>1.425066666666666</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.7887</v>
+        <v>0.6602</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.207566666666667</v>
+        <v>1.099988888888889</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.222011111111111</v>
+        <v>1.060788888888889</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-11</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-12</t>
         </is>
       </c>
     </row>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.3806</v>
+        <v>0.7779</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.9254</v>
+        <v>0.7711</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>617</v>
+        <v>1261</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
-      <c r="J23" s="69" t="inlineStr">
-        <is>
-          <t>▼ -35.1%</t>
+      <c r="J23" s="71" t="inlineStr">
+        <is>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>1.3023</v>
+        <v>0.9302</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>1.186</v>
+        <v>0.9302</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -3774,23 +3774,23 @@
         </is>
       </c>
       <c r="E43" s="66" t="n">
-        <v>1.0416</v>
+        <v>1.0606</v>
       </c>
       <c r="F43" s="66" t="n">
-        <v>1.0416</v>
+        <v>1.0606</v>
       </c>
       <c r="G43" s="67" t="n">
-        <v>4812</v>
+        <v>4900</v>
       </c>
       <c r="H43" s="67" t="n">
-        <v>4812</v>
+        <v>4900</v>
       </c>
       <c r="I43" s="68" t="n">
         <v>4620</v>
       </c>
       <c r="J43" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.8%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="K43" s="70" t="inlineStr">
@@ -3915,23 +3915,23 @@
         </is>
       </c>
       <c r="E46" s="57" t="n">
-        <v>1.2454</v>
+        <v>1.5742</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.0198</v>
+        <v>1.5072</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>1822</v>
+        <v>2303</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>1492</v>
+        <v>2205</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
       </c>
-      <c r="J46" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.0%</t>
+      <c r="J46" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="K46" s="61" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+      <c r="J49" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>1.551</v>
+        <v>1.2555</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>2.0679</v>
+        <v>1.3294</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
       <c r="J54" s="71" t="inlineStr">
         <is>
-          <t>▲ +35.8%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4392,23 +4392,23 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>1.3037</v>
+        <v>0.8892</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>1.2462</v>
+        <v>0.8892</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>83.56999999999999</v>
+        <v>57</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>79.88</v>
+        <v>57</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="J57" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -32.1%</t>
         </is>
       </c>
       <c r="K57" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.1154</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.0181</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>25</v>
+        <v>18.53</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+      <c r="J59" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.209046296296296</v>
+        <v>1.18702037037037</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.189162962962963</v>
+        <v>1.153072222222222</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-11</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-12</t>
         </is>
       </c>
     </row>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.3806</v>
-      </c>
-      <c r="E24" s="69" t="inlineStr">
-        <is>
-          <t>▼ -35.1%</t>
+        <v>0.7779</v>
+      </c>
+      <c r="E24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.9254</v>
+        <v>0.7711</v>
       </c>
       <c r="H24" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.0%</t>
+          <t>▲ +4.2%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>617</v>
+        <v>1261</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>1.3023</v>
-      </c>
-      <c r="E36" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9302</v>
+      </c>
+      <c r="E36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>1.186</v>
-      </c>
-      <c r="H36" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9302</v>
+      </c>
+      <c r="H36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -21.6%</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -6437,29 +6437,29 @@
         <v>1.1939</v>
       </c>
       <c r="D44" s="91" t="n">
-        <v>1.0416</v>
+        <v>1.0606</v>
       </c>
       <c r="E44" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.8%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="F44" s="90" t="n">
         <v>1.1199</v>
       </c>
       <c r="G44" s="91" t="n">
-        <v>1.0416</v>
+        <v>1.0606</v>
       </c>
       <c r="H44" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.0%</t>
+          <t>▼ -5.3%</t>
         </is>
       </c>
       <c r="I44" s="58" t="n">
-        <v>4812</v>
+        <v>4900</v>
       </c>
       <c r="J44" s="58" t="n">
-        <v>4812</v>
+        <v>4900</v>
       </c>
       <c r="K44" s="61" t="inlineStr">
         <is>
@@ -6572,29 +6572,29 @@
         <v>1.3691</v>
       </c>
       <c r="D47" s="89" t="n">
-        <v>1.2454</v>
-      </c>
-      <c r="E47" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.0%</t>
+        <v>1.5742</v>
+      </c>
+      <c r="E47" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="F47" s="90" t="n">
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.0198</v>
-      </c>
-      <c r="H47" s="69" t="inlineStr">
-        <is>
-          <t>▼ -24.0%</t>
+        <v>1.5072</v>
+      </c>
+      <c r="H47" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.3%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
-        <v>1822</v>
+        <v>2303</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>1492</v>
+        <v>2205</v>
       </c>
       <c r="K47" s="70" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>1.2544</v>
-      </c>
-      <c r="E50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="E50" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>1.2544</v>
-      </c>
-      <c r="H50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="H50" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -6894,29 +6894,29 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>1.551</v>
+        <v>1.2555</v>
       </c>
       <c r="E55" s="71" t="inlineStr">
         <is>
-          <t>▲ +35.8%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>2.0679</v>
+        <v>1.3294</v>
       </c>
       <c r="H55" s="71" t="inlineStr">
         <is>
-          <t>▲ +72.0%</t>
+          <t>▲ +10.6%</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>1.3037</v>
+        <v>0.8892</v>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -32.1%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>1.2462</v>
+        <v>0.8892</v>
       </c>
       <c r="H58" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.3%</t>
+          <t>▼ -28.9%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>83.56999999999999</v>
+        <v>57</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>79.88</v>
+        <v>57</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="E60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>1.1154</v>
+      </c>
+      <c r="E60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="H60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+        <v>1.0181</v>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -21.0%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>25</v>
+        <v>18.53</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7562,23 +7562,23 @@
       </c>
       <c r="G9" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Nigeria</t>
+          <t xml:space="preserve">  5.  South Sudan</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.3806</v>
+        <v>0.6602</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.9254</v>
-      </c>
-      <c r="K9" s="110" t="inlineStr">
-        <is>
-          <t>▼ -35.1%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="K9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7606,23 +7606,23 @@
       </c>
       <c r="G10" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Burundi</t>
+          <t xml:space="preserve">  6.  Nigeria</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.7887</v>
+        <v>0.7779</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>1.3442</v>
-      </c>
-      <c r="K10" s="110" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
+        <v>0.7711</v>
+      </c>
+      <c r="K10" s="106" t="inlineStr">
+        <is>
+          <t>▲ +32.7%</t>
         </is>
       </c>
     </row>
@@ -7650,63 +7650,63 @@
       </c>
       <c r="G11" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Niger</t>
+          <t xml:space="preserve">  7.  Burundi</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8262</v>
+        <v>0.7887</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K11" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.3442</v>
+      </c>
+      <c r="K11" s="110" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Sierra Leone</t>
+          <t xml:space="preserve">  8.  Rwanda</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
         <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C12" s="104" t="n">
+        <v>1.5742</v>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>1.5072</v>
+      </c>
+      <c r="E12" s="106" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Niger</t>
+        </is>
+      </c>
+      <c r="H12" s="107" t="inlineStr">
+        <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C12" s="104" t="n">
-        <v>1.5556</v>
-      </c>
-      <c r="D12" s="105" t="n">
-        <v>1.7778</v>
-      </c>
-      <c r="E12" s="106" t="inlineStr">
-        <is>
-          <t>▲ +9.4%</t>
-        </is>
-      </c>
-      <c r="G12" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Tunisia</t>
-        </is>
-      </c>
-      <c r="H12" s="107" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
       <c r="I12" s="108" t="n">
-        <v>0.8377</v>
+        <v>0.8262</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.7318</v>
+        <v>1.0232</v>
       </c>
       <c r="K12" s="99" t="inlineStr">
         <is>
@@ -7717,44 +7717,44 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Botswana</t>
+          <t xml:space="preserve">  9.  Sierra Leone</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.551</v>
+        <v>1.5556</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>2.0679</v>
+        <v>1.7778</v>
       </c>
       <c r="E13" s="106" t="inlineStr">
         <is>
-          <t>▲ +35.8%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G13" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Ghana</t>
+          <t xml:space="preserve">  9.  Tunisia</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8471</v>
+        <v>0.8377</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K13" s="110" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K13" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7782,23 +7782,23 @@
       </c>
       <c r="G14" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Eswatini</t>
+          <t xml:space="preserve">  10.  Ghana</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.8625</v>
+        <v>0.8471</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8625</v>
+        <v>1.0892</v>
       </c>
       <c r="K14" s="110" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,28 +7860,28 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6602</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.2544</v>
+        <v>1.0871</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.5942</v>
+        <v>0.4424</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
@@ -7891,28 +7891,28 @@
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.0871</v>
+        <v>1.6</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.4424</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
@@ -7922,146 +7922,146 @@
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.15</v>
+        <v>1.0616</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.6</v>
+        <v>1.4096</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.45</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.1425</v>
+        <v>0.5861</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.551</v>
+        <v>0.7779</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +35.8%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.4085</v>
+        <v>0.1918</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.0882</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.4096</v>
+        <v>1.3014</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.348</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0316</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.3014</v>
+        <v>1.2129</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.3691</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.2129</v>
+        <v>1.5742</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -8129,7 +8129,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
@@ -8139,22 +8139,22 @@
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.1425</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.3736</v>
+        <v>1.2555</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -8408,69 +8408,69 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.31</v>
+        <v>1.3289</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3037</v>
+        <v>1.3146</v>
       </c>
       <c r="F37" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G37" s="119" t="n">
-        <v>-0.0063</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.3986</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3146</v>
+        <v>1.3661</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
@@ -8480,76 +8480,76 @@
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.784</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3661</v>
+        <v>1.6851</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.784</v>
+        <v>1.2262</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.6851</v>
+        <v>1.1507</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0755</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.0641</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.1507</v>
+        <v>0.9982</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
@@ -8557,137 +8557,137 @@
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0755</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.0641</v>
+        <v>0.914</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>0.9982</v>
+        <v>0.8471</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>0.914</v>
+        <v>1.0671</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>0.8471</v>
+        <v>0.9851</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.2212</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>0.9851</v>
+        <v>1.1258</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.2332</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>1.1258</v>
+        <v>1.1154</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.1178</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
@@ -8697,115 +8697,115 @@
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.1939</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>1.2454</v>
+        <v>1.0606</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.0%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.1237</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2886</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.0416</v>
+        <v>1.0635</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.8%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.1523</v>
+        <v>-0.2251</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.0722</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.0635</v>
+        <v>0.8625</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.2251</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Sao Tome</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>STN</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.3023</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>0.8625</v>
+        <v>0.9302</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.3721</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -8842,32 +8842,32 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.31</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.3806</v>
+        <v>0.8892</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -35.1%</t>
+          <t>▼ -32.1%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.2055</v>
+        <v>-0.4208</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -9231,13 +9231,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.18256875</v>
+        <v>1.2074</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.1628875</v>
+        <v>1.15324375</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.3806</v>
+        <v>0.7779</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9707,20 +9707,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.3806</v>
+        <v>0.7779</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.9254</v>
+        <v>0.7711</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>617</v>
+        <v>1261</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G28" s="69" t="inlineStr">
-        <is>
-          <t>▼ -35.1%</t>
+        <v>1250</v>
+      </c>
+      <c r="G28" s="71" t="inlineStr">
+        <is>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9847,10 +9847,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2173625</v>
+        <v>1.17085</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1930875</v>
+        <v>1.1611125</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10153,20 +10153,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>1.3023</v>
+        <v>0.9302</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>1.186</v>
+        <v>0.9302</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G43" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>20</v>
+      </c>
+      <c r="G43" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">
@@ -10191,13 +10191,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.457393333333334</v>
+        <v>1.440966666666667</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.43092</v>
+        <v>1.425066666666666</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.7887</v>
+        <v>0.6602</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10463,20 +10463,20 @@
         </is>
       </c>
       <c r="C54" s="57" t="n">
-        <v>1.0416</v>
+        <v>1.0606</v>
       </c>
       <c r="D54" s="57" t="n">
-        <v>1.0416</v>
+        <v>1.0606</v>
       </c>
       <c r="E54" s="58" t="n">
-        <v>4812</v>
+        <v>4900</v>
       </c>
       <c r="F54" s="58" t="n">
-        <v>4812</v>
+        <v>4900</v>
       </c>
       <c r="G54" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.8%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="H54" s="61" t="inlineStr">
@@ -10565,20 +10565,20 @@
         </is>
       </c>
       <c r="C57" s="66" t="n">
-        <v>1.2454</v>
+        <v>1.5742</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.0198</v>
+        <v>1.5072</v>
       </c>
       <c r="E57" s="67" t="n">
-        <v>1822</v>
+        <v>2303</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>1492</v>
-      </c>
-      <c r="G57" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.0%</t>
+        <v>2205</v>
+      </c>
+      <c r="G57" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="H57" s="70" t="inlineStr">
@@ -10667,20 +10667,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>3000</v>
+      </c>
+      <c r="G60" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">
@@ -10773,10 +10773,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.207566666666667</v>
+        <v>1.099988888888889</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.222011111111111</v>
+        <v>1.060788888888889</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10875,20 +10875,20 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>1.551</v>
+        <v>1.2555</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>2.0679</v>
+        <v>1.3294</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G68" s="71" t="inlineStr">
         <is>
-          <t>▲ +35.8%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="H68" s="70" t="inlineStr">
@@ -10977,20 +10977,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>1.3037</v>
+        <v>0.8892</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>1.2462</v>
+        <v>0.8892</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>83.56999999999999</v>
+        <v>57</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>79.88</v>
+        <v>57</v>
       </c>
       <c r="G71" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -32.1%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">
@@ -11045,20 +11045,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.1154</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.0181</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>25</v>
-      </c>
-      <c r="G73" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>18.53</v>
+      </c>
+      <c r="G73" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1073,29 +1073,29 @@
     <xf numFmtId="164" fontId="19" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-12</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-13</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.187</t>
+          <t>$1.200</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+68.6%</t>
+          <t>+90.0%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.153</t>
+          <t>$1.169</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.17085</v>
+        <v>1.1809875</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1611125</v>
+        <v>1.15925</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.440966666666667</v>
+        <v>1.485293333333334</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.425066666666666</v>
+        <v>1.465926666666667</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.6602</v>
+        <v>0.7887</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,16 +1853,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.099988888888889</v>
+        <v>1.0948</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.060788888888889</v>
+        <v>1.091055555555555</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>2.1808</v>
+        <v>1.3736</v>
       </c>
     </row>
     <row r="18" ht="10" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-12</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+      <c r="J34" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -3777,13 +3777,13 @@
         <v>1.0606</v>
       </c>
       <c r="F43" s="66" t="n">
-        <v>1.0606</v>
+        <v>1.0087</v>
       </c>
       <c r="G43" s="67" t="n">
         <v>4900</v>
       </c>
       <c r="H43" s="67" t="n">
-        <v>4900</v>
+        <v>4660</v>
       </c>
       <c r="I43" s="68" t="n">
         <v>4620</v>
@@ -3962,23 +3962,23 @@
         </is>
       </c>
       <c r="E47" s="66" t="n">
-        <v>1.4261</v>
+        <v>1.4968</v>
       </c>
       <c r="F47" s="66" t="n">
-        <v>1.4269</v>
+        <v>1.4975</v>
       </c>
       <c r="G47" s="67" t="n">
-        <v>20.18</v>
+        <v>21.18</v>
       </c>
       <c r="H47" s="67" t="n">
-        <v>20.19</v>
+        <v>21.19</v>
       </c>
       <c r="I47" s="68" t="n">
         <v>14.15</v>
       </c>
       <c r="J47" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="K47" s="70" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J49" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
       <c r="J55" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="K55" s="70" t="inlineStr">
@@ -4392,23 +4392,23 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>0.8892</v>
+        <v>1.3037</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>0.8892</v>
+        <v>1.2462</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>57</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>57</v>
+        <v>79.88</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="J57" s="69" t="inlineStr">
         <is>
-          <t>▼ -32.1%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="K57" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.1154</v>
+        <v>1.3736</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.0181</v>
+        <v>1.3736</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>18.53</v>
+        <v>25</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+      <c r="J59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4580,23 +4580,23 @@
         </is>
       </c>
       <c r="E61" s="66" t="n">
-        <v>2.1808</v>
+        <v>1.2754</v>
       </c>
       <c r="F61" s="66" t="n">
-        <v>1.9231</v>
+        <v>1.2754</v>
       </c>
       <c r="G61" s="67" t="n">
-        <v>56.7</v>
+        <v>33.16</v>
       </c>
       <c r="H61" s="67" t="n">
-        <v>50</v>
+        <v>33.16</v>
       </c>
       <c r="I61" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="J61" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+      <c r="J61" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.2%</t>
         </is>
       </c>
       <c r="K61" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.18702037037037</v>
+        <v>1.19997037037037</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.153072222222222</v>
+        <v>1.16919074074074</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-12</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-13</t>
         </is>
       </c>
     </row>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="E35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>1.0662</v>
+      </c>
+      <c r="E35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9685</v>
-      </c>
-      <c r="H35" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.5%</t>
+        <v>0.9536</v>
+      </c>
+      <c r="H35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6448,18 +6448,18 @@
         <v>1.1199</v>
       </c>
       <c r="G44" s="91" t="n">
-        <v>1.0606</v>
+        <v>1.0087</v>
       </c>
       <c r="H44" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.3%</t>
+          <t>▼ -9.9%</t>
         </is>
       </c>
       <c r="I44" s="58" t="n">
         <v>4900</v>
       </c>
       <c r="J44" s="58" t="n">
-        <v>4900</v>
+        <v>4660</v>
       </c>
       <c r="K44" s="61" t="inlineStr">
         <is>
@@ -6617,29 +6617,29 @@
         <v>1.4106</v>
       </c>
       <c r="D48" s="91" t="n">
-        <v>1.4261</v>
+        <v>1.4968</v>
       </c>
       <c r="E48" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="F48" s="90" t="n">
         <v>1.33</v>
       </c>
       <c r="G48" s="91" t="n">
-        <v>1.4269</v>
+        <v>1.4975</v>
       </c>
       <c r="H48" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.3%</t>
+          <t>▲ +12.6%</t>
         </is>
       </c>
       <c r="I48" s="58" t="n">
-        <v>20.18</v>
+        <v>21.18</v>
       </c>
       <c r="J48" s="58" t="n">
-        <v>20.19</v>
+        <v>21.19</v>
       </c>
       <c r="K48" s="61" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="E50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="E50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="H50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="H50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="H56" s="69" t="inlineStr">
         <is>
-          <t>▼ -24.8%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>0.8892</v>
+        <v>1.3037</v>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>▼ -32.1%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>0.8892</v>
+        <v>1.2462</v>
       </c>
       <c r="H58" s="69" t="inlineStr">
         <is>
-          <t>▼ -28.9%</t>
+          <t>▼ -0.3%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>57</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>57</v>
+        <v>79.88</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.1154</v>
-      </c>
-      <c r="E60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="E60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.0181</v>
-      </c>
-      <c r="H60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -21.0%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="H60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>18.53</v>
+        <v>25</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7209,29 +7209,29 @@
         <v>2.17</v>
       </c>
       <c r="D62" s="91" t="n">
-        <v>2.1808</v>
-      </c>
-      <c r="E62" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+        <v>1.2754</v>
+      </c>
+      <c r="E62" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.2%</t>
         </is>
       </c>
       <c r="F62" s="90" t="n">
         <v>2.05</v>
       </c>
       <c r="G62" s="91" t="n">
-        <v>1.9231</v>
+        <v>1.2754</v>
       </c>
       <c r="H62" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -37.8%</t>
         </is>
       </c>
       <c r="I62" s="58" t="n">
-        <v>56.7</v>
+        <v>33.16</v>
       </c>
       <c r="J62" s="58" t="n">
-        <v>50</v>
+        <v>33.16</v>
       </c>
       <c r="K62" s="61" t="inlineStr">
         <is>
@@ -7409,39 +7409,39 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Zimbabwe</t>
+          <t xml:space="preserve">  2.  Eritrea</t>
         </is>
       </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C6" s="104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="105" t="n">
+        <v>1.7333</v>
+      </c>
+      <c r="E6" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2.  Angola</t>
+        </is>
+      </c>
+      <c r="H6" s="106" t="inlineStr">
+        <is>
           <t>Southern Africa</t>
         </is>
       </c>
-      <c r="C6" s="104" t="n">
-        <v>2.1808</v>
-      </c>
-      <c r="D6" s="105" t="n">
-        <v>1.9231</v>
-      </c>
-      <c r="E6" s="106" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
-        </is>
-      </c>
-      <c r="G6" s="95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2.  Angola</t>
-        </is>
-      </c>
-      <c r="H6" s="107" t="inlineStr">
-        <is>
-          <t>Southern Africa</t>
-        </is>
-      </c>
-      <c r="I6" s="108" t="n">
+      <c r="I6" s="107" t="n">
         <v>0.3272</v>
       </c>
-      <c r="J6" s="109" t="n">
+      <c r="J6" s="108" t="n">
         <v>0.2181</v>
       </c>
       <c r="K6" s="99" t="inlineStr">
@@ -7453,19 +7453,19 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Eritrea</t>
+          <t xml:space="preserve">  3.  CAR</t>
         </is>
       </c>
       <c r="B7" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C7" s="97" t="n">
-        <v>2</v>
+        <v>1.7384</v>
       </c>
       <c r="D7" s="98" t="n">
-        <v>1.7333</v>
+        <v>2.1523</v>
       </c>
       <c r="E7" s="99" t="inlineStr">
         <is>
@@ -7488,278 +7488,278 @@
       <c r="J7" s="102" t="n">
         <v>0.2684</v>
       </c>
-      <c r="K7" s="110" t="inlineStr">
+      <c r="K7" s="109" t="inlineStr">
         <is>
           <t>▼ -29.2%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  CAR</t>
+      <c r="A8" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Comoros</t>
         </is>
       </c>
       <c r="B8" s="103" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C8" s="104" t="n">
-        <v>1.7384</v>
+        <v>1.6851</v>
       </c>
       <c r="D8" s="105" t="n">
-        <v>2.1523</v>
-      </c>
-      <c r="E8" s="99" t="inlineStr">
+        <v>1.5078</v>
+      </c>
+      <c r="E8" s="109" t="inlineStr">
+        <is>
+          <t>▼ -5.5%</t>
+        </is>
+      </c>
+      <c r="G8" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Algeria</t>
+        </is>
+      </c>
+      <c r="H8" s="106" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="I8" s="107" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="J8" s="108" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="K8" s="99" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Algeria</t>
-        </is>
-      </c>
-      <c r="H8" s="107" t="inlineStr">
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Senegal</t>
+        </is>
+      </c>
+      <c r="B9" s="96" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="C9" s="97" t="n">
+        <v>1.6391</v>
+      </c>
+      <c r="D9" s="98" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E9" s="113" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
+        </is>
+      </c>
+      <c r="G9" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Nigeria</t>
+        </is>
+      </c>
+      <c r="H9" s="100" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="I9" s="101" t="n">
+        <v>0.7779</v>
+      </c>
+      <c r="J9" s="102" t="n">
+        <v>0.7711</v>
+      </c>
+      <c r="K9" s="113" t="inlineStr">
+        <is>
+          <t>▲ +32.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Somalia</t>
+        </is>
+      </c>
+      <c r="B10" s="103" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="104" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D10" s="105" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E10" s="113" t="inlineStr">
+        <is>
+          <t>▲ +39.1%</t>
+        </is>
+      </c>
+      <c r="G10" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Burundi</t>
+        </is>
+      </c>
+      <c r="H10" s="106" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="I10" s="107" t="n">
+        <v>0.7887</v>
+      </c>
+      <c r="J10" s="108" t="n">
+        <v>1.3442</v>
+      </c>
+      <c r="K10" s="109" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Rwanda</t>
+        </is>
+      </c>
+      <c r="B11" s="96" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C11" s="97" t="n">
+        <v>1.5742</v>
+      </c>
+      <c r="D11" s="98" t="n">
+        <v>1.5072</v>
+      </c>
+      <c r="E11" s="113" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
+        </is>
+      </c>
+      <c r="G11" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Niger</t>
+        </is>
+      </c>
+      <c r="H11" s="100" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="I11" s="101" t="n">
+        <v>0.8262</v>
+      </c>
+      <c r="J11" s="102" t="n">
+        <v>1.0232</v>
+      </c>
+      <c r="K11" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Sierra Leone</t>
+        </is>
+      </c>
+      <c r="B12" s="103" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="C12" s="104" t="n">
+        <v>1.5556</v>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>1.7778</v>
+      </c>
+      <c r="E12" s="113" t="inlineStr">
+        <is>
+          <t>▲ +9.4%</t>
+        </is>
+      </c>
+      <c r="G12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Tunisia</t>
+        </is>
+      </c>
+      <c r="H12" s="106" t="inlineStr">
         <is>
           <t>North Africa</t>
         </is>
       </c>
-      <c r="I8" s="108" t="n">
-        <v>0.3494</v>
-      </c>
-      <c r="J8" s="109" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K8" s="99" t="inlineStr">
+      <c r="I12" s="107" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="J12" s="108" t="n">
+        <v>0.7318</v>
+      </c>
+      <c r="K12" s="99" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Comoros</t>
-        </is>
-      </c>
-      <c r="B9" s="96" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Seychelles</t>
+        </is>
+      </c>
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C9" s="97" t="n">
-        <v>1.6851</v>
-      </c>
-      <c r="D9" s="98" t="n">
-        <v>1.5078</v>
-      </c>
-      <c r="E9" s="110" t="inlineStr">
-        <is>
-          <t>▼ -5.5%</t>
-        </is>
-      </c>
-      <c r="G9" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  South Sudan</t>
-        </is>
-      </c>
-      <c r="H9" s="100" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="I9" s="101" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="J9" s="102" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="K9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Senegal</t>
-        </is>
-      </c>
-      <c r="B10" s="103" t="inlineStr">
+      <c r="C13" s="97" t="n">
+        <v>1.4968</v>
+      </c>
+      <c r="D13" s="98" t="n">
+        <v>1.4975</v>
+      </c>
+      <c r="E13" s="113" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
+        </is>
+      </c>
+      <c r="G13" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Ghana</t>
+        </is>
+      </c>
+      <c r="H13" s="100" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n">
-        <v>1.6391</v>
-      </c>
-      <c r="D10" s="105" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E10" s="106" t="inlineStr">
-        <is>
-          <t>▲ +7.5%</t>
-        </is>
-      </c>
-      <c r="G10" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Nigeria</t>
-        </is>
-      </c>
-      <c r="H10" s="107" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="I10" s="108" t="n">
-        <v>0.7779</v>
-      </c>
-      <c r="J10" s="109" t="n">
-        <v>0.7711</v>
-      </c>
-      <c r="K10" s="106" t="inlineStr">
-        <is>
-          <t>▲ +32.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Somalia</t>
-        </is>
-      </c>
-      <c r="B11" s="96" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="C11" s="97" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D11" s="98" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E11" s="106" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
-        </is>
-      </c>
-      <c r="G11" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Burundi</t>
-        </is>
-      </c>
-      <c r="H11" s="100" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="I11" s="101" t="n">
-        <v>0.7887</v>
-      </c>
-      <c r="J11" s="102" t="n">
-        <v>1.3442</v>
-      </c>
-      <c r="K11" s="110" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Rwanda</t>
-        </is>
-      </c>
-      <c r="B12" s="103" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="C12" s="104" t="n">
-        <v>1.5742</v>
-      </c>
-      <c r="D12" s="105" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="E12" s="106" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
-        </is>
-      </c>
-      <c r="G12" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Niger</t>
-        </is>
-      </c>
-      <c r="H12" s="107" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="I12" s="108" t="n">
-        <v>0.8262</v>
-      </c>
-      <c r="J12" s="109" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Sierra Leone</t>
-        </is>
-      </c>
-      <c r="B13" s="96" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="C13" s="97" t="n">
-        <v>1.5556</v>
-      </c>
-      <c r="D13" s="98" t="n">
-        <v>1.7778</v>
-      </c>
-      <c r="E13" s="106" t="inlineStr">
-        <is>
-          <t>▲ +9.4%</t>
-        </is>
-      </c>
-      <c r="G13" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Tunisia</t>
-        </is>
-      </c>
-      <c r="H13" s="100" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
       <c r="I13" s="101" t="n">
-        <v>0.8377</v>
+        <v>0.8471</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.7318</v>
-      </c>
-      <c r="K13" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0892</v>
+      </c>
+      <c r="K13" s="109" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="111" t="inlineStr">
+      <c r="A14" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Uganda</t>
         </is>
@@ -7775,30 +7775,30 @@
       <c r="D14" s="105" t="n">
         <v>1.421</v>
       </c>
-      <c r="E14" s="106" t="inlineStr">
+      <c r="E14" s="113" t="inlineStr">
         <is>
           <t>▲ +6.9%</t>
         </is>
       </c>
-      <c r="G14" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Ghana</t>
-        </is>
-      </c>
-      <c r="H14" s="107" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="I14" s="108" t="n">
-        <v>0.8471</v>
-      </c>
-      <c r="J14" s="109" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K14" s="110" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+      <c r="G14" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Equatorial Guinea</t>
+        </is>
+      </c>
+      <c r="H14" s="106" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="I14" s="107" t="n">
+        <v>0.9106</v>
+      </c>
+      <c r="J14" s="108" t="n">
+        <v>0.8609</v>
+      </c>
+      <c r="K14" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,28 +7860,28 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.0871</v>
+        <v>1.2544</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.4424</v>
+        <v>0.5942</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
@@ -7891,28 +7891,28 @@
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>1.15</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.6</v>
+        <v>1.0871</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.45</v>
+        <v>0.4424</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
@@ -7922,59 +7922,59 @@
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.15</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.4096</v>
+        <v>1.6</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.348</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0616</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>0.7779</v>
+        <v>1.4096</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.1918</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
@@ -7984,121 +7984,121 @@
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0882</v>
+        <v>0.5861</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.3014</v>
+        <v>0.7779</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.1918</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.0882</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.2129</v>
+        <v>1.3014</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.0316</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.5742</v>
+        <v>1.2129</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.2831</v>
+        <v>1.3691</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.4487</v>
+        <v>1.5742</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.9%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1656</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
@@ -8108,208 +8108,208 @@
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.2831</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.4487</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.1425</v>
+        <v>0.8608</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.2555</v>
+        <v>0.9639</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.2332</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.5556</v>
+        <v>1.3736</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.1425</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.6391</v>
+        <v>1.2555</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.4222</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.4768</v>
+        <v>1.5556</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.9%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.0949</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.5244</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.2961</v>
+        <v>1.6391</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.0199</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3819</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.4768</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -8332,449 +8332,449 @@
         <v>1.4106</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4261</v>
+        <v>1.4968</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0155</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>2.17</v>
+        <v>1.2762</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>2.1808</v>
+        <v>1.2961</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.5%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0108</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3681</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.0582</v>
+        <v>1.3873</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.0555</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3146</v>
-      </c>
-      <c r="F37" s="69" t="inlineStr">
-        <is>
-          <t>▼ -1.1%</t>
-        </is>
-      </c>
-      <c r="G37" s="119" t="n">
-        <v>-0.0143</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F37" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G37" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.31</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3661</v>
+        <v>1.3037</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.784</v>
+        <v>1.3289</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.6851</v>
+        <v>1.3146</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.0722</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.1507</v>
+        <v>1.0485</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0755</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.3986</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>0.9982</v>
+        <v>1.3661</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>0.914</v>
+        <v>1.784</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>0.8471</v>
+        <v>1.6851</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.2262</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>0.9851</v>
+        <v>1.1507</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0755</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0641</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.1258</v>
+        <v>0.9982</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.2332</v>
+        <v>0.914</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>1.1154</v>
+        <v>0.8471</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.6%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.1178</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2212</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>1.0606</v>
+        <v>1.1258</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.1939</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.0635</v>
+        <v>1.0606</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.2251</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.2886</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>0.8625</v>
+        <v>1.0635</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.2251</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -8842,7 +8842,7 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
@@ -8852,22 +8852,22 @@
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.31</v>
+        <v>2.17</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.8892</v>
+        <v>1.2754</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -32.1%</t>
+          <t>▼ -41.2%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.4208</v>
+        <v>-0.8946</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -9847,10 +9847,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.17085</v>
+        <v>1.1809875</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1611125</v>
+        <v>1.15925</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10119,20 +10119,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>585</v>
-      </c>
-      <c r="G42" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>576</v>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10191,13 +10191,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.440966666666667</v>
+        <v>1.485293333333334</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.425066666666666</v>
+        <v>1.465926666666667</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.6602</v>
+        <v>0.7887</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10466,13 +10466,13 @@
         <v>1.0606</v>
       </c>
       <c r="D54" s="57" t="n">
-        <v>1.0606</v>
+        <v>1.0087</v>
       </c>
       <c r="E54" s="58" t="n">
         <v>4900</v>
       </c>
       <c r="F54" s="58" t="n">
-        <v>4900</v>
+        <v>4660</v>
       </c>
       <c r="G54" s="69" t="inlineStr">
         <is>
@@ -10599,20 +10599,20 @@
         </is>
       </c>
       <c r="C58" s="57" t="n">
-        <v>1.4261</v>
+        <v>1.4968</v>
       </c>
       <c r="D58" s="57" t="n">
-        <v>1.4269</v>
+        <v>1.4975</v>
       </c>
       <c r="E58" s="58" t="n">
-        <v>20.18</v>
+        <v>21.18</v>
       </c>
       <c r="F58" s="58" t="n">
-        <v>20.19</v>
+        <v>21.19</v>
       </c>
       <c r="G58" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.1%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="H58" s="61" t="inlineStr">
@@ -10667,20 +10667,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G60" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5700</v>
+      </c>
+      <c r="G60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">
@@ -10773,16 +10773,16 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.099988888888889</v>
+        <v>1.0948</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.060788888888889</v>
+        <v>1.091055555555555</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
       </c>
       <c r="F65" s="153" t="n">
-        <v>2.1808</v>
+        <v>1.3736</v>
       </c>
       <c r="G65" s="150" t="n"/>
       <c r="H65" s="150" t="n"/>
@@ -10909,20 +10909,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="G69" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">
@@ -10977,20 +10977,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>0.8892</v>
+        <v>1.3037</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>0.8892</v>
+        <v>1.2462</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>57</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>57</v>
+        <v>79.88</v>
       </c>
       <c r="G71" s="69" t="inlineStr">
         <is>
-          <t>▼ -32.1%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">
@@ -11045,20 +11045,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.1154</v>
+        <v>1.3736</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.0181</v>
+        <v>1.3736</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="G73" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+        <v>25</v>
+      </c>
+      <c r="G73" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">
@@ -11113,20 +11113,20 @@
         </is>
       </c>
       <c r="C75" s="57" t="n">
-        <v>2.1808</v>
+        <v>1.2754</v>
       </c>
       <c r="D75" s="57" t="n">
-        <v>1.9231</v>
+        <v>1.2754</v>
       </c>
       <c r="E75" s="58" t="n">
-        <v>56.7</v>
+        <v>33.16</v>
       </c>
       <c r="F75" s="58" t="n">
-        <v>50</v>
-      </c>
-      <c r="G75" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+        <v>33.16</v>
+      </c>
+      <c r="G75" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.2%</t>
         </is>
       </c>
       <c r="H75" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1073,6 +1073,9 @@
     <xf numFmtId="164" fontId="19" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1093,9 +1096,6 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-13</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-14</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.200</t>
+          <t>$1.219</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.169</t>
+          <t>$1.184</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.6388333333333334</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.5892499999999999</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.2074</v>
+        <v>1.19945625</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.15324375</v>
+        <v>1.145725</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.1809875</v>
+        <v>1.2173625</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.15925</v>
+        <v>1.1930875</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1834,7 +1834,7 @@
         <v>1.485293333333334</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.465926666666667</v>
+        <v>1.469386666666666</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.7887</v>
@@ -1853,16 +1853,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.0948</v>
+        <v>1.1954</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.091055555555555</v>
+        <v>1.163022222222222</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>1.3736</v>
+        <v>2.1808</v>
       </c>
     </row>
     <row r="18" ht="10" customHeight="1"/>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-13</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-14</t>
         </is>
       </c>
     </row>
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J8" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.7711</v>
+        <v>0.6508</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1261</v>
+        <v>1055</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1250</v>
+        <v>1055</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J34" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.3023</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.186</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+      <c r="J35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -3777,13 +3777,13 @@
         <v>1.0606</v>
       </c>
       <c r="F43" s="66" t="n">
-        <v>1.0087</v>
+        <v>1.0606</v>
       </c>
       <c r="G43" s="67" t="n">
         <v>4900</v>
       </c>
       <c r="H43" s="67" t="n">
-        <v>4660</v>
+        <v>4900</v>
       </c>
       <c r="I43" s="68" t="n">
         <v>4620</v>
@@ -4580,23 +4580,23 @@
         </is>
       </c>
       <c r="E61" s="66" t="n">
-        <v>1.2754</v>
+        <v>2.1808</v>
       </c>
       <c r="F61" s="66" t="n">
-        <v>1.2754</v>
+        <v>1.9231</v>
       </c>
       <c r="G61" s="67" t="n">
-        <v>33.16</v>
+        <v>56.7</v>
       </c>
       <c r="H61" s="67" t="n">
-        <v>33.16</v>
+        <v>50</v>
       </c>
       <c r="I61" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="J61" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.2%</t>
+      <c r="J61" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="K61" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.19997037037037</v>
+        <v>1.21854074074074</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.16919074074074</v>
+        <v>1.1837</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-13</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-14</t>
         </is>
       </c>
     </row>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.0474</v>
-      </c>
-      <c r="E9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9809</v>
+      </c>
+      <c r="E9" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.0474</v>
-      </c>
-      <c r="H9" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.8%</t>
+        <v>0.9809</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.7711</v>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>▲ +4.2%</t>
+        <v>0.6508</v>
+      </c>
+      <c r="H24" s="69" t="inlineStr">
+        <is>
+          <t>▼ -12.1%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1261</v>
+        <v>1055</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1250</v>
+        <v>1055</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>1.0662</v>
-      </c>
-      <c r="E35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9851</v>
+      </c>
+      <c r="E35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9536</v>
-      </c>
-      <c r="H35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9685</v>
+      </c>
+      <c r="H35" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.5%</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="E36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>1.3023</v>
+      </c>
+      <c r="E36" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="H36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -21.6%</t>
+        <v>1.186</v>
+      </c>
+      <c r="H36" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -6448,18 +6448,18 @@
         <v>1.1199</v>
       </c>
       <c r="G44" s="91" t="n">
-        <v>1.0087</v>
+        <v>1.0606</v>
       </c>
       <c r="H44" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.9%</t>
+          <t>▼ -5.3%</t>
         </is>
       </c>
       <c r="I44" s="58" t="n">
         <v>4900</v>
       </c>
       <c r="J44" s="58" t="n">
-        <v>4660</v>
+        <v>4900</v>
       </c>
       <c r="K44" s="61" t="inlineStr">
         <is>
@@ -7209,29 +7209,29 @@
         <v>2.17</v>
       </c>
       <c r="D62" s="91" t="n">
-        <v>1.2754</v>
-      </c>
-      <c r="E62" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.2%</t>
+        <v>2.1808</v>
+      </c>
+      <c r="E62" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="F62" s="90" t="n">
         <v>2.05</v>
       </c>
       <c r="G62" s="91" t="n">
-        <v>1.2754</v>
+        <v>1.9231</v>
       </c>
       <c r="H62" s="69" t="inlineStr">
         <is>
-          <t>▼ -37.8%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="I62" s="58" t="n">
-        <v>33.16</v>
+        <v>56.7</v>
       </c>
       <c r="J62" s="58" t="n">
-        <v>33.16</v>
+        <v>50</v>
       </c>
       <c r="K62" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7409,23 +7409,23 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Eritrea</t>
+          <t xml:space="preserve">  2.  Zimbabwe</t>
         </is>
       </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2</v>
+        <v>2.1808</v>
       </c>
       <c r="D6" s="105" t="n">
-        <v>1.7333</v>
-      </c>
-      <c r="E6" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.9231</v>
+      </c>
+      <c r="E6" s="106" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
@@ -7433,15 +7433,15 @@
           <t xml:space="preserve">  2.  Angola</t>
         </is>
       </c>
-      <c r="H6" s="106" t="inlineStr">
+      <c r="H6" s="107" t="inlineStr">
         <is>
           <t>Southern Africa</t>
         </is>
       </c>
-      <c r="I6" s="107" t="n">
+      <c r="I6" s="108" t="n">
         <v>0.3272</v>
       </c>
-      <c r="J6" s="108" t="n">
+      <c r="J6" s="109" t="n">
         <v>0.2181</v>
       </c>
       <c r="K6" s="99" t="inlineStr">
@@ -7453,19 +7453,19 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  CAR</t>
+          <t xml:space="preserve">  3.  Eritrea</t>
         </is>
       </c>
       <c r="B7" s="96" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C7" s="97" t="n">
-        <v>1.7384</v>
+        <v>2</v>
       </c>
       <c r="D7" s="98" t="n">
-        <v>2.1523</v>
+        <v>1.7333</v>
       </c>
       <c r="E7" s="99" t="inlineStr">
         <is>
@@ -7488,164 +7488,164 @@
       <c r="J7" s="102" t="n">
         <v>0.2684</v>
       </c>
-      <c r="K7" s="109" t="inlineStr">
+      <c r="K7" s="110" t="inlineStr">
         <is>
           <t>▼ -29.2%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Comoros</t>
+      <c r="A8" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  CAR</t>
         </is>
       </c>
       <c r="B8" s="103" t="inlineStr">
         <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="C8" s="104" t="n">
+        <v>1.7384</v>
+      </c>
+      <c r="D8" s="105" t="n">
+        <v>2.1523</v>
+      </c>
+      <c r="E8" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Algeria</t>
+        </is>
+      </c>
+      <c r="H8" s="107" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="I8" s="108" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="J8" s="109" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="K8" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Comoros</t>
+        </is>
+      </c>
+      <c r="B9" s="96" t="inlineStr">
+        <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C8" s="104" t="n">
+      <c r="C9" s="97" t="n">
         <v>1.6851</v>
       </c>
-      <c r="D8" s="105" t="n">
+      <c r="D9" s="98" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E8" s="109" t="inlineStr">
+      <c r="E9" s="110" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
       </c>
-      <c r="G8" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Algeria</t>
-        </is>
-      </c>
-      <c r="H8" s="106" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="I8" s="107" t="n">
-        <v>0.3494</v>
-      </c>
-      <c r="J8" s="108" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K8" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Senegal</t>
-        </is>
-      </c>
-      <c r="B9" s="96" t="inlineStr">
+      <c r="G9" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Nigeria</t>
+        </is>
+      </c>
+      <c r="H9" s="100" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C9" s="97" t="n">
+      <c r="I9" s="101" t="n">
+        <v>0.6508</v>
+      </c>
+      <c r="J9" s="102" t="n">
+        <v>0.6508</v>
+      </c>
+      <c r="K9" s="106" t="inlineStr">
+        <is>
+          <t>▲ +11.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Senegal</t>
+        </is>
+      </c>
+      <c r="B10" s="103" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="104" t="n">
         <v>1.6391</v>
       </c>
-      <c r="D9" s="98" t="n">
+      <c r="D10" s="105" t="n">
         <v>1.25</v>
       </c>
-      <c r="E9" s="113" t="inlineStr">
+      <c r="E10" s="106" t="inlineStr">
         <is>
           <t>▲ +7.5%</t>
         </is>
       </c>
-      <c r="G9" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Nigeria</t>
-        </is>
-      </c>
-      <c r="H9" s="100" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="I9" s="101" t="n">
-        <v>0.7779</v>
-      </c>
-      <c r="J9" s="102" t="n">
-        <v>0.7711</v>
-      </c>
-      <c r="K9" s="113" t="inlineStr">
-        <is>
-          <t>▲ +32.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Somalia</t>
-        </is>
-      </c>
-      <c r="B10" s="103" t="inlineStr">
+      <c r="G10" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Burundi</t>
+        </is>
+      </c>
+      <c r="H10" s="107" t="inlineStr">
         <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n">
+      <c r="I10" s="108" t="n">
+        <v>0.7887</v>
+      </c>
+      <c r="J10" s="109" t="n">
+        <v>1.3442</v>
+      </c>
+      <c r="K10" s="110" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Somalia</t>
+        </is>
+      </c>
+      <c r="B11" s="96" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C11" s="97" t="n">
         <v>1.6</v>
       </c>
-      <c r="D10" s="105" t="n">
+      <c r="D11" s="98" t="n">
         <v>1.4</v>
       </c>
-      <c r="E10" s="113" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>▲ +39.1%</t>
-        </is>
-      </c>
-      <c r="G10" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Burundi</t>
-        </is>
-      </c>
-      <c r="H10" s="106" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="I10" s="107" t="n">
-        <v>0.7887</v>
-      </c>
-      <c r="J10" s="108" t="n">
-        <v>1.3442</v>
-      </c>
-      <c r="K10" s="109" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Rwanda</t>
-        </is>
-      </c>
-      <c r="B11" s="96" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="C11" s="97" t="n">
-        <v>1.5742</v>
-      </c>
-      <c r="D11" s="98" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="E11" s="113" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G11" s="114" t="inlineStr">
@@ -7671,69 +7671,69 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Sierra Leone</t>
+      <c r="A12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Rwanda</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
         <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C12" s="104" t="n">
+        <v>1.5742</v>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>1.5072</v>
+      </c>
+      <c r="E12" s="106" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Tunisia</t>
+        </is>
+      </c>
+      <c r="H12" s="107" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="I12" s="108" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="J12" s="109" t="n">
+        <v>0.7318</v>
+      </c>
+      <c r="K12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Sierra Leone</t>
+        </is>
+      </c>
+      <c r="B13" s="96" t="inlineStr">
+        <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C12" s="104" t="n">
+      <c r="C13" s="97" t="n">
         <v>1.5556</v>
       </c>
-      <c r="D12" s="105" t="n">
+      <c r="D13" s="98" t="n">
         <v>1.7778</v>
       </c>
-      <c r="E12" s="113" t="inlineStr">
+      <c r="E13" s="106" t="inlineStr">
         <is>
           <t>▲ +9.4%</t>
-        </is>
-      </c>
-      <c r="G12" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Tunisia</t>
-        </is>
-      </c>
-      <c r="H12" s="106" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="I12" s="107" t="n">
-        <v>0.8377</v>
-      </c>
-      <c r="J12" s="108" t="n">
-        <v>0.7318</v>
-      </c>
-      <c r="K12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Seychelles</t>
-        </is>
-      </c>
-      <c r="B13" s="96" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="C13" s="97" t="n">
-        <v>1.4968</v>
-      </c>
-      <c r="D13" s="98" t="n">
-        <v>1.4975</v>
-      </c>
-      <c r="E13" s="113" t="inlineStr">
-        <is>
-          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G13" s="114" t="inlineStr">
@@ -7752,16 +7752,16 @@
       <c r="J13" s="102" t="n">
         <v>1.0892</v>
       </c>
-      <c r="K13" s="109" t="inlineStr">
+      <c r="K13" s="110" t="inlineStr">
         <is>
           <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Uganda</t>
+      <c r="A14" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Seychelles</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
@@ -7770,30 +7770,30 @@
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.4768</v>
+        <v>1.4968</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.421</v>
-      </c>
-      <c r="E14" s="113" t="inlineStr">
-        <is>
-          <t>▲ +6.9%</t>
-        </is>
-      </c>
-      <c r="G14" s="111" t="inlineStr">
+        <v>1.4975</v>
+      </c>
+      <c r="E14" s="106" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
+        </is>
+      </c>
+      <c r="G14" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Equatorial Guinea</t>
         </is>
       </c>
-      <c r="H14" s="106" t="inlineStr">
+      <c r="H14" s="107" t="inlineStr">
         <is>
           <t>Central Africa</t>
         </is>
       </c>
-      <c r="I14" s="107" t="n">
+      <c r="I14" s="108" t="n">
         <v>0.9106</v>
       </c>
-      <c r="J14" s="108" t="n">
+      <c r="J14" s="109" t="n">
         <v>0.8609</v>
       </c>
       <c r="K14" s="99" t="inlineStr">
@@ -7974,7 +7974,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
@@ -7984,121 +7984,121 @@
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0882</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>0.7779</v>
+        <v>1.3014</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.1918</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0316</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.3014</v>
+        <v>1.2129</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.3691</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.2129</v>
+        <v>1.5742</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.2831</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.5742</v>
+        <v>1.4487</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
@@ -8108,84 +8108,84 @@
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.2831</v>
+        <v>0.8608</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.4487</v>
+        <v>0.9639</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.9%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1656</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.2332</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.9639</v>
+        <v>1.3736</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.2332</v>
+        <v>0.5861</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.3736</v>
+        <v>0.6508</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.06469999999999999</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -8408,7 +8408,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,28 +8418,28 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.0555</v>
+        <v>2.17</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.0582</v>
+        <v>2.1808</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
@@ -8449,121 +8449,121 @@
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0555</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F38" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G38" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F38" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G38" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.31</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3146</v>
+        <v>1.3037</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.3289</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.0485</v>
+        <v>1.3146</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0237</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.0722</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.3661</v>
+        <v>1.0485</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
@@ -8573,76 +8573,76 @@
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.784</v>
+        <v>1.3986</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.6851</v>
+        <v>1.3661</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -2.3%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.784</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.1507</v>
+        <v>1.6851</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0755</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.2262</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>0.9982</v>
+        <v>1.1507</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
@@ -8650,254 +8650,285 @@
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0755</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>0.914</v>
+        <v>1.0641</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.8471</v>
+        <v>0.9982</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0474</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>1.1258</v>
+        <v>0.9809</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.1939</v>
+        <v>0.914</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.0606</v>
+        <v>0.8471</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.0671</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.0635</v>
+        <v>0.9851</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.2251</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Sao Tome</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>STN</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.3023</v>
+        <v>1.2212</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>0.9302</v>
+        <v>1.1258</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -28.6%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.3721</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.1939</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>0.338</v>
+        <v>1.0606</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.1391</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>2.17</v>
+        <v>1.2886</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>1.2754</v>
+        <v>1.0635</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.2%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.8946</v>
+        <v>-0.2251</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="C52" s="118" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="D52" s="88" t="n">
+        <v>0.4771</v>
+      </c>
+      <c r="E52" s="89" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="F52" s="69" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
+        </is>
+      </c>
+      <c r="G52" s="119" t="n">
+        <v>-0.1391</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="53" t="inlineStr">
+        <is>
           <t>Burundi</t>
         </is>
       </c>
-      <c r="B52" s="63" t="inlineStr">
+      <c r="B53" s="54" t="inlineStr">
         <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C52" s="118" t="inlineStr">
+      <c r="C53" s="116" t="inlineStr">
         <is>
           <t>BIF</t>
         </is>
       </c>
-      <c r="D52" s="88" t="n">
+      <c r="D53" s="88" t="n">
         <v>1.3479</v>
       </c>
-      <c r="E52" s="89" t="n">
+      <c r="E53" s="91" t="n">
         <v>0.7887</v>
       </c>
-      <c r="F52" s="69" t="inlineStr">
+      <c r="F53" s="69" t="inlineStr">
         <is>
           <t>▼ -41.5%</t>
         </is>
       </c>
-      <c r="G52" s="119" t="n">
+      <c r="G53" s="119" t="n">
         <v>-0.5592</v>
       </c>
     </row>
@@ -8955,10 +8986,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.6388333333333334</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.5892499999999999</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9159,20 +9190,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>630</v>
-      </c>
-      <c r="G10" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>590</v>
+      </c>
+      <c r="G10" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9231,13 +9262,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.2074</v>
+        <v>1.19945625</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.15324375</v>
+        <v>1.145725</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9707,20 +9738,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.7711</v>
+        <v>0.6508</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1261</v>
+        <v>1055</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1250</v>
+        <v>1055</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9847,10 +9878,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.1809875</v>
+        <v>1.2173625</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.15925</v>
+        <v>1.1930875</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10119,20 +10150,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>576</v>
-      </c>
-      <c r="G42" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>585</v>
+      </c>
+      <c r="G42" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10153,20 +10184,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.3023</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.186</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>20</v>
-      </c>
-      <c r="G43" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>25.5</v>
+      </c>
+      <c r="G43" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">
@@ -10194,7 +10225,7 @@
         <v>1.485293333333334</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.465926666666667</v>
+        <v>1.469386666666666</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>0.7887</v>
@@ -10466,13 +10497,13 @@
         <v>1.0606</v>
       </c>
       <c r="D54" s="57" t="n">
-        <v>1.0087</v>
+        <v>1.0606</v>
       </c>
       <c r="E54" s="58" t="n">
         <v>4900</v>
       </c>
       <c r="F54" s="58" t="n">
-        <v>4660</v>
+        <v>4900</v>
       </c>
       <c r="G54" s="69" t="inlineStr">
         <is>
@@ -10773,16 +10804,16 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.0948</v>
+        <v>1.1954</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.091055555555555</v>
+        <v>1.163022222222222</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
       </c>
       <c r="F65" s="153" t="n">
-        <v>1.3736</v>
+        <v>2.1808</v>
       </c>
       <c r="G65" s="150" t="n"/>
       <c r="H65" s="150" t="n"/>
@@ -11113,20 +11144,20 @@
         </is>
       </c>
       <c r="C75" s="57" t="n">
-        <v>1.2754</v>
+        <v>2.1808</v>
       </c>
       <c r="D75" s="57" t="n">
-        <v>1.2754</v>
+        <v>1.9231</v>
       </c>
       <c r="E75" s="58" t="n">
-        <v>33.16</v>
+        <v>56.7</v>
       </c>
       <c r="F75" s="58" t="n">
-        <v>33.16</v>
-      </c>
-      <c r="G75" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.2%</t>
+        <v>50</v>
+      </c>
+      <c r="G75" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="H75" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-14</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-15</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.219</t>
+          <t>$1.224</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.184</t>
+          <t>$1.189</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6388333333333334</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.5892499999999999</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.19945625</v>
+        <v>1.19886875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.145725</v>
+        <v>1.14461875</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6508</v>
+        <v>0.6663</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1831,10 +1831,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.485293333333334</v>
+        <v>1.499953333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.469386666666666</v>
+        <v>1.486513333333333</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.7887</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-14</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+      <c r="J8" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2350,23 +2350,23 @@
         </is>
       </c>
       <c r="E11" s="66" t="n">
-        <v>1.1507</v>
+        <v>1.1258</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>1.1921</v>
+        <v>1.1589</v>
       </c>
       <c r="G11" s="67" t="n">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
       </c>
       <c r="J11" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="K11" s="70" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6508</v>
+        <v>0.6663</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6508</v>
+        <v>0.6663</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1055</v>
+        <v>1080</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1055</v>
+        <v>1080</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3727,28 +3727,28 @@
         </is>
       </c>
       <c r="E42" s="57" t="n">
-        <v>1.3661</v>
+        <v>1.586</v>
       </c>
       <c r="F42" s="57" t="n">
-        <v>1.2762</v>
+        <v>1.585</v>
       </c>
       <c r="G42" s="58" t="n">
-        <v>178.28</v>
+        <v>206.97</v>
       </c>
       <c r="H42" s="58" t="n">
-        <v>166.54</v>
+        <v>206.84</v>
       </c>
       <c r="I42" s="59" t="n">
         <v>130.5</v>
       </c>
-      <c r="J42" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
+      <c r="J42" s="71" t="inlineStr">
+        <is>
+          <t>▲ +13.4%</t>
         </is>
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -3777,13 +3777,13 @@
         <v>1.0606</v>
       </c>
       <c r="F43" s="66" t="n">
-        <v>1.0606</v>
+        <v>1.0087</v>
       </c>
       <c r="G43" s="67" t="n">
         <v>4900</v>
       </c>
       <c r="H43" s="67" t="n">
-        <v>4900</v>
+        <v>4660</v>
       </c>
       <c r="I43" s="68" t="n">
         <v>4620</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.21854074074074</v>
+        <v>1.22367037037037</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.1837</v>
+        <v>1.189361111111111</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-14</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="E9" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+        <v>1.0474</v>
+      </c>
+      <c r="E9" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="H9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0474</v>
+      </c>
+      <c r="H9" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.8%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5073,29 +5073,29 @@
         <v>1.2262</v>
       </c>
       <c r="D12" s="91" t="n">
-        <v>1.1507</v>
+        <v>1.1258</v>
       </c>
       <c r="E12" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="F12" s="90" t="n">
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>1.1921</v>
+        <v>1.1589</v>
       </c>
       <c r="H12" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.3%</t>
+          <t>▼ -8.0%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6508</v>
+        <v>0.6663</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6508</v>
+        <v>0.6663</v>
       </c>
       <c r="H24" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.1%</t>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1055</v>
+        <v>1080</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1055</v>
+        <v>1080</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6392,33 +6392,33 @@
         <v>1.3986</v>
       </c>
       <c r="D43" s="89" t="n">
-        <v>1.3661</v>
-      </c>
-      <c r="E43" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
+        <v>1.586</v>
+      </c>
+      <c r="E43" s="71" t="inlineStr">
+        <is>
+          <t>▲ +13.4%</t>
         </is>
       </c>
       <c r="F43" s="90" t="n">
         <v>1.3063</v>
       </c>
       <c r="G43" s="89" t="n">
-        <v>1.2762</v>
-      </c>
-      <c r="H43" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
+        <v>1.585</v>
+      </c>
+      <c r="H43" s="71" t="inlineStr">
+        <is>
+          <t>▲ +21.3%</t>
         </is>
       </c>
       <c r="I43" s="67" t="n">
-        <v>178.28</v>
+        <v>206.97</v>
       </c>
       <c r="J43" s="67" t="n">
-        <v>166.54</v>
+        <v>206.84</v>
       </c>
       <c r="K43" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -6448,18 +6448,18 @@
         <v>1.1199</v>
       </c>
       <c r="G44" s="91" t="n">
-        <v>1.0606</v>
+        <v>1.0087</v>
       </c>
       <c r="H44" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.3%</t>
+          <t>▼ -9.9%</t>
         </is>
       </c>
       <c r="I44" s="58" t="n">
         <v>4900</v>
       </c>
       <c r="J44" s="58" t="n">
-        <v>4900</v>
+        <v>4660</v>
       </c>
       <c r="K44" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7571,14 +7571,14 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6508</v>
+        <v>0.6663</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6508</v>
+        <v>0.6663</v>
       </c>
       <c r="K9" s="106" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Rwanda</t>
+          <t xml:space="preserve">  8.  Kenya</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
@@ -7682,14 +7682,14 @@
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.5742</v>
+        <v>1.586</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.5072</v>
+        <v>1.585</v>
       </c>
       <c r="E12" s="106" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +13.4%</t>
         </is>
       </c>
       <c r="G12" s="112" t="inlineStr">
@@ -7717,23 +7717,23 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Sierra Leone</t>
+          <t xml:space="preserve">  9.  Rwanda</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5556</v>
+        <v>1.5742</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.7778</v>
+        <v>1.5072</v>
       </c>
       <c r="E13" s="106" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G13" s="114" t="inlineStr">
@@ -7761,23 +7761,23 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Seychelles</t>
+          <t xml:space="preserve">  10.  Sierra Leone</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.4968</v>
+        <v>1.5556</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.4975</v>
+        <v>1.7778</v>
       </c>
       <c r="E14" s="106" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G14" s="112" t="inlineStr">
@@ -8067,7 +8067,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
@@ -8077,90 +8077,90 @@
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.2831</v>
+        <v>0.5861</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.4487</v>
+        <v>0.6663</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.9%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1656</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.3986</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.586</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +13.4%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1874</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.2831</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.3736</v>
+        <v>1.4487</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,28 +8170,28 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>0.5861</v>
+        <v>0.8608</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>0.6508</v>
+        <v>0.9639</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
@@ -8201,59 +8201,59 @@
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.2332</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.2555</v>
+        <v>1.3736</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.1425</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.5556</v>
+        <v>1.2555</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
@@ -8263,59 +8263,59 @@
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.4222</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.6391</v>
+        <v>1.5556</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.5244</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.4768</v>
+        <v>1.6391</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.9%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0949</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,121 +8325,121 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3819</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4968</v>
+        <v>1.4768</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.4106</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.2961</v>
+        <v>1.4968</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0199</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.2762</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3873</v>
+        <v>1.2961</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>2.17</v>
+        <v>1.3681</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>2.1808</v>
+        <v>1.3873</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.5%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0108</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
@@ -8449,28 +8449,28 @@
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.0555</v>
+        <v>2.17</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.0582</v>
+        <v>2.1808</v>
       </c>
       <c r="F38" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G38" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
@@ -8480,115 +8480,115 @@
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0555</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F39" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G39" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F39" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G39" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.31</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3146</v>
+        <v>1.3037</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.3289</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.0485</v>
+        <v>1.3146</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0237</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.0722</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.3661</v>
+        <v>1.0485</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.3%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0325</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -8625,24 +8625,24 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.0641</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.1507</v>
+        <v>0.9982</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
@@ -8650,75 +8650,75 @@
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0755</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.0641</v>
+        <v>0.914</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.9982</v>
+        <v>0.8471</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.0474</v>
+        <v>1.0671</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.9809</v>
+        <v>0.9851</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.3%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0665</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
@@ -8728,207 +8728,176 @@
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>0.914</v>
+        <v>1.2212</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.8471</v>
+        <v>1.1258</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.2262</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>0.9851</v>
+        <v>1.1258</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.1004</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.1939</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.1258</v>
+        <v>1.0606</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2886</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.0606</v>
+        <v>1.0635</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -17.5%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.2251</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.2886</v>
+        <v>0.4771</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>1.0635</v>
+        <v>0.338</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.2251</v>
+        <v>-0.1391</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.3479</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.338</v>
+        <v>0.7887</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -41.5%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.1391</v>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="53" t="inlineStr">
-        <is>
-          <t>Burundi</t>
-        </is>
-      </c>
-      <c r="B53" s="54" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="C53" s="116" t="inlineStr">
-        <is>
-          <t>BIF</t>
-        </is>
-      </c>
-      <c r="D53" s="88" t="n">
-        <v>1.3479</v>
-      </c>
-      <c r="E53" s="91" t="n">
-        <v>0.7887</v>
-      </c>
-      <c r="F53" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
-        </is>
-      </c>
-      <c r="G53" s="119" t="n">
         <v>-0.5592</v>
       </c>
     </row>
@@ -8986,10 +8955,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6388333333333334</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.5892499999999999</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9190,20 +9159,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>590</v>
-      </c>
-      <c r="G10" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+        <v>630</v>
+      </c>
+      <c r="G10" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9262,13 +9231,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.19945625</v>
+        <v>1.19886875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.145725</v>
+        <v>1.14461875</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6508</v>
+        <v>0.6663</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9330,20 +9299,20 @@
         </is>
       </c>
       <c r="C16" s="57" t="n">
-        <v>1.1507</v>
+        <v>1.1258</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>1.1921</v>
+        <v>1.1589</v>
       </c>
       <c r="E16" s="58" t="n">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="F16" s="58" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="G16" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="H16" s="61" t="inlineStr">
@@ -9738,20 +9707,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6508</v>
+        <v>0.6663</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6508</v>
+        <v>0.6663</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1055</v>
+        <v>1080</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1055</v>
+        <v>1080</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -10222,10 +10191,10 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.485293333333334</v>
+        <v>1.499953333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.469386666666666</v>
+        <v>1.486513333333333</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>0.7887</v>
@@ -10460,25 +10429,25 @@
         </is>
       </c>
       <c r="C53" s="66" t="n">
-        <v>1.3661</v>
+        <v>1.586</v>
       </c>
       <c r="D53" s="66" t="n">
-        <v>1.2762</v>
+        <v>1.585</v>
       </c>
       <c r="E53" s="67" t="n">
-        <v>178.28</v>
+        <v>206.97</v>
       </c>
       <c r="F53" s="67" t="n">
-        <v>166.54</v>
-      </c>
-      <c r="G53" s="69" t="inlineStr">
-        <is>
-          <t>▼ -2.3%</t>
+        <v>206.84</v>
+      </c>
+      <c r="G53" s="71" t="inlineStr">
+        <is>
+          <t>▲ +13.4%</t>
         </is>
       </c>
       <c r="H53" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -10497,13 +10466,13 @@
         <v>1.0606</v>
       </c>
       <c r="D54" s="57" t="n">
-        <v>1.0606</v>
+        <v>1.0087</v>
       </c>
       <c r="E54" s="58" t="n">
         <v>4900</v>
       </c>
       <c r="F54" s="58" t="n">
-        <v>4900</v>
+        <v>4660</v>
       </c>
       <c r="G54" s="69" t="inlineStr">
         <is>

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1085,14 +1085,14 @@
     <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-15</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-16</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.224</t>
+          <t>$1.221</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.189</t>
+          <t>$1.178</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.6520833333333333</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.6025</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.19886875</v>
+        <v>1.20803125</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.14461875</v>
+        <v>1.1249375</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6663</v>
+        <v>0.7779</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1831,10 +1831,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.499953333333333</v>
+        <v>1.49924</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.486513333333333</v>
+        <v>1.4858</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.7887</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.1954</v>
+        <v>1.160522222222222</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.163022222222222</v>
+        <v>1.1324</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-15</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-16</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.338</v>
+        <v>0.4175</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.3479</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J8" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="E13" s="66" t="n">
-        <v>1.0635</v>
+        <v>1.266</v>
       </c>
       <c r="F13" s="66" t="n">
         <v>1.0635</v>
       </c>
       <c r="G13" s="67" t="n">
-        <v>117.52</v>
+        <v>139.89</v>
       </c>
       <c r="H13" s="67" t="n">
         <v>117.52</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="J13" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="K13" s="70" t="inlineStr">
@@ -2538,23 +2538,23 @@
         </is>
       </c>
       <c r="E15" s="66" t="n">
-        <v>0.8471</v>
+        <v>0.8452</v>
       </c>
       <c r="F15" s="66" t="n">
-        <v>1.0892</v>
+        <v>1.0255</v>
       </c>
       <c r="G15" s="67" t="n">
-        <v>13.3</v>
+        <v>13.27</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>17.1</v>
+        <v>16.1</v>
       </c>
       <c r="I15" s="68" t="n">
         <v>15.7</v>
       </c>
       <c r="J15" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="K15" s="70" t="inlineStr">
@@ -2773,23 +2773,23 @@
         </is>
       </c>
       <c r="E20" s="57" t="n">
-        <v>1.4487</v>
+        <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.5563</v>
+        <v>1.2003</v>
       </c>
       <c r="G20" s="58" t="n">
-        <v>875</v>
+        <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>940</v>
+        <v>725</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J20" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.9%</t>
+      <c r="J20" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K20" s="61" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.7779</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.7711</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1080</v>
+        <v>1261</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3868,23 +3868,23 @@
         </is>
       </c>
       <c r="E45" s="66" t="n">
-        <v>1.2677</v>
+        <v>1.257</v>
       </c>
       <c r="F45" s="66" t="n">
-        <v>1.2677</v>
+        <v>1.257</v>
       </c>
       <c r="G45" s="67" t="n">
-        <v>58.95</v>
+        <v>58.45</v>
       </c>
       <c r="H45" s="67" t="n">
-        <v>58.95</v>
+        <v>58.45</v>
       </c>
       <c r="I45" s="68" t="n">
         <v>46.5</v>
       </c>
-      <c r="J45" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J45" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="K45" s="70" t="inlineStr">
@@ -4392,23 +4392,23 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>1.3037</v>
+        <v>1.248</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>1.2462</v>
+        <v>1.3261</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>83.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>79.88</v>
+        <v>85</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="J57" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="K57" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.1154</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.0181</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>25</v>
+        <v>18.53</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+      <c r="J59" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.22367037037037</v>
+        <v>1.220614814814814</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.189361111111111</v>
+        <v>1.178468518518518</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-15</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-16</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.338</v>
+        <v>0.4175</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2684</v>
+        <v>0.3479</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -34.1%</t>
+          <t>▼ -14.7%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.0474</v>
-      </c>
-      <c r="E9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9809</v>
+      </c>
+      <c r="E9" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.0474</v>
-      </c>
-      <c r="H9" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.8%</t>
+        <v>0.9809</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5163,11 +5163,11 @@
         <v>1.2886</v>
       </c>
       <c r="D14" s="91" t="n">
-        <v>1.0635</v>
+        <v>1.266</v>
       </c>
       <c r="E14" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="F14" s="90" t="n">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="I14" s="58" t="n">
-        <v>117.52</v>
+        <v>139.89</v>
       </c>
       <c r="J14" s="58" t="n">
         <v>117.52</v>
@@ -5253,29 +5253,29 @@
         <v>0.914</v>
       </c>
       <c r="D16" s="91" t="n">
-        <v>0.8471</v>
+        <v>0.8452</v>
       </c>
       <c r="E16" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="F16" s="90" t="n">
         <v>0.914</v>
       </c>
       <c r="G16" s="91" t="n">
-        <v>1.0892</v>
+        <v>1.0255</v>
       </c>
       <c r="H16" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.2%</t>
+          <t>▲ +12.2%</t>
         </is>
       </c>
       <c r="I16" s="58" t="n">
-        <v>13.3</v>
+        <v>13.27</v>
       </c>
       <c r="J16" s="58" t="n">
-        <v>17.1</v>
+        <v>16.1</v>
       </c>
       <c r="K16" s="61" t="inlineStr">
         <is>
@@ -5478,29 +5478,29 @@
         <v>1.2831</v>
       </c>
       <c r="D21" s="89" t="n">
-        <v>1.4487</v>
-      </c>
-      <c r="E21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.9%</t>
+        <v>1.2831</v>
+      </c>
+      <c r="E21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="90" t="n">
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.5563</v>
-      </c>
-      <c r="H21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +29.7%</t>
+        <v>1.2003</v>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
-        <v>875</v>
+        <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>940</v>
+        <v>725</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6663</v>
+        <v>0.7779</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="H24" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>0.7711</v>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +4.2%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1080</v>
+        <v>1261</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6527,29 +6527,29 @@
         <v>1.2677</v>
       </c>
       <c r="D46" s="91" t="n">
-        <v>1.2677</v>
-      </c>
-      <c r="E46" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.257</v>
+      </c>
+      <c r="E46" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="F46" s="90" t="n">
         <v>1.2677</v>
       </c>
       <c r="G46" s="91" t="n">
-        <v>1.2677</v>
-      </c>
-      <c r="H46" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.257</v>
+      </c>
+      <c r="H46" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="I46" s="58" t="n">
-        <v>58.95</v>
+        <v>58.45</v>
       </c>
       <c r="J46" s="58" t="n">
-        <v>58.95</v>
+        <v>58.45</v>
       </c>
       <c r="K46" s="61" t="inlineStr">
         <is>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>1.3037</v>
+        <v>1.248</v>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>1.2462</v>
-      </c>
-      <c r="H58" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.3%</t>
+        <v>1.3261</v>
+      </c>
+      <c r="H58" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>83.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>79.88</v>
+        <v>85</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="E60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>1.1154</v>
+      </c>
+      <c r="E60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="H60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+        <v>1.0181</v>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -21.0%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>25</v>
+        <v>18.53</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Egypt</t>
+          <t xml:space="preserve">  3.  Algeria</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
@@ -7483,19 +7483,19 @@
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.338</v>
+        <v>0.3494</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2684</v>
-      </c>
-      <c r="K7" s="110" t="inlineStr">
-        <is>
-          <t>▼ -29.2%</t>
+        <v>0.2305</v>
+      </c>
+      <c r="K7" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="111" t="inlineStr">
+      <c r="A8" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  CAR</t>
         </is>
@@ -7516,9 +7516,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Algeria</t>
+      <c r="G8" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Egypt</t>
         </is>
       </c>
       <c r="H8" s="107" t="inlineStr">
@@ -7527,14 +7527,14 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.3494</v>
+        <v>0.4175</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K8" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.3479</v>
+      </c>
+      <c r="K8" s="112" t="inlineStr">
+        <is>
+          <t>▼ -12.5%</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       <c r="D9" s="98" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E9" s="110" t="inlineStr">
+      <c r="E9" s="112" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
@@ -7571,19 +7571,19 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6663</v>
+        <v>0.7779</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6663</v>
+        <v>0.7711</v>
       </c>
       <c r="K9" s="106" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="111" t="inlineStr">
+      <c r="A10" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  Senegal</t>
         </is>
@@ -7604,7 +7604,7 @@
           <t>▲ +7.5%</t>
         </is>
       </c>
-      <c r="G10" s="112" t="inlineStr">
+      <c r="G10" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  Burundi</t>
         </is>
@@ -7620,7 +7620,7 @@
       <c r="J10" s="109" t="n">
         <v>1.3442</v>
       </c>
-      <c r="K10" s="110" t="inlineStr">
+      <c r="K10" s="112" t="inlineStr">
         <is>
           <t>▼ -41.5%</t>
         </is>
@@ -7671,7 +7671,7 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="111" t="inlineStr">
+      <c r="A12" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  8.  Kenya</t>
         </is>
@@ -7692,7 +7692,7 @@
           <t>▲ +13.4%</t>
         </is>
       </c>
-      <c r="G12" s="112" t="inlineStr">
+      <c r="G12" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  8.  Tunisia</t>
         </is>
@@ -7747,19 +7747,19 @@
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8471</v>
+        <v>0.8452</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K13" s="110" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>1.0255</v>
+      </c>
+      <c r="K13" s="112" t="inlineStr">
+        <is>
+          <t>▼ -7.5%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="111" t="inlineStr">
+      <c r="A14" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Sierra Leone</t>
         </is>
@@ -7780,7 +7780,7 @@
           <t>▲ +9.4%</t>
         </is>
       </c>
-      <c r="G14" s="112" t="inlineStr">
+      <c r="G14" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Equatorial Guinea</t>
         </is>
@@ -7974,7 +7974,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
@@ -7984,115 +7984,115 @@
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0882</v>
+        <v>0.5861</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.3014</v>
+        <v>0.7779</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.1918</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.0882</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.2129</v>
+        <v>1.3014</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.0316</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.5742</v>
+        <v>1.2129</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.3691</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>0.6663</v>
+        <v>1.5742</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -8129,7 +8129,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
@@ -8139,431 +8139,431 @@
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.2831</v>
+        <v>0.8608</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.4487</v>
+        <v>0.9639</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.9%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1656</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.1425</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.2555</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.4222</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.3736</v>
+        <v>1.5556</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.5244</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.2555</v>
+        <v>1.6391</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.3819</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.5556</v>
+        <v>1.4768</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.4106</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.4968</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.2762</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4768</v>
+        <v>1.2961</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.9%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0949</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3681</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.4968</v>
+        <v>1.3873</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.2762</v>
+        <v>2.17</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.2961</v>
+        <v>2.1808</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +0.5%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0199</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.0555</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.0582</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>2.17</v>
+        <v>1.2677</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>2.1808</v>
-      </c>
-      <c r="F38" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
-        </is>
-      </c>
-      <c r="G38" s="117" t="n">
-        <v>0.0108</v>
+        <v>1.257</v>
+      </c>
+      <c r="F38" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
+        </is>
+      </c>
+      <c r="G38" s="119" t="n">
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3289</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.0582</v>
-      </c>
-      <c r="F39" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
-        </is>
-      </c>
-      <c r="G39" s="117" t="n">
-        <v>0.0027</v>
+        <v>1.3146</v>
+      </c>
+      <c r="F39" s="69" t="inlineStr">
+        <is>
+          <t>▼ -1.1%</t>
+        </is>
+      </c>
+      <c r="G39" s="119" t="n">
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.31</v>
+        <v>1.2886</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3037</v>
+        <v>1.266</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0063</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.0722</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.3146</v>
+        <v>1.0485</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
@@ -8573,22 +8573,22 @@
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.31</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.0485</v>
+        <v>1.248</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0237</v>
+        <v>-0.062</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -8656,100 +8656,100 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>0.914</v>
+        <v>1.0474</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.8471</v>
+        <v>0.9809</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.0671</v>
+        <v>0.914</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.9851</v>
+        <v>0.8452</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0688</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0671</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.1258</v>
+        <v>0.9851</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
@@ -8763,141 +8763,172 @@
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2212</v>
       </c>
       <c r="E48" s="89" t="n">
         <v>1.1258</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1004</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2262</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.0606</v>
+        <v>1.1258</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.1004</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.2332</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.0635</v>
+        <v>1.1154</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.2251</v>
+        <v>-0.1178</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.1939</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.338</v>
+        <v>1.0606</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.1391</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="C52" s="118" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="D52" s="88" t="n">
+        <v>0.4771</v>
+      </c>
+      <c r="E52" s="89" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="F52" s="69" t="inlineStr">
+        <is>
+          <t>▼ -12.5%</t>
+        </is>
+      </c>
+      <c r="G52" s="119" t="n">
+        <v>-0.0596</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="53" t="inlineStr">
+        <is>
           <t>Burundi</t>
         </is>
       </c>
-      <c r="B52" s="63" t="inlineStr">
+      <c r="B53" s="54" t="inlineStr">
         <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C52" s="118" t="inlineStr">
+      <c r="C53" s="116" t="inlineStr">
         <is>
           <t>BIF</t>
         </is>
       </c>
-      <c r="D52" s="88" t="n">
+      <c r="D53" s="88" t="n">
         <v>1.3479</v>
       </c>
-      <c r="E52" s="89" t="n">
+      <c r="E53" s="91" t="n">
         <v>0.7887</v>
       </c>
-      <c r="F52" s="69" t="inlineStr">
+      <c r="F53" s="69" t="inlineStr">
         <is>
           <t>▼ -41.5%</t>
         </is>
       </c>
-      <c r="G52" s="119" t="n">
+      <c r="G53" s="119" t="n">
         <v>-0.5592</v>
       </c>
     </row>
@@ -8955,10 +8986,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.6520833333333333</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.6025</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9057,20 +9088,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.338</v>
+        <v>0.4175</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.3479</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9159,20 +9190,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>630</v>
-      </c>
-      <c r="G10" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>590</v>
+      </c>
+      <c r="G10" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9231,13 +9262,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.19886875</v>
+        <v>1.20803125</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.14461875</v>
+        <v>1.1249375</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6663</v>
+        <v>0.7779</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9367,20 +9398,20 @@
         </is>
       </c>
       <c r="C18" s="57" t="n">
-        <v>1.0635</v>
+        <v>1.266</v>
       </c>
       <c r="D18" s="57" t="n">
         <v>1.0635</v>
       </c>
       <c r="E18" s="58" t="n">
-        <v>117.52</v>
+        <v>139.89</v>
       </c>
       <c r="F18" s="58" t="n">
         <v>117.52</v>
       </c>
       <c r="G18" s="69" t="inlineStr">
         <is>
-          <t>▼ -17.5%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="H18" s="61" t="inlineStr">
@@ -9435,20 +9466,20 @@
         </is>
       </c>
       <c r="C20" s="57" t="n">
-        <v>0.8471</v>
+        <v>0.8452</v>
       </c>
       <c r="D20" s="57" t="n">
-        <v>1.0892</v>
+        <v>1.0255</v>
       </c>
       <c r="E20" s="58" t="n">
-        <v>13.3</v>
+        <v>13.27</v>
       </c>
       <c r="F20" s="58" t="n">
-        <v>17.1</v>
+        <v>16.1</v>
       </c>
       <c r="G20" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="H20" s="61" t="inlineStr">
@@ -9605,20 +9636,20 @@
         </is>
       </c>
       <c r="C25" s="66" t="n">
-        <v>1.4487</v>
+        <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.5563</v>
+        <v>1.2003</v>
       </c>
       <c r="E25" s="67" t="n">
-        <v>875</v>
+        <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>940</v>
-      </c>
-      <c r="G25" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.9%</t>
+        <v>725</v>
+      </c>
+      <c r="G25" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="70" t="inlineStr">
@@ -9707,20 +9738,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.7779</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.7711</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1080</v>
+        <v>1261</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -10191,10 +10222,10 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.499953333333333</v>
+        <v>1.49924</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.486513333333333</v>
+        <v>1.4858</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>0.7887</v>
@@ -10531,20 +10562,20 @@
         </is>
       </c>
       <c r="C56" s="57" t="n">
-        <v>1.2677</v>
+        <v>1.257</v>
       </c>
       <c r="D56" s="57" t="n">
-        <v>1.2677</v>
+        <v>1.257</v>
       </c>
       <c r="E56" s="58" t="n">
-        <v>58.95</v>
+        <v>58.45</v>
       </c>
       <c r="F56" s="58" t="n">
-        <v>58.95</v>
-      </c>
-      <c r="G56" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>58.45</v>
+      </c>
+      <c r="G56" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="H56" s="61" t="inlineStr">
@@ -10773,10 +10804,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.1954</v>
+        <v>1.160522222222222</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.163022222222222</v>
+        <v>1.1324</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10977,20 +11008,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>1.3037</v>
+        <v>1.248</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>1.2462</v>
+        <v>1.3261</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>83.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>79.88</v>
+        <v>85</v>
       </c>
       <c r="G71" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">
@@ -11045,20 +11076,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.1154</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.0181</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>25</v>
-      </c>
-      <c r="G73" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>18.53</v>
+      </c>
+      <c r="G73" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1085,14 +1085,14 @@
     <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-16</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-17</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.221</t>
+          <t>$1.222</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.178</t>
+          <t>$1.194</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6520833333333333</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6025</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.20803125</v>
+        <v>1.2000875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.1249375</v>
+        <v>1.14298125</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1831,10 +1831,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.49924</v>
+        <v>1.490733333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.4858</v>
+        <v>1.479813333333333</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.7887</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.160522222222222</v>
+        <v>1.199544444444444</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.1324</v>
+        <v>1.205577777777778</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-16</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-17</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.338</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.3479</v>
+        <v>0.2684</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+      <c r="J8" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2682,13 +2682,13 @@
         <v>1.3576</v>
       </c>
       <c r="F18" s="57" t="n">
-        <v>1.1175</v>
+        <v>1.4437</v>
       </c>
       <c r="G18" s="58" t="n">
         <v>820</v>
       </c>
       <c r="H18" s="58" t="n">
-        <v>675</v>
+        <v>872</v>
       </c>
       <c r="I18" s="59" t="n">
         <v>604</v>
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.7711</v>
+        <v>0.6508</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1261</v>
+        <v>1055</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1250</v>
+        <v>1055</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3727,28 +3727,28 @@
         </is>
       </c>
       <c r="E42" s="57" t="n">
-        <v>1.586</v>
+        <v>1.5142</v>
       </c>
       <c r="F42" s="57" t="n">
-        <v>1.585</v>
+        <v>1.5067</v>
       </c>
       <c r="G42" s="58" t="n">
-        <v>206.97</v>
+        <v>197.6</v>
       </c>
       <c r="H42" s="58" t="n">
-        <v>206.84</v>
+        <v>196.63</v>
       </c>
       <c r="I42" s="59" t="n">
         <v>130.5</v>
       </c>
       <c r="J42" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.4%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -4150,23 +4150,23 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.4768</v>
+        <v>1.421</v>
       </c>
       <c r="F51" s="66" t="n">
-        <v>1.421</v>
+        <v>1.4095</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>5290</v>
+        <v>5090</v>
       </c>
       <c r="H51" s="67" t="n">
-        <v>5090</v>
+        <v>5049</v>
       </c>
       <c r="I51" s="68" t="n">
         <v>3582</v>
       </c>
       <c r="J51" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.9%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="K51" s="70" t="inlineStr">
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>1.2555</v>
+        <v>1.551</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>1.3294</v>
+        <v>2.0679</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
       <c r="J54" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +35.8%</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4392,23 +4392,23 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>1.248</v>
+        <v>1.3037</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>1.3261</v>
+        <v>1.2462</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>80</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>85</v>
+        <v>79.88</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="J57" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="K57" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.220614814814814</v>
+        <v>1.222161111111111</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.178468518518518</v>
+        <v>1.194107407407407</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-16</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-17</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.4175</v>
+        <v>0.338</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.3479</v>
+        <v>0.2684</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -14.7%</t>
+          <t>▼ -34.1%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="E9" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+        <v>1.0474</v>
+      </c>
+      <c r="E9" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="H9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0474</v>
+      </c>
+      <c r="H9" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.8%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5399,18 +5399,18 @@
         <v>1.1185</v>
       </c>
       <c r="G19" s="89" t="n">
-        <v>1.1175</v>
-      </c>
-      <c r="H19" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.4437</v>
+      </c>
+      <c r="H19" s="71" t="inlineStr">
+        <is>
+          <t>▲ +29.1%</t>
         </is>
       </c>
       <c r="I19" s="67" t="n">
         <v>820</v>
       </c>
       <c r="J19" s="67" t="n">
-        <v>675</v>
+        <v>872</v>
       </c>
       <c r="K19" s="70" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2003</v>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2831</v>
+      </c>
+      <c r="H21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.7711</v>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>▲ +4.2%</t>
+        <v>0.6508</v>
+      </c>
+      <c r="H24" s="69" t="inlineStr">
+        <is>
+          <t>▼ -12.1%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1261</v>
+        <v>1055</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1250</v>
+        <v>1055</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6392,33 +6392,33 @@
         <v>1.3986</v>
       </c>
       <c r="D43" s="89" t="n">
-        <v>1.586</v>
+        <v>1.5142</v>
       </c>
       <c r="E43" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.4%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="F43" s="90" t="n">
         <v>1.3063</v>
       </c>
       <c r="G43" s="89" t="n">
-        <v>1.585</v>
+        <v>1.5067</v>
       </c>
       <c r="H43" s="71" t="inlineStr">
         <is>
-          <t>▲ +21.3%</t>
+          <t>▲ +15.3%</t>
         </is>
       </c>
       <c r="I43" s="67" t="n">
-        <v>206.97</v>
+        <v>197.6</v>
       </c>
       <c r="J43" s="67" t="n">
-        <v>206.84</v>
+        <v>196.63</v>
       </c>
       <c r="K43" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -6797,29 +6797,29 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.4768</v>
+        <v>1.421</v>
       </c>
       <c r="E52" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.9%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
         <v>1.2741</v>
       </c>
       <c r="G52" s="91" t="n">
-        <v>1.421</v>
+        <v>1.4095</v>
       </c>
       <c r="H52" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.5%</t>
+          <t>▲ +10.6%</t>
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>5290</v>
+        <v>5090</v>
       </c>
       <c r="J52" s="58" t="n">
-        <v>5090</v>
+        <v>5049</v>
       </c>
       <c r="K52" s="61" t="inlineStr">
         <is>
@@ -6894,29 +6894,29 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>1.2555</v>
+        <v>1.551</v>
       </c>
       <c r="E55" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +35.8%</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>1.3294</v>
+        <v>2.0679</v>
       </c>
       <c r="H55" s="71" t="inlineStr">
         <is>
-          <t>▲ +10.6%</t>
+          <t>▲ +72.0%</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>1.248</v>
+        <v>1.3037</v>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>1.3261</v>
-      </c>
-      <c r="H58" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.1%</t>
+        <v>1.2462</v>
+      </c>
+      <c r="H58" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.3%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>80</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>85</v>
+        <v>79.88</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Algeria</t>
+          <t xml:space="preserve">  3.  Egypt</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
@@ -7483,19 +7483,19 @@
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.3494</v>
+        <v>0.338</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K7" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2684</v>
+      </c>
+      <c r="K7" s="110" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="110" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  CAR</t>
         </is>
@@ -7516,9 +7516,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Egypt</t>
+      <c r="G8" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Algeria</t>
         </is>
       </c>
       <c r="H8" s="107" t="inlineStr">
@@ -7527,14 +7527,14 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.4175</v>
+        <v>0.3494</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.3479</v>
-      </c>
-      <c r="K8" s="112" t="inlineStr">
-        <is>
-          <t>▼ -12.5%</t>
+        <v>0.2305</v>
+      </c>
+      <c r="K8" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       <c r="D9" s="98" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E9" s="112" t="inlineStr">
+      <c r="E9" s="110" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
@@ -7571,19 +7571,19 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.7711</v>
+        <v>0.6508</v>
       </c>
       <c r="K9" s="106" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="110" t="inlineStr">
+      <c r="A10" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  Senegal</t>
         </is>
@@ -7604,7 +7604,7 @@
           <t>▲ +7.5%</t>
         </is>
       </c>
-      <c r="G10" s="111" t="inlineStr">
+      <c r="G10" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  Burundi</t>
         </is>
@@ -7620,7 +7620,7 @@
       <c r="J10" s="109" t="n">
         <v>1.3442</v>
       </c>
-      <c r="K10" s="112" t="inlineStr">
+      <c r="K10" s="110" t="inlineStr">
         <is>
           <t>▼ -41.5%</t>
         </is>
@@ -7671,9 +7671,9 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Kenya</t>
+      <c r="A12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Rwanda</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
@@ -7682,17 +7682,17 @@
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.586</v>
+        <v>1.5742</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.585</v>
+        <v>1.5072</v>
       </c>
       <c r="E12" s="106" t="inlineStr">
         <is>
-          <t>▲ +13.4%</t>
-        </is>
-      </c>
-      <c r="G12" s="111" t="inlineStr">
+          <t>▲ +15.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  8.  Tunisia</t>
         </is>
@@ -7717,23 +7717,23 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Rwanda</t>
+          <t xml:space="preserve">  9.  Sierra Leone</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5742</v>
+        <v>1.5556</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.5072</v>
+        <v>1.7778</v>
       </c>
       <c r="E13" s="106" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G13" s="114" t="inlineStr">
@@ -7752,35 +7752,35 @@
       <c r="J13" s="102" t="n">
         <v>1.0255</v>
       </c>
-      <c r="K13" s="112" t="inlineStr">
+      <c r="K13" s="110" t="inlineStr">
         <is>
           <t>▼ -7.5%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Sierra Leone</t>
+      <c r="A14" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Botswana</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.5556</v>
+        <v>1.551</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.7778</v>
+        <v>2.0679</v>
       </c>
       <c r="E14" s="106" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
-        </is>
-      </c>
-      <c r="G14" s="111" t="inlineStr">
+          <t>▲ +35.8%</t>
+        </is>
+      </c>
+      <c r="G14" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Equatorial Guinea</t>
         </is>
@@ -7943,63 +7943,63 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.1425</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.4096</v>
+        <v>1.551</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +35.8%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.348</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0616</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>0.7779</v>
+        <v>1.4096</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.1918</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -8098,38 +8098,38 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.3986</v>
+        <v>0.8608</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.586</v>
+        <v>0.9639</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.4%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1874</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
@@ -8139,84 +8139,84 @@
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.8608</v>
+        <v>0.5861</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.9639</v>
+        <v>0.6508</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.06469999999999999</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.4222</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.2555</v>
+        <v>1.5556</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.3986</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.5556</v>
+        <v>1.5142</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -8253,7 +8253,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
@@ -8263,28 +8263,28 @@
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.4106</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.4768</v>
+        <v>1.4968</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.9%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.0949</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,22 +8294,22 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3819</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.4968</v>
+        <v>1.421</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -8439,69 +8439,69 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.31</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.257</v>
+        <v>1.3037</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2677</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3146</v>
+        <v>1.257</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
@@ -8511,59 +8511,59 @@
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3289</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.266</v>
+        <v>1.3146</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.2886</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.0485</v>
+        <v>1.266</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0237</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
@@ -8573,22 +8573,22 @@
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0722</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.248</v>
+        <v>1.0485</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.062</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -8656,100 +8656,100 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.0474</v>
+        <v>0.914</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.9809</v>
+        <v>0.8452</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.3%</t>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0665</v>
+        <v>-0.0688</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>0.914</v>
+        <v>1.0671</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.8452</v>
+        <v>0.9851</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.5%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0688</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.2212</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.9851</v>
+        <v>1.1258</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
@@ -8763,172 +8763,141 @@
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.2262</v>
       </c>
       <c r="E48" s="89" t="n">
         <v>1.1258</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.1004</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2332</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.1258</v>
+        <v>1.1154</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1004</v>
+        <v>-0.1178</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.1939</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.1154</v>
+        <v>1.0606</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.6%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.1178</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.1939</v>
+        <v>0.4771</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>1.0606</v>
+        <v>0.338</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.1391</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.3479</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.4175</v>
+        <v>0.7887</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -41.5%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.0596</v>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="53" t="inlineStr">
-        <is>
-          <t>Burundi</t>
-        </is>
-      </c>
-      <c r="B53" s="54" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="C53" s="116" t="inlineStr">
-        <is>
-          <t>BIF</t>
-        </is>
-      </c>
-      <c r="D53" s="88" t="n">
-        <v>1.3479</v>
-      </c>
-      <c r="E53" s="91" t="n">
-        <v>0.7887</v>
-      </c>
-      <c r="F53" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
-        </is>
-      </c>
-      <c r="G53" s="119" t="n">
         <v>-0.5592</v>
       </c>
     </row>
@@ -8986,10 +8955,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6520833333333333</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6025</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9088,20 +9057,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.338</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.3479</v>
+        <v>0.2684</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9190,20 +9159,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.0474</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>590</v>
-      </c>
-      <c r="G10" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+        <v>630</v>
+      </c>
+      <c r="G10" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9262,13 +9231,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.20803125</v>
+        <v>1.2000875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.1249375</v>
+        <v>1.14298125</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9571,13 +9540,13 @@
         <v>1.3576</v>
       </c>
       <c r="D23" s="66" t="n">
-        <v>1.1175</v>
+        <v>1.4437</v>
       </c>
       <c r="E23" s="67" t="n">
         <v>820</v>
       </c>
       <c r="F23" s="67" t="n">
-        <v>675</v>
+        <v>872</v>
       </c>
       <c r="G23" s="60" t="inlineStr">
         <is>
@@ -9639,13 +9608,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9738,20 +9707,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.7779</v>
+        <v>0.6508</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.7711</v>
+        <v>0.6508</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1261</v>
+        <v>1055</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1250</v>
+        <v>1055</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -10222,10 +10191,10 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.49924</v>
+        <v>1.490733333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.4858</v>
+        <v>1.479813333333333</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>0.7887</v>
@@ -10460,25 +10429,25 @@
         </is>
       </c>
       <c r="C53" s="66" t="n">
-        <v>1.586</v>
+        <v>1.5142</v>
       </c>
       <c r="D53" s="66" t="n">
-        <v>1.585</v>
+        <v>1.5067</v>
       </c>
       <c r="E53" s="67" t="n">
-        <v>206.97</v>
+        <v>197.6</v>
       </c>
       <c r="F53" s="67" t="n">
-        <v>206.84</v>
+        <v>196.63</v>
       </c>
       <c r="G53" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.4%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="H53" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -10766,20 +10735,20 @@
         </is>
       </c>
       <c r="C62" s="57" t="n">
-        <v>1.4768</v>
+        <v>1.421</v>
       </c>
       <c r="D62" s="57" t="n">
-        <v>1.421</v>
+        <v>1.4095</v>
       </c>
       <c r="E62" s="58" t="n">
-        <v>5290</v>
+        <v>5090</v>
       </c>
       <c r="F62" s="58" t="n">
-        <v>5090</v>
+        <v>5049</v>
       </c>
       <c r="G62" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.9%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="H62" s="61" t="inlineStr">
@@ -10804,10 +10773,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.160522222222222</v>
+        <v>1.199544444444444</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.1324</v>
+        <v>1.205577777777778</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10906,20 +10875,20 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>1.2555</v>
+        <v>1.551</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>1.3294</v>
+        <v>2.0679</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G68" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +35.8%</t>
         </is>
       </c>
       <c r="H68" s="70" t="inlineStr">
@@ -11008,20 +10977,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>1.248</v>
+        <v>1.3037</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>1.3261</v>
+        <v>1.2462</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>80</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>85</v>
+        <v>79.88</v>
       </c>
       <c r="G71" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1073,32 +1073,32 @@
     <xf numFmtId="164" fontId="19" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-17</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-18</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.222</t>
+          <t>$1.221</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.194</t>
+          <t>$1.184</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.6631666666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.6135833333333333</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.2000875</v>
+        <v>1.21335</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.14298125</v>
+        <v>1.15106875</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6508</v>
+        <v>0.8262</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2173625</v>
+        <v>1.2275</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1930875</v>
+        <v>1.191225</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1834,7 +1834,7 @@
         <v>1.490733333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.479813333333333</v>
+        <v>1.479466666666666</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.7887</v>
@@ -1853,16 +1853,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.199544444444444</v>
+        <v>1.149311111111111</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.205577777777778</v>
+        <v>1.123522222222222</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>2.1808</v>
+        <v>2.0242</v>
       </c>
     </row>
     <row r="18" ht="10" customHeight="1"/>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-17</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-18</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.338</v>
+        <v>0.4175</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.3479</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6508</v>
+        <v>0.863</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6508</v>
+        <v>0.863</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1055</v>
+        <v>1399</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1055</v>
+        <v>1399</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+      <c r="J34" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -4106,13 +4106,13 @@
         <v>1.4096</v>
       </c>
       <c r="F50" s="57" t="n">
-        <v>1.4096</v>
+        <v>1.4044</v>
       </c>
       <c r="G50" s="58" t="n">
         <v>3820</v>
       </c>
       <c r="H50" s="58" t="n">
-        <v>3820</v>
+        <v>3806</v>
       </c>
       <c r="I50" s="59" t="n">
         <v>2710</v>
@@ -4251,23 +4251,23 @@
         </is>
       </c>
       <c r="E54" s="57" t="n">
-        <v>1.551</v>
+        <v>1.2555</v>
       </c>
       <c r="F54" s="57" t="n">
-        <v>2.0679</v>
+        <v>1.3294</v>
       </c>
       <c r="G54" s="58" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H54" s="58" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>13.54</v>
       </c>
       <c r="J54" s="71" t="inlineStr">
         <is>
-          <t>▲ +35.8%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="K54" s="61" t="inlineStr">
@@ -4580,13 +4580,13 @@
         </is>
       </c>
       <c r="E61" s="66" t="n">
-        <v>2.1808</v>
+        <v>2.0242</v>
       </c>
       <c r="F61" s="66" t="n">
         <v>1.9231</v>
       </c>
       <c r="G61" s="67" t="n">
-        <v>56.7</v>
+        <v>52.63</v>
       </c>
       <c r="H61" s="67" t="n">
         <v>50</v>
@@ -4594,9 +4594,9 @@
       <c r="I61" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="J61" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+      <c r="J61" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="K61" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.222161111111111</v>
+        <v>1.220692592592592</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.194107407407407</v>
+        <v>1.183927777777778</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-17</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-18</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.338</v>
+        <v>0.4175</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2684</v>
+        <v>0.3479</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -34.1%</t>
+          <t>▼ -14.7%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2831</v>
-      </c>
-      <c r="H21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.9%</t>
+        <v>1.2003</v>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6508</v>
+        <v>0.863</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6508</v>
-      </c>
-      <c r="H24" s="69" t="inlineStr">
-        <is>
-          <t>▼ -12.1%</t>
+        <v>0.863</v>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +16.6%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1055</v>
+        <v>1399</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1055</v>
+        <v>1399</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="E35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>1.0662</v>
+      </c>
+      <c r="E35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9685</v>
-      </c>
-      <c r="H35" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.5%</t>
+        <v>0.9536</v>
+      </c>
+      <c r="H35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6763,18 +6763,18 @@
         <v>1.021</v>
       </c>
       <c r="G51" s="89" t="n">
-        <v>1.4096</v>
+        <v>1.4044</v>
       </c>
       <c r="H51" s="71" t="inlineStr">
         <is>
-          <t>▲ +38.1%</t>
+          <t>▲ +37.5%</t>
         </is>
       </c>
       <c r="I51" s="67" t="n">
         <v>3820</v>
       </c>
       <c r="J51" s="67" t="n">
-        <v>3820</v>
+        <v>3806</v>
       </c>
       <c r="K51" s="70" t="inlineStr">
         <is>
@@ -6894,29 +6894,29 @@
         <v>1.1425</v>
       </c>
       <c r="D55" s="89" t="n">
-        <v>1.551</v>
+        <v>1.2555</v>
       </c>
       <c r="E55" s="71" t="inlineStr">
         <is>
-          <t>▲ +35.8%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="F55" s="90" t="n">
         <v>1.2024</v>
       </c>
       <c r="G55" s="89" t="n">
-        <v>2.0679</v>
+        <v>1.3294</v>
       </c>
       <c r="H55" s="71" t="inlineStr">
         <is>
-          <t>▲ +72.0%</t>
+          <t>▲ +10.6%</t>
         </is>
       </c>
       <c r="I55" s="67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J55" s="67" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K55" s="70" t="inlineStr">
         <is>
@@ -7209,11 +7209,11 @@
         <v>2.17</v>
       </c>
       <c r="D62" s="91" t="n">
-        <v>2.1808</v>
-      </c>
-      <c r="E62" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+        <v>2.0242</v>
+      </c>
+      <c r="E62" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="F62" s="90" t="n">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="I62" s="58" t="n">
-        <v>56.7</v>
+        <v>52.63</v>
       </c>
       <c r="J62" s="58" t="n">
         <v>50</v>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7418,14 +7418,14 @@
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2.1808</v>
+        <v>2.0242</v>
       </c>
       <c r="D6" s="105" t="n">
         <v>1.9231</v>
       </c>
       <c r="E6" s="106" t="inlineStr">
         <is>
-          <t>▲ +0.5%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Egypt</t>
+          <t xml:space="preserve">  3.  Algeria</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
@@ -7483,19 +7483,19 @@
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.338</v>
+        <v>0.3494</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2684</v>
-      </c>
-      <c r="K7" s="110" t="inlineStr">
-        <is>
-          <t>▼ -29.2%</t>
+        <v>0.2305</v>
+      </c>
+      <c r="K7" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="111" t="inlineStr">
+      <c r="A8" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  CAR</t>
         </is>
@@ -7516,9 +7516,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Algeria</t>
+      <c r="G8" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Egypt</t>
         </is>
       </c>
       <c r="H8" s="107" t="inlineStr">
@@ -7527,19 +7527,19 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.3494</v>
+        <v>0.4175</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K8" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.3479</v>
+      </c>
+      <c r="K8" s="106" t="inlineStr">
+        <is>
+          <t>▼ -12.5%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="113" t="inlineStr">
+      <c r="A9" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  5.  Comoros</t>
         </is>
@@ -7555,35 +7555,35 @@
       <c r="D9" s="98" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E9" s="110" t="inlineStr">
+      <c r="E9" s="106" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
       </c>
-      <c r="G9" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Nigeria</t>
+      <c r="G9" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Burundi</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6508</v>
+        <v>0.7887</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6508</v>
+        <v>1.3442</v>
       </c>
       <c r="K9" s="106" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▼ -41.5%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="111" t="inlineStr">
+      <c r="A10" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  Senegal</t>
         </is>
@@ -7599,35 +7599,35 @@
       <c r="D10" s="105" t="n">
         <v>1.25</v>
       </c>
-      <c r="E10" s="106" t="inlineStr">
+      <c r="E10" s="114" t="inlineStr">
         <is>
           <t>▲ +7.5%</t>
         </is>
       </c>
-      <c r="G10" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Burundi</t>
+      <c r="G10" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Niger</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.7887</v>
+        <v>0.8262</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>1.3442</v>
-      </c>
-      <c r="K10" s="110" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
+        <v>1.0232</v>
+      </c>
+      <c r="K10" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="113" t="inlineStr">
+      <c r="A11" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  7.  Somalia</t>
         </is>
@@ -7643,26 +7643,26 @@
       <c r="D11" s="98" t="n">
         <v>1.4</v>
       </c>
-      <c r="E11" s="106" t="inlineStr">
+      <c r="E11" s="114" t="inlineStr">
         <is>
           <t>▲ +39.1%</t>
         </is>
       </c>
-      <c r="G11" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Niger</t>
+      <c r="G11" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Tunisia</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8262</v>
+        <v>0.8377</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>1.0232</v>
+        <v>0.7318</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="111" t="inlineStr">
+      <c r="A12" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  8.  Rwanda</t>
         </is>
@@ -7687,35 +7687,35 @@
       <c r="D12" s="105" t="n">
         <v>1.5072</v>
       </c>
-      <c r="E12" s="106" t="inlineStr">
+      <c r="E12" s="114" t="inlineStr">
         <is>
           <t>▲ +15.0%</t>
         </is>
       </c>
-      <c r="G12" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Tunisia</t>
+      <c r="G12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Ghana</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8377</v>
+        <v>0.8452</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.7318</v>
-      </c>
-      <c r="K12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0255</v>
+      </c>
+      <c r="K12" s="106" t="inlineStr">
+        <is>
+          <t>▼ -7.5%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="113" t="inlineStr">
+      <c r="A13" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  9.  Sierra Leone</t>
         </is>
@@ -7731,14 +7731,14 @@
       <c r="D13" s="98" t="n">
         <v>1.7778</v>
       </c>
-      <c r="E13" s="106" t="inlineStr">
+      <c r="E13" s="114" t="inlineStr">
         <is>
           <t>▲ +9.4%</t>
         </is>
       </c>
-      <c r="G13" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Ghana</t>
+      <c r="G13" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Nigeria</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
@@ -7747,40 +7747,40 @@
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8452</v>
+        <v>0.863</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>1.0255</v>
-      </c>
-      <c r="K13" s="110" t="inlineStr">
-        <is>
-          <t>▼ -7.5%</t>
+        <v>0.863</v>
+      </c>
+      <c r="K13" s="114" t="inlineStr">
+        <is>
+          <t>▲ +47.2%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Botswana</t>
+      <c r="A14" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Kenya</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.551</v>
+        <v>1.5142</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>2.0679</v>
-      </c>
-      <c r="E14" s="106" t="inlineStr">
-        <is>
-          <t>▲ +35.8%</t>
-        </is>
-      </c>
-      <c r="G14" s="112" t="inlineStr">
+        <v>1.5067</v>
+      </c>
+      <c r="E14" s="114" t="inlineStr">
+        <is>
+          <t>▲ +8.3%</t>
+        </is>
+      </c>
+      <c r="G14" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Equatorial Guinea</t>
         </is>
@@ -7912,63 +7912,63 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.15</v>
+        <v>0.5861</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.6</v>
+        <v>0.863</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.45</v>
+        <v>0.2769</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.15</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.551</v>
+        <v>1.6</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +35.8%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.4085</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -8129,32 +8129,32 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.1425</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.6508</v>
+        <v>1.2555</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -8377,7 +8377,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
@@ -8387,28 +8387,28 @@
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>2.17</v>
+        <v>1.0555</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>2.1808</v>
+        <v>1.0582</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.5%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0108</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,90 +8418,90 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.31</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.0582</v>
-      </c>
-      <c r="F37" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
-        </is>
-      </c>
-      <c r="G37" s="117" t="n">
-        <v>0.0027</v>
+        <v>1.3037</v>
+      </c>
+      <c r="F37" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
+        </is>
+      </c>
+      <c r="G37" s="119" t="n">
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.31</v>
+        <v>1.2677</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3037</v>
+        <v>1.257</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0063</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.3289</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.257</v>
+        <v>1.3146</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
@@ -8511,121 +8511,121 @@
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2886</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3146</v>
+        <v>1.266</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.0722</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.266</v>
+        <v>1.0485</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.784</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.0485</v>
+        <v>1.6851</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0237</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.784</v>
+        <v>1.0641</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.6851</v>
+        <v>0.9982</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
@@ -8635,22 +8635,22 @@
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.0641</v>
+        <v>2.17</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>0.9982</v>
+        <v>2.0242</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.1458</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -8687,38 +8687,38 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.2212</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.9851</v>
+        <v>1.1258</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
@@ -8732,172 +8732,141 @@
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.2262</v>
       </c>
       <c r="E47" s="91" t="n">
         <v>1.1258</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.1004</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2332</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.1258</v>
+        <v>1.1154</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1004</v>
+        <v>-0.1178</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.1939</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.1154</v>
+        <v>1.0606</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.6%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1178</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.1939</v>
+        <v>0.4771</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.0606</v>
+        <v>0.4175</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.0596</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.3479</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.338</v>
+        <v>0.7887</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -41.5%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.1391</v>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="62" t="inlineStr">
-        <is>
-          <t>Burundi</t>
-        </is>
-      </c>
-      <c r="B52" s="63" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="C52" s="118" t="inlineStr">
-        <is>
-          <t>BIF</t>
-        </is>
-      </c>
-      <c r="D52" s="88" t="n">
-        <v>1.3479</v>
-      </c>
-      <c r="E52" s="89" t="n">
-        <v>0.7887</v>
-      </c>
-      <c r="F52" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
-        </is>
-      </c>
-      <c r="G52" s="119" t="n">
         <v>-0.5592</v>
       </c>
     </row>
@@ -8955,10 +8924,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.6631666666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.6135833333333333</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9057,20 +9026,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.338</v>
+        <v>0.4175</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.3479</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9231,13 +9200,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.2000875</v>
+        <v>1.21335</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.14298125</v>
+        <v>1.15106875</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6508</v>
+        <v>0.8262</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9608,13 +9577,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9707,20 +9676,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6508</v>
+        <v>0.863</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6508</v>
+        <v>0.863</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1055</v>
+        <v>1399</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1055</v>
+        <v>1399</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9847,10 +9816,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2173625</v>
+        <v>1.2275</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1930875</v>
+        <v>1.191225</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10119,20 +10088,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>585</v>
-      </c>
-      <c r="G42" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>576</v>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10194,7 +10163,7 @@
         <v>1.490733333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.479813333333333</v>
+        <v>1.479466666666666</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>0.7887</v>
@@ -10704,13 +10673,13 @@
         <v>1.4096</v>
       </c>
       <c r="D61" s="66" t="n">
-        <v>1.4096</v>
+        <v>1.4044</v>
       </c>
       <c r="E61" s="67" t="n">
         <v>3820</v>
       </c>
       <c r="F61" s="67" t="n">
-        <v>3820</v>
+        <v>3806</v>
       </c>
       <c r="G61" s="71" t="inlineStr">
         <is>
@@ -10773,16 +10742,16 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.199544444444444</v>
+        <v>1.149311111111111</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.205577777777778</v>
+        <v>1.123522222222222</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
       </c>
       <c r="F65" s="153" t="n">
-        <v>2.1808</v>
+        <v>2.0242</v>
       </c>
       <c r="G65" s="150" t="n"/>
       <c r="H65" s="150" t="n"/>
@@ -10875,20 +10844,20 @@
         </is>
       </c>
       <c r="C68" s="66" t="n">
-        <v>1.551</v>
+        <v>1.2555</v>
       </c>
       <c r="D68" s="66" t="n">
-        <v>2.0679</v>
+        <v>1.3294</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F68" s="67" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G68" s="71" t="inlineStr">
         <is>
-          <t>▲ +35.8%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="H68" s="70" t="inlineStr">
@@ -11113,20 +11082,20 @@
         </is>
       </c>
       <c r="C75" s="57" t="n">
-        <v>2.1808</v>
+        <v>2.0242</v>
       </c>
       <c r="D75" s="57" t="n">
         <v>1.9231</v>
       </c>
       <c r="E75" s="58" t="n">
-        <v>56.7</v>
+        <v>52.63</v>
       </c>
       <c r="F75" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="G75" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.5%</t>
+      <c r="G75" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="H75" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-18</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-20</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.221</t>
+          <t>$1.217</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.184</t>
+          <t>$1.177</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6631666666666667</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6135833333333333</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.21335</v>
+        <v>1.2000875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.15106875</v>
+        <v>1.12259375</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.8262</v>
+        <v>0.6508</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1834,7 +1834,7 @@
         <v>1.490733333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.479466666666666</v>
+        <v>1.479813333333333</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.7887</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.149311111111111</v>
+        <v>1.157333333333333</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.123522222222222</v>
+        <v>1.139955555555556</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-18</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.338</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.3479</v>
+        <v>0.2684</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2682,13 +2682,13 @@
         <v>1.3576</v>
       </c>
       <c r="F18" s="57" t="n">
-        <v>1.4437</v>
+        <v>1.1175</v>
       </c>
       <c r="G18" s="58" t="n">
         <v>820</v>
       </c>
       <c r="H18" s="58" t="n">
-        <v>872</v>
+        <v>675</v>
       </c>
       <c r="I18" s="59" t="n">
         <v>604</v>
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.863</v>
+        <v>0.6508</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.863</v>
+        <v>0.6508</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1399</v>
+        <v>1055</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1399</v>
+        <v>1055</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -4106,13 +4106,13 @@
         <v>1.4096</v>
       </c>
       <c r="F50" s="57" t="n">
-        <v>1.4044</v>
+        <v>1.4096</v>
       </c>
       <c r="G50" s="58" t="n">
         <v>3820</v>
       </c>
       <c r="H50" s="58" t="n">
-        <v>3806</v>
+        <v>3820</v>
       </c>
       <c r="I50" s="59" t="n">
         <v>2710</v>
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
       <c r="J55" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="K55" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.1154</v>
+        <v>1.3736</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.0181</v>
+        <v>1.3736</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>18.53</v>
+        <v>25</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+      <c r="J59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.220692592592592</v>
+        <v>1.216627777777777</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.183927777777778</v>
+        <v>1.176853703703704</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-18</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.4175</v>
+        <v>0.338</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.3479</v>
+        <v>0.2684</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -14.7%</t>
+          <t>▼ -34.1%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -5399,18 +5399,18 @@
         <v>1.1185</v>
       </c>
       <c r="G19" s="89" t="n">
-        <v>1.4437</v>
-      </c>
-      <c r="H19" s="71" t="inlineStr">
-        <is>
-          <t>▲ +29.1%</t>
+        <v>1.1175</v>
+      </c>
+      <c r="H19" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I19" s="67" t="n">
         <v>820</v>
       </c>
       <c r="J19" s="67" t="n">
-        <v>872</v>
+        <v>675</v>
       </c>
       <c r="K19" s="70" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2003</v>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2831</v>
+      </c>
+      <c r="H21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.863</v>
+        <v>0.6508</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>▲ +16.6%</t>
+        <v>0.6508</v>
+      </c>
+      <c r="H24" s="69" t="inlineStr">
+        <is>
+          <t>▼ -12.1%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1399</v>
+        <v>1055</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1399</v>
+        <v>1055</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6763,18 +6763,18 @@
         <v>1.021</v>
       </c>
       <c r="G51" s="89" t="n">
-        <v>1.4044</v>
+        <v>1.4096</v>
       </c>
       <c r="H51" s="71" t="inlineStr">
         <is>
-          <t>▲ +37.5%</t>
+          <t>▲ +38.1%</t>
         </is>
       </c>
       <c r="I51" s="67" t="n">
         <v>3820</v>
       </c>
       <c r="J51" s="67" t="n">
-        <v>3806</v>
+        <v>3820</v>
       </c>
       <c r="K51" s="70" t="inlineStr">
         <is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="H56" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -24.8%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.1154</v>
-      </c>
-      <c r="E60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="E60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.0181</v>
-      </c>
-      <c r="H60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -21.0%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="H60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>18.53</v>
+        <v>25</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Algeria</t>
+          <t xml:space="preserve">  3.  Egypt</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
@@ -7483,14 +7483,14 @@
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.3494</v>
+        <v>0.338</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K7" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2684</v>
+      </c>
+      <c r="K7" s="106" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="G8" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  Egypt</t>
+          <t xml:space="preserve">  4.  Algeria</t>
         </is>
       </c>
       <c r="H8" s="107" t="inlineStr">
@@ -7527,14 +7527,14 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.4175</v>
+        <v>0.3494</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.3479</v>
-      </c>
-      <c r="K8" s="106" t="inlineStr">
-        <is>
-          <t>▼ -12.5%</t>
+        <v>0.2305</v>
+      </c>
+      <c r="K8" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7562,23 +7562,23 @@
       </c>
       <c r="G9" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Burundi</t>
+          <t xml:space="preserve">  5.  Nigeria</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.7887</v>
+        <v>0.6508</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>1.3442</v>
-      </c>
-      <c r="K9" s="106" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
+        <v>0.6508</v>
+      </c>
+      <c r="K9" s="114" t="inlineStr">
+        <is>
+          <t>▲ +11.0%</t>
         </is>
       </c>
     </row>
@@ -7606,23 +7606,23 @@
       </c>
       <c r="G10" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Niger</t>
+          <t xml:space="preserve">  6.  Burundi</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.8262</v>
+        <v>0.7887</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K10" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.3442</v>
+      </c>
+      <c r="K10" s="106" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
         </is>
       </c>
     </row>
@@ -7650,19 +7650,19 @@
       </c>
       <c r="G11" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Tunisia</t>
+          <t xml:space="preserve">  7.  Niger</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8377</v>
+        <v>0.8262</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.7318</v>
+        <v>1.0232</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7694,23 +7694,23 @@
       </c>
       <c r="G12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Ghana</t>
+          <t xml:space="preserve">  8.  Tunisia</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8452</v>
+        <v>0.8377</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>1.0255</v>
-      </c>
-      <c r="K12" s="106" t="inlineStr">
-        <is>
-          <t>▼ -7.5%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Nigeria</t>
+          <t xml:space="preserve">  9.  Ghana</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
@@ -7747,14 +7747,14 @@
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.863</v>
+        <v>0.8452</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="K13" s="114" t="inlineStr">
-        <is>
-          <t>▲ +47.2%</t>
+        <v>1.0255</v>
+      </c>
+      <c r="K13" s="106" t="inlineStr">
+        <is>
+          <t>▼ -7.5%</t>
         </is>
       </c>
     </row>
@@ -7782,23 +7782,23 @@
       </c>
       <c r="G14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Equatorial Guinea</t>
+          <t xml:space="preserve">  10.  Eswatini</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.9106</v>
+        <v>0.8625</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8609</v>
-      </c>
-      <c r="K14" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8625</v>
+      </c>
+      <c r="K14" s="106" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
@@ -7912,38 +7912,38 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.15</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>0.863</v>
+        <v>1.6</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.2769</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
@@ -7953,338 +7953,338 @@
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.15</v>
+        <v>1.0616</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.6</v>
+        <v>1.4096</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.45</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.0882</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.4096</v>
+        <v>1.3014</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.348</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0316</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.3014</v>
+        <v>1.2129</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.3691</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.2129</v>
+        <v>1.5742</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.3691</v>
+        <v>0.8608</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.5742</v>
+        <v>0.9639</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.2332</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.3736</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.1425</v>
+        <v>0.5861</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.2555</v>
+        <v>0.6508</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.113</v>
+        <v>0.06469999999999999</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.1425</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.5556</v>
+        <v>1.2555</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.4222</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.5142</v>
+        <v>1.5556</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3986</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.5142</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.5244</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.4968</v>
+        <v>1.6391</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,121 +8294,121 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.4106</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.421</v>
+        <v>1.4968</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.3819</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.2961</v>
+        <v>1.421</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0199</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.2762</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.2961</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3681</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.0582</v>
+        <v>1.3873</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,90 +8418,90 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0555</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F37" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G37" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F37" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G37" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.31</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.257</v>
+        <v>1.3037</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2677</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3146</v>
+        <v>1.257</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
@@ -8511,53 +8511,53 @@
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3289</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.266</v>
+        <v>1.3146</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.2886</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.0485</v>
+        <v>1.266</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0237</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -8749,63 +8749,63 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.1939</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.1154</v>
+        <v>1.0606</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.6%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1178</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.0722</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.0606</v>
+        <v>0.8625</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -8828,15 +8828,15 @@
         <v>0.4771</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>0.4175</v>
+        <v>0.338</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.0596</v>
+        <v>-0.1391</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -8924,10 +8924,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6631666666666667</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6135833333333333</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9026,20 +9026,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.338</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.3479</v>
+        <v>0.2684</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9200,13 +9200,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.21335</v>
+        <v>1.2000875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.15106875</v>
+        <v>1.12259375</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.8262</v>
+        <v>0.6508</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9509,13 +9509,13 @@
         <v>1.3576</v>
       </c>
       <c r="D23" s="66" t="n">
-        <v>1.4437</v>
+        <v>1.1175</v>
       </c>
       <c r="E23" s="67" t="n">
         <v>820</v>
       </c>
       <c r="F23" s="67" t="n">
-        <v>872</v>
+        <v>675</v>
       </c>
       <c r="G23" s="60" t="inlineStr">
         <is>
@@ -9577,13 +9577,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9676,20 +9676,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.863</v>
+        <v>0.6508</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.863</v>
+        <v>0.6508</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1399</v>
+        <v>1055</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1399</v>
+        <v>1055</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -10163,7 +10163,7 @@
         <v>1.490733333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.479466666666666</v>
+        <v>1.479813333333333</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>0.7887</v>
@@ -10673,13 +10673,13 @@
         <v>1.4096</v>
       </c>
       <c r="D61" s="66" t="n">
-        <v>1.4044</v>
+        <v>1.4096</v>
       </c>
       <c r="E61" s="67" t="n">
         <v>3820</v>
       </c>
       <c r="F61" s="67" t="n">
-        <v>3806</v>
+        <v>3820</v>
       </c>
       <c r="G61" s="71" t="inlineStr">
         <is>
@@ -10742,10 +10742,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.149311111111111</v>
+        <v>1.157333333333333</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.123522222222222</v>
+        <v>1.139955555555556</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10878,20 +10878,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="G69" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">
@@ -11014,20 +11014,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.1154</v>
+        <v>1.3736</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.0181</v>
+        <v>1.3736</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="G73" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+        <v>25</v>
+      </c>
+      <c r="G73" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-20</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-21</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.217</t>
+          <t>$1.213</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.177</t>
+          <t>$1.176</t>
         </is>
       </c>
     </row>
@@ -1787,10 +1787,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.2000875</v>
+        <v>1.20020625</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.12259375</v>
+        <v>1.1214</v>
       </c>
       <c r="F13" s="32" t="n">
         <v>0.6508</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2275</v>
+        <v>1.2173625</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.191225</v>
+        <v>1.1930875</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.157333333333333</v>
+        <v>1.143122222222222</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.139955555555556</v>
+        <v>1.1324</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-20</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2538,23 +2538,23 @@
         </is>
       </c>
       <c r="E15" s="66" t="n">
-        <v>0.8452</v>
+        <v>0.8471</v>
       </c>
       <c r="F15" s="66" t="n">
-        <v>1.0255</v>
+        <v>1.0892</v>
       </c>
       <c r="G15" s="67" t="n">
-        <v>13.27</v>
+        <v>13.3</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>16.1</v>
+        <v>17.1</v>
       </c>
       <c r="I15" s="68" t="n">
         <v>15.7</v>
       </c>
       <c r="J15" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.5%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="K15" s="70" t="inlineStr">
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J34" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
       <c r="J55" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="K55" s="70" t="inlineStr">
@@ -4392,23 +4392,23 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>1.3037</v>
+        <v>1.248</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>1.2462</v>
+        <v>1.3261</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>83.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>79.88</v>
+        <v>85</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="J57" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="K57" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.1154</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.0181</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>25</v>
+        <v>18.53</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+      <c r="J59" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.216627777777777</v>
+        <v>1.212792592592592</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.176853703703704</v>
+        <v>1.175516666666667</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-20</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-21</t>
         </is>
       </c>
     </row>
@@ -5253,29 +5253,29 @@
         <v>0.914</v>
       </c>
       <c r="D16" s="91" t="n">
-        <v>0.8452</v>
+        <v>0.8471</v>
       </c>
       <c r="E16" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.5%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="F16" s="90" t="n">
         <v>0.914</v>
       </c>
       <c r="G16" s="91" t="n">
-        <v>1.0255</v>
+        <v>1.0892</v>
       </c>
       <c r="H16" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.2%</t>
+          <t>▲ +19.2%</t>
         </is>
       </c>
       <c r="I16" s="58" t="n">
-        <v>13.27</v>
+        <v>13.3</v>
       </c>
       <c r="J16" s="58" t="n">
-        <v>16.1</v>
+        <v>17.1</v>
       </c>
       <c r="K16" s="61" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2831</v>
-      </c>
-      <c r="H21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.9%</t>
+        <v>1.2003</v>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>1.0662</v>
-      </c>
-      <c r="E35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9851</v>
+      </c>
+      <c r="E35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9536</v>
-      </c>
-      <c r="H35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9685</v>
+      </c>
+      <c r="H35" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.5%</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="H56" s="69" t="inlineStr">
         <is>
-          <t>▼ -24.8%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>1.3037</v>
+        <v>1.248</v>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>1.2462</v>
-      </c>
-      <c r="H58" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.3%</t>
+        <v>1.3261</v>
+      </c>
+      <c r="H58" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>83.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>79.88</v>
+        <v>85</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="E60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>1.1154</v>
+      </c>
+      <c r="E60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="H60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+        <v>1.0181</v>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -21.0%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>25</v>
+        <v>18.53</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7747,14 +7747,14 @@
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8452</v>
+        <v>0.8471</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>1.0255</v>
+        <v>1.0892</v>
       </c>
       <c r="K13" s="106" t="inlineStr">
         <is>
-          <t>▼ -7.5%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
@@ -7782,23 +7782,23 @@
       </c>
       <c r="G14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Eswatini</t>
+          <t xml:space="preserve">  10.  Equatorial Guinea</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.8625</v>
+        <v>0.9106</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="K14" s="106" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+        <v>0.8609</v>
+      </c>
+      <c r="K14" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8098,193 +8098,193 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.2332</v>
+        <v>0.5861</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.3736</v>
+        <v>0.6508</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.06469999999999999</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.1425</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.6508</v>
+        <v>1.2555</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.4222</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.2555</v>
+        <v>1.5556</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.3986</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.5556</v>
+        <v>1.5142</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.5244</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.5142</v>
+        <v>1.6391</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.4106</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.6391</v>
+        <v>1.4968</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,270 +8294,270 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3819</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.4968</v>
+        <v>1.421</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.2762</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.421</v>
+        <v>1.2961</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.3681</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.2961</v>
+        <v>1.3873</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0199</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.0555</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3873</v>
+        <v>1.0582</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.2677</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.0582</v>
-      </c>
-      <c r="F37" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
-        </is>
-      </c>
-      <c r="G37" s="117" t="n">
-        <v>0.0027</v>
+        <v>1.257</v>
+      </c>
+      <c r="F37" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
+        </is>
+      </c>
+      <c r="G37" s="119" t="n">
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.31</v>
+        <v>1.3289</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3037</v>
+        <v>1.3146</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0063</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.2886</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.257</v>
+        <v>1.266</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.0722</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3146</v>
+        <v>1.0485</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.31</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.266</v>
+        <v>1.248</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.062</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -8673,52 +8673,52 @@
         <v>0.914</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.8452</v>
+        <v>0.8471</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.5%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0688</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0671</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>1.1258</v>
+        <v>0.9851</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
@@ -8732,55 +8732,55 @@
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2212</v>
       </c>
       <c r="E47" s="91" t="n">
         <v>1.1258</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.1004</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2262</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.0606</v>
+        <v>1.1258</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.1004</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
@@ -8790,83 +8790,114 @@
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.2332</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>0.8625</v>
+        <v>1.1154</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.1178</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.1939</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>0.338</v>
+        <v>1.0606</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.1391</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B51" s="54" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="C51" s="116" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="D51" s="88" t="n">
+        <v>0.4771</v>
+      </c>
+      <c r="E51" s="91" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="F51" s="69" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
+        </is>
+      </c>
+      <c r="G51" s="119" t="n">
+        <v>-0.1391</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="62" t="inlineStr">
+        <is>
           <t>Burundi</t>
         </is>
       </c>
-      <c r="B51" s="54" t="inlineStr">
+      <c r="B52" s="63" t="inlineStr">
         <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C51" s="116" t="inlineStr">
+      <c r="C52" s="118" t="inlineStr">
         <is>
           <t>BIF</t>
         </is>
       </c>
-      <c r="D51" s="88" t="n">
+      <c r="D52" s="88" t="n">
         <v>1.3479</v>
       </c>
-      <c r="E51" s="91" t="n">
+      <c r="E52" s="89" t="n">
         <v>0.7887</v>
       </c>
-      <c r="F51" s="69" t="inlineStr">
+      <c r="F52" s="69" t="inlineStr">
         <is>
           <t>▼ -41.5%</t>
         </is>
       </c>
-      <c r="G51" s="119" t="n">
+      <c r="G52" s="119" t="n">
         <v>-0.5592</v>
       </c>
     </row>
@@ -9200,10 +9231,10 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.2000875</v>
+        <v>1.20020625</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.12259375</v>
+        <v>1.1214</v>
       </c>
       <c r="E14" s="131" t="n">
         <v>0.6508</v>
@@ -9404,20 +9435,20 @@
         </is>
       </c>
       <c r="C20" s="57" t="n">
-        <v>0.8452</v>
+        <v>0.8471</v>
       </c>
       <c r="D20" s="57" t="n">
-        <v>1.0255</v>
+        <v>1.0892</v>
       </c>
       <c r="E20" s="58" t="n">
-        <v>13.27</v>
+        <v>13.3</v>
       </c>
       <c r="F20" s="58" t="n">
-        <v>16.1</v>
+        <v>17.1</v>
       </c>
       <c r="G20" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.5%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="H20" s="61" t="inlineStr">
@@ -9577,13 +9608,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9816,10 +9847,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2275</v>
+        <v>1.2173625</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.191225</v>
+        <v>1.1930875</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10088,20 +10119,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>576</v>
-      </c>
-      <c r="G42" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>585</v>
+      </c>
+      <c r="G42" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10742,10 +10773,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.157333333333333</v>
+        <v>1.143122222222222</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.139955555555556</v>
+        <v>1.1324</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10878,20 +10909,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>0.8625</v>
+        <v>1.0485</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>0.8625</v>
+        <v>1.0701</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>16</v>
+        <v>19.45</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>16</v>
+        <v>19.85</v>
       </c>
       <c r="G69" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">
@@ -10946,20 +10977,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>1.3037</v>
+        <v>1.248</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>1.2462</v>
+        <v>1.3261</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>83.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>79.88</v>
+        <v>85</v>
       </c>
       <c r="G71" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">
@@ -11014,20 +11045,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.1154</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.0181</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>25</v>
-      </c>
-      <c r="G73" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>18.53</v>
+      </c>
+      <c r="G73" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-21</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-22</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.213</t>
+          <t>$1.211</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.176</t>
+          <t>$1.178</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.6399666666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.6019833333333334</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.20020625</v>
+        <v>1.2002875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.1214</v>
+        <v>1.12665625</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2173625</v>
+        <v>1.17085</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1930875</v>
+        <v>1.1611125</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.143122222222222</v>
+        <v>1.178</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.1324</v>
+        <v>1.163022222222222</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-21</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-22</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.338</v>
+        <v>0.2783</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.2783</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -41.7%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>1.3023</v>
+        <v>0.9302</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>1.186</v>
+        <v>0.9302</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -4392,23 +4392,23 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>1.248</v>
+        <v>1.3037</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>1.3261</v>
+        <v>1.2462</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>80</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>85</v>
+        <v>79.88</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="J57" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="K57" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.1154</v>
+        <v>1.3736</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.0181</v>
+        <v>1.3736</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>18.53</v>
+        <v>25</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+      <c r="J59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.212792592592592</v>
+        <v>1.210633333333333</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.175516666666667</v>
+        <v>1.177624074074074</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-21</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-22</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.338</v>
+        <v>0.2783</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -41.7%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2684</v>
+        <v>0.2783</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -34.1%</t>
+          <t>▼ -31.7%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2003</v>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2831</v>
+      </c>
+      <c r="H21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="H24" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.1%</t>
+          <t>▼ -11.9%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>1.3023</v>
-      </c>
-      <c r="E36" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9302</v>
+      </c>
+      <c r="E36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>1.186</v>
-      </c>
-      <c r="H36" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9302</v>
+      </c>
+      <c r="H36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -21.6%</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>1.248</v>
+        <v>1.3037</v>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>1.3261</v>
-      </c>
-      <c r="H58" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.1%</t>
+        <v>1.2462</v>
+      </c>
+      <c r="H58" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.3%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>80</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>85</v>
+        <v>79.88</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.1154</v>
-      </c>
-      <c r="E60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="E60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.0181</v>
-      </c>
-      <c r="H60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -21.0%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="H60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>18.53</v>
+        <v>25</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7430,23 +7430,23 @@
       </c>
       <c r="G6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Angola</t>
+          <t xml:space="preserve">  2.  Egypt</t>
         </is>
       </c>
       <c r="H6" s="107" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I6" s="108" t="n">
-        <v>0.3272</v>
+        <v>0.2783</v>
       </c>
       <c r="J6" s="109" t="n">
-        <v>0.2181</v>
-      </c>
-      <c r="K6" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2783</v>
+      </c>
+      <c r="K6" s="106" t="inlineStr">
+        <is>
+          <t>▼ -41.7%</t>
         </is>
       </c>
     </row>
@@ -7474,23 +7474,23 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Egypt</t>
+          <t xml:space="preserve">  3.  Angola</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.338</v>
+        <v>0.3272</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2684</v>
-      </c>
-      <c r="K7" s="106" t="inlineStr">
-        <is>
-          <t>▼ -29.2%</t>
+        <v>0.2181</v>
+      </c>
+      <c r="K7" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7571,14 +7571,14 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="K9" s="114" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
     </row>
@@ -8098,193 +8098,193 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.2332</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>0.6508</v>
+        <v>1.3736</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.1425</v>
+        <v>0.5861</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.2555</v>
+        <v>0.6521</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.113</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.1425</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.5556</v>
+        <v>1.2555</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.4222</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.5142</v>
+        <v>1.5556</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3986</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.5142</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.5244</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.4968</v>
+        <v>1.6391</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,338 +8294,338 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.4106</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.421</v>
+        <v>1.4968</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.3819</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.2961</v>
+        <v>1.421</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0199</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.2762</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.2961</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3681</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.0582</v>
+        <v>1.3873</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.0555</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.257</v>
-      </c>
-      <c r="F37" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.8%</t>
-        </is>
-      </c>
-      <c r="G37" s="119" t="n">
-        <v>-0.0107</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F37" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G37" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.31</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3146</v>
+        <v>1.3037</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.2677</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.266</v>
+        <v>1.257</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.3289</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.0485</v>
+        <v>1.3146</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0237</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.31</v>
+        <v>1.2886</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.248</v>
+        <v>1.266</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.062</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.784</v>
+        <v>1.0722</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.6851</v>
+        <v>1.0485</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.784</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>0.9982</v>
+        <v>1.6851</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
@@ -8635,121 +8635,121 @@
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>2.17</v>
+        <v>1.0641</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>2.0242</v>
+        <v>0.9982</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.1458</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>0.914</v>
+        <v>2.17</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.8471</v>
+        <v>2.0242</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.1458</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.0671</v>
+        <v>0.914</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.9851</v>
+        <v>0.8471</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0671</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.1258</v>
+        <v>0.9851</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
@@ -8763,49 +8763,49 @@
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2212</v>
       </c>
       <c r="E48" s="89" t="n">
         <v>1.1258</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1004</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.2262</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.1154</v>
+        <v>1.1258</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.6%</t>
+          <t>▼ -8.2%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1178</v>
+        <v>-0.1004</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -8842,32 +8842,32 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Sao Tome</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>STN</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.3023</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.338</v>
+        <v>0.9302</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.1391</v>
+        <v>-0.3721</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -8899,6 +8899,37 @@
       </c>
       <c r="G52" s="119" t="n">
         <v>-0.5592</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="53" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B53" s="54" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="C53" s="116" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="D53" s="88" t="n">
+        <v>0.4771</v>
+      </c>
+      <c r="E53" s="91" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="F53" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.7%</t>
+        </is>
+      </c>
+      <c r="G53" s="119" t="n">
+        <v>-0.1988</v>
       </c>
     </row>
   </sheetData>
@@ -8955,10 +8986,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.6399666666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.6019833333333334</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9057,20 +9088,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.338</v>
+        <v>0.2783</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.2783</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -41.7%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9231,13 +9262,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.20020625</v>
+        <v>1.2002875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.1214</v>
+        <v>1.12665625</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9608,13 +9639,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9707,20 +9738,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9847,10 +9878,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2173625</v>
+        <v>1.17085</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1930875</v>
+        <v>1.1611125</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10153,20 +10184,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>1.3023</v>
+        <v>0.9302</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>1.186</v>
+        <v>0.9302</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G43" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>20</v>
+      </c>
+      <c r="G43" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">
@@ -10773,10 +10804,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.143122222222222</v>
+        <v>1.178</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.1324</v>
+        <v>1.163022222222222</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10977,20 +11008,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>1.248</v>
+        <v>1.3037</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>1.3261</v>
+        <v>1.2462</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>80</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>85</v>
+        <v>79.88</v>
       </c>
       <c r="G71" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">
@@ -11045,20 +11076,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.1154</v>
+        <v>1.3736</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.0181</v>
+        <v>1.3736</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="G73" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+        <v>25</v>
+      </c>
+      <c r="G73" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1094,11 +1094,11 @@
     <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-22</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-23</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.178</t>
+          <t>$1.186</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6399666666666667</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6019833333333334</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.2002875</v>
+        <v>1.17445</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.12665625</v>
+        <v>1.1438625</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6521</v>
+        <v>0.7779</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.17085</v>
+        <v>1.279825</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1611125</v>
+        <v>1.2464625</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.178</v>
+        <v>1.122455555555556</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.163022222222222</v>
+        <v>1.109333333333333</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-22</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-23</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.338</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.2684</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.7%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2350,23 +2350,23 @@
         </is>
       </c>
       <c r="E11" s="66" t="n">
-        <v>1.1258</v>
+        <v>1.0927</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>1.1589</v>
+        <v>0.9603</v>
       </c>
       <c r="G11" s="67" t="n">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
       </c>
       <c r="J11" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -10.9%</t>
         </is>
       </c>
       <c r="K11" s="70" t="inlineStr">
@@ -2397,23 +2397,23 @@
         </is>
       </c>
       <c r="E12" s="57" t="n">
-        <v>1.3919</v>
+        <v>0.8858</v>
       </c>
       <c r="F12" s="57" t="n">
-        <v>1.1997</v>
+        <v>1.6374</v>
       </c>
       <c r="G12" s="58" t="n">
-        <v>840</v>
+        <v>535</v>
       </c>
       <c r="H12" s="58" t="n">
-        <v>724</v>
+        <v>989</v>
       </c>
       <c r="I12" s="59" t="n">
-        <v>603.5</v>
-      </c>
-      <c r="J12" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>604</v>
+      </c>
+      <c r="J12" s="69" t="inlineStr">
+        <is>
+          <t>▼ -36.4%</t>
         </is>
       </c>
       <c r="K12" s="61" t="inlineStr">
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.7779</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.7711</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1057</v>
+        <v>1261</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1057</v>
+        <v>1250</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+      <c r="J34" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.7209</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.6279</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+      <c r="J35" s="71" t="inlineStr">
+        <is>
+          <t>▲ +32.1%</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
       <c r="J55" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="K55" s="70" t="inlineStr">
@@ -4392,23 +4392,23 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>1.3037</v>
+        <v>1.248</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>1.2462</v>
+        <v>1.3261</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>83.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>79.88</v>
+        <v>85</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="J57" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="K57" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.1154</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.0181</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>25</v>
+        <v>18.53</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+      <c r="J59" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.210633333333333</v>
+        <v>1.21097037037037</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.177624074074074</v>
+        <v>1.186235185185185</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-22</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-23</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.2783</v>
+        <v>0.338</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.7%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2783</v>
+        <v>0.2684</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -31.7%</t>
+          <t>▼ -34.1%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -5073,29 +5073,29 @@
         <v>1.2262</v>
       </c>
       <c r="D12" s="91" t="n">
-        <v>1.1258</v>
+        <v>1.0927</v>
       </c>
       <c r="E12" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -10.9%</t>
         </is>
       </c>
       <c r="F12" s="90" t="n">
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>1.1589</v>
+        <v>0.9603</v>
       </c>
       <c r="H12" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.0%</t>
+          <t>▼ -23.7%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -5118,29 +5118,29 @@
         <v>1.3919</v>
       </c>
       <c r="D13" s="89" t="n">
-        <v>1.3919</v>
-      </c>
-      <c r="E13" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8858</v>
+      </c>
+      <c r="E13" s="69" t="inlineStr">
+        <is>
+          <t>▼ -36.4%</t>
         </is>
       </c>
       <c r="F13" s="90" t="n">
         <v>1.1997</v>
       </c>
       <c r="G13" s="89" t="n">
-        <v>1.1997</v>
-      </c>
-      <c r="H13" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.6374</v>
+      </c>
+      <c r="H13" s="71" t="inlineStr">
+        <is>
+          <t>▲ +36.5%</t>
         </is>
       </c>
       <c r="I13" s="67" t="n">
-        <v>840</v>
+        <v>535</v>
       </c>
       <c r="J13" s="67" t="n">
-        <v>724</v>
+        <v>989</v>
       </c>
       <c r="K13" s="70" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2831</v>
-      </c>
-      <c r="H21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.9%</t>
+        <v>1.2003</v>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6521</v>
+        <v>0.7779</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="H24" s="69" t="inlineStr">
-        <is>
-          <t>▼ -11.9%</t>
+        <v>0.7711</v>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +4.2%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1057</v>
+        <v>1261</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1057</v>
+        <v>1250</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="E35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>1.0662</v>
+      </c>
+      <c r="E35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9685</v>
-      </c>
-      <c r="H35" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.5%</t>
+        <v>0.9536</v>
+      </c>
+      <c r="H35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="E36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>1.7209</v>
+      </c>
+      <c r="E36" s="71" t="inlineStr">
+        <is>
+          <t>▲ +32.1%</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="H36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -21.6%</t>
+        <v>1.6279</v>
+      </c>
+      <c r="H36" s="71" t="inlineStr">
+        <is>
+          <t>▲ +37.3%</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="H56" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -24.8%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>1.3037</v>
+        <v>1.248</v>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>1.2462</v>
-      </c>
-      <c r="H58" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.3%</t>
+        <v>1.3261</v>
+      </c>
+      <c r="H58" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>83.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>79.88</v>
+        <v>85</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="E60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>1.1154</v>
+      </c>
+      <c r="E60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.3736</v>
-      </c>
-      <c r="H60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+        <v>1.0181</v>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -21.0%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>25</v>
+        <v>18.53</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7430,23 +7430,23 @@
       </c>
       <c r="G6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Egypt</t>
+          <t xml:space="preserve">  2.  Angola</t>
         </is>
       </c>
       <c r="H6" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I6" s="108" t="n">
-        <v>0.2783</v>
+        <v>0.3272</v>
       </c>
       <c r="J6" s="109" t="n">
-        <v>0.2783</v>
-      </c>
-      <c r="K6" s="106" t="inlineStr">
-        <is>
-          <t>▼ -41.7%</t>
+        <v>0.2181</v>
+      </c>
+      <c r="K6" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7474,23 +7474,23 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Angola</t>
+          <t xml:space="preserve">  3.  Egypt</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.3272</v>
+        <v>0.338</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2181</v>
-      </c>
-      <c r="K7" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2684</v>
+      </c>
+      <c r="K7" s="106" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
         </is>
       </c>
     </row>
@@ -7541,26 +7541,26 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Comoros</t>
+          <t xml:space="preserve">  5.  Sao Tome</t>
         </is>
       </c>
       <c r="B9" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C9" s="97" t="n">
-        <v>1.6851</v>
+        <v>1.7209</v>
       </c>
       <c r="D9" s="98" t="n">
-        <v>1.5078</v>
-      </c>
-      <c r="E9" s="106" t="inlineStr">
-        <is>
-          <t>▼ -5.5%</t>
-        </is>
-      </c>
-      <c r="G9" s="113" t="inlineStr">
+        <v>1.6279</v>
+      </c>
+      <c r="E9" s="113" t="inlineStr">
+        <is>
+          <t>▲ +32.1%</t>
+        </is>
+      </c>
+      <c r="G9" s="114" t="inlineStr">
         <is>
           <t xml:space="preserve">  5.  Nigeria</t>
         </is>
@@ -7571,37 +7571,37 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6521</v>
+        <v>0.7779</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="K9" s="114" t="inlineStr">
-        <is>
-          <t>▲ +11.3%</t>
+        <v>0.7711</v>
+      </c>
+      <c r="K9" s="113" t="inlineStr">
+        <is>
+          <t>▲ +32.7%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Senegal</t>
+          <t xml:space="preserve">  6.  Comoros</t>
         </is>
       </c>
       <c r="B10" s="103" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C10" s="104" t="n">
-        <v>1.6391</v>
+        <v>1.6851</v>
       </c>
       <c r="D10" s="105" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E10" s="114" t="inlineStr">
-        <is>
-          <t>▲ +7.5%</t>
+        <v>1.5078</v>
+      </c>
+      <c r="E10" s="106" t="inlineStr">
+        <is>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G10" s="111" t="inlineStr">
@@ -7629,26 +7629,26 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Somalia</t>
+          <t xml:space="preserve">  7.  Senegal</t>
         </is>
       </c>
       <c r="B11" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C11" s="97" t="n">
-        <v>1.6</v>
+        <v>1.6391</v>
       </c>
       <c r="D11" s="98" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E11" s="114" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
-        </is>
-      </c>
-      <c r="G11" s="113" t="inlineStr">
+        <v>1.25</v>
+      </c>
+      <c r="E11" s="113" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
+        </is>
+      </c>
+      <c r="G11" s="114" t="inlineStr">
         <is>
           <t xml:space="preserve">  7.  Niger</t>
         </is>
@@ -7673,7 +7673,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Rwanda</t>
+          <t xml:space="preserve">  8.  Somalia</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
@@ -7682,14 +7682,14 @@
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.5742</v>
+        <v>1.6</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="E12" s="114" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+        <v>1.4</v>
+      </c>
+      <c r="E12" s="113" t="inlineStr">
+        <is>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G12" s="111" t="inlineStr">
@@ -7717,26 +7717,26 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Sierra Leone</t>
+          <t xml:space="preserve">  9.  Rwanda</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5556</v>
+        <v>1.5742</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.7778</v>
-      </c>
-      <c r="E13" s="114" t="inlineStr">
-        <is>
-          <t>▲ +9.4%</t>
-        </is>
-      </c>
-      <c r="G13" s="113" t="inlineStr">
+        <v>1.5072</v>
+      </c>
+      <c r="E13" s="113" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
+        </is>
+      </c>
+      <c r="G13" s="114" t="inlineStr">
         <is>
           <t xml:space="preserve">  9.  Ghana</t>
         </is>
@@ -7761,44 +7761,44 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Kenya</t>
+          <t xml:space="preserve">  10.  Sierra Leone</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.5142</v>
+        <v>1.5556</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.5067</v>
-      </c>
-      <c r="E14" s="114" t="inlineStr">
-        <is>
-          <t>▲ +8.3%</t>
+        <v>1.7778</v>
+      </c>
+      <c r="E14" s="113" t="inlineStr">
+        <is>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Equatorial Guinea</t>
+          <t xml:space="preserve">  10.  Eswatini</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.9106</v>
+        <v>0.8625</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8609</v>
-      </c>
-      <c r="K14" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.8625</v>
+      </c>
+      <c r="K14" s="106" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
@@ -7984,152 +7984,152 @@
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0882</v>
+        <v>0.5861</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.3014</v>
+        <v>0.7779</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.1918</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Sao Tome</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>STN</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.3023</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.2129</v>
+        <v>1.7209</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +32.1%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.4186</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.0882</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.5742</v>
+        <v>1.3014</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.0316</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>0.9639</v>
+        <v>1.2129</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.3691</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.3736</v>
+        <v>1.5742</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
@@ -8139,22 +8139,22 @@
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.5861</v>
+        <v>0.8608</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.6521</v>
+        <v>0.9639</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.066</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -8439,69 +8439,69 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.31</v>
+        <v>1.2677</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3037</v>
+        <v>1.257</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0063</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.3289</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.257</v>
+        <v>1.3146</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
@@ -8511,121 +8511,121 @@
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2886</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3146</v>
+        <v>1.266</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.31</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.266</v>
+        <v>1.248</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.062</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.784</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.0485</v>
+        <v>1.6851</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0237</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.784</v>
+        <v>1.0641</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.6851</v>
+        <v>0.9982</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
@@ -8635,59 +8635,59 @@
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.0641</v>
+        <v>2.17</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>0.9982</v>
+        <v>2.0242</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.1458</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>2.17</v>
+        <v>0.914</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>2.0242</v>
+        <v>0.8471</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.1458</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
@@ -8697,59 +8697,59 @@
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>0.914</v>
+        <v>1.2212</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.8471</v>
+        <v>1.1258</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.2332</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.9851</v>
+        <v>1.1154</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.1178</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
@@ -8763,173 +8763,173 @@
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.2262</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.1258</v>
+        <v>1.0927</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -10.9%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.1335</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.1939</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.1258</v>
+        <v>1.0606</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1004</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.0722</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.0606</v>
+        <v>0.8625</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Sao Tome</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>STN</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.3023</v>
+        <v>0.4771</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.9302</v>
+        <v>0.338</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -28.6%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.3721</v>
+        <v>-0.1391</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3919</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.7887</v>
+        <v>0.8858</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.5%</t>
+          <t>▼ -36.4%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.5592</v>
+        <v>-0.5061</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B53" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C53" s="116" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D53" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.3479</v>
       </c>
       <c r="E53" s="91" t="n">
-        <v>0.2783</v>
+        <v>0.7887</v>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.7%</t>
+          <t>▼ -41.5%</t>
         </is>
       </c>
       <c r="G53" s="119" t="n">
-        <v>-0.1988</v>
+        <v>-0.5592</v>
       </c>
     </row>
   </sheetData>
@@ -8986,10 +8986,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6399666666666667</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6019833333333334</v>
+        <v>0.6003333333333334</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9088,20 +9088,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.338</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.2684</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.7%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9262,13 +9262,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.2002875</v>
+        <v>1.17445</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.12665625</v>
+        <v>1.1438625</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6521</v>
+        <v>0.7779</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9330,20 +9330,20 @@
         </is>
       </c>
       <c r="C16" s="57" t="n">
-        <v>1.1258</v>
+        <v>1.0927</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>1.1589</v>
+        <v>0.9603</v>
       </c>
       <c r="E16" s="58" t="n">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="F16" s="58" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="G16" s="69" t="inlineStr">
         <is>
-          <t>▼ -8.2%</t>
+          <t>▼ -10.9%</t>
         </is>
       </c>
       <c r="H16" s="61" t="inlineStr">
@@ -9364,20 +9364,20 @@
         </is>
       </c>
       <c r="C17" s="66" t="n">
-        <v>1.3919</v>
+        <v>0.8858</v>
       </c>
       <c r="D17" s="66" t="n">
-        <v>1.1997</v>
+        <v>1.6374</v>
       </c>
       <c r="E17" s="67" t="n">
-        <v>840</v>
+        <v>535</v>
       </c>
       <c r="F17" s="67" t="n">
-        <v>724</v>
-      </c>
-      <c r="G17" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>989</v>
+      </c>
+      <c r="G17" s="69" t="inlineStr">
+        <is>
+          <t>▼ -36.4%</t>
         </is>
       </c>
       <c r="H17" s="70" t="inlineStr">
@@ -9639,13 +9639,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9738,20 +9738,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6521</v>
+        <v>0.7779</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6521</v>
+        <v>0.7711</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1057</v>
+        <v>1261</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1057</v>
+        <v>1250</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9878,10 +9878,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.17085</v>
+        <v>1.279825</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1611125</v>
+        <v>1.2464625</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10150,20 +10150,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>585</v>
-      </c>
-      <c r="G42" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>576</v>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10184,20 +10184,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.7209</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.6279</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>20</v>
-      </c>
-      <c r="G43" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>35</v>
+      </c>
+      <c r="G43" s="71" t="inlineStr">
+        <is>
+          <t>▲ +32.1%</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">
@@ -10804,10 +10804,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.178</v>
+        <v>1.122455555555556</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.163022222222222</v>
+        <v>1.109333333333333</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -10940,20 +10940,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>1.0485</v>
+        <v>0.8625</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>1.0701</v>
+        <v>0.8625</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>19.45</v>
+        <v>16</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>19.85</v>
+        <v>16</v>
       </c>
       <c r="G69" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">
@@ -11008,20 +11008,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>1.3037</v>
+        <v>1.248</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>1.2462</v>
+        <v>1.3261</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>83.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>79.88</v>
+        <v>85</v>
       </c>
       <c r="G71" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -4.7%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">
@@ -11076,20 +11076,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.1154</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.0181</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>25</v>
-      </c>
-      <c r="G73" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.4%</t>
+        <v>18.53</v>
+      </c>
+      <c r="G73" s="69" t="inlineStr">
+        <is>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-23</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-24</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.211</t>
+          <t>$1.209</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.186</t>
+          <t>$1.185</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.6399666666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.6019833333333334</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.279825</v>
+        <v>1.2696875</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.2464625</v>
+        <v>1.248325</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,7 +1831,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.490733333333333</v>
+        <v>1.489966666666667</v>
       </c>
       <c r="E15" s="31" t="n">
         <v>1.479813333333333</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.122455555555556</v>
+        <v>1.128644444444445</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.109333333333333</v>
+        <v>1.100455555555556</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-23</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.338</v>
+        <v>0.2783</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.2783</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -41.7%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J34" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.421</v>
+        <v>1.4095</v>
       </c>
       <c r="F51" s="66" t="n">
         <v>1.4095</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>5090</v>
+        <v>5049</v>
       </c>
       <c r="H51" s="67" t="n">
         <v>5049</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="J51" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +2.0%</t>
         </is>
       </c>
       <c r="K51" s="70" t="inlineStr">
@@ -4392,23 +4392,23 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>1.248</v>
+        <v>1.3037</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>1.3261</v>
+        <v>1.2462</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>80</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>85</v>
+        <v>79.88</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
       <c r="J57" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="K57" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.21097037037037</v>
+        <v>1.209181481481481</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.186235185185185</v>
+        <v>1.185214814814815</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-23</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.338</v>
+        <v>0.2783</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -41.7%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2684</v>
+        <v>0.2783</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -34.1%</t>
+          <t>▼ -31.7%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>1.0662</v>
-      </c>
-      <c r="E35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9851</v>
+      </c>
+      <c r="E35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9536</v>
-      </c>
-      <c r="H35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9685</v>
+      </c>
+      <c r="H35" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.5%</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6797,11 +6797,11 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.421</v>
+        <v>1.4095</v>
       </c>
       <c r="E52" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +2.0%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>5090</v>
+        <v>5049</v>
       </c>
       <c r="J52" s="58" t="n">
         <v>5049</v>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>1.248</v>
+        <v>1.3037</v>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>1.3261</v>
-      </c>
-      <c r="H58" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.1%</t>
+        <v>1.2462</v>
+      </c>
+      <c r="H58" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.3%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>80</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>85</v>
+        <v>79.88</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7430,23 +7430,23 @@
       </c>
       <c r="G6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Angola</t>
+          <t xml:space="preserve">  2.  Egypt</t>
         </is>
       </c>
       <c r="H6" s="107" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I6" s="108" t="n">
-        <v>0.3272</v>
+        <v>0.2783</v>
       </c>
       <c r="J6" s="109" t="n">
-        <v>0.2181</v>
-      </c>
-      <c r="K6" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2783</v>
+      </c>
+      <c r="K6" s="106" t="inlineStr">
+        <is>
+          <t>▼ -41.7%</t>
         </is>
       </c>
     </row>
@@ -7474,23 +7474,23 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Egypt</t>
+          <t xml:space="preserve">  3.  Angola</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.338</v>
+        <v>0.3272</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2684</v>
-      </c>
-      <c r="K7" s="106" t="inlineStr">
-        <is>
-          <t>▼ -29.2%</t>
+        <v>0.2181</v>
+      </c>
+      <c r="K7" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8332,15 +8332,15 @@
         <v>1.3819</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.421</v>
+        <v>1.4095</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +2.0%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -8439,69 +8439,69 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.31</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.257</v>
+        <v>1.3037</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2677</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3146</v>
+        <v>1.257</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
@@ -8511,53 +8511,53 @@
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3289</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.266</v>
+        <v>1.3146</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.31</v>
+        <v>1.2886</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.248</v>
+        <v>1.266</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.062</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -8687,187 +8687,187 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0671</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>1.1258</v>
+        <v>0.9851</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.2212</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.1154</v>
+        <v>1.1258</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.6%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.1178</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2332</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.0927</v>
+        <v>1.1154</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.9%</t>
+          <t>▼ -9.6%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1335</v>
+        <v>-0.1178</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2262</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.0606</v>
+        <v>1.0927</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -10.9%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.1335</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.1939</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>0.8625</v>
+        <v>1.0606</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.0722</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.338</v>
+        <v>0.8625</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.1391</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -8930,6 +8930,37 @@
       </c>
       <c r="G53" s="119" t="n">
         <v>-0.5592</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="62" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="C54" s="118" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="D54" s="88" t="n">
+        <v>0.4771</v>
+      </c>
+      <c r="E54" s="89" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="F54" s="69" t="inlineStr">
+        <is>
+          <t>▼ -41.7%</t>
+        </is>
+      </c>
+      <c r="G54" s="119" t="n">
+        <v>-0.1988</v>
       </c>
     </row>
   </sheetData>
@@ -8986,10 +9017,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.6399666666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6003333333333334</v>
+        <v>0.6019833333333334</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9088,20 +9119,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.338</v>
+        <v>0.2783</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.2783</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -41.7%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9878,10 +9909,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.279825</v>
+        <v>1.2696875</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.2464625</v>
+        <v>1.248325</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10150,20 +10181,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>576</v>
-      </c>
-      <c r="G42" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>585</v>
+      </c>
+      <c r="G42" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10222,7 +10253,7 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.490733333333333</v>
+        <v>1.489966666666667</v>
       </c>
       <c r="D46" s="144" t="n">
         <v>1.479813333333333</v>
@@ -10766,20 +10797,20 @@
         </is>
       </c>
       <c r="C62" s="57" t="n">
-        <v>1.421</v>
+        <v>1.4095</v>
       </c>
       <c r="D62" s="57" t="n">
         <v>1.4095</v>
       </c>
       <c r="E62" s="58" t="n">
-        <v>5090</v>
+        <v>5049</v>
       </c>
       <c r="F62" s="58" t="n">
         <v>5049</v>
       </c>
       <c r="G62" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +2.0%</t>
         </is>
       </c>
       <c r="H62" s="61" t="inlineStr">
@@ -10804,10 +10835,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.122455555555556</v>
+        <v>1.128644444444445</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.109333333333333</v>
+        <v>1.100455555555556</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -11008,20 +11039,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>1.248</v>
+        <v>1.3037</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>1.3261</v>
+        <v>1.2462</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>80</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>85</v>
+        <v>79.88</v>
       </c>
       <c r="G71" s="69" t="inlineStr">
         <is>
-          <t>▼ -4.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1094,11 +1094,11 @@
     <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-24</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-25</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.209</t>
+          <t>$1.211</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.185</t>
+          <t>$1.188</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6399666666666667</v>
+        <v>0.6631666666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6019833333333334</v>
+        <v>0.6135833333333333</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.17445</v>
+        <v>1.17976875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.1438625</v>
+        <v>1.15478125</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.7779</v>
+        <v>0.8262</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2696875</v>
+        <v>1.2173625</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.248325</v>
+        <v>1.1930875</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,7 +1831,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.489966666666667</v>
+        <v>1.490733333333333</v>
       </c>
       <c r="E15" s="31" t="n">
         <v>1.479813333333333</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.128644444444445</v>
+        <v>1.157333333333333</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.100455555555556</v>
+        <v>1.139955555555556</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-24</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.4175</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.3479</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.7%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.7779</v>
+        <v>0.863</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.7711</v>
+        <v>0.863</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1261</v>
+        <v>1399</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1250</v>
+        <v>1399</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>1.7209</v>
+        <v>1.3023</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>1.6279</v>
+        <v>1.186</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>35</v>
+        <v>25.5</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="71" t="inlineStr">
-        <is>
-          <t>▲ +32.1%</t>
+      <c r="J35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.4095</v>
+        <v>1.421</v>
       </c>
       <c r="F51" s="66" t="n">
         <v>1.4095</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>5049</v>
+        <v>5090</v>
       </c>
       <c r="H51" s="67" t="n">
         <v>5049</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="J51" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.0%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="K51" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.1154</v>
+        <v>1.3736</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.0181</v>
+        <v>1.3736</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>18.53</v>
+        <v>25</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="J59" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+      <c r="J59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.209181481481481</v>
+        <v>1.210577777777777</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.185214814814815</v>
+        <v>1.188138888888889</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-24</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.2783</v>
+        <v>0.4175</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.7%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2783</v>
+        <v>0.3479</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -31.7%</t>
+          <t>▼ -14.7%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2003</v>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2831</v>
+      </c>
+      <c r="H21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.7779</v>
+        <v>0.863</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.7711</v>
+        <v>0.863</v>
       </c>
       <c r="H24" s="71" t="inlineStr">
         <is>
-          <t>▲ +4.2%</t>
+          <t>▲ +16.6%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1261</v>
+        <v>1399</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1250</v>
+        <v>1399</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>1.7209</v>
-      </c>
-      <c r="E36" s="71" t="inlineStr">
-        <is>
-          <t>▲ +32.1%</t>
+        <v>1.3023</v>
+      </c>
+      <c r="E36" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>1.6279</v>
-      </c>
-      <c r="H36" s="71" t="inlineStr">
-        <is>
-          <t>▲ +37.3%</t>
+        <v>1.186</v>
+      </c>
+      <c r="H36" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>35</v>
+        <v>25.5</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -6797,11 +6797,11 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.4095</v>
+        <v>1.421</v>
       </c>
       <c r="E52" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.0%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>5049</v>
+        <v>5090</v>
       </c>
       <c r="J52" s="58" t="n">
         <v>5049</v>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.1154</v>
-      </c>
-      <c r="E60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="E60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.0181</v>
-      </c>
-      <c r="H60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -21.0%</t>
+        <v>1.3736</v>
+      </c>
+      <c r="H60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>18.53</v>
+        <v>25</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7430,23 +7430,23 @@
       </c>
       <c r="G6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Egypt</t>
+          <t xml:space="preserve">  2.  Angola</t>
         </is>
       </c>
       <c r="H6" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I6" s="108" t="n">
-        <v>0.2783</v>
+        <v>0.3272</v>
       </c>
       <c r="J6" s="109" t="n">
-        <v>0.2783</v>
-      </c>
-      <c r="K6" s="106" t="inlineStr">
-        <is>
-          <t>▼ -41.7%</t>
+        <v>0.2181</v>
+      </c>
+      <c r="K6" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7474,19 +7474,19 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Angola</t>
+          <t xml:space="preserve">  3.  Algeria</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.3272</v>
+        <v>0.3494</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2181</v>
+        <v>0.2305</v>
       </c>
       <c r="K7" s="99" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="G8" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  Algeria</t>
+          <t xml:space="preserve">  4.  Egypt</t>
         </is>
       </c>
       <c r="H8" s="107" t="inlineStr">
@@ -7527,142 +7527,142 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.3494</v>
+        <v>0.4175</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K8" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.3479</v>
+      </c>
+      <c r="K8" s="106" t="inlineStr">
+        <is>
+          <t>▼ -12.5%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Sao Tome</t>
+          <t xml:space="preserve">  5.  Comoros</t>
         </is>
       </c>
       <c r="B9" s="96" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C9" s="97" t="n">
-        <v>1.7209</v>
+        <v>1.6851</v>
       </c>
       <c r="D9" s="98" t="n">
-        <v>1.6279</v>
-      </c>
-      <c r="E9" s="113" t="inlineStr">
-        <is>
-          <t>▲ +32.1%</t>
-        </is>
-      </c>
-      <c r="G9" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Nigeria</t>
+        <v>1.5078</v>
+      </c>
+      <c r="E9" s="106" t="inlineStr">
+        <is>
+          <t>▼ -5.5%</t>
+        </is>
+      </c>
+      <c r="G9" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Burundi</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.7779</v>
+        <v>0.7887</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.7711</v>
-      </c>
-      <c r="K9" s="113" t="inlineStr">
-        <is>
-          <t>▲ +32.7%</t>
+        <v>1.3442</v>
+      </c>
+      <c r="K9" s="106" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Comoros</t>
+          <t xml:space="preserve">  6.  Senegal</t>
         </is>
       </c>
       <c r="B10" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C10" s="104" t="n">
-        <v>1.6851</v>
+        <v>1.6391</v>
       </c>
       <c r="D10" s="105" t="n">
-        <v>1.5078</v>
-      </c>
-      <c r="E10" s="106" t="inlineStr">
-        <is>
-          <t>▼ -5.5%</t>
+        <v>1.25</v>
+      </c>
+      <c r="E10" s="114" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G10" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Burundi</t>
+          <t xml:space="preserve">  6.  Niger</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.7887</v>
+        <v>0.8262</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>1.3442</v>
-      </c>
-      <c r="K10" s="106" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
+        <v>1.0232</v>
+      </c>
+      <c r="K10" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Senegal</t>
+          <t xml:space="preserve">  7.  Somalia</t>
         </is>
       </c>
       <c r="B11" s="96" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C11" s="97" t="n">
-        <v>1.6391</v>
+        <v>1.6</v>
       </c>
       <c r="D11" s="98" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E11" s="113" t="inlineStr">
-        <is>
-          <t>▲ +7.5%</t>
-        </is>
-      </c>
-      <c r="G11" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Niger</t>
+        <v>1.4</v>
+      </c>
+      <c r="E11" s="114" t="inlineStr">
+        <is>
+          <t>▲ +39.1%</t>
+        </is>
+      </c>
+      <c r="G11" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Tunisia</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8262</v>
+        <v>0.8377</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>1.0232</v>
+        <v>0.7318</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Somalia</t>
+          <t xml:space="preserve">  8.  Rwanda</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
@@ -7682,123 +7682,123 @@
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.6</v>
+        <v>1.5742</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E12" s="113" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
+        <v>1.5072</v>
+      </c>
+      <c r="E12" s="114" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Tunisia</t>
+          <t xml:space="preserve">  8.  Ghana</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8377</v>
+        <v>0.8471</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.7318</v>
-      </c>
-      <c r="K12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.0892</v>
+      </c>
+      <c r="K12" s="106" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Rwanda</t>
+          <t xml:space="preserve">  9.  Sierra Leone</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5742</v>
+        <v>1.5556</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="E13" s="113" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
-        </is>
-      </c>
-      <c r="G13" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Ghana</t>
+        <v>1.7778</v>
+      </c>
+      <c r="E13" s="114" t="inlineStr">
+        <is>
+          <t>▲ +9.4%</t>
+        </is>
+      </c>
+      <c r="G13" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Eswatini</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8471</v>
+        <v>0.8625</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>1.0892</v>
+        <v>0.8625</v>
       </c>
       <c r="K13" s="106" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Sierra Leone</t>
+          <t xml:space="preserve">  10.  Kenya</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C14" s="104" t="n">
+        <v>1.5142</v>
+      </c>
+      <c r="D14" s="105" t="n">
+        <v>1.5067</v>
+      </c>
+      <c r="E14" s="114" t="inlineStr">
+        <is>
+          <t>▲ +8.3%</t>
+        </is>
+      </c>
+      <c r="G14" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Nigeria</t>
+        </is>
+      </c>
+      <c r="H14" s="107" t="inlineStr">
+        <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C14" s="104" t="n">
-        <v>1.5556</v>
-      </c>
-      <c r="D14" s="105" t="n">
-        <v>1.7778</v>
-      </c>
-      <c r="E14" s="113" t="inlineStr">
-        <is>
-          <t>▲ +9.4%</t>
-        </is>
-      </c>
-      <c r="G14" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Eswatini</t>
-        </is>
-      </c>
-      <c r="H14" s="107" t="inlineStr">
-        <is>
-          <t>Southern Africa</t>
-        </is>
-      </c>
       <c r="I14" s="108" t="n">
-        <v>0.8625</v>
+        <v>0.863</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="K14" s="106" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+        <v>0.863</v>
+      </c>
+      <c r="K14" s="114" t="inlineStr">
+        <is>
+          <t>▲ +47.2%</t>
         </is>
       </c>
     </row>
@@ -7912,38 +7912,38 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.15</v>
+        <v>0.5861</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.6</v>
+        <v>0.863</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.45</v>
+        <v>0.2769</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
@@ -7953,208 +7953,208 @@
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.15</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.4096</v>
+        <v>1.6</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.348</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0616</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>0.7779</v>
+        <v>1.4096</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.1918</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Sao Tome</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>STN</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.3023</v>
+        <v>1.0882</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.7209</v>
+        <v>1.3014</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.1%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.4186</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0316</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.3014</v>
+        <v>1.2129</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.3691</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.2129</v>
+        <v>1.5742</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.3691</v>
+        <v>0.8608</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.5742</v>
+        <v>0.9639</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.2332</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.9639</v>
+        <v>1.3736</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -8332,15 +8332,15 @@
         <v>1.3819</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4095</v>
+        <v>1.421</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.0%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0276</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -8749,94 +8749,94 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.2262</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.1154</v>
+        <v>1.0927</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.6%</t>
+          <t>▼ -10.9%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1178</v>
+        <v>-0.1335</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.1939</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.0927</v>
+        <v>1.0606</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.9%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1335</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.1939</v>
+        <v>0.4771</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.0606</v>
+        <v>0.4175</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.0596</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -8930,37 +8930,6 @@
       </c>
       <c r="G53" s="119" t="n">
         <v>-0.5592</v>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="62" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B54" s="63" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="C54" s="118" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-      <c r="D54" s="88" t="n">
-        <v>0.4771</v>
-      </c>
-      <c r="E54" s="89" t="n">
-        <v>0.2783</v>
-      </c>
-      <c r="F54" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.7%</t>
-        </is>
-      </c>
-      <c r="G54" s="119" t="n">
-        <v>-0.1988</v>
       </c>
     </row>
   </sheetData>
@@ -9017,10 +8986,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6399666666666667</v>
+        <v>0.6631666666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6019833333333334</v>
+        <v>0.6135833333333333</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9119,20 +9088,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.4175</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2783</v>
+        <v>0.3479</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.7%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9293,13 +9262,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.17445</v>
+        <v>1.17976875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.1438625</v>
+        <v>1.15478125</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.7779</v>
+        <v>0.8262</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9670,13 +9639,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9769,20 +9738,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.7779</v>
+        <v>0.863</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.7711</v>
+        <v>0.863</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1261</v>
+        <v>1399</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1250</v>
+        <v>1399</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9909,10 +9878,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2696875</v>
+        <v>1.2173625</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.248325</v>
+        <v>1.1930875</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10215,20 +10184,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>1.7209</v>
+        <v>1.3023</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>1.6279</v>
+        <v>1.186</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>35</v>
-      </c>
-      <c r="G43" s="71" t="inlineStr">
-        <is>
-          <t>▲ +32.1%</t>
+        <v>25.5</v>
+      </c>
+      <c r="G43" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">
@@ -10253,7 +10222,7 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.489966666666667</v>
+        <v>1.490733333333333</v>
       </c>
       <c r="D46" s="144" t="n">
         <v>1.479813333333333</v>
@@ -10797,20 +10766,20 @@
         </is>
       </c>
       <c r="C62" s="57" t="n">
-        <v>1.4095</v>
+        <v>1.421</v>
       </c>
       <c r="D62" s="57" t="n">
         <v>1.4095</v>
       </c>
       <c r="E62" s="58" t="n">
-        <v>5049</v>
+        <v>5090</v>
       </c>
       <c r="F62" s="58" t="n">
         <v>5049</v>
       </c>
       <c r="G62" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.0%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="H62" s="61" t="inlineStr">
@@ -10835,10 +10804,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.128644444444445</v>
+        <v>1.157333333333333</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.100455555555556</v>
+        <v>1.139955555555556</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -11107,20 +11076,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.1154</v>
+        <v>1.3736</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.0181</v>
+        <v>1.3736</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>20.3</v>
+        <v>25</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="G73" s="69" t="inlineStr">
-        <is>
-          <t>▼ -9.6%</t>
+        <v>25</v>
+      </c>
+      <c r="G73" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-25</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-26</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.211</t>
+          <t>$1.198</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.188</t>
+          <t>$1.175</t>
         </is>
       </c>
     </row>
@@ -1765,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6631666666666667</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6135833333333333</v>
+        <v>0.5892499999999999</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.17976875</v>
+        <v>1.1665875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.15478125</v>
+        <v>1.136425</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.8262</v>
+        <v>0.6521</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2173625</v>
+        <v>1.17085</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1930875</v>
+        <v>1.1611125</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-25</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.338</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.3479</v>
+        <v>0.2684</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2252,13 +2252,13 @@
         <v>1.0474</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="G8" s="58" t="n">
         <v>630</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.863</v>
+        <v>0.6521</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.863</v>
+        <v>0.6521</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>1.3023</v>
+        <v>0.9302</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>1.186</v>
+        <v>0.9302</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.210577777777777</v>
+        <v>1.198309259259259</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.188138888888889</v>
+        <v>1.175259259259259</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-25</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.4175</v>
+        <v>0.338</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.3479</v>
+        <v>0.2684</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -14.7%</t>
+          <t>▼ -34.1%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4987,18 +4987,18 @@
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.0474</v>
-      </c>
-      <c r="H9" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.8%</t>
+        <v>0.9809</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
         <v>630</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2831</v>
-      </c>
-      <c r="H21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.9%</t>
+        <v>1.2003</v>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.863</v>
+        <v>0.6521</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>▲ +16.6%</t>
+        <v>0.6521</v>
+      </c>
+      <c r="H24" s="69" t="inlineStr">
+        <is>
+          <t>▼ -11.9%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>1.3023</v>
-      </c>
-      <c r="E36" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9302</v>
+      </c>
+      <c r="E36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>1.186</v>
-      </c>
-      <c r="H36" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9302</v>
+      </c>
+      <c r="H36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -21.6%</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Algeria</t>
+          <t xml:space="preserve">  3.  Egypt</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
@@ -7483,14 +7483,14 @@
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.3494</v>
+        <v>0.338</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K7" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2684</v>
+      </c>
+      <c r="K7" s="106" t="inlineStr">
+        <is>
+          <t>▼ -29.2%</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="G8" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  Egypt</t>
+          <t xml:space="preserve">  4.  Algeria</t>
         </is>
       </c>
       <c r="H8" s="107" t="inlineStr">
@@ -7527,14 +7527,14 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.4175</v>
+        <v>0.3494</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.3479</v>
-      </c>
-      <c r="K8" s="106" t="inlineStr">
-        <is>
-          <t>▼ -12.5%</t>
+        <v>0.2305</v>
+      </c>
+      <c r="K8" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7562,23 +7562,23 @@
       </c>
       <c r="G9" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Burundi</t>
+          <t xml:space="preserve">  5.  Nigeria</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.7887</v>
+        <v>0.6521</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>1.3442</v>
-      </c>
-      <c r="K9" s="106" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
+        <v>0.6521</v>
+      </c>
+      <c r="K9" s="114" t="inlineStr">
+        <is>
+          <t>▲ +11.3%</t>
         </is>
       </c>
     </row>
@@ -7606,23 +7606,23 @@
       </c>
       <c r="G10" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Niger</t>
+          <t xml:space="preserve">  6.  Burundi</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.8262</v>
+        <v>0.7887</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K10" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.3442</v>
+      </c>
+      <c r="K10" s="106" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
         </is>
       </c>
     </row>
@@ -7650,19 +7650,19 @@
       </c>
       <c r="G11" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Tunisia</t>
+          <t xml:space="preserve">  7.  Niger</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8377</v>
+        <v>0.8262</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.7318</v>
+        <v>1.0232</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7694,23 +7694,23 @@
       </c>
       <c r="G12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Ghana</t>
+          <t xml:space="preserve">  8.  Tunisia</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8471</v>
+        <v>0.8377</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K12" s="106" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7738,23 +7738,23 @@
       </c>
       <c r="G13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Eswatini</t>
+          <t xml:space="preserve">  9.  Ghana</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8625</v>
+        <v>0.8471</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.8625</v>
+        <v>1.0892</v>
       </c>
       <c r="K13" s="106" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
@@ -7782,23 +7782,23 @@
       </c>
       <c r="G14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Nigeria</t>
+          <t xml:space="preserve">  10.  Eswatini</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.863</v>
+        <v>0.8625</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="K14" s="114" t="inlineStr">
-        <is>
-          <t>▲ +47.2%</t>
+        <v>0.8625</v>
+      </c>
+      <c r="K14" s="106" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
@@ -7912,38 +7912,38 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.15</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>0.863</v>
+        <v>1.6</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.2769</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
@@ -7953,208 +7953,208 @@
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.15</v>
+        <v>1.0616</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.6</v>
+        <v>1.4096</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.45</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.0882</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.4096</v>
+        <v>1.3014</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.348</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0316</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.3014</v>
+        <v>1.2129</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.3691</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.2129</v>
+        <v>1.5742</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.3691</v>
+        <v>0.8608</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.5742</v>
+        <v>0.9639</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.2332</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.3736</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.2332</v>
+        <v>0.5861</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.3736</v>
+        <v>0.6521</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -8811,124 +8811,155 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.0722</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>0.4175</v>
+        <v>0.8625</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.0596</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Sao Tome</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>STN</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.3023</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.8625</v>
+        <v>0.9302</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.3721</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>1.3919</v>
+        <v>0.4771</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.8858</v>
+        <v>0.338</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -36.4%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.5061</v>
+        <v>-0.1391</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="B53" s="54" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="C53" s="116" t="inlineStr">
+        <is>
+          <t>XOF</t>
+        </is>
+      </c>
+      <c r="D53" s="88" t="n">
+        <v>1.3919</v>
+      </c>
+      <c r="E53" s="91" t="n">
+        <v>0.8858</v>
+      </c>
+      <c r="F53" s="69" t="inlineStr">
+        <is>
+          <t>▼ -36.4%</t>
+        </is>
+      </c>
+      <c r="G53" s="119" t="n">
+        <v>-0.5061</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="62" t="inlineStr">
+        <is>
           <t>Burundi</t>
         </is>
       </c>
-      <c r="B53" s="54" t="inlineStr">
+      <c r="B54" s="63" t="inlineStr">
         <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C53" s="116" t="inlineStr">
+      <c r="C54" s="118" t="inlineStr">
         <is>
           <t>BIF</t>
         </is>
       </c>
-      <c r="D53" s="88" t="n">
+      <c r="D54" s="88" t="n">
         <v>1.3479</v>
       </c>
-      <c r="E53" s="91" t="n">
+      <c r="E54" s="89" t="n">
         <v>0.7887</v>
       </c>
-      <c r="F53" s="69" t="inlineStr">
+      <c r="F54" s="69" t="inlineStr">
         <is>
           <t>▼ -41.5%</t>
         </is>
       </c>
-      <c r="G53" s="119" t="n">
+      <c r="G54" s="119" t="n">
         <v>-0.5592</v>
       </c>
     </row>
@@ -8986,10 +9017,10 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6631666666666667</v>
+        <v>0.6499166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6135833333333333</v>
+        <v>0.5892499999999999</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
@@ -9088,20 +9119,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.338</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.3479</v>
+        <v>0.2684</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.2%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9193,13 +9224,13 @@
         <v>1.0474</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>1.0474</v>
+        <v>0.9809</v>
       </c>
       <c r="E10" s="58" t="n">
         <v>630</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="G10" s="60" t="inlineStr">
         <is>
@@ -9262,13 +9293,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.17976875</v>
+        <v>1.1665875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.15478125</v>
+        <v>1.136425</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.8262</v>
+        <v>0.6521</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9639,13 +9670,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9738,20 +9769,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.863</v>
+        <v>0.6521</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.863</v>
+        <v>0.6521</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9878,10 +9909,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2173625</v>
+        <v>1.17085</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1930875</v>
+        <v>1.1611125</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10184,20 +10215,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>1.3023</v>
+        <v>0.9302</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>1.186</v>
+        <v>0.9302</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G43" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>20</v>
+      </c>
+      <c r="G43" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1073,18 +1073,21 @@
     <xf numFmtId="164" fontId="19" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1096,9 +1099,6 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-26</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-27</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,27 +1658,27 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
+          <t>$1.235</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>$2.862</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>$0.031</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>+216.7%</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
           <t>$1.198</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>$2.862</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>$0.031</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>+90.0%</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>$1.175</t>
         </is>
       </c>
     </row>
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.7272833333333334</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.5892499999999999</v>
+        <v>0.6178499999999999</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.2961</v>
+        <v>1.5116</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.1665875</v>
+        <v>1.18685</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.136425</v>
+        <v>1.18135</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6521</v>
+        <v>0.8262</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.17085</v>
+        <v>1.2173625</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1611125</v>
+        <v>1.1930875</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,10 +1831,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.490733333333333</v>
+        <v>1.546486666666667</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.479813333333333</v>
+        <v>1.484213333333333</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.7887</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-26</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.0474</v>
+        <v>1.5116</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.1525</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>630</v>
+        <v>909.2</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>590</v>
+        <v>693.251</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J8" s="71" t="inlineStr">
+        <is>
+          <t>▲ +44.3%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2726,23 +2726,23 @@
         </is>
       </c>
       <c r="E19" s="66" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="F19" s="66" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="G19" s="67" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="I19" s="68" t="n">
         <v>194</v>
       </c>
       <c r="J19" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="K19" s="70" t="inlineStr">
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.863</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.863</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1057</v>
+        <v>1399</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1057</v>
+        <v>1399</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.3023</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.186</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+      <c r="J35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>1.2544</v>
+        <v>2.0907</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>1.2544</v>
+        <v>1.3204</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>5700</v>
+        <v>9500</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
       <c r="J49" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +216.7%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.198309259259259</v>
+        <v>1.235287037037037</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.175259259259259</v>
+        <v>1.197707407407407</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-26</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-27</t>
         </is>
       </c>
     </row>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.0474</v>
-      </c>
-      <c r="E9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.5116</v>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>▲ +44.3%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="H9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.1525</v>
+      </c>
+      <c r="H9" s="71" t="inlineStr">
+        <is>
+          <t>▲ +17.5%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>630</v>
+        <v>909.2</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>590</v>
+        <v>693.251</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5433,29 +5433,29 @@
         <v>0.8608</v>
       </c>
       <c r="D20" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="E20" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="F20" s="90" t="n">
         <v>0.9124</v>
       </c>
       <c r="G20" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="H20" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.6%</t>
+          <t>▲ +52.2%</t>
         </is>
       </c>
       <c r="I20" s="58" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="J20" s="58" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="K20" s="61" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2003</v>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2831</v>
+      </c>
+      <c r="H21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.9%</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6521</v>
+        <v>0.863</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="H24" s="69" t="inlineStr">
-        <is>
-          <t>▼ -11.9%</t>
+        <v>0.863</v>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +16.6%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1057</v>
+        <v>1399</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1057</v>
+        <v>1399</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="E36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>1.3023</v>
+      </c>
+      <c r="E36" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="H36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -21.6%</t>
+        <v>1.186</v>
+      </c>
+      <c r="H36" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>1.2544</v>
+        <v>2.0907</v>
       </c>
       <c r="E50" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +216.7%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>1.2544</v>
+        <v>1.3204</v>
       </c>
       <c r="H50" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +100.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>5700</v>
+        <v>9500</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -7409,23 +7409,23 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Zimbabwe</t>
+          <t xml:space="preserve">  2.  South Sudan</t>
         </is>
       </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2.0242</v>
+        <v>2.0907</v>
       </c>
       <c r="D6" s="105" t="n">
-        <v>1.9231</v>
+        <v>1.3204</v>
       </c>
       <c r="E6" s="106" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▲ +216.7%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
@@ -7453,23 +7453,23 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Eritrea</t>
+          <t xml:space="preserve">  3.  Zimbabwe</t>
         </is>
       </c>
       <c r="B7" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C7" s="97" t="n">
-        <v>2</v>
+        <v>2.0242</v>
       </c>
       <c r="D7" s="98" t="n">
-        <v>1.7333</v>
-      </c>
-      <c r="E7" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.9231</v>
+      </c>
+      <c r="E7" s="110" t="inlineStr">
+        <is>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G7" s="95" t="inlineStr">
@@ -7488,35 +7488,35 @@
       <c r="J7" s="102" t="n">
         <v>0.2684</v>
       </c>
-      <c r="K7" s="106" t="inlineStr">
+      <c r="K7" s="110" t="inlineStr">
         <is>
           <t>▼ -29.2%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  CAR</t>
+      <c r="A8" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Eritrea</t>
         </is>
       </c>
       <c r="B8" s="103" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C8" s="104" t="n">
-        <v>1.7384</v>
+        <v>2</v>
       </c>
       <c r="D8" s="105" t="n">
-        <v>2.1523</v>
+        <v>1.7333</v>
       </c>
       <c r="E8" s="99" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="111" t="inlineStr">
+      <c r="G8" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  Algeria</t>
         </is>
@@ -7539,266 +7539,266 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Comoros</t>
+      <c r="A9" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  CAR</t>
         </is>
       </c>
       <c r="B9" s="96" t="inlineStr">
         <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="C9" s="97" t="n">
+        <v>1.7384</v>
+      </c>
+      <c r="D9" s="98" t="n">
+        <v>2.1523</v>
+      </c>
+      <c r="E9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Burundi</t>
+        </is>
+      </c>
+      <c r="H9" s="100" t="inlineStr">
+        <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C9" s="97" t="n">
+      <c r="I9" s="101" t="n">
+        <v>0.7887</v>
+      </c>
+      <c r="J9" s="102" t="n">
+        <v>1.3442</v>
+      </c>
+      <c r="K9" s="110" t="inlineStr">
+        <is>
+          <t>▼ -41.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Comoros</t>
+        </is>
+      </c>
+      <c r="B10" s="103" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="104" t="n">
         <v>1.6851</v>
       </c>
-      <c r="D9" s="98" t="n">
+      <c r="D10" s="105" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E9" s="106" t="inlineStr">
+      <c r="E10" s="110" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
       </c>
-      <c r="G9" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Nigeria</t>
-        </is>
-      </c>
-      <c r="H9" s="100" t="inlineStr">
+      <c r="G10" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Niger</t>
+        </is>
+      </c>
+      <c r="H10" s="107" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="I9" s="101" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="J9" s="102" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="K9" s="114" t="inlineStr">
-        <is>
-          <t>▲ +11.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Senegal</t>
-        </is>
-      </c>
-      <c r="B10" s="103" t="inlineStr">
+      <c r="I10" s="108" t="n">
+        <v>0.8262</v>
+      </c>
+      <c r="J10" s="109" t="n">
+        <v>1.0232</v>
+      </c>
+      <c r="K10" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Senegal</t>
+        </is>
+      </c>
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n">
+      <c r="C11" s="97" t="n">
         <v>1.6391</v>
       </c>
-      <c r="D10" s="105" t="n">
+      <c r="D11" s="98" t="n">
         <v>1.25</v>
       </c>
-      <c r="E10" s="114" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>▲ +7.5%</t>
         </is>
       </c>
-      <c r="G10" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Burundi</t>
-        </is>
-      </c>
-      <c r="H10" s="107" t="inlineStr">
+      <c r="G11" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Tunisia</t>
+        </is>
+      </c>
+      <c r="H11" s="100" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="I11" s="101" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="J11" s="102" t="n">
+        <v>0.7318</v>
+      </c>
+      <c r="K11" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Somalia</t>
+        </is>
+      </c>
+      <c r="B12" s="103" t="inlineStr">
         <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="I10" s="108" t="n">
-        <v>0.7887</v>
-      </c>
-      <c r="J10" s="109" t="n">
-        <v>1.3442</v>
-      </c>
-      <c r="K10" s="106" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Somalia</t>
-        </is>
-      </c>
-      <c r="B11" s="96" t="inlineStr">
+      <c r="C12" s="104" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E12" s="106" t="inlineStr">
+        <is>
+          <t>▲ +39.1%</t>
+        </is>
+      </c>
+      <c r="G12" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Ghana</t>
+        </is>
+      </c>
+      <c r="H12" s="107" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="I12" s="108" t="n">
+        <v>0.8471</v>
+      </c>
+      <c r="J12" s="109" t="n">
+        <v>1.0892</v>
+      </c>
+      <c r="K12" s="110" t="inlineStr">
+        <is>
+          <t>▼ -7.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Rwanda</t>
+        </is>
+      </c>
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C11" s="97" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D11" s="98" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E11" s="114" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
-        </is>
-      </c>
-      <c r="G11" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Niger</t>
-        </is>
-      </c>
-      <c r="H11" s="100" t="inlineStr">
+      <c r="C13" s="97" t="n">
+        <v>1.5742</v>
+      </c>
+      <c r="D13" s="98" t="n">
+        <v>1.5072</v>
+      </c>
+      <c r="E13" s="106" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
+        </is>
+      </c>
+      <c r="G13" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Eswatini</t>
+        </is>
+      </c>
+      <c r="H13" s="100" t="inlineStr">
+        <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
+      <c r="I13" s="101" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="J13" s="102" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="K13" s="110" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Sierra Leone</t>
+        </is>
+      </c>
+      <c r="B14" s="103" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="I11" s="101" t="n">
-        <v>0.8262</v>
-      </c>
-      <c r="J11" s="102" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K11" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Rwanda</t>
-        </is>
-      </c>
-      <c r="B12" s="103" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="C12" s="104" t="n">
-        <v>1.5742</v>
-      </c>
-      <c r="D12" s="105" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="E12" s="114" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
-        </is>
-      </c>
-      <c r="G12" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Tunisia</t>
-        </is>
-      </c>
-      <c r="H12" s="107" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="I12" s="108" t="n">
-        <v>0.8377</v>
-      </c>
-      <c r="J12" s="109" t="n">
-        <v>0.7318</v>
-      </c>
-      <c r="K12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Sierra Leone</t>
-        </is>
-      </c>
-      <c r="B13" s="96" t="inlineStr">
+      <c r="C14" s="104" t="n">
+        <v>1.5556</v>
+      </c>
+      <c r="D14" s="105" t="n">
+        <v>1.7778</v>
+      </c>
+      <c r="E14" s="106" t="inlineStr">
+        <is>
+          <t>▲ +9.4%</t>
+        </is>
+      </c>
+      <c r="G14" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Nigeria</t>
+        </is>
+      </c>
+      <c r="H14" s="107" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C13" s="97" t="n">
-        <v>1.5556</v>
-      </c>
-      <c r="D13" s="98" t="n">
-        <v>1.7778</v>
-      </c>
-      <c r="E13" s="114" t="inlineStr">
-        <is>
-          <t>▲ +9.4%</t>
-        </is>
-      </c>
-      <c r="G13" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Ghana</t>
-        </is>
-      </c>
-      <c r="H13" s="100" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="I13" s="101" t="n">
-        <v>0.8471</v>
-      </c>
-      <c r="J13" s="102" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K13" s="106" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Kenya</t>
-        </is>
-      </c>
-      <c r="B14" s="103" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="C14" s="104" t="n">
-        <v>1.5142</v>
-      </c>
-      <c r="D14" s="105" t="n">
-        <v>1.5067</v>
-      </c>
-      <c r="E14" s="114" t="inlineStr">
-        <is>
-          <t>▲ +8.3%</t>
-        </is>
-      </c>
-      <c r="G14" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Eswatini</t>
-        </is>
-      </c>
-      <c r="H14" s="107" t="inlineStr">
-        <is>
-          <t>Southern Africa</t>
-        </is>
-      </c>
       <c r="I14" s="108" t="n">
-        <v>0.8625</v>
+        <v>0.863</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8625</v>
+        <v>0.863</v>
       </c>
       <c r="K14" s="106" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
     </row>
@@ -7867,15 +7867,15 @@
         <v>0.6602</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.2544</v>
+        <v>2.0907</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +216.7%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.5942</v>
+        <v>1.4305</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -7912,162 +7912,162 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.15</v>
+        <v>0.5861</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.6</v>
+        <v>0.863</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.45</v>
+        <v>0.2769</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.0474</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.4096</v>
+        <v>1.5116</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +44.3%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.348</v>
+        <v>0.4642</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.15</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.3014</v>
+        <v>1.6</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.0616</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.2129</v>
+        <v>1.4096</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.3691</v>
+        <v>0.8608</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.5742</v>
+        <v>1.0772</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.2164</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
@@ -8077,28 +8077,28 @@
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.0882</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>0.9639</v>
+        <v>1.3014</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
@@ -8108,59 +8108,59 @@
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.0316</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.3736</v>
+        <v>1.2129</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.3691</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.6521</v>
+        <v>1.5742</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.066</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,152 +8170,152 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.2332</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.2555</v>
+        <v>1.3736</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.1425</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.5556</v>
+        <v>1.2555</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.4222</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.5142</v>
+        <v>1.5556</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3986</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.6391</v>
+        <v>1.5142</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.5244</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.4968</v>
+        <v>1.6391</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,121 +8325,121 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.4106</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.421</v>
+        <v>1.4968</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.3819</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.2961</v>
+        <v>1.421</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0199</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.2762</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3873</v>
+        <v>1.2961</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3681</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.0582</v>
+        <v>1.3873</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
@@ -8449,90 +8449,90 @@
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0555</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F38" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G38" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F38" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G38" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.31</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.257</v>
+        <v>1.3037</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2677</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3146</v>
+        <v>1.257</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
@@ -8542,90 +8542,90 @@
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3289</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.266</v>
+        <v>1.3146</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.784</v>
+        <v>1.2886</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.6851</v>
+        <v>1.266</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.784</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>0.9982</v>
+        <v>1.6851</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
@@ -8635,121 +8635,121 @@
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>2.17</v>
+        <v>1.0641</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>2.0242</v>
+        <v>0.9982</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.1458</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>0.914</v>
+        <v>2.17</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.8471</v>
+        <v>2.0242</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.1458</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.0671</v>
+        <v>0.914</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.9851</v>
+        <v>0.8471</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0671</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.1258</v>
+        <v>0.9851</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
@@ -8763,111 +8763,111 @@
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2212</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.0927</v>
+        <v>1.1258</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.9%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1335</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2262</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.0606</v>
+        <v>1.0927</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -10.9%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.1335</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.1939</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>0.8625</v>
+        <v>1.0606</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Sao Tome</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>STN</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.3023</v>
+        <v>1.0722</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.9302</v>
+        <v>0.8625</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -28.6%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.3721</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -9017,16 +9017,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6499166666666667</v>
+        <v>0.7272833333333334</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.5892499999999999</v>
+        <v>0.6178499999999999</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.2961</v>
+        <v>1.5116</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9221,20 +9221,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.0474</v>
+        <v>1.5116</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.1525</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>630</v>
+        <v>909.2</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>590</v>
-      </c>
-      <c r="G10" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>693.251</v>
+      </c>
+      <c r="G10" s="71" t="inlineStr">
+        <is>
+          <t>▲ +44.3%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9293,13 +9293,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.1665875</v>
+        <v>1.18685</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.136425</v>
+        <v>1.18135</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6521</v>
+        <v>0.8262</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9633,20 +9633,20 @@
         </is>
       </c>
       <c r="C24" s="57" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="D24" s="57" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="E24" s="58" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="F24" s="58" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="G24" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="H24" s="61" t="inlineStr">
@@ -9670,13 +9670,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2003</v>
+        <v>1.2831</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9769,20 +9769,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6521</v>
+        <v>0.863</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6521</v>
+        <v>0.863</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1057</v>
+        <v>1399</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1057</v>
+        <v>1399</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9909,10 +9909,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.17085</v>
+        <v>1.2173625</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1611125</v>
+        <v>1.1930875</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10215,20 +10215,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.3023</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.186</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>20</v>
-      </c>
-      <c r="G43" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>25.5</v>
+      </c>
+      <c r="G43" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">
@@ -10253,10 +10253,10 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.490733333333333</v>
+        <v>1.546486666666667</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.479813333333333</v>
+        <v>1.484213333333333</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>0.7887</v>
@@ -10729,20 +10729,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>1.2544</v>
+        <v>2.0907</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>1.2544</v>
+        <v>1.3204</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>5700</v>
+        <v>9500</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="G60" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +216.7%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1073,32 +1073,32 @@
     <xf numFmtId="164" fontId="19" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-27</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-29</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.235</t>
+          <t>$1.212</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+216.7%</t>
+          <t>+68.6%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.198</t>
+          <t>$1.174</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.7272833333333334</v>
+        <v>0.7401666666666666</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6178499999999999</v>
+        <v>0.6300666666666667</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.5116</v>
+        <v>1.5094</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,10 +1787,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.18685</v>
+        <v>1.17976875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.18135</v>
+        <v>1.14960625</v>
       </c>
       <c r="F13" s="32" t="n">
         <v>0.8262</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2173625</v>
+        <v>1.17085</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1930875</v>
+        <v>1.1611125</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.546486666666667</v>
+        <v>1.489866666666667</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.484213333333333</v>
+        <v>1.444913333333333</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.7887</v>
+        <v>0.6602</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-27</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.338</v>
+        <v>0.4175</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.3479</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.5116</v>
+        <v>1.5094</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>1.1525</v>
+        <v>1.1463</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>909.2</v>
+        <v>907.9</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>693.251</v>
+        <v>689.498</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
       <c r="J8" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.3%</t>
+          <t>▲ +44.1%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2726,23 +2726,23 @@
         </is>
       </c>
       <c r="E19" s="66" t="n">
-        <v>1.0772</v>
+        <v>0.9639</v>
       </c>
       <c r="F19" s="66" t="n">
-        <v>1.389</v>
+        <v>0.9639</v>
       </c>
       <c r="G19" s="67" t="n">
-        <v>208.97</v>
+        <v>187</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>269.46</v>
+        <v>187</v>
       </c>
       <c r="I19" s="68" t="n">
         <v>194</v>
       </c>
       <c r="J19" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="K19" s="70" t="inlineStr">
@@ -2776,13 +2776,13 @@
         <v>1.2831</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="G20" s="58" t="n">
         <v>775</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>1.3023</v>
+        <v>0.9302</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>1.186</v>
+        <v>0.9302</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -3492,13 +3492,13 @@
         </is>
       </c>
       <c r="E37" s="66" t="n">
-        <v>0.7887</v>
+        <v>1.3699</v>
       </c>
       <c r="F37" s="66" t="n">
         <v>1.3442</v>
       </c>
       <c r="G37" s="67" t="n">
-        <v>2303</v>
+        <v>4000</v>
       </c>
       <c r="H37" s="67" t="n">
         <v>3925</v>
@@ -3506,9 +3506,9 @@
       <c r="I37" s="68" t="n">
         <v>2920</v>
       </c>
-      <c r="J37" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
+      <c r="J37" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="K37" s="70" t="inlineStr">
@@ -3965,13 +3965,13 @@
         <v>1.4968</v>
       </c>
       <c r="F47" s="66" t="n">
-        <v>1.4975</v>
+        <v>1.5682</v>
       </c>
       <c r="G47" s="67" t="n">
         <v>21.18</v>
       </c>
       <c r="H47" s="67" t="n">
-        <v>21.19</v>
+        <v>22.19</v>
       </c>
       <c r="I47" s="68" t="n">
         <v>14.15</v>
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>2.0907</v>
+        <v>0.6602</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>1.3204</v>
+        <v>0.6602</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>9500</v>
+        <v>3000</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="71" t="inlineStr">
-        <is>
-          <t>▲ +216.7%</t>
+      <c r="J49" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.235287037037037</v>
+        <v>1.212001851851852</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.197707407407407</v>
+        <v>1.174005555555555</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-27</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.338</v>
+        <v>0.4175</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2684</v>
+        <v>0.3479</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -34.1%</t>
+          <t>▼ -14.7%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.5116</v>
+        <v>1.5094</v>
       </c>
       <c r="E9" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.3%</t>
+          <t>▲ +44.1%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.1525</v>
+        <v>1.1463</v>
       </c>
       <c r="H9" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.5%</t>
+          <t>▲ +16.9%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>909.2</v>
+        <v>907.9</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>693.251</v>
+        <v>689.498</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5433,29 +5433,29 @@
         <v>0.8608</v>
       </c>
       <c r="D20" s="91" t="n">
-        <v>1.0772</v>
+        <v>0.9639</v>
       </c>
       <c r="E20" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="F20" s="90" t="n">
         <v>0.9124</v>
       </c>
       <c r="G20" s="91" t="n">
-        <v>1.389</v>
+        <v>0.9639</v>
       </c>
       <c r="H20" s="71" t="inlineStr">
         <is>
-          <t>▲ +52.2%</t>
+          <t>▲ +5.6%</t>
         </is>
       </c>
       <c r="I20" s="58" t="n">
-        <v>208.97</v>
+        <v>187</v>
       </c>
       <c r="J20" s="58" t="n">
-        <v>269.46</v>
+        <v>187</v>
       </c>
       <c r="K20" s="61" t="inlineStr">
         <is>
@@ -5489,18 +5489,18 @@
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2831</v>
-      </c>
-      <c r="H21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.9%</t>
+        <v>1.2003</v>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
         <v>775</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>1.3023</v>
-      </c>
-      <c r="E36" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9302</v>
+      </c>
+      <c r="E36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>1.186</v>
-      </c>
-      <c r="H36" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9302</v>
+      </c>
+      <c r="H36" s="69" t="inlineStr">
+        <is>
+          <t>▼ -21.6%</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -6167,11 +6167,11 @@
         <v>1.3479</v>
       </c>
       <c r="D38" s="91" t="n">
-        <v>0.7887</v>
-      </c>
-      <c r="E38" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
+        <v>1.3699</v>
+      </c>
+      <c r="E38" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="F38" s="90" t="n">
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="I38" s="58" t="n">
-        <v>2303</v>
+        <v>4000</v>
       </c>
       <c r="J38" s="58" t="n">
         <v>3925</v>
@@ -6628,18 +6628,18 @@
         <v>1.33</v>
       </c>
       <c r="G48" s="91" t="n">
-        <v>1.4975</v>
+        <v>1.5682</v>
       </c>
       <c r="H48" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.6%</t>
+          <t>▲ +17.9%</t>
         </is>
       </c>
       <c r="I48" s="58" t="n">
         <v>21.18</v>
       </c>
       <c r="J48" s="58" t="n">
-        <v>21.19</v>
+        <v>22.19</v>
       </c>
       <c r="K48" s="61" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>2.0907</v>
-      </c>
-      <c r="E50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +216.7%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="E50" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>1.3204</v>
-      </c>
-      <c r="H50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +100.0%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="H50" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>9500</v>
+        <v>3000</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -7409,23 +7409,23 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  South Sudan</t>
+          <t xml:space="preserve">  2.  Zimbabwe</t>
         </is>
       </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2.0907</v>
+        <v>2.0242</v>
       </c>
       <c r="D6" s="105" t="n">
-        <v>1.3204</v>
+        <v>1.9231</v>
       </c>
       <c r="E6" s="106" t="inlineStr">
         <is>
-          <t>▲ +216.7%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
@@ -7453,28 +7453,28 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Zimbabwe</t>
+          <t xml:space="preserve">  3.  Eritrea</t>
         </is>
       </c>
       <c r="B7" s="96" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C7" s="97" t="n">
-        <v>2.0242</v>
+        <v>2</v>
       </c>
       <c r="D7" s="98" t="n">
-        <v>1.9231</v>
-      </c>
-      <c r="E7" s="110" t="inlineStr">
-        <is>
-          <t>▼ -6.7%</t>
+        <v>1.7333</v>
+      </c>
+      <c r="E7" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Egypt</t>
+          <t xml:space="preserve">  3.  Algeria</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
@@ -7483,128 +7483,128 @@
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.338</v>
+        <v>0.3494</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2684</v>
-      </c>
-      <c r="K7" s="110" t="inlineStr">
-        <is>
-          <t>▼ -29.2%</t>
+        <v>0.2305</v>
+      </c>
+      <c r="K7" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Eritrea</t>
+      <c r="A8" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  CAR</t>
         </is>
       </c>
       <c r="B8" s="103" t="inlineStr">
         <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="C8" s="104" t="n">
+        <v>1.7384</v>
+      </c>
+      <c r="D8" s="105" t="n">
+        <v>2.1523</v>
+      </c>
+      <c r="E8" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Egypt</t>
+        </is>
+      </c>
+      <c r="H8" s="107" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="I8" s="108" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="J8" s="109" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="K8" s="106" t="inlineStr">
+        <is>
+          <t>▼ -12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Comoros</t>
+        </is>
+      </c>
+      <c r="B9" s="96" t="inlineStr">
+        <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C8" s="104" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="105" t="n">
-        <v>1.7333</v>
-      </c>
-      <c r="E8" s="99" t="inlineStr">
+      <c r="C9" s="97" t="n">
+        <v>1.6851</v>
+      </c>
+      <c r="D9" s="98" t="n">
+        <v>1.5078</v>
+      </c>
+      <c r="E9" s="106" t="inlineStr">
+        <is>
+          <t>▼ -5.5%</t>
+        </is>
+      </c>
+      <c r="G9" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  South Sudan</t>
+        </is>
+      </c>
+      <c r="H9" s="100" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="I9" s="101" t="n">
+        <v>0.6602</v>
+      </c>
+      <c r="J9" s="102" t="n">
+        <v>0.6602</v>
+      </c>
+      <c r="K9" s="99" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Algeria</t>
-        </is>
-      </c>
-      <c r="H8" s="107" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="I8" s="108" t="n">
-        <v>0.3494</v>
-      </c>
-      <c r="J8" s="109" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K8" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  CAR</t>
-        </is>
-      </c>
-      <c r="B9" s="96" t="inlineStr">
-        <is>
-          <t>Central Africa</t>
-        </is>
-      </c>
-      <c r="C9" s="97" t="n">
-        <v>1.7384</v>
-      </c>
-      <c r="D9" s="98" t="n">
-        <v>2.1523</v>
-      </c>
-      <c r="E9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Burundi</t>
-        </is>
-      </c>
-      <c r="H9" s="100" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="I9" s="101" t="n">
-        <v>0.7887</v>
-      </c>
-      <c r="J9" s="102" t="n">
-        <v>1.3442</v>
-      </c>
-      <c r="K9" s="110" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Comoros</t>
+      <c r="A10" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Senegal</t>
         </is>
       </c>
       <c r="B10" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C10" s="104" t="n">
-        <v>1.6851</v>
+        <v>1.6391</v>
       </c>
       <c r="D10" s="105" t="n">
-        <v>1.5078</v>
-      </c>
-      <c r="E10" s="110" t="inlineStr">
-        <is>
-          <t>▼ -5.5%</t>
-        </is>
-      </c>
-      <c r="G10" s="112" t="inlineStr">
+        <v>1.25</v>
+      </c>
+      <c r="E10" s="114" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
+        </is>
+      </c>
+      <c r="G10" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  Niger</t>
         </is>
@@ -7627,28 +7627,28 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Senegal</t>
+      <c r="A11" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Somalia</t>
         </is>
       </c>
       <c r="B11" s="96" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C11" s="97" t="n">
-        <v>1.6391</v>
+        <v>1.6</v>
       </c>
       <c r="D11" s="98" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E11" s="106" t="inlineStr">
-        <is>
-          <t>▲ +7.5%</t>
-        </is>
-      </c>
-      <c r="G11" s="114" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="E11" s="114" t="inlineStr">
+        <is>
+          <t>▲ +39.1%</t>
+        </is>
+      </c>
+      <c r="G11" s="113" t="inlineStr">
         <is>
           <t xml:space="preserve">  7.  Tunisia</t>
         </is>
@@ -7671,9 +7671,9 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Somalia</t>
+      <c r="A12" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Rwanda</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
@@ -7682,17 +7682,17 @@
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.6</v>
+        <v>1.5742</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E12" s="106" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
-        </is>
-      </c>
-      <c r="G12" s="112" t="inlineStr">
+        <v>1.5072</v>
+      </c>
+      <c r="E12" s="114" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  8.  Ghana</t>
         </is>
@@ -7708,35 +7708,35 @@
       <c r="J12" s="109" t="n">
         <v>1.0892</v>
       </c>
-      <c r="K12" s="110" t="inlineStr">
+      <c r="K12" s="106" t="inlineStr">
         <is>
           <t>▼ -7.3%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Rwanda</t>
+      <c r="A13" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Sierra Leone</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5742</v>
+        <v>1.5556</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="E13" s="106" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
-        </is>
-      </c>
-      <c r="G13" s="114" t="inlineStr">
+        <v>1.7778</v>
+      </c>
+      <c r="E13" s="114" t="inlineStr">
+        <is>
+          <t>▲ +9.4%</t>
+        </is>
+      </c>
+      <c r="G13" s="113" t="inlineStr">
         <is>
           <t xml:space="preserve">  9.  Eswatini</t>
         </is>
@@ -7752,35 +7752,35 @@
       <c r="J13" s="102" t="n">
         <v>0.8625</v>
       </c>
-      <c r="K13" s="110" t="inlineStr">
+      <c r="K13" s="106" t="inlineStr">
         <is>
           <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Sierra Leone</t>
+      <c r="A14" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Kenya</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.5556</v>
+        <v>1.5142</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.7778</v>
-      </c>
-      <c r="E14" s="106" t="inlineStr">
-        <is>
-          <t>▲ +9.4%</t>
-        </is>
-      </c>
-      <c r="G14" s="112" t="inlineStr">
+        <v>1.5067</v>
+      </c>
+      <c r="E14" s="114" t="inlineStr">
+        <is>
+          <t>▲ +8.3%</t>
+        </is>
+      </c>
+      <c r="G14" s="111" t="inlineStr">
         <is>
           <t xml:space="preserve">  10.  Nigeria</t>
         </is>
@@ -7796,7 +7796,7 @@
       <c r="J14" s="109" t="n">
         <v>0.863</v>
       </c>
-      <c r="K14" s="106" t="inlineStr">
+      <c r="K14" s="114" t="inlineStr">
         <is>
           <t>▲ +47.2%</t>
         </is>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,121 +7860,121 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6602</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>2.0907</v>
+        <v>1.0871</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +216.7%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>1.4305</v>
+        <v>0.4424</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.5861</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.0871</v>
+        <v>0.863</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.4424</v>
+        <v>0.2769</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0474</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>0.863</v>
+        <v>1.5094</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +44.1%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.2769</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0474</v>
+        <v>1.15</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.5116</v>
+        <v>1.6</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.3%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.4642</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
@@ -7984,183 +7984,183 @@
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.15</v>
+        <v>1.0616</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.6</v>
+        <v>1.4096</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +32.8%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.45</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.0882</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.4096</v>
+        <v>1.3014</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +19.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.348</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.0316</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.0772</v>
+        <v>1.2129</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2164</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.3691</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.3014</v>
+        <v>1.5742</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.0316</v>
+        <v>0.8608</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.2129</v>
+        <v>0.9639</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.2332</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.5742</v>
+        <v>1.3736</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,152 +8170,152 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.1425</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.3736</v>
+        <v>1.2555</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.4222</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.2555</v>
+        <v>1.5556</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.3986</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.5556</v>
+        <v>1.5142</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.5244</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.5142</v>
+        <v>1.6391</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.4106</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.4968</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,28 +8325,28 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3819</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4968</v>
+        <v>1.421</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
@@ -8356,22 +8356,22 @@
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.3479</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.421</v>
+        <v>1.3699</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -8842,125 +8842,125 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.0722</v>
+        <v>0.4771</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.8625</v>
+        <v>0.4175</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.0596</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.0722</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.338</v>
+        <v>0.8625</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.1391</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Sao Tome</t>
         </is>
       </c>
       <c r="B53" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C53" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>STN</t>
         </is>
       </c>
       <c r="D53" s="88" t="n">
-        <v>1.3919</v>
+        <v>1.3023</v>
       </c>
       <c r="E53" s="91" t="n">
-        <v>0.8858</v>
+        <v>0.9302</v>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>▼ -36.4%</t>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="G53" s="119" t="n">
-        <v>-0.5061</v>
+        <v>-0.3721</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="B54" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C54" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D54" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3919</v>
       </c>
       <c r="E54" s="89" t="n">
-        <v>0.7887</v>
+        <v>0.8858</v>
       </c>
       <c r="F54" s="69" t="inlineStr">
         <is>
-          <t>▼ -41.5%</t>
+          <t>▼ -36.4%</t>
         </is>
       </c>
       <c r="G54" s="119" t="n">
-        <v>-0.5592</v>
+        <v>-0.5061</v>
       </c>
     </row>
   </sheetData>
@@ -9017,16 +9017,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.7272833333333334</v>
+        <v>0.7401666666666666</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6178499999999999</v>
+        <v>0.6300666666666667</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.5116</v>
+        <v>1.5094</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9119,20 +9119,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.338</v>
+        <v>0.4175</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2684</v>
+        <v>0.3479</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9221,20 +9221,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.5116</v>
+        <v>1.5094</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>1.1525</v>
+        <v>1.1463</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>909.2</v>
+        <v>907.9</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>693.251</v>
+        <v>689.498</v>
       </c>
       <c r="G10" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.3%</t>
+          <t>▲ +44.1%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9293,10 +9293,10 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.18685</v>
+        <v>1.17976875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.18135</v>
+        <v>1.14960625</v>
       </c>
       <c r="E14" s="131" t="n">
         <v>0.8262</v>
@@ -9633,20 +9633,20 @@
         </is>
       </c>
       <c r="C24" s="57" t="n">
-        <v>1.0772</v>
+        <v>0.9639</v>
       </c>
       <c r="D24" s="57" t="n">
-        <v>1.389</v>
+        <v>0.9639</v>
       </c>
       <c r="E24" s="58" t="n">
-        <v>208.97</v>
+        <v>187</v>
       </c>
       <c r="F24" s="58" t="n">
-        <v>269.46</v>
+        <v>187</v>
       </c>
       <c r="G24" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="H24" s="61" t="inlineStr">
@@ -9670,13 +9670,13 @@
         <v>1.2831</v>
       </c>
       <c r="D25" s="66" t="n">
-        <v>1.2831</v>
+        <v>1.2003</v>
       </c>
       <c r="E25" s="67" t="n">
         <v>775</v>
       </c>
       <c r="F25" s="67" t="n">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="G25" s="60" t="inlineStr">
         <is>
@@ -9909,10 +9909,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2173625</v>
+        <v>1.17085</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1930875</v>
+        <v>1.1611125</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10215,20 +10215,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>1.3023</v>
+        <v>0.9302</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>1.186</v>
+        <v>0.9302</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G43" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>20</v>
+      </c>
+      <c r="G43" s="69" t="inlineStr">
+        <is>
+          <t>▼ -28.6%</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">
@@ -10253,13 +10253,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.546486666666667</v>
+        <v>1.489866666666667</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.484213333333333</v>
+        <v>1.444913333333333</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.7887</v>
+        <v>0.6602</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10321,20 +10321,20 @@
         </is>
       </c>
       <c r="C48" s="57" t="n">
-        <v>0.7887</v>
+        <v>1.3699</v>
       </c>
       <c r="D48" s="57" t="n">
         <v>1.3442</v>
       </c>
       <c r="E48" s="58" t="n">
-        <v>2303</v>
+        <v>4000</v>
       </c>
       <c r="F48" s="58" t="n">
         <v>3925</v>
       </c>
-      <c r="G48" s="69" t="inlineStr">
-        <is>
-          <t>▼ -41.5%</t>
+      <c r="G48" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="H48" s="61" t="inlineStr">
@@ -10664,13 +10664,13 @@
         <v>1.4968</v>
       </c>
       <c r="D58" s="57" t="n">
-        <v>1.4975</v>
+        <v>1.5682</v>
       </c>
       <c r="E58" s="58" t="n">
         <v>21.18</v>
       </c>
       <c r="F58" s="58" t="n">
-        <v>21.19</v>
+        <v>22.19</v>
       </c>
       <c r="G58" s="71" t="inlineStr">
         <is>
@@ -10729,20 +10729,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>2.0907</v>
+        <v>0.6602</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>1.3204</v>
+        <v>0.6602</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>9500</v>
+        <v>3000</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +216.7%</t>
+        <v>3000</v>
+      </c>
+      <c r="G60" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-29</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-30</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.212</t>
+          <t>$1.222</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+68.6%</t>
+          <t>+90.0%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.174</t>
+          <t>$1.177</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.7401666666666666</v>
+        <v>0.7398333333333333</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6300666666666667</v>
+        <v>0.6295333333333333</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.5094</v>
+        <v>1.5074</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.17976875</v>
+        <v>1.16696875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.14960625</v>
+        <v>1.13701875</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.8262</v>
+        <v>0.6663</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.17085</v>
+        <v>1.2152875</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1611125</v>
+        <v>1.1548125</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.489866666666667</v>
+        <v>1.515166666666667</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.444913333333333</v>
+        <v>1.472813333333333</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.6602</v>
+        <v>1.0606</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-29</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.5094</v>
+        <v>1.5074</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>1.1463</v>
+        <v>1.1431</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>907.9</v>
+        <v>906.7</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>689.498</v>
+        <v>687.5650000000001</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
       <c r="J8" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.1%</t>
+          <t>▲ +43.9%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2444,23 +2444,23 @@
         </is>
       </c>
       <c r="E13" s="66" t="n">
-        <v>1.266</v>
+        <v>1.2579</v>
       </c>
       <c r="F13" s="66" t="n">
-        <v>1.0635</v>
+        <v>1.0588</v>
       </c>
       <c r="G13" s="67" t="n">
-        <v>139.89</v>
+        <v>139</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>117.52</v>
+        <v>117</v>
       </c>
       <c r="I13" s="68" t="n">
         <v>110.5</v>
       </c>
       <c r="J13" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -2.4%</t>
         </is>
       </c>
       <c r="K13" s="70" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.863</v>
+        <v>0.6663</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.863</v>
+        <v>0.6663</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1399</v>
+        <v>1080</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1399</v>
+        <v>1080</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>0.9851</v>
+        <v>0.9685</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.6623</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>585</v>
+        <v>400</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
       <c r="J34" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -9.2%</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="E35" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.3023</v>
       </c>
       <c r="F35" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.186</v>
       </c>
       <c r="G35" s="67" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H35" s="67" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="I35" s="68" t="n">
         <v>21.5</v>
       </c>
-      <c r="J35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+      <c r="J35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K35" s="70" t="inlineStr">
@@ -3915,23 +3915,23 @@
         </is>
       </c>
       <c r="E46" s="57" t="n">
-        <v>1.5742</v>
+        <v>1.3595</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.5072</v>
+        <v>1.3315</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>2303</v>
+        <v>1989</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>2205</v>
+        <v>1948</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
       </c>
-      <c r="J46" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+      <c r="J46" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="K46" s="61" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J49" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.212001851851852</v>
+        <v>1.221783333333333</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.174005555555555</v>
+        <v>1.177033333333333</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-29</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.5094</v>
+        <v>1.5074</v>
       </c>
       <c r="E9" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.1%</t>
+          <t>▲ +43.9%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.1463</v>
+        <v>1.1431</v>
       </c>
       <c r="H9" s="71" t="inlineStr">
         <is>
-          <t>▲ +16.9%</t>
+          <t>▲ +16.5%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>907.9</v>
+        <v>906.7</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>689.498</v>
+        <v>687.5650000000001</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5163,29 +5163,29 @@
         <v>1.2886</v>
       </c>
       <c r="D14" s="91" t="n">
-        <v>1.266</v>
+        <v>1.2579</v>
       </c>
       <c r="E14" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -2.4%</t>
         </is>
       </c>
       <c r="F14" s="90" t="n">
         <v>1.0826</v>
       </c>
       <c r="G14" s="91" t="n">
-        <v>1.0635</v>
+        <v>1.0588</v>
       </c>
       <c r="H14" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -2.2%</t>
         </is>
       </c>
       <c r="I14" s="58" t="n">
-        <v>139.89</v>
+        <v>139</v>
       </c>
       <c r="J14" s="58" t="n">
-        <v>117.52</v>
+        <v>117</v>
       </c>
       <c r="K14" s="61" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.863</v>
+        <v>0.6663</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>▲ +16.6%</t>
+        <v>0.6663</v>
+      </c>
+      <c r="H24" s="69" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1399</v>
+        <v>1080</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1399</v>
+        <v>1080</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>0.9851</v>
+        <v>0.9685</v>
       </c>
       <c r="E35" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -9.2%</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9685</v>
-      </c>
-      <c r="H35" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.5%</t>
+        <v>0.6623</v>
+      </c>
+      <c r="H35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -30.6%</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>585</v>
+        <v>400</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6115,29 +6115,29 @@
         <v>1.3023</v>
       </c>
       <c r="D36" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="E36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>1.3023</v>
+      </c>
+      <c r="E36" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="90" t="n">
         <v>1.186</v>
       </c>
       <c r="G36" s="91" t="n">
-        <v>0.9302</v>
-      </c>
-      <c r="H36" s="69" t="inlineStr">
-        <is>
-          <t>▼ -21.6%</t>
+        <v>1.186</v>
+      </c>
+      <c r="H36" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" s="58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J36" s="58" t="n">
-        <v>20</v>
+        <v>25.5</v>
       </c>
       <c r="K36" s="61" t="inlineStr">
         <is>
@@ -6572,29 +6572,29 @@
         <v>1.3691</v>
       </c>
       <c r="D47" s="89" t="n">
-        <v>1.5742</v>
-      </c>
-      <c r="E47" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+        <v>1.3595</v>
+      </c>
+      <c r="E47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="F47" s="90" t="n">
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="H47" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.3%</t>
+        <v>1.3315</v>
+      </c>
+      <c r="H47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
-        <v>2303</v>
+        <v>1989</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>2205</v>
+        <v>1948</v>
       </c>
       <c r="K47" s="70" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="E50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="E50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="H50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="H50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -7562,23 +7562,23 @@
       </c>
       <c r="G9" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  South Sudan</t>
+          <t xml:space="preserve">  5.  Nigeria</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6602</v>
+        <v>0.6663</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="K9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.6663</v>
+      </c>
+      <c r="K9" s="114" t="inlineStr">
+        <is>
+          <t>▲ +13.7%</t>
         </is>
       </c>
     </row>
@@ -7673,23 +7673,23 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Rwanda</t>
+          <t xml:space="preserve">  8.  Sierra Leone</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.5742</v>
+        <v>1.5556</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.5072</v>
+        <v>1.7778</v>
       </c>
       <c r="E12" s="114" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G12" s="111" t="inlineStr">
@@ -7717,23 +7717,23 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Sierra Leone</t>
+          <t xml:space="preserve">  9.  Kenya</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5556</v>
+        <v>1.5142</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.7778</v>
+        <v>1.5067</v>
       </c>
       <c r="E13" s="114" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G13" s="113" t="inlineStr">
@@ -7761,28 +7761,28 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Kenya</t>
+          <t xml:space="preserve">  10.  Sudan</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.5142</v>
+        <v>1.5074</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.5067</v>
+        <v>1.1431</v>
       </c>
       <c r="E14" s="114" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +43.9%</t>
         </is>
       </c>
       <c r="G14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Nigeria</t>
+          <t xml:space="preserve">  10.  Burkina Faso</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
@@ -7791,14 +7791,14 @@
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.863</v>
+        <v>0.8858</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="K14" s="114" t="inlineStr">
-        <is>
-          <t>▲ +47.2%</t>
+        <v>1.6374</v>
+      </c>
+      <c r="K14" s="106" t="inlineStr">
+        <is>
+          <t>▼ -36.4%</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,53 +7860,53 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.0871</v>
+        <v>1.2544</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.4424</v>
+        <v>0.5942</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>0.5861</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>0.863</v>
+        <v>1.0871</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +68.6%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.2769</v>
+        <v>0.4424</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -7929,15 +7929,15 @@
         <v>1.0474</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.5094</v>
+        <v>1.5074</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.1%</t>
+          <t>▲ +43.9%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.462</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -8067,32 +8067,32 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.3691</v>
+        <v>0.5861</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.5742</v>
+        <v>0.6663</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -8501,7 +8501,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
@@ -8511,59 +8511,59 @@
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.3691</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.257</v>
+        <v>1.3595</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.009599999999999999</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2677</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.3146</v>
+        <v>1.257</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
@@ -8573,90 +8573,90 @@
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3289</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.266</v>
+        <v>1.3146</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.784</v>
+        <v>1.2886</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.6851</v>
+        <v>1.2579</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -2.4%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0307</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.784</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>0.9982</v>
+        <v>1.6851</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
@@ -8666,84 +8666,84 @@
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>2.17</v>
+        <v>1.0641</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>2.0242</v>
+        <v>0.9982</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.1458</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>0.914</v>
+        <v>2.17</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.8471</v>
+        <v>2.0242</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.1458</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.0671</v>
+        <v>0.914</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.9851</v>
+        <v>0.8471</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -7.3%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0669</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -8780,156 +8780,156 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.0671</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.0927</v>
+        <v>0.9685</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.9%</t>
+          <t>▼ -9.2%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.1335</v>
+        <v>-0.09859999999999999</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2262</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.0606</v>
+        <v>1.0927</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -10.9%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.1335</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.1939</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.4175</v>
+        <v>1.0606</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.0596</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>1.0722</v>
+        <v>0.4771</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.8625</v>
+        <v>0.4175</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.0596</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
-          <t>Sao Tome</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B53" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C53" s="116" t="inlineStr">
         <is>
-          <t>STN</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D53" s="88" t="n">
-        <v>1.3023</v>
+        <v>1.0722</v>
       </c>
       <c r="E53" s="91" t="n">
-        <v>0.9302</v>
+        <v>0.8625</v>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>▼ -28.6%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G53" s="119" t="n">
-        <v>-0.3721</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -9017,16 +9017,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.7401666666666666</v>
+        <v>0.7398333333333333</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6300666666666667</v>
+        <v>0.6295333333333333</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.5094</v>
+        <v>1.5074</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9221,20 +9221,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.5094</v>
+        <v>1.5074</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>1.1463</v>
+        <v>1.1431</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>907.9</v>
+        <v>906.7</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>689.498</v>
+        <v>687.5650000000001</v>
       </c>
       <c r="G10" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.1%</t>
+          <t>▲ +43.9%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9293,13 +9293,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.17976875</v>
+        <v>1.16696875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.14960625</v>
+        <v>1.13701875</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.8262</v>
+        <v>0.6663</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9429,20 +9429,20 @@
         </is>
       </c>
       <c r="C18" s="57" t="n">
-        <v>1.266</v>
+        <v>1.2579</v>
       </c>
       <c r="D18" s="57" t="n">
-        <v>1.0635</v>
+        <v>1.0588</v>
       </c>
       <c r="E18" s="58" t="n">
-        <v>139.89</v>
+        <v>139</v>
       </c>
       <c r="F18" s="58" t="n">
-        <v>117.52</v>
+        <v>117</v>
       </c>
       <c r="G18" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -2.4%</t>
         </is>
       </c>
       <c r="H18" s="61" t="inlineStr">
@@ -9769,20 +9769,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.863</v>
+        <v>0.6663</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.863</v>
+        <v>0.6663</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1399</v>
+        <v>1080</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1399</v>
+        <v>1080</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +13.7%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9909,10 +9909,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.17085</v>
+        <v>1.2152875</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1611125</v>
+        <v>1.1548125</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10181,20 +10181,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>0.9851</v>
+        <v>0.9685</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.6623</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>585</v>
+        <v>400</v>
       </c>
       <c r="G42" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -9.2%</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10215,20 +10215,20 @@
         </is>
       </c>
       <c r="C43" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.3023</v>
       </c>
       <c r="D43" s="66" t="n">
-        <v>0.9302</v>
+        <v>1.186</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F43" s="67" t="n">
-        <v>20</v>
-      </c>
-      <c r="G43" s="69" t="inlineStr">
-        <is>
-          <t>▼ -28.6%</t>
+        <v>25.5</v>
+      </c>
+      <c r="G43" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="70" t="inlineStr">
@@ -10253,13 +10253,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.489866666666667</v>
+        <v>1.515166666666667</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.444913333333333</v>
+        <v>1.472813333333333</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.6602</v>
+        <v>1.0606</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10627,20 +10627,20 @@
         </is>
       </c>
       <c r="C57" s="66" t="n">
-        <v>1.5742</v>
+        <v>1.3595</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.5072</v>
+        <v>1.3315</v>
       </c>
       <c r="E57" s="67" t="n">
-        <v>2303</v>
+        <v>1989</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>2205</v>
-      </c>
-      <c r="G57" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+        <v>1948</v>
+      </c>
+      <c r="G57" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="H57" s="70" t="inlineStr">
@@ -10729,20 +10729,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G60" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5700</v>
+      </c>
+      <c r="G60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1073,18 +1073,21 @@
     <xf numFmtId="164" fontId="19" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1096,9 +1099,6 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-04-30</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-01</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+90.0%</t>
+          <t>+216.7%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.177</t>
+          <t>$1.188</t>
         </is>
       </c>
     </row>
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.7398333333333333</v>
+        <v>0.7820833333333334</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6295333333333333</v>
+        <v>0.656</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.5074</v>
+        <v>1.5444</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.16696875</v>
+        <v>1.16639375</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.13701875</v>
+        <v>1.2078125</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6663</v>
+        <v>0.7742</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.515166666666667</v>
+        <v>1.494333333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.472813333333333</v>
+        <v>1.410433333333333</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>1.0606</v>
+        <v>0.7476</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.157333333333333</v>
+        <v>1.163444444444445</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.139955555555556</v>
+        <v>1.163255555555556</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-04-30</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2111,13 @@
         <v>0.4175</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.3479</v>
+        <v>0.2584</v>
       </c>
       <c r="G5" s="67" t="n">
         <v>21</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.2961</v>
+        <v>1.5444</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.2961</v>
+        <v>1.5444</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>13</v>
+        <v>15.49</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>13</v>
+        <v>15.49</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +21.0%</t>
         </is>
       </c>
       <c r="K7" s="70" t="inlineStr">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.5074</v>
+        <v>1.5126</v>
       </c>
       <c r="F8" s="57" t="n">
         <v>1.1431</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>906.7</v>
+        <v>909.8</v>
       </c>
       <c r="H8" s="58" t="n">
         <v>687.5650000000001</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="J8" s="71" t="inlineStr">
         <is>
-          <t>▲ +43.9%</t>
+          <t>▲ +44.4%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2350,23 +2350,23 @@
         </is>
       </c>
       <c r="E11" s="66" t="n">
-        <v>1.0927</v>
+        <v>1.2003</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>0.9603</v>
+        <v>1.2417</v>
       </c>
       <c r="G11" s="67" t="n">
-        <v>660</v>
+        <v>725</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>580</v>
+        <v>750</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
       </c>
       <c r="J11" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.9%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="K11" s="70" t="inlineStr">
@@ -2444,23 +2444,23 @@
         </is>
       </c>
       <c r="E13" s="66" t="n">
-        <v>1.2579</v>
+        <v>1.266</v>
       </c>
       <c r="F13" s="66" t="n">
-        <v>1.0588</v>
+        <v>1.0635</v>
       </c>
       <c r="G13" s="67" t="n">
-        <v>139</v>
+        <v>139.89</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>117</v>
+        <v>117.52</v>
       </c>
       <c r="I13" s="68" t="n">
         <v>110.5</v>
       </c>
       <c r="J13" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.4%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="K13" s="70" t="inlineStr">
@@ -2491,23 +2491,23 @@
         </is>
       </c>
       <c r="E14" s="57" t="n">
-        <v>1.3014</v>
+        <v>1.5342</v>
       </c>
       <c r="F14" s="57" t="n">
-        <v>0.6493</v>
+        <v>1.6438</v>
       </c>
       <c r="G14" s="58" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="H14" s="58" t="n">
-        <v>47.4</v>
+        <v>120</v>
       </c>
       <c r="I14" s="59" t="n">
         <v>73</v>
       </c>
       <c r="J14" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="K14" s="61" t="inlineStr">
@@ -2538,23 +2538,23 @@
         </is>
       </c>
       <c r="E15" s="66" t="n">
-        <v>0.8471</v>
+        <v>0.8439</v>
       </c>
       <c r="F15" s="66" t="n">
-        <v>1.0892</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="G15" s="67" t="n">
-        <v>13.3</v>
+        <v>13.25</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>17.1</v>
+        <v>14.3</v>
       </c>
       <c r="I15" s="68" t="n">
         <v>15.7</v>
       </c>
       <c r="J15" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="K15" s="70" t="inlineStr">
@@ -2585,23 +2585,23 @@
         </is>
       </c>
       <c r="E16" s="57" t="n">
-        <v>1.3873</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="F16" s="57" t="n">
-        <v>1.3873</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="G16" s="58" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="H16" s="58" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="I16" s="59" t="n">
         <v>8650</v>
       </c>
-      <c r="J16" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.4%</t>
+      <c r="J16" s="69" t="inlineStr">
+        <is>
+          <t>▼ -32.4%</t>
         </is>
       </c>
       <c r="K16" s="61" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6663</v>
+        <v>0.7742</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6663</v>
+        <v>1.1592</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1080</v>
+        <v>1255</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1080</v>
+        <v>1879</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +32.1%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="K28" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -3680,23 +3680,23 @@
         </is>
       </c>
       <c r="E41" s="66" t="n">
-        <v>1.0871</v>
+        <v>0.9856</v>
       </c>
       <c r="F41" s="66" t="n">
-        <v>1.245</v>
+        <v>0.9856</v>
       </c>
       <c r="G41" s="67" t="n">
-        <v>142.41</v>
+        <v>129.12</v>
       </c>
       <c r="H41" s="67" t="n">
-        <v>163.09</v>
+        <v>129.12</v>
       </c>
       <c r="I41" s="68" t="n">
         <v>131</v>
       </c>
       <c r="J41" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +52.9%</t>
         </is>
       </c>
       <c r="K41" s="70" t="inlineStr">
@@ -3730,13 +3730,13 @@
         <v>1.5142</v>
       </c>
       <c r="F42" s="57" t="n">
-        <v>1.5067</v>
+        <v>1.5142</v>
       </c>
       <c r="G42" s="58" t="n">
         <v>197.6</v>
       </c>
       <c r="H42" s="58" t="n">
-        <v>196.63</v>
+        <v>197.6</v>
       </c>
       <c r="I42" s="59" t="n">
         <v>130.5</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -3871,13 +3871,13 @@
         <v>1.257</v>
       </c>
       <c r="F45" s="66" t="n">
-        <v>1.257</v>
+        <v>1.3935</v>
       </c>
       <c r="G45" s="67" t="n">
         <v>58.45</v>
       </c>
       <c r="H45" s="67" t="n">
-        <v>58.45</v>
+        <v>64.8</v>
       </c>
       <c r="I45" s="68" t="n">
         <v>46.5</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="K45" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -3915,23 +3915,23 @@
         </is>
       </c>
       <c r="E46" s="57" t="n">
-        <v>1.3595</v>
+        <v>1.5742</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.3315</v>
+        <v>1.5072</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>1989</v>
+        <v>2303</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>1948</v>
+        <v>2205</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
       </c>
-      <c r="J46" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+      <c r="J46" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="K46" s="61" t="inlineStr">
@@ -4009,23 +4009,23 @@
         </is>
       </c>
       <c r="E48" s="57" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="F48" s="57" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G48" s="58" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="H48" s="58" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="I48" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="71" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
+      <c r="J48" s="69" t="inlineStr">
+        <is>
+          <t>▼ -13.0%</t>
         </is>
       </c>
       <c r="K48" s="61" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>1.2544</v>
+        <v>2.0907</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>1.2544</v>
+        <v>1.3204</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>5700</v>
+        <v>9500</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
       <c r="J49" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +216.7%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4103,23 +4103,23 @@
         </is>
       </c>
       <c r="E50" s="57" t="n">
-        <v>1.4096</v>
+        <v>0.7476</v>
       </c>
       <c r="F50" s="57" t="n">
-        <v>1.4096</v>
+        <v>0.7476</v>
       </c>
       <c r="G50" s="58" t="n">
-        <v>3820</v>
+        <v>2026</v>
       </c>
       <c r="H50" s="58" t="n">
-        <v>3820</v>
+        <v>2026</v>
       </c>
       <c r="I50" s="59" t="n">
         <v>2710</v>
       </c>
-      <c r="J50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +32.8%</t>
+      <c r="J50" s="69" t="inlineStr">
+        <is>
+          <t>▼ -29.6%</t>
         </is>
       </c>
       <c r="K50" s="61" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.4286</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.3736</v>
+        <v>1.4286</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
       <c r="J59" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4536,13 +4536,13 @@
         <v>0.9982</v>
       </c>
       <c r="F60" s="57" t="n">
-        <v>1.0949</v>
+        <v>1.2496</v>
       </c>
       <c r="G60" s="58" t="n">
         <v>27.15</v>
       </c>
       <c r="H60" s="58" t="n">
-        <v>29.78</v>
+        <v>33.99</v>
       </c>
       <c r="I60" s="59" t="n">
         <v>27.2</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.221783333333333</v>
+        <v>1.221538888888888</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.177033333333333</v>
+        <v>1.187505555555555</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-04-30</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4852,18 +4852,18 @@
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.3479</v>
+        <v>0.2584</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -14.7%</t>
+          <t>▼ -36.6%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
         <v>21</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.2961</v>
+        <v>1.5444</v>
       </c>
       <c r="E8" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +21.0%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.2961</v>
+        <v>1.5444</v>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.0%</t>
+          <t>▲ +34.7%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>13</v>
+        <v>15.49</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>13</v>
+        <v>15.49</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -4976,11 +4976,11 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.5074</v>
+        <v>1.5126</v>
       </c>
       <c r="E9" s="71" t="inlineStr">
         <is>
-          <t>▲ +43.9%</t>
+          <t>▲ +44.4%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>906.7</v>
+        <v>909.8</v>
       </c>
       <c r="J9" s="67" t="n">
         <v>687.5650000000001</v>
@@ -5073,29 +5073,29 @@
         <v>1.2262</v>
       </c>
       <c r="D12" s="91" t="n">
-        <v>1.0927</v>
+        <v>1.2003</v>
       </c>
       <c r="E12" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.9%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="F12" s="90" t="n">
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>0.9603</v>
+        <v>1.2417</v>
       </c>
       <c r="H12" s="69" t="inlineStr">
         <is>
-          <t>▼ -23.7%</t>
+          <t>▼ -1.4%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
-        <v>660</v>
+        <v>725</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>580</v>
+        <v>750</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -5163,29 +5163,29 @@
         <v>1.2886</v>
       </c>
       <c r="D14" s="91" t="n">
-        <v>1.2579</v>
+        <v>1.266</v>
       </c>
       <c r="E14" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.4%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="F14" s="90" t="n">
         <v>1.0826</v>
       </c>
       <c r="G14" s="91" t="n">
-        <v>1.0588</v>
+        <v>1.0635</v>
       </c>
       <c r="H14" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.2%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="I14" s="58" t="n">
-        <v>139</v>
+        <v>139.89</v>
       </c>
       <c r="J14" s="58" t="n">
-        <v>117</v>
+        <v>117.52</v>
       </c>
       <c r="K14" s="61" t="inlineStr">
         <is>
@@ -5208,29 +5208,29 @@
         <v>1.0882</v>
       </c>
       <c r="D15" s="89" t="n">
-        <v>1.3014</v>
+        <v>1.5342</v>
       </c>
       <c r="E15" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="F15" s="90" t="n">
         <v>0.9559</v>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.6493</v>
-      </c>
-      <c r="H15" s="69" t="inlineStr">
-        <is>
-          <t>▼ -32.1%</t>
+        <v>1.6438</v>
+      </c>
+      <c r="H15" s="71" t="inlineStr">
+        <is>
+          <t>▲ +72.0%</t>
         </is>
       </c>
       <c r="I15" s="67" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="J15" s="67" t="n">
-        <v>47.4</v>
+        <v>120</v>
       </c>
       <c r="K15" s="70" t="inlineStr">
         <is>
@@ -5253,29 +5253,29 @@
         <v>0.914</v>
       </c>
       <c r="D16" s="91" t="n">
-        <v>0.8471</v>
+        <v>0.8439</v>
       </c>
       <c r="E16" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="F16" s="90" t="n">
         <v>0.914</v>
       </c>
       <c r="G16" s="91" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="H16" s="71" t="inlineStr">
-        <is>
-          <t>▲ +19.2%</t>
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="H16" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.3%</t>
         </is>
       </c>
       <c r="I16" s="58" t="n">
-        <v>13.3</v>
+        <v>13.25</v>
       </c>
       <c r="J16" s="58" t="n">
-        <v>17.1</v>
+        <v>14.3</v>
       </c>
       <c r="K16" s="61" t="inlineStr">
         <is>
@@ -5298,29 +5298,29 @@
         <v>1.3681</v>
       </c>
       <c r="D17" s="89" t="n">
-        <v>1.3873</v>
-      </c>
-      <c r="E17" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.4%</t>
+        <v>0.9249000000000001</v>
+      </c>
+      <c r="E17" s="69" t="inlineStr">
+        <is>
+          <t>▼ -32.4%</t>
         </is>
       </c>
       <c r="F17" s="90" t="n">
         <v>1.341</v>
       </c>
       <c r="G17" s="89" t="n">
-        <v>1.3873</v>
-      </c>
-      <c r="H17" s="71" t="inlineStr">
-        <is>
-          <t>▲ +3.5%</t>
+        <v>0.9249000000000001</v>
+      </c>
+      <c r="H17" s="69" t="inlineStr">
+        <is>
+          <t>▼ -31.0%</t>
         </is>
       </c>
       <c r="I17" s="67" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="J17" s="67" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="K17" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6663</v>
+        <v>0.7742</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +32.1%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="H24" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>1.1592</v>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +56.6%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1080</v>
+        <v>1255</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1080</v>
+        <v>1879</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K29" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -6347,29 +6347,29 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="D42" s="91" t="n">
-        <v>1.0871</v>
+        <v>0.9856</v>
       </c>
       <c r="E42" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +52.9%</t>
         </is>
       </c>
       <c r="F42" s="90" t="n">
         <v>0.6288</v>
       </c>
       <c r="G42" s="91" t="n">
-        <v>1.245</v>
+        <v>0.9856</v>
       </c>
       <c r="H42" s="71" t="inlineStr">
         <is>
-          <t>▲ +98.0%</t>
+          <t>▲ +56.7%</t>
         </is>
       </c>
       <c r="I42" s="58" t="n">
-        <v>142.41</v>
+        <v>129.12</v>
       </c>
       <c r="J42" s="58" t="n">
-        <v>163.09</v>
+        <v>129.12</v>
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
@@ -6403,22 +6403,22 @@
         <v>1.3063</v>
       </c>
       <c r="G43" s="89" t="n">
-        <v>1.5067</v>
+        <v>1.5142</v>
       </c>
       <c r="H43" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.3%</t>
+          <t>▲ +15.9%</t>
         </is>
       </c>
       <c r="I43" s="67" t="n">
         <v>197.6</v>
       </c>
       <c r="J43" s="67" t="n">
-        <v>196.63</v>
+        <v>197.6</v>
       </c>
       <c r="K43" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -6538,22 +6538,22 @@
         <v>1.2677</v>
       </c>
       <c r="G46" s="91" t="n">
-        <v>1.257</v>
-      </c>
-      <c r="H46" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.8%</t>
+        <v>1.3935</v>
+      </c>
+      <c r="H46" s="71" t="inlineStr">
+        <is>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="I46" s="58" t="n">
         <v>58.45</v>
       </c>
       <c r="J46" s="58" t="n">
-        <v>58.45</v>
+        <v>64.8</v>
       </c>
       <c r="K46" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -6572,29 +6572,29 @@
         <v>1.3691</v>
       </c>
       <c r="D47" s="89" t="n">
-        <v>1.3595</v>
-      </c>
-      <c r="E47" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+        <v>1.5742</v>
+      </c>
+      <c r="E47" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="F47" s="90" t="n">
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.3315</v>
-      </c>
-      <c r="H47" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.8%</t>
+        <v>1.5072</v>
+      </c>
+      <c r="H47" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.3%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
-        <v>1989</v>
+        <v>2303</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>1948</v>
+        <v>2205</v>
       </c>
       <c r="K47" s="70" t="inlineStr">
         <is>
@@ -6662,29 +6662,29 @@
         <v>1.15</v>
       </c>
       <c r="D49" s="89" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E49" s="71" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
+        <v>1</v>
+      </c>
+      <c r="E49" s="69" t="inlineStr">
+        <is>
+          <t>▼ -13.0%</t>
         </is>
       </c>
       <c r="F49" s="90" t="n">
         <v>1.05</v>
       </c>
       <c r="G49" s="89" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H49" s="71" t="inlineStr">
-        <is>
-          <t>▲ +33.3%</t>
+        <v>1</v>
+      </c>
+      <c r="H49" s="69" t="inlineStr">
+        <is>
+          <t>▼ -4.8%</t>
         </is>
       </c>
       <c r="I49" s="67" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J49" s="67" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K49" s="70" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>1.2544</v>
+        <v>2.0907</v>
       </c>
       <c r="E50" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +216.7%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>1.2544</v>
+        <v>1.3204</v>
       </c>
       <c r="H50" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +100.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>5700</v>
+        <v>9500</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -6752,29 +6752,29 @@
         <v>1.0616</v>
       </c>
       <c r="D51" s="89" t="n">
-        <v>1.4096</v>
-      </c>
-      <c r="E51" s="71" t="inlineStr">
-        <is>
-          <t>▲ +32.8%</t>
+        <v>0.7476</v>
+      </c>
+      <c r="E51" s="69" t="inlineStr">
+        <is>
+          <t>▼ -29.6%</t>
         </is>
       </c>
       <c r="F51" s="90" t="n">
         <v>1.021</v>
       </c>
       <c r="G51" s="89" t="n">
-        <v>1.4096</v>
-      </c>
-      <c r="H51" s="71" t="inlineStr">
-        <is>
-          <t>▲ +38.1%</t>
+        <v>0.7476</v>
+      </c>
+      <c r="H51" s="69" t="inlineStr">
+        <is>
+          <t>▼ -26.8%</t>
         </is>
       </c>
       <c r="I51" s="67" t="n">
-        <v>3820</v>
+        <v>2026</v>
       </c>
       <c r="J51" s="67" t="n">
-        <v>3820</v>
+        <v>2026</v>
       </c>
       <c r="K51" s="70" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.3736</v>
+        <v>1.4286</v>
       </c>
       <c r="E60" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.3736</v>
+        <v>1.4286</v>
       </c>
       <c r="H60" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.6%</t>
+          <t>▲ +10.9%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7175,18 +7175,18 @@
         <v>0.9351</v>
       </c>
       <c r="G61" s="89" t="n">
-        <v>1.0949</v>
+        <v>1.2496</v>
       </c>
       <c r="H61" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.1%</t>
+          <t>▲ +33.6%</t>
         </is>
       </c>
       <c r="I61" s="67" t="n">
         <v>27.15</v>
       </c>
       <c r="J61" s="67" t="n">
-        <v>29.78</v>
+        <v>33.99</v>
       </c>
       <c r="K61" s="70" t="inlineStr">
         <is>
@@ -7409,23 +7409,23 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Zimbabwe</t>
+          <t xml:space="preserve">  2.  South Sudan</t>
         </is>
       </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2.0242</v>
+        <v>2.0907</v>
       </c>
       <c r="D6" s="105" t="n">
-        <v>1.9231</v>
+        <v>1.3204</v>
       </c>
       <c r="E6" s="106" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▲ +216.7%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
@@ -7453,23 +7453,23 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Eritrea</t>
+          <t xml:space="preserve">  3.  Zimbabwe</t>
         </is>
       </c>
       <c r="B7" s="96" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C7" s="97" t="n">
-        <v>2</v>
+        <v>2.0242</v>
       </c>
       <c r="D7" s="98" t="n">
-        <v>1.7333</v>
-      </c>
-      <c r="E7" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.9231</v>
+      </c>
+      <c r="E7" s="110" t="inlineStr">
+        <is>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G7" s="95" t="inlineStr">
@@ -7495,28 +7495,28 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  CAR</t>
+      <c r="A8" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Eritrea</t>
         </is>
       </c>
       <c r="B8" s="103" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C8" s="104" t="n">
-        <v>1.7384</v>
+        <v>2</v>
       </c>
       <c r="D8" s="105" t="n">
-        <v>2.1523</v>
+        <v>1.7333</v>
       </c>
       <c r="E8" s="99" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="111" t="inlineStr">
+      <c r="G8" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  4.  Egypt</t>
         </is>
@@ -7530,275 +7530,275 @@
         <v>0.4175</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.3479</v>
-      </c>
-      <c r="K8" s="106" t="inlineStr">
+        <v>0.2584</v>
+      </c>
+      <c r="K8" s="110" t="inlineStr">
         <is>
           <t>▼ -12.5%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Comoros</t>
+      <c r="A9" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  CAR</t>
         </is>
       </c>
       <c r="B9" s="96" t="inlineStr">
         <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="C9" s="97" t="n">
+        <v>1.7384</v>
+      </c>
+      <c r="D9" s="98" t="n">
+        <v>2.1523</v>
+      </c>
+      <c r="E9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Tanzania</t>
+        </is>
+      </c>
+      <c r="H9" s="100" t="inlineStr">
+        <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C9" s="97" t="n">
+      <c r="I9" s="101" t="n">
+        <v>0.7476</v>
+      </c>
+      <c r="J9" s="102" t="n">
+        <v>0.7476</v>
+      </c>
+      <c r="K9" s="110" t="inlineStr">
+        <is>
+          <t>▼ -29.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Comoros</t>
+        </is>
+      </c>
+      <c r="B10" s="103" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="104" t="n">
         <v>1.6851</v>
       </c>
-      <c r="D9" s="98" t="n">
+      <c r="D10" s="105" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E9" s="106" t="inlineStr">
+      <c r="E10" s="110" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
       </c>
-      <c r="G9" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  Nigeria</t>
-        </is>
-      </c>
-      <c r="H9" s="100" t="inlineStr">
+      <c r="G10" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Nigeria</t>
+        </is>
+      </c>
+      <c r="H10" s="107" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="I9" s="101" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="J9" s="102" t="n">
-        <v>0.6663</v>
-      </c>
-      <c r="K9" s="114" t="inlineStr">
-        <is>
-          <t>▲ +13.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Senegal</t>
-        </is>
-      </c>
-      <c r="B10" s="103" t="inlineStr">
+      <c r="I10" s="108" t="n">
+        <v>0.7742</v>
+      </c>
+      <c r="J10" s="109" t="n">
+        <v>1.1592</v>
+      </c>
+      <c r="K10" s="106" t="inlineStr">
+        <is>
+          <t>▲ +32.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Senegal</t>
+        </is>
+      </c>
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n">
+      <c r="C11" s="97" t="n">
         <v>1.6391</v>
       </c>
-      <c r="D10" s="105" t="n">
+      <c r="D11" s="98" t="n">
         <v>1.25</v>
       </c>
-      <c r="E10" s="114" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>▲ +7.5%</t>
         </is>
       </c>
-      <c r="G10" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Niger</t>
-        </is>
-      </c>
-      <c r="H10" s="107" t="inlineStr">
+      <c r="G11" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Niger</t>
+        </is>
+      </c>
+      <c r="H11" s="100" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="I10" s="108" t="n">
+      <c r="I11" s="101" t="n">
         <v>0.8262</v>
       </c>
-      <c r="J10" s="109" t="n">
+      <c r="J11" s="102" t="n">
         <v>1.0232</v>
       </c>
-      <c r="K10" s="99" t="inlineStr">
+      <c r="K11" s="99" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Somalia</t>
-        </is>
-      </c>
-      <c r="B11" s="96" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Rwanda</t>
+        </is>
+      </c>
+      <c r="B12" s="103" t="inlineStr">
         <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C11" s="97" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D11" s="98" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E11" s="114" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
-        </is>
-      </c>
-      <c r="G11" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Tunisia</t>
-        </is>
-      </c>
-      <c r="H11" s="100" t="inlineStr">
+      <c r="C12" s="104" t="n">
+        <v>1.5742</v>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>1.5072</v>
+      </c>
+      <c r="E12" s="106" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Tunisia</t>
+        </is>
+      </c>
+      <c r="H12" s="107" t="inlineStr">
         <is>
           <t>North Africa</t>
         </is>
       </c>
-      <c r="I11" s="101" t="n">
+      <c r="I12" s="108" t="n">
         <v>0.8377</v>
       </c>
-      <c r="J11" s="102" t="n">
+      <c r="J12" s="109" t="n">
         <v>0.7318</v>
       </c>
-      <c r="K11" s="99" t="inlineStr">
+      <c r="K12" s="99" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Sierra Leone</t>
-        </is>
-      </c>
-      <c r="B12" s="103" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Sierra Leone</t>
+        </is>
+      </c>
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C12" s="104" t="n">
+      <c r="C13" s="97" t="n">
         <v>1.5556</v>
       </c>
-      <c r="D12" s="105" t="n">
+      <c r="D13" s="98" t="n">
         <v>1.7778</v>
       </c>
-      <c r="E12" s="114" t="inlineStr">
+      <c r="E13" s="106" t="inlineStr">
         <is>
           <t>▲ +9.4%</t>
         </is>
       </c>
-      <c r="G12" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Ghana</t>
-        </is>
-      </c>
-      <c r="H12" s="107" t="inlineStr">
+      <c r="G13" s="114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Ghana</t>
+        </is>
+      </c>
+      <c r="H13" s="100" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="I12" s="108" t="n">
-        <v>0.8471</v>
-      </c>
-      <c r="J12" s="109" t="n">
-        <v>1.0892</v>
-      </c>
-      <c r="K12" s="106" t="inlineStr">
-        <is>
-          <t>▼ -7.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Kenya</t>
-        </is>
-      </c>
-      <c r="B13" s="96" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="C13" s="97" t="n">
-        <v>1.5142</v>
-      </c>
-      <c r="D13" s="98" t="n">
-        <v>1.5067</v>
-      </c>
-      <c r="E13" s="114" t="inlineStr">
-        <is>
-          <t>▲ +8.3%</t>
-        </is>
-      </c>
-      <c r="G13" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Eswatini</t>
-        </is>
-      </c>
-      <c r="H13" s="100" t="inlineStr">
+      <c r="I13" s="101" t="n">
+        <v>0.8439</v>
+      </c>
+      <c r="J13" s="102" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="K13" s="110" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Morocco</t>
+        </is>
+      </c>
+      <c r="B14" s="103" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="C14" s="104" t="n">
+        <v>1.5444</v>
+      </c>
+      <c r="D14" s="105" t="n">
+        <v>1.5444</v>
+      </c>
+      <c r="E14" s="106" t="inlineStr">
+        <is>
+          <t>▲ +21.0%</t>
+        </is>
+      </c>
+      <c r="G14" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Eswatini</t>
+        </is>
+      </c>
+      <c r="H14" s="107" t="inlineStr">
         <is>
           <t>Southern Africa</t>
         </is>
       </c>
-      <c r="I13" s="101" t="n">
+      <c r="I14" s="108" t="n">
         <v>0.8625</v>
       </c>
-      <c r="J13" s="102" t="n">
+      <c r="J14" s="109" t="n">
         <v>0.8625</v>
       </c>
-      <c r="K13" s="106" t="inlineStr">
+      <c r="K14" s="110" t="inlineStr">
         <is>
           <t>▼ -19.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Sudan</t>
-        </is>
-      </c>
-      <c r="B14" s="103" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="C14" s="104" t="n">
-        <v>1.5074</v>
-      </c>
-      <c r="D14" s="105" t="n">
-        <v>1.1431</v>
-      </c>
-      <c r="E14" s="114" t="inlineStr">
-        <is>
-          <t>▲ +43.9%</t>
-        </is>
-      </c>
-      <c r="G14" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Burkina Faso</t>
-        </is>
-      </c>
-      <c r="H14" s="107" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="I14" s="108" t="n">
-        <v>0.8858</v>
-      </c>
-      <c r="J14" s="109" t="n">
-        <v>1.6374</v>
-      </c>
-      <c r="K14" s="106" t="inlineStr">
-        <is>
-          <t>▼ -36.4%</t>
         </is>
       </c>
     </row>
@@ -7867,15 +7867,15 @@
         <v>0.6602</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.2544</v>
+        <v>2.0907</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +216.7%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.5942</v>
+        <v>1.4305</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -7898,15 +7898,15 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.0871</v>
+        <v>0.9856</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +52.9%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.4424</v>
+        <v>0.3409</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -7929,108 +7929,108 @@
         <v>1.0474</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.5074</v>
+        <v>1.5126</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +43.9%</t>
+          <t>▲ +44.4%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.46</v>
+        <v>0.4652</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.15</v>
+        <v>1.0882</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.6</v>
+        <v>1.5342</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.45</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0616</v>
+        <v>0.5861</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.4096</v>
+        <v>0.7742</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.8%</t>
+          <t>▲ +32.1%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.348</v>
+        <v>0.1881</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.2762</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.3014</v>
+        <v>1.5444</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +21.0%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2132</v>
+        <v>0.2682</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -8067,94 +8067,94 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.2332</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>0.6663</v>
+        <v>1.4286</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.3691</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.5742</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.2332</v>
+        <v>0.8608</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.3736</v>
+        <v>0.9639</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1404</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -8377,559 +8377,559 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.0555</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.2961</v>
+        <v>1.0582</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0199</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.31</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3873</v>
-      </c>
-      <c r="F37" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.4%</t>
-        </is>
-      </c>
-      <c r="G37" s="117" t="n">
-        <v>0.0192</v>
+        <v>1.3037</v>
+      </c>
+      <c r="F37" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
+        </is>
+      </c>
+      <c r="G37" s="119" t="n">
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.2677</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.0582</v>
-      </c>
-      <c r="F38" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
-        </is>
-      </c>
-      <c r="G38" s="117" t="n">
-        <v>0.0027</v>
+        <v>1.257</v>
+      </c>
+      <c r="F38" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
+        </is>
+      </c>
+      <c r="G38" s="119" t="n">
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.31</v>
+        <v>1.3289</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3037</v>
+        <v>1.3146</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0063</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.2886</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3595</v>
+        <v>1.266</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.7%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.2262</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.257</v>
+        <v>1.2003</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.784</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.3146</v>
+        <v>1.6851</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.0641</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.2579</v>
+        <v>0.9982</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.4%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0307</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.784</v>
+        <v>2.17</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.6851</v>
+        <v>2.0242</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.1458</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.0641</v>
+        <v>0.914</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.9982</v>
+        <v>0.8439</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0701</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>2.17</v>
+        <v>1.2212</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>2.0242</v>
+        <v>1.1258</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.1458</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>0.914</v>
+        <v>1.0671</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.8471</v>
+        <v>0.9685</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -9.2%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0669</v>
+        <v>-0.09859999999999999</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.1939</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.1258</v>
+        <v>1.0606</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.0671</v>
+        <v>0.4771</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>0.9685</v>
+        <v>0.4175</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0596</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.15</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.0927</v>
+        <v>1</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.9%</t>
+          <t>▼ -13.0%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.1335</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.0722</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>1.0606</v>
+        <v>0.8625</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.0616</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.4175</v>
+        <v>0.7476</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.6%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.0596</v>
+        <v>-0.314</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B53" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C53" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D53" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.3681</v>
       </c>
       <c r="E53" s="91" t="n">
-        <v>0.8625</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -32.4%</t>
         </is>
       </c>
       <c r="G53" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.4432</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -9017,16 +9017,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.7398333333333333</v>
+        <v>0.7820833333333334</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6295333333333333</v>
+        <v>0.656</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.5074</v>
+        <v>1.5444</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9122,13 +9122,13 @@
         <v>0.4175</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.3479</v>
+        <v>0.2584</v>
       </c>
       <c r="E7" s="67" t="n">
         <v>21</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
@@ -9187,20 +9187,20 @@
         </is>
       </c>
       <c r="C9" s="66" t="n">
-        <v>1.2961</v>
+        <v>1.5444</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.2961</v>
+        <v>1.5444</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>13</v>
+        <v>15.49</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>13</v>
+        <v>15.49</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +21.0%</t>
         </is>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -9221,20 +9221,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.5074</v>
+        <v>1.5126</v>
       </c>
       <c r="D10" s="57" t="n">
         <v>1.1431</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>906.7</v>
+        <v>909.8</v>
       </c>
       <c r="F10" s="58" t="n">
         <v>687.5650000000001</v>
       </c>
       <c r="G10" s="71" t="inlineStr">
         <is>
-          <t>▲ +43.9%</t>
+          <t>▲ +44.4%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9293,13 +9293,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.16696875</v>
+        <v>1.16639375</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.13701875</v>
+        <v>1.2078125</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6663</v>
+        <v>0.7742</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9361,20 +9361,20 @@
         </is>
       </c>
       <c r="C16" s="57" t="n">
-        <v>1.0927</v>
+        <v>1.2003</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>0.9603</v>
+        <v>1.2417</v>
       </c>
       <c r="E16" s="58" t="n">
-        <v>660</v>
+        <v>725</v>
       </c>
       <c r="F16" s="58" t="n">
-        <v>580</v>
+        <v>750</v>
       </c>
       <c r="G16" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.9%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="H16" s="61" t="inlineStr">
@@ -9429,20 +9429,20 @@
         </is>
       </c>
       <c r="C18" s="57" t="n">
-        <v>1.2579</v>
+        <v>1.266</v>
       </c>
       <c r="D18" s="57" t="n">
-        <v>1.0588</v>
+        <v>1.0635</v>
       </c>
       <c r="E18" s="58" t="n">
-        <v>139</v>
+        <v>139.89</v>
       </c>
       <c r="F18" s="58" t="n">
-        <v>117</v>
+        <v>117.52</v>
       </c>
       <c r="G18" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.4%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="H18" s="61" t="inlineStr">
@@ -9463,20 +9463,20 @@
         </is>
       </c>
       <c r="C19" s="66" t="n">
-        <v>1.3014</v>
+        <v>1.5342</v>
       </c>
       <c r="D19" s="66" t="n">
-        <v>0.6493</v>
+        <v>1.6438</v>
       </c>
       <c r="E19" s="67" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="F19" s="67" t="n">
-        <v>47.4</v>
+        <v>120</v>
       </c>
       <c r="G19" s="71" t="inlineStr">
         <is>
-          <t>▲ +19.6%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="H19" s="70" t="inlineStr">
@@ -9497,20 +9497,20 @@
         </is>
       </c>
       <c r="C20" s="57" t="n">
-        <v>0.8471</v>
+        <v>0.8439</v>
       </c>
       <c r="D20" s="57" t="n">
-        <v>1.0892</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="E20" s="58" t="n">
-        <v>13.3</v>
+        <v>13.25</v>
       </c>
       <c r="F20" s="58" t="n">
-        <v>17.1</v>
+        <v>14.3</v>
       </c>
       <c r="G20" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.3%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="H20" s="61" t="inlineStr">
@@ -9531,20 +9531,20 @@
         </is>
       </c>
       <c r="C21" s="66" t="n">
-        <v>1.3873</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="D21" s="66" t="n">
-        <v>1.3873</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="E21" s="67" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="F21" s="67" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.4%</t>
+        <v>8000</v>
+      </c>
+      <c r="G21" s="69" t="inlineStr">
+        <is>
+          <t>▼ -32.4%</t>
         </is>
       </c>
       <c r="H21" s="70" t="inlineStr">
@@ -9769,20 +9769,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6663</v>
+        <v>0.7742</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6663</v>
+        <v>1.1592</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1080</v>
+        <v>1255</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1080</v>
+        <v>1879</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +13.7%</t>
+          <t>▲ +32.1%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="H36" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -10253,13 +10253,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.515166666666667</v>
+        <v>1.494333333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.472813333333333</v>
+        <v>1.410433333333333</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>1.0606</v>
+        <v>0.7476</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10457,20 +10457,20 @@
         </is>
       </c>
       <c r="C52" s="57" t="n">
-        <v>1.0871</v>
+        <v>0.9856</v>
       </c>
       <c r="D52" s="57" t="n">
-        <v>1.245</v>
+        <v>0.9856</v>
       </c>
       <c r="E52" s="58" t="n">
-        <v>142.41</v>
+        <v>129.12</v>
       </c>
       <c r="F52" s="58" t="n">
-        <v>163.09</v>
+        <v>129.12</v>
       </c>
       <c r="G52" s="71" t="inlineStr">
         <is>
-          <t>▲ +68.6%</t>
+          <t>▲ +52.9%</t>
         </is>
       </c>
       <c r="H52" s="61" t="inlineStr">
@@ -10494,13 +10494,13 @@
         <v>1.5142</v>
       </c>
       <c r="D53" s="66" t="n">
-        <v>1.5067</v>
+        <v>1.5142</v>
       </c>
       <c r="E53" s="67" t="n">
         <v>197.6</v>
       </c>
       <c r="F53" s="67" t="n">
-        <v>196.63</v>
+        <v>197.6</v>
       </c>
       <c r="G53" s="71" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="H53" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -10596,13 +10596,13 @@
         <v>1.257</v>
       </c>
       <c r="D56" s="57" t="n">
-        <v>1.257</v>
+        <v>1.3935</v>
       </c>
       <c r="E56" s="58" t="n">
         <v>58.45</v>
       </c>
       <c r="F56" s="58" t="n">
-        <v>58.45</v>
+        <v>64.8</v>
       </c>
       <c r="G56" s="69" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="H56" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -10627,20 +10627,20 @@
         </is>
       </c>
       <c r="C57" s="66" t="n">
-        <v>1.3595</v>
+        <v>1.5742</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.3315</v>
+        <v>1.5072</v>
       </c>
       <c r="E57" s="67" t="n">
-        <v>1989</v>
+        <v>2303</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>1948</v>
-      </c>
-      <c r="G57" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+        <v>2205</v>
+      </c>
+      <c r="G57" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="H57" s="70" t="inlineStr">
@@ -10695,20 +10695,20 @@
         </is>
       </c>
       <c r="C59" s="66" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="D59" s="66" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="E59" s="67" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="F59" s="67" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G59" s="71" t="inlineStr">
-        <is>
-          <t>▲ +39.1%</t>
+        <v>1</v>
+      </c>
+      <c r="G59" s="69" t="inlineStr">
+        <is>
+          <t>▼ -13.0%</t>
         </is>
       </c>
       <c r="H59" s="70" t="inlineStr">
@@ -10729,20 +10729,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>1.2544</v>
+        <v>2.0907</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>1.2544</v>
+        <v>1.3204</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>5700</v>
+        <v>9500</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="G60" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +216.7%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">
@@ -10763,20 +10763,20 @@
         </is>
       </c>
       <c r="C61" s="66" t="n">
-        <v>1.4096</v>
+        <v>0.7476</v>
       </c>
       <c r="D61" s="66" t="n">
-        <v>1.4096</v>
+        <v>0.7476</v>
       </c>
       <c r="E61" s="67" t="n">
-        <v>3820</v>
+        <v>2026</v>
       </c>
       <c r="F61" s="67" t="n">
-        <v>3820</v>
-      </c>
-      <c r="G61" s="71" t="inlineStr">
-        <is>
-          <t>▲ +32.8%</t>
+        <v>2026</v>
+      </c>
+      <c r="G61" s="69" t="inlineStr">
+        <is>
+          <t>▼ -29.6%</t>
         </is>
       </c>
       <c r="H61" s="70" t="inlineStr">
@@ -10835,10 +10835,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.157333333333333</v>
+        <v>1.163444444444445</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.139955555555556</v>
+        <v>1.163255555555556</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -11107,20 +11107,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.4286</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.3736</v>
+        <v>1.4286</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G73" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">
@@ -11144,13 +11144,13 @@
         <v>0.9982</v>
       </c>
       <c r="D74" s="66" t="n">
-        <v>1.0949</v>
+        <v>1.2496</v>
       </c>
       <c r="E74" s="67" t="n">
         <v>27.15</v>
       </c>
       <c r="F74" s="67" t="n">
-        <v>29.78</v>
+        <v>33.99</v>
       </c>
       <c r="G74" s="69" t="inlineStr">
         <is>

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1073,23 +1073,23 @@
     <xf numFmtId="164" fontId="19" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="57" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-01</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-02</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.222</t>
+          <t>$1.218</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+216.7%</t>
+          <t>+73.9%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.188</t>
+          <t>$1.195</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.7820833333333334</v>
+        <v>0.7376166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.656</v>
+        <v>0.6393833333333333</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.5444</v>
+        <v>1.5134</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.16639375</v>
+        <v>1.2121625</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.2078125</v>
+        <v>1.23669375</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.7742</v>
+        <v>0.8439</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.494333333333333</v>
+        <v>1.45132</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.410433333333333</v>
+        <v>1.412273333333333</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.7476</v>
+        <v>0.6602</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-01</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-02</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.1988</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2584</v>
+        <v>0.1988</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -58.3%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.5444</v>
+        <v>1.4955</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.5444</v>
+        <v>1.4955</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>15.49</v>
+        <v>15</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>15.49</v>
+        <v>15</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
-          <t>▲ +21.0%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="K7" s="70" t="inlineStr">
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.5126</v>
+        <v>1.5134</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>1.1431</v>
+        <v>1.1519</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>909.8</v>
+        <v>910.3</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>687.5650000000001</v>
+        <v>692.849</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
       <c r="J8" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.4%</t>
+          <t>▲ +44.5%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2585,23 +2585,23 @@
         </is>
       </c>
       <c r="E16" s="57" t="n">
-        <v>0.9249000000000001</v>
+        <v>1.3873</v>
       </c>
       <c r="F16" s="57" t="n">
-        <v>0.9249000000000001</v>
+        <v>1.3873</v>
       </c>
       <c r="G16" s="58" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="H16" s="58" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="I16" s="59" t="n">
         <v>8650</v>
       </c>
-      <c r="J16" s="69" t="inlineStr">
-        <is>
-          <t>▼ -32.4%</t>
+      <c r="J16" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="K16" s="61" t="inlineStr">
@@ -2726,23 +2726,23 @@
         </is>
       </c>
       <c r="E19" s="66" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="F19" s="66" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="G19" s="67" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="I19" s="68" t="n">
         <v>194</v>
       </c>
       <c r="J19" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="K19" s="70" t="inlineStr">
@@ -2867,23 +2867,23 @@
         </is>
       </c>
       <c r="E22" s="57" t="n">
-        <v>0.8262</v>
+        <v>0.894</v>
       </c>
       <c r="F22" s="57" t="n">
-        <v>1.0232</v>
+        <v>0.894</v>
       </c>
       <c r="G22" s="58" t="n">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="H22" s="58" t="n">
-        <v>618</v>
+        <v>540</v>
       </c>
       <c r="I22" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J22" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J22" s="71" t="inlineStr">
+        <is>
+          <t>▲ +8.2%</t>
         </is>
       </c>
       <c r="K22" s="61" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.7742</v>
+        <v>0.863</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>1.1592</v>
+        <v>0.863</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1255</v>
+        <v>1399</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1879</v>
+        <v>1399</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.1%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="K28" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -3871,13 +3871,13 @@
         <v>1.257</v>
       </c>
       <c r="F45" s="66" t="n">
-        <v>1.3935</v>
+        <v>1.257</v>
       </c>
       <c r="G45" s="67" t="n">
         <v>58.45</v>
       </c>
       <c r="H45" s="67" t="n">
-        <v>64.8</v>
+        <v>58.45</v>
       </c>
       <c r="I45" s="68" t="n">
         <v>46.5</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="K45" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -3915,23 +3915,23 @@
         </is>
       </c>
       <c r="E46" s="57" t="n">
-        <v>1.5742</v>
+        <v>1.3595</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.5072</v>
+        <v>1.3315</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>2303</v>
+        <v>1989</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>2205</v>
+        <v>1948</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
       </c>
-      <c r="J46" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+      <c r="J46" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="K46" s="61" t="inlineStr">
@@ -4009,23 +4009,23 @@
         </is>
       </c>
       <c r="E48" s="57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" s="58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="69" t="inlineStr">
-        <is>
-          <t>▼ -13.0%</t>
+      <c r="J48" s="71" t="inlineStr">
+        <is>
+          <t>▲ +73.9%</t>
         </is>
       </c>
       <c r="K48" s="61" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>2.0907</v>
+        <v>0.6602</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>1.3204</v>
+        <v>0.6602</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>9500</v>
+        <v>3000</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="71" t="inlineStr">
-        <is>
-          <t>▲ +216.7%</t>
+      <c r="J49" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.221538888888888</v>
+        <v>1.218211111111111</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.187505555555555</v>
+        <v>1.194727777777778</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-01</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-02</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.4175</v>
+        <v>0.1988</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -58.3%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2584</v>
+        <v>0.1988</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -36.6%</t>
+          <t>▼ -51.2%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.5444</v>
+        <v>1.4955</v>
       </c>
       <c r="E8" s="71" t="inlineStr">
         <is>
-          <t>▲ +21.0%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.5444</v>
+        <v>1.4955</v>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>▲ +34.7%</t>
+          <t>▲ +30.4%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>15.49</v>
+        <v>15</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>15.49</v>
+        <v>15</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.5126</v>
+        <v>1.5134</v>
       </c>
       <c r="E9" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.4%</t>
+          <t>▲ +44.5%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.1431</v>
+        <v>1.1519</v>
       </c>
       <c r="H9" s="71" t="inlineStr">
         <is>
-          <t>▲ +16.5%</t>
+          <t>▲ +17.4%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>909.8</v>
+        <v>910.3</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>687.5650000000001</v>
+        <v>692.849</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5298,29 +5298,29 @@
         <v>1.3681</v>
       </c>
       <c r="D17" s="89" t="n">
-        <v>0.9249000000000001</v>
-      </c>
-      <c r="E17" s="69" t="inlineStr">
-        <is>
-          <t>▼ -32.4%</t>
+        <v>1.3873</v>
+      </c>
+      <c r="E17" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="F17" s="90" t="n">
         <v>1.341</v>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.9249000000000001</v>
-      </c>
-      <c r="H17" s="69" t="inlineStr">
-        <is>
-          <t>▼ -31.0%</t>
+        <v>1.3873</v>
+      </c>
+      <c r="H17" s="71" t="inlineStr">
+        <is>
+          <t>▲ +3.5%</t>
         </is>
       </c>
       <c r="I17" s="67" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="J17" s="67" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="K17" s="70" t="inlineStr">
         <is>
@@ -5433,29 +5433,29 @@
         <v>0.8608</v>
       </c>
       <c r="D20" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="E20" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="F20" s="90" t="n">
         <v>0.9124</v>
       </c>
       <c r="G20" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="H20" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.6%</t>
+          <t>▲ +52.2%</t>
         </is>
       </c>
       <c r="I20" s="58" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="J20" s="58" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="K20" s="61" t="inlineStr">
         <is>
@@ -5568,29 +5568,29 @@
         <v>0.8262</v>
       </c>
       <c r="D23" s="89" t="n">
-        <v>0.8262</v>
-      </c>
-      <c r="E23" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.894</v>
+      </c>
+      <c r="E23" s="71" t="inlineStr">
+        <is>
+          <t>▲ +8.2%</t>
         </is>
       </c>
       <c r="F23" s="90" t="n">
         <v>1.0232</v>
       </c>
       <c r="G23" s="89" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="H23" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.894</v>
+      </c>
+      <c r="H23" s="69" t="inlineStr">
+        <is>
+          <t>▼ -12.6%</t>
         </is>
       </c>
       <c r="I23" s="67" t="n">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="J23" s="67" t="n">
-        <v>618</v>
+        <v>540</v>
       </c>
       <c r="K23" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.7742</v>
+        <v>0.863</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.1%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>1.1592</v>
+        <v>0.863</v>
       </c>
       <c r="H24" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.6%</t>
+          <t>▲ +16.6%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1255</v>
+        <v>1399</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1879</v>
+        <v>1399</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K29" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -6538,22 +6538,22 @@
         <v>1.2677</v>
       </c>
       <c r="G46" s="91" t="n">
-        <v>1.3935</v>
-      </c>
-      <c r="H46" s="71" t="inlineStr">
-        <is>
-          <t>▲ +9.9%</t>
+        <v>1.257</v>
+      </c>
+      <c r="H46" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="I46" s="58" t="n">
         <v>58.45</v>
       </c>
       <c r="J46" s="58" t="n">
-        <v>64.8</v>
+        <v>58.45</v>
       </c>
       <c r="K46" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -6572,29 +6572,29 @@
         <v>1.3691</v>
       </c>
       <c r="D47" s="89" t="n">
-        <v>1.5742</v>
-      </c>
-      <c r="E47" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+        <v>1.3595</v>
+      </c>
+      <c r="E47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="F47" s="90" t="n">
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="H47" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.3%</t>
+        <v>1.3315</v>
+      </c>
+      <c r="H47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
-        <v>2303</v>
+        <v>1989</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>2205</v>
+        <v>1948</v>
       </c>
       <c r="K47" s="70" t="inlineStr">
         <is>
@@ -6662,29 +6662,29 @@
         <v>1.15</v>
       </c>
       <c r="D49" s="89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="69" t="inlineStr">
-        <is>
-          <t>▼ -13.0%</t>
+        <v>2</v>
+      </c>
+      <c r="E49" s="71" t="inlineStr">
+        <is>
+          <t>▲ +73.9%</t>
         </is>
       </c>
       <c r="F49" s="90" t="n">
         <v>1.05</v>
       </c>
       <c r="G49" s="89" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="69" t="inlineStr">
-        <is>
-          <t>▼ -4.8%</t>
+        <v>2</v>
+      </c>
+      <c r="H49" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.5%</t>
         </is>
       </c>
       <c r="I49" s="67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" s="67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" s="70" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>2.0907</v>
-      </c>
-      <c r="E50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +216.7%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="E50" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>1.3204</v>
-      </c>
-      <c r="H50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +100.0%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="H50" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>9500</v>
+        <v>3000</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -7409,84 +7409,84 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  South Sudan</t>
+          <t xml:space="preserve">  2.  Zimbabwe</t>
         </is>
       </c>
       <c r="B6" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2.0907</v>
+        <v>2.0242</v>
       </c>
       <c r="D6" s="105" t="n">
-        <v>1.3204</v>
+        <v>1.9231</v>
       </c>
       <c r="E6" s="106" t="inlineStr">
         <is>
-          <t>▲ +216.7%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Angola</t>
+          <t xml:space="preserve">  2.  Egypt</t>
         </is>
       </c>
       <c r="H6" s="107" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I6" s="108" t="n">
-        <v>0.3272</v>
+        <v>0.1988</v>
       </c>
       <c r="J6" s="109" t="n">
-        <v>0.2181</v>
-      </c>
-      <c r="K6" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.1988</v>
+      </c>
+      <c r="K6" s="106" t="inlineStr">
+        <is>
+          <t>▼ -58.3%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Zimbabwe</t>
+          <t xml:space="preserve">  3.  Eritrea</t>
         </is>
       </c>
       <c r="B7" s="96" t="inlineStr">
         <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C7" s="97" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="98" t="n">
+        <v>1.7333</v>
+      </c>
+      <c r="E7" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3.  Angola</t>
+        </is>
+      </c>
+      <c r="H7" s="100" t="inlineStr">
+        <is>
           <t>Southern Africa</t>
         </is>
       </c>
-      <c r="C7" s="97" t="n">
-        <v>2.0242</v>
-      </c>
-      <c r="D7" s="98" t="n">
-        <v>1.9231</v>
-      </c>
-      <c r="E7" s="110" t="inlineStr">
-        <is>
-          <t>▼ -6.7%</t>
-        </is>
-      </c>
-      <c r="G7" s="95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3.  Algeria</t>
-        </is>
-      </c>
-      <c r="H7" s="100" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
       <c r="I7" s="101" t="n">
-        <v>0.3494</v>
+        <v>0.3272</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2305</v>
+        <v>0.2181</v>
       </c>
       <c r="K7" s="99" t="inlineStr">
         <is>
@@ -7495,9 +7495,9 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Eritrea</t>
+      <c r="A8" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Somalia</t>
         </is>
       </c>
       <c r="B8" s="103" t="inlineStr">
@@ -7509,32 +7509,32 @@
         <v>2</v>
       </c>
       <c r="D8" s="105" t="n">
-        <v>1.7333</v>
-      </c>
-      <c r="E8" s="99" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E8" s="111" t="inlineStr">
+        <is>
+          <t>▲ +73.9%</t>
+        </is>
+      </c>
+      <c r="G8" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Algeria</t>
+        </is>
+      </c>
+      <c r="H8" s="107" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="I8" s="108" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="J8" s="109" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="K8" s="99" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Egypt</t>
-        </is>
-      </c>
-      <c r="H8" s="107" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="I8" s="108" t="n">
-        <v>0.4175</v>
-      </c>
-      <c r="J8" s="109" t="n">
-        <v>0.2584</v>
-      </c>
-      <c r="K8" s="110" t="inlineStr">
-        <is>
-          <t>▼ -12.5%</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="G9" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Tanzania</t>
+          <t xml:space="preserve">  5.  South Sudan</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
@@ -7571,19 +7571,19 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.7476</v>
+        <v>0.6602</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.7476</v>
-      </c>
-      <c r="K9" s="110" t="inlineStr">
-        <is>
-          <t>▼ -29.6%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="K9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="111" t="inlineStr">
+      <c r="A10" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">  6.  Comoros</t>
         </is>
@@ -7599,30 +7599,30 @@
       <c r="D10" s="105" t="n">
         <v>1.5078</v>
       </c>
-      <c r="E10" s="110" t="inlineStr">
+      <c r="E10" s="106" t="inlineStr">
         <is>
           <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G10" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Nigeria</t>
+          <t xml:space="preserve">  6.  Tanzania</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.7742</v>
+        <v>0.7476</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>1.1592</v>
+        <v>0.7476</v>
       </c>
       <c r="K10" s="106" t="inlineStr">
         <is>
-          <t>▲ +32.1%</t>
+          <t>▼ -29.6%</t>
         </is>
       </c>
     </row>
@@ -7643,81 +7643,81 @@
       <c r="D11" s="98" t="n">
         <v>1.25</v>
       </c>
-      <c r="E11" s="106" t="inlineStr">
+      <c r="E11" s="111" t="inlineStr">
         <is>
           <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G11" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Niger</t>
+          <t xml:space="preserve">  7.  Tunisia</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="I11" s="101" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="J11" s="102" t="n">
+        <v>0.7318</v>
+      </c>
+      <c r="K11" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Sierra Leone</t>
+        </is>
+      </c>
+      <c r="B12" s="103" t="inlineStr">
+        <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="I11" s="101" t="n">
-        <v>0.8262</v>
-      </c>
-      <c r="J11" s="102" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K11" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Rwanda</t>
-        </is>
-      </c>
-      <c r="B12" s="103" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
       <c r="C12" s="104" t="n">
-        <v>1.5742</v>
+        <v>1.5556</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="E12" s="106" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+        <v>1.7778</v>
+      </c>
+      <c r="E12" s="111" t="inlineStr">
+        <is>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G12" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Tunisia</t>
+          <t xml:space="preserve">  8.  Ghana</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8377</v>
+        <v>0.8439</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.7318</v>
-      </c>
-      <c r="K12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="K12" s="106" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Sierra Leone</t>
+          <t xml:space="preserve">  9.  Gambia</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
@@ -7726,79 +7726,79 @@
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5556</v>
+        <v>1.5342</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.7778</v>
-      </c>
-      <c r="E13" s="106" t="inlineStr">
-        <is>
-          <t>▲ +9.4%</t>
+        <v>1.6438</v>
+      </c>
+      <c r="E13" s="111" t="inlineStr">
+        <is>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="G13" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Ghana</t>
+          <t xml:space="preserve">  9.  Eswatini</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
+          <t>Southern Africa</t>
+        </is>
+      </c>
+      <c r="I13" s="101" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="J13" s="102" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="K13" s="106" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Kenya</t>
+        </is>
+      </c>
+      <c r="B14" s="103" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C14" s="104" t="n">
+        <v>1.5142</v>
+      </c>
+      <c r="D14" s="105" t="n">
+        <v>1.5142</v>
+      </c>
+      <c r="E14" s="111" t="inlineStr">
+        <is>
+          <t>▲ +8.3%</t>
+        </is>
+      </c>
+      <c r="G14" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Nigeria</t>
+        </is>
+      </c>
+      <c r="H14" s="107" t="inlineStr">
+        <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="I13" s="101" t="n">
-        <v>0.8439</v>
-      </c>
-      <c r="J13" s="102" t="n">
-        <v>0.9108000000000001</v>
-      </c>
-      <c r="K13" s="110" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Morocco</t>
-        </is>
-      </c>
-      <c r="B14" s="103" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="C14" s="104" t="n">
-        <v>1.5444</v>
-      </c>
-      <c r="D14" s="105" t="n">
-        <v>1.5444</v>
-      </c>
-      <c r="E14" s="106" t="inlineStr">
-        <is>
-          <t>▲ +21.0%</t>
-        </is>
-      </c>
-      <c r="G14" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Eswatini</t>
-        </is>
-      </c>
-      <c r="H14" s="107" t="inlineStr">
-        <is>
-          <t>Southern Africa</t>
-        </is>
-      </c>
       <c r="I14" s="108" t="n">
-        <v>0.8625</v>
+        <v>0.863</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="K14" s="110" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+        <v>0.863</v>
+      </c>
+      <c r="K14" s="111" t="inlineStr">
+        <is>
+          <t>▲ +47.2%</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,22 +7860,22 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6602</v>
+        <v>1.15</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>2.0907</v>
+        <v>2</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +216.7%</t>
+          <t>▲ +73.9%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>1.4305</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -7912,69 +7912,69 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.0474</v>
+        <v>0.5861</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.5126</v>
+        <v>0.863</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.4%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.4652</v>
+        <v>0.2769</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0474</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.5342</v>
+        <v>1.5134</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +41.0%</t>
+          <t>▲ +44.5%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.446</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
@@ -7984,53 +7984,53 @@
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0882</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>0.7742</v>
+        <v>1.5342</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.1%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.1881</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.2762</v>
+        <v>0.8608</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.5444</v>
+        <v>1.0772</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +21.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2682</v>
+        <v>0.2164</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -8067,187 +8067,187 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.2762</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.4286</v>
+        <v>1.4955</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.8%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1954</v>
+        <v>0.2193</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.2332</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.5742</v>
+        <v>1.4286</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.1425</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.9639</v>
+        <v>1.2555</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.4222</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.2555</v>
+        <v>1.5556</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.3986</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.5556</v>
+        <v>1.5142</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.3986</v>
+        <v>0.8262</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.5142</v>
+        <v>0.894</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +8.2%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.0678</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -8377,38 +8377,38 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3681</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.0582</v>
+        <v>1.3873</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,121 +8418,121 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0555</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F37" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G37" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F37" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G37" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.31</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.257</v>
+        <v>1.3037</v>
       </c>
       <c r="F38" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G38" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.3691</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3146</v>
+        <v>1.3595</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.009599999999999999</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.2677</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.266</v>
+        <v>1.257</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
@@ -8546,272 +8546,272 @@
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.3289</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.2003</v>
+        <v>1.3146</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.1%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0259</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.784</v>
+        <v>1.2886</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.6851</v>
+        <v>1.266</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.2262</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>0.9982</v>
+        <v>1.2003</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>2.17</v>
+        <v>1.784</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>2.0242</v>
+        <v>1.6851</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.1458</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>0.914</v>
+        <v>1.0641</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.8439</v>
+        <v>0.9982</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0701</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.2212</v>
+        <v>2.17</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>1.1258</v>
+        <v>2.0242</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.1458</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.0671</v>
+        <v>0.914</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.9685</v>
+        <v>0.8439</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.2%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0701</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2212</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.0606</v>
+        <v>1.1258</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.0671</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>0.4175</v>
+        <v>0.9685</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -9.2%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.0596</v>
+        <v>-0.09859999999999999</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
@@ -8821,22 +8821,22 @@
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.15</v>
+        <v>1.1939</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1</v>
+        <v>1.0606</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -13.0%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.15</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -8904,7 +8904,7 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="B53" s="54" t="inlineStr">
@@ -8914,53 +8914,53 @@
       </c>
       <c r="C53" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D53" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3919</v>
       </c>
       <c r="E53" s="91" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.8858</v>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>▼ -32.4%</t>
+          <t>▼ -36.4%</t>
         </is>
       </c>
       <c r="G53" s="119" t="n">
-        <v>-0.4432</v>
+        <v>-0.5061</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="62" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B54" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C54" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D54" s="88" t="n">
-        <v>1.3919</v>
+        <v>0.4771</v>
       </c>
       <c r="E54" s="89" t="n">
-        <v>0.8858</v>
+        <v>0.1988</v>
       </c>
       <c r="F54" s="69" t="inlineStr">
         <is>
-          <t>▼ -36.4%</t>
+          <t>▼ -58.3%</t>
         </is>
       </c>
       <c r="G54" s="119" t="n">
-        <v>-0.5061</v>
+        <v>-0.2783</v>
       </c>
     </row>
   </sheetData>
@@ -9017,16 +9017,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.7820833333333334</v>
+        <v>0.7376166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.656</v>
+        <v>0.6393833333333333</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.5444</v>
+        <v>1.5134</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9119,20 +9119,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.1988</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2584</v>
+        <v>0.1988</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -58.3%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9187,20 +9187,20 @@
         </is>
       </c>
       <c r="C9" s="66" t="n">
-        <v>1.5444</v>
+        <v>1.4955</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.5444</v>
+        <v>1.4955</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>15.49</v>
+        <v>15</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>15.49</v>
+        <v>15</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
-          <t>▲ +21.0%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -9221,20 +9221,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.5126</v>
+        <v>1.5134</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>1.1431</v>
+        <v>1.1519</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>909.8</v>
+        <v>910.3</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>687.5650000000001</v>
+        <v>692.849</v>
       </c>
       <c r="G10" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.4%</t>
+          <t>▲ +44.5%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9293,13 +9293,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.16639375</v>
+        <v>1.2121625</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.2078125</v>
+        <v>1.23669375</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.7742</v>
+        <v>0.8439</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9531,20 +9531,20 @@
         </is>
       </c>
       <c r="C21" s="66" t="n">
-        <v>0.9249000000000001</v>
+        <v>1.3873</v>
       </c>
       <c r="D21" s="66" t="n">
-        <v>0.9249000000000001</v>
+        <v>1.3873</v>
       </c>
       <c r="E21" s="67" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="F21" s="67" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G21" s="69" t="inlineStr">
-        <is>
-          <t>▼ -32.4%</t>
+        <v>12000</v>
+      </c>
+      <c r="G21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="H21" s="70" t="inlineStr">
@@ -9633,20 +9633,20 @@
         </is>
       </c>
       <c r="C24" s="57" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="D24" s="57" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="E24" s="58" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="F24" s="58" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="G24" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="H24" s="61" t="inlineStr">
@@ -9735,20 +9735,20 @@
         </is>
       </c>
       <c r="C27" s="66" t="n">
-        <v>0.8262</v>
+        <v>0.894</v>
       </c>
       <c r="D27" s="66" t="n">
-        <v>1.0232</v>
+        <v>0.894</v>
       </c>
       <c r="E27" s="67" t="n">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="F27" s="67" t="n">
-        <v>618</v>
-      </c>
-      <c r="G27" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>540</v>
+      </c>
+      <c r="G27" s="71" t="inlineStr">
+        <is>
+          <t>▲ +8.2%</t>
         </is>
       </c>
       <c r="H27" s="70" t="inlineStr">
@@ -9769,20 +9769,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.7742</v>
+        <v>0.863</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>1.1592</v>
+        <v>0.863</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1255</v>
+        <v>1399</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1879</v>
+        <v>1399</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.1%</t>
+          <t>▲ +47.2%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="H36" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -10253,13 +10253,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.494333333333333</v>
+        <v>1.45132</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.410433333333333</v>
+        <v>1.412273333333333</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.7476</v>
+        <v>0.6602</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10596,13 +10596,13 @@
         <v>1.257</v>
       </c>
       <c r="D56" s="57" t="n">
-        <v>1.3935</v>
+        <v>1.257</v>
       </c>
       <c r="E56" s="58" t="n">
         <v>58.45</v>
       </c>
       <c r="F56" s="58" t="n">
-        <v>64.8</v>
+        <v>58.45</v>
       </c>
       <c r="G56" s="69" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="H56" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -10627,20 +10627,20 @@
         </is>
       </c>
       <c r="C57" s="66" t="n">
-        <v>1.5742</v>
+        <v>1.3595</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.5072</v>
+        <v>1.3315</v>
       </c>
       <c r="E57" s="67" t="n">
-        <v>2303</v>
+        <v>1989</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>2205</v>
-      </c>
-      <c r="G57" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+        <v>1948</v>
+      </c>
+      <c r="G57" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="H57" s="70" t="inlineStr">
@@ -10695,20 +10695,20 @@
         </is>
       </c>
       <c r="C59" s="66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="69" t="inlineStr">
-        <is>
-          <t>▼ -13.0%</t>
+        <v>2</v>
+      </c>
+      <c r="G59" s="71" t="inlineStr">
+        <is>
+          <t>▲ +73.9%</t>
         </is>
       </c>
       <c r="H59" s="70" t="inlineStr">
@@ -10729,20 +10729,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>2.0907</v>
+        <v>0.6602</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>1.3204</v>
+        <v>0.6602</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>9500</v>
+        <v>3000</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +216.7%</t>
+        <v>3000</v>
+      </c>
+      <c r="G60" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-02</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-03</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.218</t>
+          <t>$1.228</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+73.9%</t>
+          <t>+90.0%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.195</t>
+          <t>$1.210</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,7 +1765,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.7376166666666667</v>
+        <v>0.7378</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>0.6393833333333333</v>
@@ -1774,7 +1774,7 @@
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.5134</v>
+        <v>1.5145</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.2121625</v>
+        <v>1.19474375</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.23669375</v>
+        <v>1.234175</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.8439</v>
+        <v>0.6521</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.45132</v>
+        <v>1.506806666666666</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.412273333333333</v>
+        <v>1.46906</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.6602</v>
+        <v>0.7476</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-02</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-03</t>
         </is>
       </c>
     </row>
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.5134</v>
+        <v>1.5145</v>
       </c>
       <c r="F8" s="57" t="n">
         <v>1.1519</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>910.3</v>
+        <v>911</v>
       </c>
       <c r="H8" s="58" t="n">
         <v>692.849</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="J8" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.5%</t>
+          <t>▲ +44.6%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2682,13 +2682,13 @@
         <v>1.3576</v>
       </c>
       <c r="F18" s="57" t="n">
-        <v>1.1175</v>
+        <v>1.1589</v>
       </c>
       <c r="G18" s="58" t="n">
         <v>820</v>
       </c>
       <c r="H18" s="58" t="n">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="I18" s="59" t="n">
         <v>604</v>
@@ -2867,23 +2867,23 @@
         </is>
       </c>
       <c r="E22" s="57" t="n">
-        <v>0.894</v>
+        <v>0.8262</v>
       </c>
       <c r="F22" s="57" t="n">
-        <v>0.894</v>
+        <v>1.0232</v>
       </c>
       <c r="G22" s="58" t="n">
-        <v>540</v>
+        <v>499</v>
       </c>
       <c r="H22" s="58" t="n">
-        <v>540</v>
+        <v>618</v>
       </c>
       <c r="I22" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J22" s="71" t="inlineStr">
-        <is>
-          <t>▲ +8.2%</t>
+      <c r="J22" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K22" s="61" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.863</v>
+        <v>0.6521</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.863</v>
+        <v>0.6521</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3680,23 +3680,23 @@
         </is>
       </c>
       <c r="E41" s="66" t="n">
-        <v>0.9856</v>
+        <v>1.009</v>
       </c>
       <c r="F41" s="66" t="n">
-        <v>0.9856</v>
+        <v>1.0675</v>
       </c>
       <c r="G41" s="67" t="n">
-        <v>129.12</v>
+        <v>132.18</v>
       </c>
       <c r="H41" s="67" t="n">
-        <v>129.12</v>
+        <v>139.84</v>
       </c>
       <c r="I41" s="68" t="n">
         <v>131</v>
       </c>
       <c r="J41" s="71" t="inlineStr">
         <is>
-          <t>▲ +52.9%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="K41" s="70" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="K45" s="70" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -3915,23 +3915,23 @@
         </is>
       </c>
       <c r="E46" s="57" t="n">
-        <v>1.3595</v>
+        <v>1.5742</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.3315</v>
+        <v>1.5072</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>1989</v>
+        <v>2303</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>1948</v>
+        <v>2205</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
       </c>
-      <c r="J46" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+      <c r="J46" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="K46" s="61" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J49" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.218211111111111</v>
+        <v>1.228483333333333</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.194727777777778</v>
+        <v>1.209755555555555</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-02</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-03</t>
         </is>
       </c>
     </row>
@@ -4976,11 +4976,11 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.5134</v>
+        <v>1.5145</v>
       </c>
       <c r="E9" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.5%</t>
+          <t>▲ +44.6%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>910.3</v>
+        <v>911</v>
       </c>
       <c r="J9" s="67" t="n">
         <v>692.849</v>
@@ -5399,18 +5399,18 @@
         <v>1.1185</v>
       </c>
       <c r="G19" s="89" t="n">
-        <v>1.1175</v>
-      </c>
-      <c r="H19" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.1589</v>
+      </c>
+      <c r="H19" s="71" t="inlineStr">
+        <is>
+          <t>▲ +3.6%</t>
         </is>
       </c>
       <c r="I19" s="67" t="n">
         <v>820</v>
       </c>
       <c r="J19" s="67" t="n">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="K19" s="70" t="inlineStr">
         <is>
@@ -5568,29 +5568,29 @@
         <v>0.8262</v>
       </c>
       <c r="D23" s="89" t="n">
-        <v>0.894</v>
-      </c>
-      <c r="E23" s="71" t="inlineStr">
-        <is>
-          <t>▲ +8.2%</t>
+        <v>0.8262</v>
+      </c>
+      <c r="E23" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="90" t="n">
         <v>1.0232</v>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.894</v>
-      </c>
-      <c r="H23" s="69" t="inlineStr">
-        <is>
-          <t>▼ -12.6%</t>
+        <v>1.0232</v>
+      </c>
+      <c r="H23" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="67" t="n">
-        <v>540</v>
+        <v>499</v>
       </c>
       <c r="J23" s="67" t="n">
-        <v>540</v>
+        <v>618</v>
       </c>
       <c r="K23" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.863</v>
+        <v>0.6521</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>▲ +16.6%</t>
+        <v>0.6521</v>
+      </c>
+      <c r="H24" s="69" t="inlineStr">
+        <is>
+          <t>▼ -11.9%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6347,29 +6347,29 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="D42" s="91" t="n">
-        <v>0.9856</v>
+        <v>1.009</v>
       </c>
       <c r="E42" s="71" t="inlineStr">
         <is>
-          <t>▲ +52.9%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="F42" s="90" t="n">
         <v>0.6288</v>
       </c>
       <c r="G42" s="91" t="n">
-        <v>0.9856</v>
+        <v>1.0675</v>
       </c>
       <c r="H42" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.7%</t>
+          <t>▲ +69.8%</t>
         </is>
       </c>
       <c r="I42" s="58" t="n">
-        <v>129.12</v>
+        <v>132.18</v>
       </c>
       <c r="J42" s="58" t="n">
-        <v>129.12</v>
+        <v>139.84</v>
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="K46" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -6572,29 +6572,29 @@
         <v>1.3691</v>
       </c>
       <c r="D47" s="89" t="n">
-        <v>1.3595</v>
-      </c>
-      <c r="E47" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+        <v>1.5742</v>
+      </c>
+      <c r="E47" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="F47" s="90" t="n">
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.3315</v>
-      </c>
-      <c r="H47" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.8%</t>
+        <v>1.5072</v>
+      </c>
+      <c r="H47" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.3%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
-        <v>1989</v>
+        <v>2303</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>1948</v>
+        <v>2205</v>
       </c>
       <c r="K47" s="70" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="E50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="E50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="H50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="H50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -7562,23 +7562,23 @@
       </c>
       <c r="G9" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  South Sudan</t>
+          <t xml:space="preserve">  5.  Nigeria</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6602</v>
+        <v>0.6521</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="K9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.6521</v>
+      </c>
+      <c r="K9" s="111" t="inlineStr">
+        <is>
+          <t>▲ +11.3%</t>
         </is>
       </c>
     </row>
@@ -7650,19 +7650,19 @@
       </c>
       <c r="G11" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Tunisia</t>
+          <t xml:space="preserve">  7.  Niger</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8377</v>
+        <v>0.8262</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.7318</v>
+        <v>1.0232</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7673,51 +7673,51 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Sierra Leone</t>
+          <t xml:space="preserve">  8.  Rwanda</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.5556</v>
+        <v>1.5742</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.7778</v>
+        <v>1.5072</v>
       </c>
       <c r="E12" s="111" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G12" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Ghana</t>
+          <t xml:space="preserve">  8.  Tunisia</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8439</v>
+        <v>0.8377</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.9108000000000001</v>
-      </c>
-      <c r="K12" s="106" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Gambia</t>
+          <t xml:space="preserve">  9.  Sierra Leone</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
@@ -7726,79 +7726,79 @@
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5342</v>
+        <v>1.5556</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.6438</v>
+        <v>1.7778</v>
       </c>
       <c r="E13" s="111" t="inlineStr">
         <is>
-          <t>▲ +41.0%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G13" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Eswatini</t>
+          <t xml:space="preserve">  9.  Ghana</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8625</v>
+        <v>0.8439</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.8625</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="K13" s="106" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Kenya</t>
+          <t xml:space="preserve">  10.  Gambia</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.5142</v>
+        <v>1.5342</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.5142</v>
+        <v>1.6438</v>
       </c>
       <c r="E14" s="111" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="G14" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Nigeria</t>
+          <t xml:space="preserve">  10.  Eswatini</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.863</v>
+        <v>0.8625</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="K14" s="111" t="inlineStr">
-        <is>
-          <t>▲ +47.2%</t>
+        <v>0.8625</v>
+      </c>
+      <c r="K14" s="106" t="inlineStr">
+        <is>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,28 +7860,28 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>1.15</v>
+        <v>0.6602</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>2</v>
+        <v>1.2544</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +73.9%</t>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.85</v>
+        <v>0.5942</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
@@ -7891,53 +7891,53 @@
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>0.9856</v>
+        <v>2</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +52.9%</t>
+          <t>▲ +73.9%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.3409</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>0.5861</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>0.863</v>
+        <v>1.009</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.2769</v>
+        <v>0.3643</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -7960,15 +7960,15 @@
         <v>1.0474</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.5134</v>
+        <v>1.5145</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.5%</t>
+          <t>▲ +44.6%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.466</v>
+        <v>0.4671</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -8129,38 +8129,38 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.3691</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.2555</v>
+        <v>1.5742</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.113</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,59 +8170,59 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.4222</v>
+        <v>0.5861</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.5556</v>
+        <v>0.6521</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.1425</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.5142</v>
+        <v>1.2555</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
@@ -8232,90 +8232,90 @@
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>0.8262</v>
+        <v>1.4222</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>0.894</v>
+        <v>1.5556</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.2%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.0678</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3986</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.6391</v>
+        <v>1.5142</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.5244</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.4968</v>
+        <v>1.6391</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,28 +8325,28 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.4106</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.421</v>
+        <v>1.4968</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
@@ -8356,90 +8356,90 @@
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3819</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.3699</v>
+        <v>1.421</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.022</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3479</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3873</v>
+        <v>1.3699</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3681</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.0582</v>
+        <v>1.3873</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
@@ -8449,53 +8449,53 @@
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0555</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F38" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G38" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F38" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G38" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.31</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3595</v>
+        <v>1.3037</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.7%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.7376166666666667</v>
+        <v>0.7378</v>
       </c>
       <c r="D4" s="123" t="n">
         <v>0.6393833333333333</v>
@@ -9026,7 +9026,7 @@
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.5134</v>
+        <v>1.5145</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9221,20 +9221,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.5134</v>
+        <v>1.5145</v>
       </c>
       <c r="D10" s="57" t="n">
         <v>1.1519</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>910.3</v>
+        <v>911</v>
       </c>
       <c r="F10" s="58" t="n">
         <v>692.849</v>
       </c>
       <c r="G10" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.5%</t>
+          <t>▲ +44.6%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9293,13 +9293,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.2121625</v>
+        <v>1.19474375</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.23669375</v>
+        <v>1.234175</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.8439</v>
+        <v>0.6521</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9602,13 +9602,13 @@
         <v>1.3576</v>
       </c>
       <c r="D23" s="66" t="n">
-        <v>1.1175</v>
+        <v>1.1589</v>
       </c>
       <c r="E23" s="67" t="n">
         <v>820</v>
       </c>
       <c r="F23" s="67" t="n">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="G23" s="60" t="inlineStr">
         <is>
@@ -9735,20 +9735,20 @@
         </is>
       </c>
       <c r="C27" s="66" t="n">
-        <v>0.894</v>
+        <v>0.8262</v>
       </c>
       <c r="D27" s="66" t="n">
-        <v>0.894</v>
+        <v>1.0232</v>
       </c>
       <c r="E27" s="67" t="n">
-        <v>540</v>
+        <v>499</v>
       </c>
       <c r="F27" s="67" t="n">
-        <v>540</v>
-      </c>
-      <c r="G27" s="71" t="inlineStr">
-        <is>
-          <t>▲ +8.2%</t>
+        <v>618</v>
+      </c>
+      <c r="G27" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" s="70" t="inlineStr">
@@ -9769,20 +9769,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.863</v>
+        <v>0.6521</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.863</v>
+        <v>0.6521</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1399</v>
+        <v>1057</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.2%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -10253,13 +10253,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.45132</v>
+        <v>1.506806666666666</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.412273333333333</v>
+        <v>1.46906</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.6602</v>
+        <v>0.7476</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10457,20 +10457,20 @@
         </is>
       </c>
       <c r="C52" s="57" t="n">
-        <v>0.9856</v>
+        <v>1.009</v>
       </c>
       <c r="D52" s="57" t="n">
-        <v>0.9856</v>
+        <v>1.0675</v>
       </c>
       <c r="E52" s="58" t="n">
-        <v>129.12</v>
+        <v>132.18</v>
       </c>
       <c r="F52" s="58" t="n">
-        <v>129.12</v>
+        <v>139.84</v>
       </c>
       <c r="G52" s="71" t="inlineStr">
         <is>
-          <t>▲ +52.9%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="H52" s="61" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="H56" s="61" t="inlineStr">
         <is>
-          <t>🟢 High</t>
+          <t>🟡 Medium</t>
         </is>
       </c>
     </row>
@@ -10627,20 +10627,20 @@
         </is>
       </c>
       <c r="C57" s="66" t="n">
-        <v>1.3595</v>
+        <v>1.5742</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.3315</v>
+        <v>1.5072</v>
       </c>
       <c r="E57" s="67" t="n">
-        <v>1989</v>
+        <v>2303</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>1948</v>
-      </c>
-      <c r="G57" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
+        <v>2205</v>
+      </c>
+      <c r="G57" s="71" t="inlineStr">
+        <is>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="H57" s="70" t="inlineStr">
@@ -10729,20 +10729,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G60" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5700</v>
+      </c>
+      <c r="G60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-03</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-04</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.228</t>
+          <t>$1.222</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+90.0%</t>
+          <t>+73.9%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.210</t>
+          <t>$1.194</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.7378</v>
+        <v>0.7743166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6393833333333333</v>
+        <v>0.6493166666666667</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.5145</v>
+        <v>1.5149</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.19474375</v>
+        <v>1.2008875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.234175</v>
+        <v>1.21774375</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6521</v>
+        <v>0.8262</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.506806666666666</v>
+        <v>1.462793333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.46906</v>
+        <v>1.425046666666667</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.7476</v>
+        <v>0.5942</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-03</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.1988</v>
+        <v>0.4175</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.1988</v>
+        <v>0.2584</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -58.3%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.5145</v>
+        <v>1.5149</v>
       </c>
       <c r="F8" s="57" t="n">
         <v>1.1519</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>911</v>
+        <v>911.2</v>
       </c>
       <c r="H8" s="58" t="n">
         <v>692.849</v>
@@ -2726,23 +2726,23 @@
         </is>
       </c>
       <c r="E19" s="66" t="n">
-        <v>1.0772</v>
+        <v>0.9639</v>
       </c>
       <c r="F19" s="66" t="n">
-        <v>1.389</v>
+        <v>0.9639</v>
       </c>
       <c r="G19" s="67" t="n">
-        <v>208.97</v>
+        <v>187</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>269.46</v>
+        <v>187</v>
       </c>
       <c r="I19" s="68" t="n">
         <v>194</v>
       </c>
       <c r="J19" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="K19" s="70" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.8637</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.8143</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1057</v>
+        <v>1400</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1057</v>
+        <v>1320</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +47.4%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="K45" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>1.2544</v>
+        <v>0.5942</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>1.2544</v>
+        <v>0.5942</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+      <c r="J49" s="69" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.228483333333333</v>
+        <v>1.222135185185185</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.209755555555555</v>
+        <v>1.193764814814815</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-03</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.1988</v>
+        <v>0.4175</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -58.3%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.1988</v>
+        <v>0.2584</v>
       </c>
       <c r="H6" s="69" t="inlineStr">
         <is>
-          <t>▼ -51.2%</t>
+          <t>▼ -36.6%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.5145</v>
+        <v>1.5149</v>
       </c>
       <c r="E9" s="71" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>911</v>
+        <v>911.2</v>
       </c>
       <c r="J9" s="67" t="n">
         <v>692.849</v>
@@ -5433,29 +5433,29 @@
         <v>0.8608</v>
       </c>
       <c r="D20" s="91" t="n">
-        <v>1.0772</v>
+        <v>0.9639</v>
       </c>
       <c r="E20" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="F20" s="90" t="n">
         <v>0.9124</v>
       </c>
       <c r="G20" s="91" t="n">
-        <v>1.389</v>
+        <v>0.9639</v>
       </c>
       <c r="H20" s="71" t="inlineStr">
         <is>
-          <t>▲ +52.2%</t>
+          <t>▲ +5.6%</t>
         </is>
       </c>
       <c r="I20" s="58" t="n">
-        <v>208.97</v>
+        <v>187</v>
       </c>
       <c r="J20" s="58" t="n">
-        <v>269.46</v>
+        <v>187</v>
       </c>
       <c r="K20" s="61" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6521</v>
+        <v>0.8637</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +47.4%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="H24" s="69" t="inlineStr">
-        <is>
-          <t>▼ -11.9%</t>
+        <v>0.8143</v>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>▲ +10.0%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1057</v>
+        <v>1400</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1057</v>
+        <v>1320</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="K46" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>1.2544</v>
-      </c>
-      <c r="E50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>0.5942</v>
+      </c>
+      <c r="E50" s="69" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>1.2544</v>
-      </c>
-      <c r="H50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>0.5942</v>
+      </c>
+      <c r="H50" s="69" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -7430,23 +7430,23 @@
       </c>
       <c r="G6" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.  Egypt</t>
+          <t xml:space="preserve">  2.  Angola</t>
         </is>
       </c>
       <c r="H6" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I6" s="108" t="n">
-        <v>0.1988</v>
+        <v>0.3272</v>
       </c>
       <c r="J6" s="109" t="n">
-        <v>0.1988</v>
-      </c>
-      <c r="K6" s="106" t="inlineStr">
-        <is>
-          <t>▼ -58.3%</t>
+        <v>0.2181</v>
+      </c>
+      <c r="K6" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7474,19 +7474,19 @@
       </c>
       <c r="G7" s="95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.  Angola</t>
+          <t xml:space="preserve">  3.  Algeria</t>
         </is>
       </c>
       <c r="H7" s="100" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I7" s="101" t="n">
-        <v>0.3272</v>
+        <v>0.3494</v>
       </c>
       <c r="J7" s="102" t="n">
-        <v>0.2181</v>
+        <v>0.2305</v>
       </c>
       <c r="K7" s="99" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="G8" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  Algeria</t>
+          <t xml:space="preserve">  4.  Egypt</t>
         </is>
       </c>
       <c r="H8" s="107" t="inlineStr">
@@ -7527,14 +7527,14 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.3494</v>
+        <v>0.4175</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.2305</v>
-      </c>
-      <c r="K8" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.2584</v>
+      </c>
+      <c r="K8" s="106" t="inlineStr">
+        <is>
+          <t>▼ -12.5%</t>
         </is>
       </c>
     </row>
@@ -7562,23 +7562,23 @@
       </c>
       <c r="G9" s="114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Nigeria</t>
+          <t xml:space="preserve">  5.  South Sudan</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6521</v>
+        <v>0.5942</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6521</v>
-      </c>
-      <c r="K9" s="111" t="inlineStr">
-        <is>
-          <t>▲ +11.3%</t>
+        <v>0.5942</v>
+      </c>
+      <c r="K9" s="106" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,28 +7860,28 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6602</v>
+        <v>1.15</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.2544</v>
+        <v>2</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +73.9%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.5942</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
@@ -7891,53 +7891,53 @@
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>1.15</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>2</v>
+        <v>1.009</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +73.9%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.85</v>
+        <v>0.3643</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.5861</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.009</v>
+        <v>0.8637</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +47.4%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.3643</v>
+        <v>0.2776</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -7960,7 +7960,7 @@
         <v>1.0474</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.5145</v>
+        <v>1.5149</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.4671</v>
+        <v>0.4675</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -8005,317 +8005,317 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.0316</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.0772</v>
+        <v>1.2129</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2164</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.2762</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.2129</v>
+        <v>1.4955</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2193</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.2332</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.4955</v>
+        <v>1.4286</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.2193</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.3691</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.4286</v>
+        <v>1.5742</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.8%</t>
+          <t>▲ +15.0%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1954</v>
+        <v>0.2051</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.3691</v>
+        <v>0.8608</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.5742</v>
+        <v>0.9639</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.1425</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>0.6521</v>
+        <v>1.2555</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.066</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.4222</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.2555</v>
+        <v>1.5556</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.3986</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.5556</v>
+        <v>1.5142</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.5244</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.5142</v>
+        <v>1.6391</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.4106</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.4968</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,28 +8325,28 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3819</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4968</v>
+        <v>1.421</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
@@ -8356,90 +8356,90 @@
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.3479</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.421</v>
+        <v>1.3699</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3681</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3699</v>
+        <v>1.3873</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.022</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.0555</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.0582</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
@@ -8449,90 +8449,90 @@
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.31</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.0582</v>
-      </c>
-      <c r="F38" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
-        </is>
-      </c>
-      <c r="G38" s="117" t="n">
-        <v>0.0027</v>
+        <v>1.3037</v>
+      </c>
+      <c r="F38" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
+        </is>
+      </c>
+      <c r="G38" s="119" t="n">
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.31</v>
+        <v>1.2677</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3037</v>
+        <v>1.257</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.5%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0063</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.3289</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.257</v>
+        <v>1.3146</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
@@ -8542,28 +8542,28 @@
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2886</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.3146</v>
+        <v>1.266</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
@@ -8573,90 +8573,90 @@
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.2262</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.266</v>
+        <v>1.2003</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.784</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.2003</v>
+        <v>1.6851</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.1%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0259</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.784</v>
+        <v>1.0641</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.6851</v>
+        <v>0.9982</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
@@ -8666,59 +8666,59 @@
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.0641</v>
+        <v>2.17</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.9982</v>
+        <v>2.0242</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.1458</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>2.17</v>
+        <v>0.914</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>2.0242</v>
+        <v>0.8439</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.1458</v>
+        <v>-0.0701</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
@@ -8728,84 +8728,84 @@
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>0.914</v>
+        <v>1.2212</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.8439</v>
+        <v>1.1258</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0701</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0671</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>1.1258</v>
+        <v>0.9685</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -9.2%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.09859999999999999</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.0671</v>
+        <v>0.6602</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>0.9685</v>
+        <v>0.5942</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.2%</t>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.066</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -8842,125 +8842,125 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.0722</v>
+        <v>0.4771</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.8625</v>
+        <v>0.4175</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.0596</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.0722</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.7476</v>
+        <v>0.8625</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.6%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.314</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B53" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C53" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D53" s="88" t="n">
-        <v>1.3919</v>
+        <v>1.0616</v>
       </c>
       <c r="E53" s="91" t="n">
-        <v>0.8858</v>
+        <v>0.7476</v>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>▼ -36.4%</t>
+          <t>▼ -29.6%</t>
         </is>
       </c>
       <c r="G53" s="119" t="n">
-        <v>-0.5061</v>
+        <v>-0.314</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="B54" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C54" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D54" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.3919</v>
       </c>
       <c r="E54" s="89" t="n">
-        <v>0.1988</v>
+        <v>0.8858</v>
       </c>
       <c r="F54" s="69" t="inlineStr">
         <is>
-          <t>▼ -58.3%</t>
+          <t>▼ -36.4%</t>
         </is>
       </c>
       <c r="G54" s="119" t="n">
-        <v>-0.2783</v>
+        <v>-0.5061</v>
       </c>
     </row>
   </sheetData>
@@ -9017,16 +9017,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.7378</v>
+        <v>0.7743166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6393833333333333</v>
+        <v>0.6493166666666667</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.5145</v>
+        <v>1.5149</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9119,20 +9119,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.1988</v>
+        <v>0.4175</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.1988</v>
+        <v>0.2584</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -58.3%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9221,13 +9221,13 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.5145</v>
+        <v>1.5149</v>
       </c>
       <c r="D10" s="57" t="n">
         <v>1.1519</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>911</v>
+        <v>911.2</v>
       </c>
       <c r="F10" s="58" t="n">
         <v>692.849</v>
@@ -9293,13 +9293,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.19474375</v>
+        <v>1.2008875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.234175</v>
+        <v>1.21774375</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6521</v>
+        <v>0.8262</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9633,20 +9633,20 @@
         </is>
       </c>
       <c r="C24" s="57" t="n">
-        <v>1.0772</v>
+        <v>0.9639</v>
       </c>
       <c r="D24" s="57" t="n">
-        <v>1.389</v>
+        <v>0.9639</v>
       </c>
       <c r="E24" s="58" t="n">
-        <v>208.97</v>
+        <v>187</v>
       </c>
       <c r="F24" s="58" t="n">
-        <v>269.46</v>
+        <v>187</v>
       </c>
       <c r="G24" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="H24" s="61" t="inlineStr">
@@ -9769,20 +9769,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6521</v>
+        <v>0.8637</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6521</v>
+        <v>0.8143</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1057</v>
+        <v>1400</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1057</v>
+        <v>1320</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +47.4%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -10253,13 +10253,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.506806666666666</v>
+        <v>1.462793333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.46906</v>
+        <v>1.425046666666667</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.7476</v>
+        <v>0.5942</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="H56" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -10729,20 +10729,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>1.2544</v>
+        <v>0.5942</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>1.2544</v>
+        <v>0.5942</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>5700</v>
+        <v>2700</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>2700</v>
+      </c>
+      <c r="G60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -10.0%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1088,17 +1088,17 @@
     <xf numFmtId="0" fontId="37" fillId="21" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="44" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-04</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-05</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.222</t>
+          <t>$1.230</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+73.9%</t>
+          <t>+98.3%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.194</t>
+          <t>$1.211</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.7743166666666667</v>
+        <v>0.7556166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6493166666666667</v>
+        <v>0.6976666666666667</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.5149</v>
+        <v>1.5122</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1790,7 +1790,7 @@
         <v>1.2008875</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.21774375</v>
+        <v>1.21464375</v>
       </c>
       <c r="F13" s="32" t="n">
         <v>0.8262</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2152875</v>
+        <v>1.2173625</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1548125</v>
+        <v>1.1930875</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.462793333333333</v>
+        <v>1.498113333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.425046666666667</v>
+        <v>1.449733333333333</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.5942</v>
+        <v>0.7476</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-04</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-05</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.3678</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2584</v>
+        <v>0.5964</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -22.9%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.4955</v>
+        <v>1.4357</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.4955</v>
+        <v>1.4457</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +12.5%</t>
         </is>
       </c>
       <c r="K7" s="70" t="inlineStr">
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.5149</v>
+        <v>1.5122</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>1.1519</v>
+        <v>1.1538</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>911.2</v>
+        <v>909.6</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>692.849</v>
+        <v>694.014</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
       <c r="J8" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.6%</t>
+          <t>▲ +44.4%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2353,13 +2353,13 @@
         <v>1.2003</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>1.2417</v>
+        <v>1.1921</v>
       </c>
       <c r="G11" s="67" t="n">
         <v>725</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="F34" s="57" t="n">
         <v>0.9685</v>
       </c>
-      <c r="F34" s="57" t="n">
-        <v>0.6623</v>
-      </c>
       <c r="G34" s="58" t="n">
+        <v>595</v>
+      </c>
+      <c r="H34" s="58" t="n">
         <v>585</v>
-      </c>
-      <c r="H34" s="58" t="n">
-        <v>400</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
       <c r="J34" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.2%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -3680,23 +3680,23 @@
         </is>
       </c>
       <c r="E41" s="66" t="n">
-        <v>1.009</v>
+        <v>1.2786</v>
       </c>
       <c r="F41" s="66" t="n">
-        <v>1.0675</v>
+        <v>1.3776</v>
       </c>
       <c r="G41" s="67" t="n">
-        <v>132.18</v>
+        <v>167.5</v>
       </c>
       <c r="H41" s="67" t="n">
-        <v>139.84</v>
+        <v>180.46</v>
       </c>
       <c r="I41" s="68" t="n">
         <v>131</v>
       </c>
       <c r="J41" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +98.3%</t>
         </is>
       </c>
       <c r="K41" s="70" t="inlineStr">
@@ -4009,23 +4009,23 @@
         </is>
       </c>
       <c r="E48" s="57" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="F48" s="57" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G48" s="58" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H48" s="58" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="I48" s="59" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="71" t="inlineStr">
         <is>
-          <t>▲ +73.9%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="K48" s="61" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>0.5942</v>
+        <v>1.2544</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>0.5942</v>
+        <v>1.2544</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+      <c r="J49" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.222135185185185</v>
+        <v>1.230175925925926</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.193764814814815</v>
+        <v>1.210746296296296</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-04</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-05</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.4175</v>
+        <v>0.3678</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -22.9%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2584</v>
-      </c>
-      <c r="H6" s="69" t="inlineStr">
-        <is>
-          <t>▼ -36.6%</t>
+        <v>0.5964</v>
+      </c>
+      <c r="H6" s="71" t="inlineStr">
+        <is>
+          <t>▲ +46.3%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.4955</v>
+        <v>1.4357</v>
       </c>
       <c r="E8" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +12.5%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.4955</v>
+        <v>1.4457</v>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>▲ +30.4%</t>
+          <t>▲ +26.1%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.5149</v>
+        <v>1.5122</v>
       </c>
       <c r="E9" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.6%</t>
+          <t>▲ +44.4%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.1519</v>
+        <v>1.1538</v>
       </c>
       <c r="H9" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.4%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>911.2</v>
+        <v>909.6</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>692.849</v>
+        <v>694.014</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5084,18 +5084,18 @@
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>1.2417</v>
+        <v>1.1921</v>
       </c>
       <c r="H12" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.4%</t>
+          <t>▼ -5.3%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
         <v>725</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>0.9685</v>
+        <v>0.9851</v>
       </c>
       <c r="E35" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.2%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.6623</v>
-      </c>
-      <c r="H35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -30.6%</t>
+        <v>0.9685</v>
+      </c>
+      <c r="H35" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.5%</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
+        <v>595</v>
+      </c>
+      <c r="J35" s="67" t="n">
         <v>585</v>
-      </c>
-      <c r="J35" s="67" t="n">
-        <v>400</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6347,29 +6347,29 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="D42" s="91" t="n">
-        <v>1.009</v>
+        <v>1.2786</v>
       </c>
       <c r="E42" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +98.3%</t>
         </is>
       </c>
       <c r="F42" s="90" t="n">
         <v>0.6288</v>
       </c>
       <c r="G42" s="91" t="n">
-        <v>1.0675</v>
+        <v>1.3776</v>
       </c>
       <c r="H42" s="71" t="inlineStr">
         <is>
-          <t>▲ +69.8%</t>
+          <t>▲ +119.1%</t>
         </is>
       </c>
       <c r="I42" s="58" t="n">
-        <v>132.18</v>
+        <v>167.5</v>
       </c>
       <c r="J42" s="58" t="n">
-        <v>139.84</v>
+        <v>180.46</v>
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
@@ -6662,29 +6662,29 @@
         <v>1.15</v>
       </c>
       <c r="D49" s="89" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E49" s="71" t="inlineStr">
         <is>
-          <t>▲ +73.9%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="F49" s="90" t="n">
         <v>1.05</v>
       </c>
       <c r="G49" s="89" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="H49" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.5%</t>
+          <t>▲ +33.3%</t>
         </is>
       </c>
       <c r="I49" s="67" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J49" s="67" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="K49" s="70" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>0.5942</v>
-      </c>
-      <c r="E50" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>1.2544</v>
+      </c>
+      <c r="E50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>0.5942</v>
-      </c>
-      <c r="H50" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>1.2544</v>
+      </c>
+      <c r="H50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -7497,72 +7497,72 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.  Somalia</t>
+          <t xml:space="preserve">  4.  CAR</t>
         </is>
       </c>
       <c r="B8" s="103" t="inlineStr">
         <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="C8" s="104" t="n">
+        <v>1.7384</v>
+      </c>
+      <c r="D8" s="105" t="n">
+        <v>2.1523</v>
+      </c>
+      <c r="E8" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  Egypt</t>
+        </is>
+      </c>
+      <c r="H8" s="107" t="inlineStr">
+        <is>
+          <t>North Africa</t>
+        </is>
+      </c>
+      <c r="I8" s="108" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="J8" s="109" t="n">
+        <v>0.5964</v>
+      </c>
+      <c r="K8" s="106" t="inlineStr">
+        <is>
+          <t>▼ -22.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Comoros</t>
+        </is>
+      </c>
+      <c r="B9" s="96" t="inlineStr">
+        <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C8" s="104" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="111" t="inlineStr">
-        <is>
-          <t>▲ +73.9%</t>
-        </is>
-      </c>
-      <c r="G8" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  Egypt</t>
-        </is>
-      </c>
-      <c r="H8" s="107" t="inlineStr">
-        <is>
-          <t>North Africa</t>
-        </is>
-      </c>
-      <c r="I8" s="108" t="n">
-        <v>0.4175</v>
-      </c>
-      <c r="J8" s="109" t="n">
-        <v>0.2584</v>
-      </c>
-      <c r="K8" s="106" t="inlineStr">
-        <is>
-          <t>▼ -12.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  CAR</t>
-        </is>
-      </c>
-      <c r="B9" s="96" t="inlineStr">
-        <is>
-          <t>Central Africa</t>
-        </is>
-      </c>
       <c r="C9" s="97" t="n">
-        <v>1.7384</v>
+        <v>1.6851</v>
       </c>
       <c r="D9" s="98" t="n">
-        <v>2.1523</v>
-      </c>
-      <c r="E9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5.  South Sudan</t>
+        <v>1.5078</v>
+      </c>
+      <c r="E9" s="106" t="inlineStr">
+        <is>
+          <t>▼ -5.5%</t>
+        </is>
+      </c>
+      <c r="G9" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5.  Tanzania</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
@@ -7571,98 +7571,98 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.5942</v>
+        <v>0.7476</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.5942</v>
+        <v>0.7476</v>
       </c>
       <c r="K9" s="106" t="inlineStr">
         <is>
-          <t>▼ -10.0%</t>
+          <t>▼ -29.6%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Comoros</t>
+          <t xml:space="preserve">  6.  Senegal</t>
         </is>
       </c>
       <c r="B10" s="103" t="inlineStr">
         <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="C10" s="104" t="n">
+        <v>1.6391</v>
+      </c>
+      <c r="D10" s="105" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E10" s="114" t="inlineStr">
+        <is>
+          <t>▲ +7.5%</t>
+        </is>
+      </c>
+      <c r="G10" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6.  Niger</t>
+        </is>
+      </c>
+      <c r="H10" s="107" t="inlineStr">
+        <is>
+          <t>West Africa</t>
+        </is>
+      </c>
+      <c r="I10" s="108" t="n">
+        <v>0.8262</v>
+      </c>
+      <c r="J10" s="109" t="n">
+        <v>1.0232</v>
+      </c>
+      <c r="K10" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Somalia</t>
+        </is>
+      </c>
+      <c r="B11" s="96" t="inlineStr">
+        <is>
           <t>East Africa</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n">
-        <v>1.6851</v>
-      </c>
-      <c r="D10" s="105" t="n">
-        <v>1.5078</v>
-      </c>
-      <c r="E10" s="106" t="inlineStr">
-        <is>
-          <t>▼ -5.5%</t>
-        </is>
-      </c>
-      <c r="G10" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6.  Tanzania</t>
-        </is>
-      </c>
-      <c r="H10" s="107" t="inlineStr">
-        <is>
-          <t>East Africa</t>
-        </is>
-      </c>
-      <c r="I10" s="108" t="n">
-        <v>0.7476</v>
-      </c>
-      <c r="J10" s="109" t="n">
-        <v>0.7476</v>
-      </c>
-      <c r="K10" s="106" t="inlineStr">
-        <is>
-          <t>▼ -29.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Senegal</t>
-        </is>
-      </c>
-      <c r="B11" s="96" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
       <c r="C11" s="97" t="n">
-        <v>1.6391</v>
+        <v>1.6</v>
       </c>
       <c r="D11" s="98" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E11" s="111" t="inlineStr">
-        <is>
-          <t>▲ +7.5%</t>
-        </is>
-      </c>
-      <c r="G11" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7.  Niger</t>
+        <v>1.4</v>
+      </c>
+      <c r="E11" s="114" t="inlineStr">
+        <is>
+          <t>▲ +39.1%</t>
+        </is>
+      </c>
+      <c r="G11" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7.  Tunisia</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8262</v>
+        <v>0.8377</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>1.0232</v>
+        <v>0.7318</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7687,35 +7687,35 @@
       <c r="D12" s="105" t="n">
         <v>1.5072</v>
       </c>
-      <c r="E12" s="111" t="inlineStr">
+      <c r="E12" s="114" t="inlineStr">
         <is>
           <t>▲ +15.0%</t>
         </is>
       </c>
-      <c r="G12" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8.  Tunisia</t>
+      <c r="G12" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8.  Ghana</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8377</v>
+        <v>0.8439</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.7318</v>
-      </c>
-      <c r="K12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="K12" s="106" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="113" t="inlineStr">
+      <c r="A13" s="112" t="inlineStr">
         <is>
           <t xml:space="preserve">  9.  Sierra Leone</t>
         </is>
@@ -7731,30 +7731,30 @@
       <c r="D13" s="98" t="n">
         <v>1.7778</v>
       </c>
-      <c r="E13" s="111" t="inlineStr">
+      <c r="E13" s="114" t="inlineStr">
         <is>
           <t>▲ +9.4%</t>
         </is>
       </c>
-      <c r="G13" s="114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9.  Ghana</t>
+      <c r="G13" s="113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9.  Eswatini</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8439</v>
+        <v>0.8625</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.8625</v>
       </c>
       <c r="K13" s="106" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
     </row>
@@ -7775,30 +7775,30 @@
       <c r="D14" s="105" t="n">
         <v>1.6438</v>
       </c>
-      <c r="E14" s="111" t="inlineStr">
+      <c r="E14" s="114" t="inlineStr">
         <is>
           <t>▲ +41.0%</t>
         </is>
       </c>
-      <c r="G14" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10.  Eswatini</t>
+      <c r="G14" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  10.  Nigeria</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.8625</v>
+        <v>0.8637</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="K14" s="106" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+        <v>0.8143</v>
+      </c>
+      <c r="K14" s="114" t="inlineStr">
+        <is>
+          <t>▲ +47.4%</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,28 +7860,28 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>1.15</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>2</v>
+        <v>1.2786</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +73.9%</t>
+          <t>▲ +98.3%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.85</v>
+        <v>0.6339</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
@@ -7891,22 +7891,22 @@
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.009</v>
+        <v>1.2544</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.3643</v>
+        <v>0.5942</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -7960,15 +7960,15 @@
         <v>1.0474</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.5149</v>
+        <v>1.5122</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.6%</t>
+          <t>▲ +44.4%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.4675</v>
+        <v>0.4648</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -8005,63 +8005,63 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.15</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.2129</v>
+        <v>1.6</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.0316</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.4955</v>
+        <v>1.2129</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +17.6%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2193</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -8129,193 +8129,193 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.2762</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.9639</v>
+        <v>1.4357</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +12.5%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1595</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.1425</v>
+        <v>0.8608</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.2555</v>
+        <v>0.9639</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.1425</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.5556</v>
+        <v>1.2555</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.4222</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.5142</v>
+        <v>1.5556</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3986</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.6391</v>
+        <v>1.5142</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.5244</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.4968</v>
+        <v>1.6391</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,28 +8325,28 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.4106</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.421</v>
+        <v>1.4968</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
@@ -8356,90 +8356,90 @@
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3819</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.3699</v>
+        <v>1.421</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.022</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3479</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3873</v>
+        <v>1.3699</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3681</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.0582</v>
+        <v>1.3873</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
@@ -8449,90 +8449,90 @@
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0555</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F38" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G38" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F38" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G38" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.31</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.257</v>
+        <v>1.3037</v>
       </c>
       <c r="F39" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G39" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2677</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3146</v>
+        <v>1.257</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
@@ -8542,28 +8542,28 @@
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3289</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.266</v>
+        <v>1.3146</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
@@ -8573,90 +8573,90 @@
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2886</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.2003</v>
+        <v>1.266</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.1%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0259</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.784</v>
+        <v>1.2262</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.6851</v>
+        <v>1.2003</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.784</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>0.9982</v>
+        <v>1.6851</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
@@ -8666,59 +8666,59 @@
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>2.17</v>
+        <v>1.0641</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>2.0242</v>
+        <v>0.9982</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.1458</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>0.914</v>
+        <v>2.17</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.8439</v>
+        <v>2.0242</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -6.7%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0701</v>
+        <v>-0.1458</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
@@ -8728,22 +8728,22 @@
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.2212</v>
+        <v>0.914</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.1258</v>
+        <v>0.8439</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.0701</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -8766,46 +8766,46 @@
         <v>1.0671</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>0.9685</v>
+        <v>0.9851</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.2%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>0.6602</v>
+        <v>1.2212</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>0.5942</v>
+        <v>1.1258</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -10.0%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.066</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -8842,63 +8842,63 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.0722</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.4175</v>
+        <v>0.8625</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -19.6%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.0596</v>
+        <v>-0.2097</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>1.0722</v>
+        <v>0.4771</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.8625</v>
+        <v>0.3678</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -22.9%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.1093</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -9017,16 +9017,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.7743166666666667</v>
+        <v>0.7556166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6493166666666667</v>
+        <v>0.6976666666666667</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.5149</v>
+        <v>1.5122</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9119,20 +9119,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.3678</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2584</v>
+        <v>0.5964</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -22.9%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9187,20 +9187,20 @@
         </is>
       </c>
       <c r="C9" s="66" t="n">
-        <v>1.4955</v>
+        <v>1.4357</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.4955</v>
+        <v>1.4457</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +12.5%</t>
         </is>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -9221,20 +9221,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.5149</v>
+        <v>1.5122</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>1.1519</v>
+        <v>1.1538</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>911.2</v>
+        <v>909.6</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>692.849</v>
+        <v>694.014</v>
       </c>
       <c r="G10" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.6%</t>
+          <t>▲ +44.4%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9296,7 +9296,7 @@
         <v>1.2008875</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.21774375</v>
+        <v>1.21464375</v>
       </c>
       <c r="E14" s="131" t="n">
         <v>0.8262</v>
@@ -9364,13 +9364,13 @@
         <v>1.2003</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>1.2417</v>
+        <v>1.1921</v>
       </c>
       <c r="E16" s="58" t="n">
         <v>725</v>
       </c>
       <c r="F16" s="58" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="G16" s="69" t="inlineStr">
         <is>
@@ -9909,10 +9909,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2152875</v>
+        <v>1.2173625</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1548125</v>
+        <v>1.1930875</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10181,20 +10181,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="D42" s="57" t="n">
         <v>0.9685</v>
       </c>
-      <c r="D42" s="57" t="n">
-        <v>0.6623</v>
-      </c>
       <c r="E42" s="58" t="n">
+        <v>595</v>
+      </c>
+      <c r="F42" s="58" t="n">
         <v>585</v>
       </c>
-      <c r="F42" s="58" t="n">
-        <v>400</v>
-      </c>
       <c r="G42" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.2%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10253,13 +10253,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.462793333333333</v>
+        <v>1.498113333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.425046666666667</v>
+        <v>1.449733333333333</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.5942</v>
+        <v>0.7476</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10457,20 +10457,20 @@
         </is>
       </c>
       <c r="C52" s="57" t="n">
-        <v>1.009</v>
+        <v>1.2786</v>
       </c>
       <c r="D52" s="57" t="n">
-        <v>1.0675</v>
+        <v>1.3776</v>
       </c>
       <c r="E52" s="58" t="n">
-        <v>132.18</v>
+        <v>167.5</v>
       </c>
       <c r="F52" s="58" t="n">
-        <v>139.84</v>
+        <v>180.46</v>
       </c>
       <c r="G52" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +98.3%</t>
         </is>
       </c>
       <c r="H52" s="61" t="inlineStr">
@@ -10695,20 +10695,20 @@
         </is>
       </c>
       <c r="C59" s="66" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="D59" s="66" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="E59" s="67" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="F59" s="67" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G59" s="71" t="inlineStr">
         <is>
-          <t>▲ +73.9%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="H59" s="70" t="inlineStr">
@@ -10729,20 +10729,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>0.5942</v>
+        <v>1.2544</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>0.5942</v>
+        <v>1.2544</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>2700</v>
+        <v>5700</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>2700</v>
-      </c>
-      <c r="G60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -10.0%</t>
+        <v>5700</v>
+      </c>
+      <c r="G60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-05</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-07</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.230</t>
+          <t>$1.234</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.211</t>
+          <t>$1.212</t>
         </is>
       </c>
     </row>
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.7556166666666667</v>
+        <v>0.6853166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6976666666666667</v>
+        <v>0.6208166666666667</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.5122</v>
+        <v>1.4955</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.2008875</v>
+        <v>1.20035625</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.21464375</v>
+        <v>1.23099375</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.8262</v>
+        <v>0.6508</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2173625</v>
+        <v>1.2275</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.1930875</v>
+        <v>1.191225</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,10 +1831,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.498113333333333</v>
+        <v>1.50098</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.449733333333333</v>
+        <v>1.441566666666666</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.7476</v>
@@ -1853,16 +1853,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.163444444444445</v>
+        <v>1.219855555555555</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.163255555555556</v>
+        <v>1.208766666666667</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>2.0242</v>
+        <v>2.0331</v>
       </c>
     </row>
     <row r="18" ht="10" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-05</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-07</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.3678</v>
+        <v>0.4175</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.5964</v>
+        <v>0.2584</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -22.9%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.4357</v>
+        <v>1.4955</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.4457</v>
+        <v>1.4955</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.5%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="K7" s="70" t="inlineStr">
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.5122</v>
+        <v>0.9809</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>1.1538</v>
+        <v>0.9809</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>909.6</v>
+        <v>590</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>694.014</v>
+        <v>590</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="71" t="inlineStr">
-        <is>
-          <t>▲ +44.4%</t>
+      <c r="J8" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="E18" s="57" t="n">
-        <v>1.3576</v>
+        <v>1.4487</v>
       </c>
       <c r="F18" s="57" t="n">
         <v>1.1589</v>
       </c>
       <c r="G18" s="58" t="n">
-        <v>820</v>
+        <v>875</v>
       </c>
       <c r="H18" s="58" t="n">
         <v>700</v>
@@ -2693,9 +2693,9 @@
       <c r="I18" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J18" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J18" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="K18" s="61" t="inlineStr">
@@ -2726,23 +2726,23 @@
         </is>
       </c>
       <c r="E19" s="66" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="F19" s="66" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="G19" s="67" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="I19" s="68" t="n">
         <v>194</v>
       </c>
       <c r="J19" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="K19" s="70" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.8637</v>
+        <v>0.6508</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.8143</v>
+        <v>0.6508</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1400</v>
+        <v>1055</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1320</v>
+        <v>1055</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.4%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+      <c r="J34" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -3683,13 +3683,13 @@
         <v>1.2786</v>
       </c>
       <c r="F41" s="66" t="n">
-        <v>1.3776</v>
+        <v>1.245</v>
       </c>
       <c r="G41" s="67" t="n">
         <v>167.5</v>
       </c>
       <c r="H41" s="67" t="n">
-        <v>180.46</v>
+        <v>163.09</v>
       </c>
       <c r="I41" s="68" t="n">
         <v>131</v>
@@ -4150,23 +4150,23 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.421</v>
+        <v>1.464</v>
       </c>
       <c r="F51" s="66" t="n">
-        <v>1.4095</v>
+        <v>1.4196</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>5090</v>
+        <v>5244</v>
       </c>
       <c r="H51" s="67" t="n">
-        <v>5049</v>
+        <v>5085</v>
       </c>
       <c r="I51" s="68" t="n">
         <v>3582</v>
       </c>
       <c r="J51" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="K51" s="70" t="inlineStr">
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="E55" s="66" t="n">
-        <v>0.8625</v>
+        <v>1.2049</v>
       </c>
       <c r="F55" s="66" t="n">
-        <v>0.8625</v>
+        <v>1.3585</v>
       </c>
       <c r="G55" s="67" t="n">
-        <v>16</v>
+        <v>22.35</v>
       </c>
       <c r="H55" s="67" t="n">
-        <v>16</v>
+        <v>25.2</v>
       </c>
       <c r="I55" s="68" t="n">
         <v>18.55</v>
       </c>
-      <c r="J55" s="69" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+      <c r="J55" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.4%</t>
         </is>
       </c>
       <c r="K55" s="70" t="inlineStr">
@@ -4345,23 +4345,23 @@
         </is>
       </c>
       <c r="E56" s="57" t="n">
+        <v>1.3693</v>
+      </c>
+      <c r="F56" s="57" t="n">
         <v>1.2129</v>
       </c>
-      <c r="F56" s="57" t="n">
-        <v>1.1482</v>
-      </c>
       <c r="G56" s="58" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H56" s="58" t="n">
         <v>22.5</v>
-      </c>
-      <c r="H56" s="58" t="n">
-        <v>21.3</v>
       </c>
       <c r="I56" s="59" t="n">
         <v>18.55</v>
       </c>
       <c r="J56" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="K56" s="61" t="inlineStr">
@@ -4489,13 +4489,13 @@
         <v>1.4286</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.4286</v>
+        <v>1.2775</v>
       </c>
       <c r="G59" s="67" t="n">
         <v>26</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>26</v>
+        <v>23.25</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
@@ -4580,13 +4580,13 @@
         </is>
       </c>
       <c r="E61" s="66" t="n">
-        <v>2.0242</v>
+        <v>2.0331</v>
       </c>
       <c r="F61" s="66" t="n">
         <v>1.9231</v>
       </c>
       <c r="G61" s="67" t="n">
-        <v>52.63</v>
+        <v>52.86</v>
       </c>
       <c r="H61" s="67" t="n">
         <v>50</v>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="J61" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="K61" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.230175925925926</v>
+        <v>1.233907407407407</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.210746296296296</v>
+        <v>1.212092592592592</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-05</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-07</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.3678</v>
+        <v>0.4175</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -22.9%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.5964</v>
-      </c>
-      <c r="H6" s="71" t="inlineStr">
-        <is>
-          <t>▲ +46.3%</t>
+        <v>0.2584</v>
+      </c>
+      <c r="H6" s="69" t="inlineStr">
+        <is>
+          <t>▼ -36.6%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.4357</v>
+        <v>1.4955</v>
       </c>
       <c r="E8" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.5%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.4457</v>
+        <v>1.4955</v>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>▲ +26.1%</t>
+          <t>▲ +30.4%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.5122</v>
-      </c>
-      <c r="E9" s="71" t="inlineStr">
-        <is>
-          <t>▲ +44.4%</t>
+        <v>0.9809</v>
+      </c>
+      <c r="E9" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.1538</v>
-      </c>
-      <c r="H9" s="71" t="inlineStr">
-        <is>
-          <t>▲ +17.6%</t>
+        <v>0.9809</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>909.6</v>
+        <v>590</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>694.014</v>
+        <v>590</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5388,11 +5388,11 @@
         <v>1.3587</v>
       </c>
       <c r="D19" s="89" t="n">
-        <v>1.3576</v>
-      </c>
-      <c r="E19" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.4487</v>
+      </c>
+      <c r="E19" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="F19" s="90" t="n">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="I19" s="67" t="n">
-        <v>820</v>
+        <v>875</v>
       </c>
       <c r="J19" s="67" t="n">
         <v>700</v>
@@ -5433,29 +5433,29 @@
         <v>0.8608</v>
       </c>
       <c r="D20" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="E20" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="F20" s="90" t="n">
         <v>0.9124</v>
       </c>
       <c r="G20" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="H20" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.6%</t>
+          <t>▲ +52.2%</t>
         </is>
       </c>
       <c r="I20" s="58" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="J20" s="58" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="K20" s="61" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.8637</v>
+        <v>0.6508</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.4%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.8143</v>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>▲ +10.0%</t>
+        <v>0.6508</v>
+      </c>
+      <c r="H24" s="69" t="inlineStr">
+        <is>
+          <t>▼ -12.1%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1400</v>
+        <v>1055</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1320</v>
+        <v>1055</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="E35" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>1.0662</v>
+      </c>
+      <c r="E35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9685</v>
-      </c>
-      <c r="H35" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.5%</t>
+        <v>0.9536</v>
+      </c>
+      <c r="H35" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6358,18 +6358,18 @@
         <v>0.6288</v>
       </c>
       <c r="G42" s="91" t="n">
-        <v>1.3776</v>
+        <v>1.245</v>
       </c>
       <c r="H42" s="71" t="inlineStr">
         <is>
-          <t>▲ +119.1%</t>
+          <t>▲ +98.0%</t>
         </is>
       </c>
       <c r="I42" s="58" t="n">
         <v>167.5</v>
       </c>
       <c r="J42" s="58" t="n">
-        <v>180.46</v>
+        <v>163.09</v>
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
@@ -6797,29 +6797,29 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.421</v>
+        <v>1.464</v>
       </c>
       <c r="E52" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
         <v>1.2741</v>
       </c>
       <c r="G52" s="91" t="n">
-        <v>1.4095</v>
+        <v>1.4196</v>
       </c>
       <c r="H52" s="71" t="inlineStr">
         <is>
-          <t>▲ +10.6%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>5090</v>
+        <v>5244</v>
       </c>
       <c r="J52" s="58" t="n">
-        <v>5049</v>
+        <v>5085</v>
       </c>
       <c r="K52" s="61" t="inlineStr">
         <is>
@@ -6939,29 +6939,29 @@
         <v>1.0722</v>
       </c>
       <c r="D56" s="91" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="E56" s="69" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+        <v>1.2049</v>
+      </c>
+      <c r="E56" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.4%</t>
         </is>
       </c>
       <c r="F56" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G56" s="91" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="H56" s="69" t="inlineStr">
-        <is>
-          <t>▼ -24.8%</t>
+        <v>1.3585</v>
+      </c>
+      <c r="H56" s="71" t="inlineStr">
+        <is>
+          <t>▲ +18.5%</t>
         </is>
       </c>
       <c r="I56" s="58" t="n">
-        <v>16</v>
+        <v>22.35</v>
       </c>
       <c r="J56" s="58" t="n">
-        <v>16</v>
+        <v>25.2</v>
       </c>
       <c r="K56" s="61" t="inlineStr">
         <is>
@@ -6984,29 +6984,29 @@
         <v>1.0316</v>
       </c>
       <c r="D57" s="89" t="n">
-        <v>1.2129</v>
+        <v>1.3693</v>
       </c>
       <c r="E57" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="F57" s="90" t="n">
         <v>1.1149</v>
       </c>
       <c r="G57" s="89" t="n">
-        <v>1.1482</v>
+        <v>1.2129</v>
       </c>
       <c r="H57" s="71" t="inlineStr">
         <is>
-          <t>▲ +3.0%</t>
+          <t>▲ +8.8%</t>
         </is>
       </c>
       <c r="I57" s="67" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="J57" s="67" t="n">
         <v>22.5</v>
-      </c>
-      <c r="J57" s="67" t="n">
-        <v>21.3</v>
       </c>
       <c r="K57" s="70" t="inlineStr">
         <is>
@@ -7130,18 +7130,18 @@
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.4286</v>
-      </c>
-      <c r="H60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +10.9%</t>
+        <v>1.2775</v>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
         <v>26</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>26</v>
+        <v>23.25</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7209,11 +7209,11 @@
         <v>2.17</v>
       </c>
       <c r="D62" s="91" t="n">
-        <v>2.0242</v>
+        <v>2.0331</v>
       </c>
       <c r="E62" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="F62" s="90" t="n">
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="I62" s="58" t="n">
-        <v>52.63</v>
+        <v>52.86</v>
       </c>
       <c r="J62" s="58" t="n">
         <v>50</v>
@@ -7418,14 +7418,14 @@
         </is>
       </c>
       <c r="C6" s="104" t="n">
-        <v>2.0242</v>
+        <v>2.0331</v>
       </c>
       <c r="D6" s="105" t="n">
         <v>1.9231</v>
       </c>
       <c r="E6" s="106" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="G6" s="95" t="inlineStr">
@@ -7527,14 +7527,14 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.3678</v>
+        <v>0.4175</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.5964</v>
+        <v>0.2584</v>
       </c>
       <c r="K8" s="106" t="inlineStr">
         <is>
-          <t>▼ -22.9%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
     </row>
@@ -7562,23 +7562,23 @@
       </c>
       <c r="G9" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5.  Tanzania</t>
+          <t xml:space="preserve">  5.  Nigeria</t>
         </is>
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.7476</v>
+        <v>0.6508</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.7476</v>
-      </c>
-      <c r="K9" s="106" t="inlineStr">
-        <is>
-          <t>▼ -29.6%</t>
+        <v>0.6508</v>
+      </c>
+      <c r="K9" s="114" t="inlineStr">
+        <is>
+          <t>▲ +11.0%</t>
         </is>
       </c>
     </row>
@@ -7606,23 +7606,23 @@
       </c>
       <c r="G10" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Niger</t>
+          <t xml:space="preserve">  6.  Tanzania</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.8262</v>
+        <v>0.7476</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K10" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.7476</v>
+      </c>
+      <c r="K10" s="106" t="inlineStr">
+        <is>
+          <t>▼ -29.6%</t>
         </is>
       </c>
     </row>
@@ -7650,19 +7650,19 @@
       </c>
       <c r="G11" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Tunisia</t>
+          <t xml:space="preserve">  7.  Niger</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8377</v>
+        <v>0.8262</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.7318</v>
+        <v>1.0232</v>
       </c>
       <c r="K11" s="99" t="inlineStr">
         <is>
@@ -7694,23 +7694,23 @@
       </c>
       <c r="G12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Ghana</t>
+          <t xml:space="preserve">  8.  Tunisia</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8439</v>
+        <v>0.8377</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.9108000000000001</v>
-      </c>
-      <c r="K12" s="106" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7738,23 +7738,23 @@
       </c>
       <c r="G13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Eswatini</t>
+          <t xml:space="preserve">  9.  Ghana</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8625</v>
+        <v>0.8439</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.8625</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="K13" s="106" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="G14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Nigeria</t>
+          <t xml:space="preserve">  10.  Burkina Faso</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
@@ -7791,14 +7791,14 @@
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.8637</v>
+        <v>0.8858</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.8143</v>
-      </c>
-      <c r="K14" s="114" t="inlineStr">
-        <is>
-          <t>▲ +47.4%</t>
+        <v>1.6374</v>
+      </c>
+      <c r="K14" s="106" t="inlineStr">
+        <is>
+          <t>▼ -36.4%</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
@@ -7922,146 +7922,146 @@
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0882</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>0.8637</v>
+        <v>1.5342</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.4%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.2776</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0474</v>
+        <v>1.15</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.5122</v>
+        <v>1.6</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +44.4%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.4648</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0316</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.5342</v>
+        <v>1.3693</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +41.0%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.446</v>
+        <v>0.3377</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.15</v>
+        <v>0.8608</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.6</v>
+        <v>1.0772</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.45</v>
+        <v>0.2164</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.2762</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.2129</v>
+        <v>1.4955</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1813</v>
+        <v>0.2193</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -8129,38 +8129,38 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.0722</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.4357</v>
+        <v>1.2049</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.5%</t>
+          <t>▲ +12.4%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1595</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,22 +8170,22 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>0.8608</v>
+        <v>0.5861</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>0.9639</v>
+        <v>0.6508</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.06469999999999999</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -8315,38 +8315,38 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3587</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4968</v>
+        <v>1.4487</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
@@ -8356,28 +8356,28 @@
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.4106</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.421</v>
+        <v>1.4968</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
@@ -8387,90 +8387,90 @@
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3819</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3699</v>
+        <v>1.464</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.022</v>
+        <v>0.08210000000000001</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3479</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.3699</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3681</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.0582</v>
+        <v>1.3873</v>
       </c>
       <c r="F38" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G38" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
@@ -8480,90 +8480,90 @@
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.31</v>
+        <v>1.0555</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F39" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G39" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F39" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G39" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.31</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.257</v>
+        <v>1.3037</v>
       </c>
       <c r="F40" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G40" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.2677</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.3146</v>
+        <v>1.257</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
@@ -8573,28 +8573,28 @@
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3289</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.266</v>
+        <v>1.3146</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
@@ -8604,90 +8604,90 @@
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2886</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.2003</v>
+        <v>1.266</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.1%</t>
+          <t>▼ -1.8%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0259</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.784</v>
+        <v>1.2262</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.6851</v>
+        <v>1.2003</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.784</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.9982</v>
+        <v>1.6851</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
@@ -8697,90 +8697,90 @@
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>2.17</v>
+        <v>1.0641</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>2.0242</v>
+        <v>0.9982</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.1458</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>0.914</v>
+        <v>2.17</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.8439</v>
+        <v>2.0331</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0701</v>
+        <v>-0.1369</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.0474</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>0.9851</v>
+        <v>0.9809</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
@@ -8790,84 +8790,84 @@
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>1.2212</v>
+        <v>0.914</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>1.1258</v>
+        <v>0.8439</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.0701</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2212</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.0606</v>
+        <v>1.1258</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.1939</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>0.8625</v>
+        <v>1.0606</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -19.6%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.2097</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -8890,15 +8890,15 @@
         <v>0.4771</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.3678</v>
+        <v>0.4175</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -22.9%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.1093</v>
+        <v>-0.0596</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -9017,16 +9017,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.7556166666666667</v>
+        <v>0.6853166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6976666666666667</v>
+        <v>0.6208166666666667</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.5122</v>
+        <v>1.4955</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9119,20 +9119,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.3678</v>
+        <v>0.4175</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.5964</v>
+        <v>0.2584</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -22.9%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9187,20 +9187,20 @@
         </is>
       </c>
       <c r="C9" s="66" t="n">
-        <v>1.4357</v>
+        <v>1.4955</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.4457</v>
+        <v>1.4955</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.5%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -9221,20 +9221,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.5122</v>
+        <v>0.9809</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>1.1538</v>
+        <v>0.9809</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>909.6</v>
+        <v>590</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>694.014</v>
-      </c>
-      <c r="G10" s="71" t="inlineStr">
-        <is>
-          <t>▲ +44.4%</t>
+        <v>590</v>
+      </c>
+      <c r="G10" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9293,13 +9293,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.2008875</v>
+        <v>1.20035625</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.21464375</v>
+        <v>1.23099375</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.8262</v>
+        <v>0.6508</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9599,20 +9599,20 @@
         </is>
       </c>
       <c r="C23" s="66" t="n">
-        <v>1.3576</v>
+        <v>1.4487</v>
       </c>
       <c r="D23" s="66" t="n">
         <v>1.1589</v>
       </c>
       <c r="E23" s="67" t="n">
-        <v>820</v>
+        <v>875</v>
       </c>
       <c r="F23" s="67" t="n">
         <v>700</v>
       </c>
-      <c r="G23" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G23" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="H23" s="70" t="inlineStr">
@@ -9633,20 +9633,20 @@
         </is>
       </c>
       <c r="C24" s="57" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="D24" s="57" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="E24" s="58" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="F24" s="58" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="G24" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="H24" s="61" t="inlineStr">
@@ -9769,20 +9769,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.8637</v>
+        <v>0.6508</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.8143</v>
+        <v>0.6508</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1400</v>
+        <v>1055</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1320</v>
+        <v>1055</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +47.4%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9909,10 +9909,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2173625</v>
+        <v>1.2275</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.1930875</v>
+        <v>1.191225</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10181,20 +10181,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>0.9851</v>
+        <v>1.0662</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9685</v>
+        <v>0.9536</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>595</v>
+        <v>644</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>585</v>
-      </c>
-      <c r="G42" s="69" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>576</v>
+      </c>
+      <c r="G42" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10253,10 +10253,10 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.498113333333333</v>
+        <v>1.50098</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.449733333333333</v>
+        <v>1.441566666666666</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>0.7476</v>
@@ -10460,13 +10460,13 @@
         <v>1.2786</v>
       </c>
       <c r="D52" s="57" t="n">
-        <v>1.3776</v>
+        <v>1.245</v>
       </c>
       <c r="E52" s="58" t="n">
         <v>167.5</v>
       </c>
       <c r="F52" s="58" t="n">
-        <v>180.46</v>
+        <v>163.09</v>
       </c>
       <c r="G52" s="71" t="inlineStr">
         <is>
@@ -10797,20 +10797,20 @@
         </is>
       </c>
       <c r="C62" s="57" t="n">
-        <v>1.421</v>
+        <v>1.464</v>
       </c>
       <c r="D62" s="57" t="n">
-        <v>1.4095</v>
+        <v>1.4196</v>
       </c>
       <c r="E62" s="58" t="n">
-        <v>5090</v>
+        <v>5244</v>
       </c>
       <c r="F62" s="58" t="n">
-        <v>5049</v>
+        <v>5085</v>
       </c>
       <c r="G62" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="H62" s="61" t="inlineStr">
@@ -10835,16 +10835,16 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.163444444444445</v>
+        <v>1.219855555555555</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.163255555555556</v>
+        <v>1.208766666666667</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
       </c>
       <c r="F65" s="153" t="n">
-        <v>2.0242</v>
+        <v>2.0331</v>
       </c>
       <c r="G65" s="150" t="n"/>
       <c r="H65" s="150" t="n"/>
@@ -10971,20 +10971,20 @@
         </is>
       </c>
       <c r="C69" s="57" t="n">
-        <v>0.8625</v>
+        <v>1.2049</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>0.8625</v>
+        <v>1.3585</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>16</v>
+        <v>22.35</v>
       </c>
       <c r="F69" s="58" t="n">
-        <v>16</v>
-      </c>
-      <c r="G69" s="69" t="inlineStr">
-        <is>
-          <t>▼ -19.6%</t>
+        <v>25.2</v>
+      </c>
+      <c r="G69" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.4%</t>
         </is>
       </c>
       <c r="H69" s="61" t="inlineStr">
@@ -11005,20 +11005,20 @@
         </is>
       </c>
       <c r="C70" s="66" t="n">
+        <v>1.3693</v>
+      </c>
+      <c r="D70" s="66" t="n">
         <v>1.2129</v>
       </c>
-      <c r="D70" s="66" t="n">
-        <v>1.1482</v>
-      </c>
       <c r="E70" s="67" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F70" s="67" t="n">
         <v>22.5</v>
       </c>
-      <c r="F70" s="67" t="n">
-        <v>21.3</v>
-      </c>
       <c r="G70" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.6%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="H70" s="70" t="inlineStr">
@@ -11110,13 +11110,13 @@
         <v>1.4286</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.4286</v>
+        <v>1.2775</v>
       </c>
       <c r="E73" s="58" t="n">
         <v>26</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>26</v>
+        <v>23.25</v>
       </c>
       <c r="G73" s="71" t="inlineStr">
         <is>
@@ -11175,20 +11175,20 @@
         </is>
       </c>
       <c r="C75" s="57" t="n">
-        <v>2.0242</v>
+        <v>2.0331</v>
       </c>
       <c r="D75" s="57" t="n">
         <v>1.9231</v>
       </c>
       <c r="E75" s="58" t="n">
-        <v>52.63</v>
+        <v>52.86</v>
       </c>
       <c r="F75" s="58" t="n">
         <v>50</v>
       </c>
       <c r="G75" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.7%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="H75" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-07</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-08</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.234</t>
+          <t>$1.246</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.212</t>
+          <t>$1.229</t>
         </is>
       </c>
     </row>
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6853166666666667</v>
+        <v>0.7763</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6208166666666667</v>
+        <v>0.6504666666666666</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.4955</v>
+        <v>1.5268</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.20035625</v>
+        <v>1.2176375</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.23099375</v>
+        <v>1.23948125</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1809,10 +1809,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1.2275</v>
+        <v>1.2173625</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>1.191225</v>
+        <v>1.1930875</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>0.9106</v>
@@ -1831,10 +1831,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.50098</v>
+        <v>1.4838</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.441566666666666</v>
+        <v>1.42868</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.7476</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.219855555555555</v>
+        <v>1.241244444444445</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.208766666666667</v>
+        <v>1.292444444444445</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="45" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-07</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-08</t>
         </is>
       </c>
     </row>
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.5268</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.1588</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>590</v>
+        <v>918.4</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>590</v>
+        <v>697.034</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+      <c r="J8" s="71" t="inlineStr">
+        <is>
+          <t>▲ +45.8%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2353,13 +2353,13 @@
         <v>1.2003</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>1.1921</v>
+        <v>1.2417</v>
       </c>
       <c r="G11" s="67" t="n">
         <v>725</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
@@ -2444,23 +2444,23 @@
         </is>
       </c>
       <c r="E13" s="66" t="n">
-        <v>1.266</v>
+        <v>1.3674</v>
       </c>
       <c r="F13" s="66" t="n">
-        <v>1.0635</v>
+        <v>1.1484</v>
       </c>
       <c r="G13" s="67" t="n">
-        <v>139.89</v>
+        <v>151.1</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>117.52</v>
+        <v>126.9</v>
       </c>
       <c r="I13" s="68" t="n">
         <v>110.5</v>
       </c>
-      <c r="J13" s="69" t="inlineStr">
-        <is>
-          <t>▼ -1.8%</t>
+      <c r="J13" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="K13" s="70" t="inlineStr">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="E17" s="66" t="n">
-        <v>1.3146</v>
+        <v>1.4884</v>
       </c>
       <c r="F17" s="66" t="n">
         <v>1.1589</v>
       </c>
       <c r="G17" s="67" t="n">
-        <v>794</v>
+        <v>899</v>
       </c>
       <c r="H17" s="67" t="n">
         <v>700</v>
@@ -2646,9 +2646,9 @@
       <c r="I17" s="68" t="n">
         <v>604</v>
       </c>
-      <c r="J17" s="69" t="inlineStr">
-        <is>
-          <t>▼ -1.1%</t>
+      <c r="J17" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="K17" s="70" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3391,23 +3391,23 @@
         </is>
       </c>
       <c r="E34" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="F34" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="G34" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="H34" s="58" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="I34" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J34" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J34" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="K34" s="61" t="inlineStr">
@@ -3730,13 +3730,13 @@
         <v>1.5142</v>
       </c>
       <c r="F42" s="57" t="n">
-        <v>1.5142</v>
+        <v>1.5067</v>
       </c>
       <c r="G42" s="58" t="n">
         <v>197.6</v>
       </c>
       <c r="H42" s="58" t="n">
-        <v>197.6</v>
+        <v>196.63</v>
       </c>
       <c r="I42" s="59" t="n">
         <v>130.5</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -3915,23 +3915,23 @@
         </is>
       </c>
       <c r="E46" s="57" t="n">
-        <v>1.5742</v>
+        <v>1.3595</v>
       </c>
       <c r="F46" s="57" t="n">
-        <v>1.5072</v>
+        <v>1.3315</v>
       </c>
       <c r="G46" s="58" t="n">
-        <v>2303</v>
+        <v>1989</v>
       </c>
       <c r="H46" s="58" t="n">
-        <v>2205</v>
+        <v>1948</v>
       </c>
       <c r="I46" s="59" t="n">
         <v>1463</v>
       </c>
-      <c r="J46" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+      <c r="J46" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="K46" s="61" t="inlineStr">
@@ -4150,23 +4150,23 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.464</v>
+        <v>1.421</v>
       </c>
       <c r="F51" s="66" t="n">
-        <v>1.4196</v>
+        <v>1.4095</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>5244</v>
+        <v>5090</v>
       </c>
       <c r="H51" s="67" t="n">
-        <v>5085</v>
+        <v>5049</v>
       </c>
       <c r="I51" s="68" t="n">
         <v>3582</v>
       </c>
       <c r="J51" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.9%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="K51" s="70" t="inlineStr">
@@ -4392,23 +4392,23 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>1.3037</v>
+        <v>1.4616</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>1.2462</v>
+        <v>1.8136</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>83.56999999999999</v>
+        <v>93.69</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>79.88</v>
+        <v>116.25</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="J57" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
+      <c r="J57" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.6%</t>
         </is>
       </c>
       <c r="K57" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.4286</v>
+        <v>1.4632</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.2775</v>
+        <v>1.4632</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>26</v>
+        <v>26.63</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>23.25</v>
+        <v>26.63</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
       <c r="J59" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.8%</t>
+          <t>▲ +18.6%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.233907407407407</v>
+        <v>1.246427777777778</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.212092592592592</v>
+        <v>1.228544444444444</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-07</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-08</t>
         </is>
       </c>
     </row>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="E9" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+        <v>1.5268</v>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>▲ +45.8%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="H9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.1588</v>
+      </c>
+      <c r="H9" s="71" t="inlineStr">
+        <is>
+          <t>▲ +18.1%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>590</v>
+        <v>918.4</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>590</v>
+        <v>697.034</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5084,18 +5084,18 @@
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>1.1921</v>
+        <v>1.2417</v>
       </c>
       <c r="H12" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.3%</t>
+          <t>▼ -1.4%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
         <v>725</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -5163,29 +5163,29 @@
         <v>1.2886</v>
       </c>
       <c r="D14" s="91" t="n">
-        <v>1.266</v>
-      </c>
-      <c r="E14" s="69" t="inlineStr">
-        <is>
-          <t>▼ -1.8%</t>
+        <v>1.3674</v>
+      </c>
+      <c r="E14" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="F14" s="90" t="n">
         <v>1.0826</v>
       </c>
       <c r="G14" s="91" t="n">
-        <v>1.0635</v>
-      </c>
-      <c r="H14" s="69" t="inlineStr">
-        <is>
-          <t>▼ -1.8%</t>
+        <v>1.1484</v>
+      </c>
+      <c r="H14" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="I14" s="58" t="n">
-        <v>139.89</v>
+        <v>151.1</v>
       </c>
       <c r="J14" s="58" t="n">
-        <v>117.52</v>
+        <v>126.9</v>
       </c>
       <c r="K14" s="61" t="inlineStr">
         <is>
@@ -5343,11 +5343,11 @@
         <v>1.3289</v>
       </c>
       <c r="D18" s="91" t="n">
-        <v>1.3146</v>
-      </c>
-      <c r="E18" s="69" t="inlineStr">
-        <is>
-          <t>▼ -1.1%</t>
+        <v>1.4884</v>
+      </c>
+      <c r="E18" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="F18" s="90" t="n">
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I18" s="58" t="n">
-        <v>794</v>
+        <v>899</v>
       </c>
       <c r="J18" s="58" t="n">
         <v>700</v>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="H24" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.1%</t>
+          <t>▼ -11.9%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6070,29 +6070,29 @@
         <v>1.0671</v>
       </c>
       <c r="D35" s="89" t="n">
-        <v>1.0662</v>
-      </c>
-      <c r="E35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9851</v>
+      </c>
+      <c r="E35" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="F35" s="90" t="n">
         <v>0.9544</v>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.9536</v>
-      </c>
-      <c r="H35" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9685</v>
+      </c>
+      <c r="H35" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.5%</t>
         </is>
       </c>
       <c r="I35" s="67" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="J35" s="67" t="n">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="K35" s="70" t="inlineStr">
         <is>
@@ -6403,22 +6403,22 @@
         <v>1.3063</v>
       </c>
       <c r="G43" s="89" t="n">
-        <v>1.5142</v>
+        <v>1.5067</v>
       </c>
       <c r="H43" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.9%</t>
+          <t>▲ +15.3%</t>
         </is>
       </c>
       <c r="I43" s="67" t="n">
         <v>197.6</v>
       </c>
       <c r="J43" s="67" t="n">
-        <v>197.6</v>
+        <v>196.63</v>
       </c>
       <c r="K43" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -6572,29 +6572,29 @@
         <v>1.3691</v>
       </c>
       <c r="D47" s="89" t="n">
-        <v>1.5742</v>
-      </c>
-      <c r="E47" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+        <v>1.3595</v>
+      </c>
+      <c r="E47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="F47" s="90" t="n">
         <v>1.3418</v>
       </c>
       <c r="G47" s="89" t="n">
-        <v>1.5072</v>
-      </c>
-      <c r="H47" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.3%</t>
+        <v>1.3315</v>
+      </c>
+      <c r="H47" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="I47" s="67" t="n">
-        <v>2303</v>
+        <v>1989</v>
       </c>
       <c r="J47" s="67" t="n">
-        <v>2205</v>
+        <v>1948</v>
       </c>
       <c r="K47" s="70" t="inlineStr">
         <is>
@@ -6797,29 +6797,29 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.464</v>
+        <v>1.421</v>
       </c>
       <c r="E52" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.9%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
         <v>1.2741</v>
       </c>
       <c r="G52" s="91" t="n">
-        <v>1.4196</v>
+        <v>1.4095</v>
       </c>
       <c r="H52" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +10.6%</t>
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>5244</v>
+        <v>5090</v>
       </c>
       <c r="J52" s="58" t="n">
-        <v>5085</v>
+        <v>5049</v>
       </c>
       <c r="K52" s="61" t="inlineStr">
         <is>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="E58" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
+        <v>1.4616</v>
+      </c>
+      <c r="E58" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.6%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>1.2462</v>
-      </c>
-      <c r="H58" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.3%</t>
+        <v>1.8136</v>
+      </c>
+      <c r="H58" s="71" t="inlineStr">
+        <is>
+          <t>▲ +45.1%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>83.56999999999999</v>
+        <v>93.69</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>79.88</v>
+        <v>116.25</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.4286</v>
+        <v>1.4632</v>
       </c>
       <c r="E60" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.8%</t>
+          <t>▲ +18.6%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.2775</v>
-      </c>
-      <c r="H60" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.8%</t>
+        <v>1.4632</v>
+      </c>
+      <c r="H60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +13.6%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>26</v>
+        <v>26.63</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>23.25</v>
+        <v>26.63</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7571,14 +7571,14 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="K9" s="114" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
     </row>
@@ -7673,23 +7673,23 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Rwanda</t>
+          <t xml:space="preserve">  8.  Sierra Leone</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.5742</v>
+        <v>1.5556</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.5072</v>
+        <v>1.7778</v>
       </c>
       <c r="E12" s="114" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G12" s="111" t="inlineStr">
@@ -7717,7 +7717,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Sierra Leone</t>
+          <t xml:space="preserve">  9.  Gambia</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
@@ -7726,14 +7726,14 @@
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5556</v>
+        <v>1.5342</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.7778</v>
+        <v>1.6438</v>
       </c>
       <c r="E13" s="114" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="G13" s="113" t="inlineStr">
@@ -7761,23 +7761,23 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Gambia</t>
+          <t xml:space="preserve">  10.  Sudan</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.5342</v>
+        <v>1.5268</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.6438</v>
+        <v>1.1588</v>
       </c>
       <c r="E14" s="114" t="inlineStr">
         <is>
-          <t>▲ +41.0%</t>
+          <t>▲ +45.8%</t>
         </is>
       </c>
       <c r="G14" s="111" t="inlineStr">
@@ -7912,156 +7912,156 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0474</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.5342</v>
+        <v>1.5268</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +41.0%</t>
+          <t>▲ +45.8%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.446</v>
+        <v>0.4794</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.15</v>
+        <v>1.0882</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.6</v>
+        <v>1.5342</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.45</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.15</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.3693</v>
+        <v>1.6</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.3377</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.0316</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.0772</v>
+        <v>1.3693</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.2164</v>
+        <v>0.3377</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.2762</v>
+        <v>0.8608</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.4955</v>
+        <v>1.0772</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2193</v>
+        <v>0.2164</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -8084,46 +8084,46 @@
         <v>1.2332</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.4286</v>
+        <v>1.4632</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.8%</t>
+          <t>▲ +18.6%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1954</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.2762</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.5742</v>
+        <v>1.4955</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.0%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.2051</v>
+        <v>0.2193</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -8160,7 +8160,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,28 +8170,28 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.3289</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>0.6508</v>
+        <v>1.4884</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.1595</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
@@ -8201,28 +8201,28 @@
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.31</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.2555</v>
+        <v>1.4616</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +11.6%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1516</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
@@ -8232,59 +8232,59 @@
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.4222</v>
+        <v>0.5861</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.5556</v>
+        <v>0.6521</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.1425</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.5142</v>
+        <v>1.2555</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,431 +8294,431 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.4222</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.5556</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.3587</v>
+        <v>1.3986</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4487</v>
+        <v>1.5142</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.6%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.09</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.5244</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.4968</v>
+        <v>1.6391</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.3587</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.464</v>
+        <v>1.4487</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.9%</t>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.2886</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3699</v>
+        <v>1.3674</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.022</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.4106</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.3873</v>
+        <v>1.4968</v>
       </c>
       <c r="F38" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G38" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3819</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.0582</v>
+        <v>1.421</v>
       </c>
       <c r="F39" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G39" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.31</v>
+        <v>1.3479</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F40" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G40" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.3699</v>
+      </c>
+      <c r="F40" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.6%</t>
+        </is>
+      </c>
+      <c r="G40" s="117" t="n">
+        <v>0.022</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.3681</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.257</v>
-      </c>
-      <c r="F41" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.8%</t>
-        </is>
-      </c>
-      <c r="G41" s="119" t="n">
-        <v>-0.0107</v>
+        <v>1.3873</v>
+      </c>
+      <c r="F41" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.4%</t>
+        </is>
+      </c>
+      <c r="G41" s="117" t="n">
+        <v>0.0192</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.0555</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.3146</v>
-      </c>
-      <c r="F42" s="69" t="inlineStr">
-        <is>
-          <t>▼ -1.1%</t>
-        </is>
-      </c>
-      <c r="G42" s="119" t="n">
-        <v>-0.0143</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F42" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G42" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3691</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.266</v>
+        <v>1.3595</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.8%</t>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0226</v>
+        <v>-0.009599999999999999</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2677</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.2003</v>
+        <v>1.257</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.1%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0259</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.784</v>
+        <v>1.2262</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>1.6851</v>
+        <v>1.2003</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.784</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>0.9982</v>
+        <v>1.6851</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
@@ -8728,45 +8728,45 @@
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>2.17</v>
+        <v>1.0641</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>2.0331</v>
+        <v>0.9982</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.3%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.1369</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>1.0474</v>
+        <v>2.17</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>0.9809</v>
+        <v>2.0331</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.0665</v>
+        <v>-0.1369</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -8811,155 +8811,186 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.0671</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>1.1258</v>
+        <v>0.9851</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.2212</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>1.0606</v>
+        <v>1.1258</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.1939</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.4175</v>
+        <v>1.0606</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.0596</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B53" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C53" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D53" s="88" t="n">
-        <v>1.0616</v>
+        <v>0.4771</v>
       </c>
       <c r="E53" s="91" t="n">
-        <v>0.7476</v>
+        <v>0.4175</v>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.6%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="G53" s="119" t="n">
-        <v>-0.314</v>
+        <v>-0.0596</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="62" t="inlineStr">
         <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="inlineStr">
+        <is>
+          <t>East Africa</t>
+        </is>
+      </c>
+      <c r="C54" s="118" t="inlineStr">
+        <is>
+          <t>TZS</t>
+        </is>
+      </c>
+      <c r="D54" s="88" t="n">
+        <v>1.0616</v>
+      </c>
+      <c r="E54" s="89" t="n">
+        <v>0.7476</v>
+      </c>
+      <c r="F54" s="69" t="inlineStr">
+        <is>
+          <t>▼ -29.6%</t>
+        </is>
+      </c>
+      <c r="G54" s="119" t="n">
+        <v>-0.314</v>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="53" t="inlineStr">
+        <is>
           <t>Burkina Faso</t>
         </is>
       </c>
-      <c r="B54" s="63" t="inlineStr">
+      <c r="B55" s="54" t="inlineStr">
         <is>
           <t>West Africa</t>
         </is>
       </c>
-      <c r="C54" s="118" t="inlineStr">
+      <c r="C55" s="116" t="inlineStr">
         <is>
           <t>XOF</t>
         </is>
       </c>
-      <c r="D54" s="88" t="n">
+      <c r="D55" s="88" t="n">
         <v>1.3919</v>
       </c>
-      <c r="E54" s="89" t="n">
+      <c r="E55" s="91" t="n">
         <v>0.8858</v>
       </c>
-      <c r="F54" s="69" t="inlineStr">
+      <c r="F55" s="69" t="inlineStr">
         <is>
           <t>▼ -36.4%</t>
         </is>
       </c>
-      <c r="G54" s="119" t="n">
+      <c r="G55" s="119" t="n">
         <v>-0.5061</v>
       </c>
     </row>
@@ -9017,16 +9048,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6853166666666667</v>
+        <v>0.7763</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6208166666666667</v>
+        <v>0.6504666666666666</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.4955</v>
+        <v>1.5268</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9221,20 +9252,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.5268</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.1588</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>590</v>
+        <v>918.4</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>590</v>
-      </c>
-      <c r="G10" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+        <v>697.034</v>
+      </c>
+      <c r="G10" s="71" t="inlineStr">
+        <is>
+          <t>▲ +45.8%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9293,13 +9324,13 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.20035625</v>
+        <v>1.2176375</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.23099375</v>
+        <v>1.23948125</v>
       </c>
       <c r="E14" s="131" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="F14" s="132" t="n">
         <v>1.6391</v>
@@ -9364,13 +9395,13 @@
         <v>1.2003</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>1.1921</v>
+        <v>1.2417</v>
       </c>
       <c r="E16" s="58" t="n">
         <v>725</v>
       </c>
       <c r="F16" s="58" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="G16" s="69" t="inlineStr">
         <is>
@@ -9429,20 +9460,20 @@
         </is>
       </c>
       <c r="C18" s="57" t="n">
-        <v>1.266</v>
+        <v>1.3674</v>
       </c>
       <c r="D18" s="57" t="n">
-        <v>1.0635</v>
+        <v>1.1484</v>
       </c>
       <c r="E18" s="58" t="n">
-        <v>139.89</v>
+        <v>151.1</v>
       </c>
       <c r="F18" s="58" t="n">
-        <v>117.52</v>
-      </c>
-      <c r="G18" s="69" t="inlineStr">
-        <is>
-          <t>▼ -1.8%</t>
+        <v>126.9</v>
+      </c>
+      <c r="G18" s="71" t="inlineStr">
+        <is>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="H18" s="61" t="inlineStr">
@@ -9565,20 +9596,20 @@
         </is>
       </c>
       <c r="C22" s="57" t="n">
-        <v>1.3146</v>
+        <v>1.4884</v>
       </c>
       <c r="D22" s="57" t="n">
         <v>1.1589</v>
       </c>
       <c r="E22" s="58" t="n">
-        <v>794</v>
+        <v>899</v>
       </c>
       <c r="F22" s="58" t="n">
         <v>700</v>
       </c>
-      <c r="G22" s="69" t="inlineStr">
-        <is>
-          <t>▼ -1.1%</t>
+      <c r="G22" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="H22" s="61" t="inlineStr">
@@ -9769,20 +9800,20 @@
         </is>
       </c>
       <c r="C28" s="57" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="D28" s="57" t="n">
-        <v>0.6508</v>
+        <v>0.6521</v>
       </c>
       <c r="E28" s="58" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="F28" s="58" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="G28" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.0%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="H28" s="61" t="inlineStr">
@@ -9909,10 +9940,10 @@
       </c>
       <c r="B34" s="136" t="n"/>
       <c r="C34" s="137" t="n">
-        <v>1.2275</v>
+        <v>1.2173625</v>
       </c>
       <c r="D34" s="137" t="n">
-        <v>1.191225</v>
+        <v>1.1930875</v>
       </c>
       <c r="E34" s="138" t="n">
         <v>0.9106</v>
@@ -10181,20 +10212,20 @@
         </is>
       </c>
       <c r="C42" s="57" t="n">
-        <v>1.0662</v>
+        <v>0.9851</v>
       </c>
       <c r="D42" s="57" t="n">
-        <v>0.9536</v>
+        <v>0.9685</v>
       </c>
       <c r="E42" s="58" t="n">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="F42" s="58" t="n">
-        <v>576</v>
-      </c>
-      <c r="G42" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>585</v>
+      </c>
+      <c r="G42" s="69" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="H42" s="61" t="inlineStr">
@@ -10253,10 +10284,10 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.50098</v>
+        <v>1.4838</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.441566666666666</v>
+        <v>1.42868</v>
       </c>
       <c r="E46" s="145" t="n">
         <v>0.7476</v>
@@ -10494,13 +10525,13 @@
         <v>1.5142</v>
       </c>
       <c r="D53" s="66" t="n">
-        <v>1.5142</v>
+        <v>1.5067</v>
       </c>
       <c r="E53" s="67" t="n">
         <v>197.6</v>
       </c>
       <c r="F53" s="67" t="n">
-        <v>197.6</v>
+        <v>196.63</v>
       </c>
       <c r="G53" s="71" t="inlineStr">
         <is>
@@ -10509,7 +10540,7 @@
       </c>
       <c r="H53" s="70" t="inlineStr">
         <is>
-          <t>🟡 Medium</t>
+          <t>🟢 High</t>
         </is>
       </c>
     </row>
@@ -10627,20 +10658,20 @@
         </is>
       </c>
       <c r="C57" s="66" t="n">
-        <v>1.5742</v>
+        <v>1.3595</v>
       </c>
       <c r="D57" s="66" t="n">
-        <v>1.5072</v>
+        <v>1.3315</v>
       </c>
       <c r="E57" s="67" t="n">
-        <v>2303</v>
+        <v>1989</v>
       </c>
       <c r="F57" s="67" t="n">
-        <v>2205</v>
-      </c>
-      <c r="G57" s="71" t="inlineStr">
-        <is>
-          <t>▲ +15.0%</t>
+        <v>1948</v>
+      </c>
+      <c r="G57" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="H57" s="70" t="inlineStr">
@@ -10797,20 +10828,20 @@
         </is>
       </c>
       <c r="C62" s="57" t="n">
-        <v>1.464</v>
+        <v>1.421</v>
       </c>
       <c r="D62" s="57" t="n">
-        <v>1.4196</v>
+        <v>1.4095</v>
       </c>
       <c r="E62" s="58" t="n">
-        <v>5244</v>
+        <v>5090</v>
       </c>
       <c r="F62" s="58" t="n">
-        <v>5085</v>
+        <v>5049</v>
       </c>
       <c r="G62" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.9%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="H62" s="61" t="inlineStr">
@@ -10835,10 +10866,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.219855555555555</v>
+        <v>1.241244444444445</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.208766666666667</v>
+        <v>1.292444444444445</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -11039,20 +11070,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>1.3037</v>
+        <v>1.4616</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>1.2462</v>
+        <v>1.8136</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>83.56999999999999</v>
+        <v>93.69</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>79.88</v>
-      </c>
-      <c r="G71" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
+        <v>116.25</v>
+      </c>
+      <c r="G71" s="71" t="inlineStr">
+        <is>
+          <t>▲ +11.6%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">
@@ -11107,20 +11138,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.4286</v>
+        <v>1.4632</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.2775</v>
+        <v>1.4632</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>26</v>
+        <v>26.63</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>23.25</v>
+        <v>26.63</v>
       </c>
       <c r="G73" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.8%</t>
+          <t>▲ +18.6%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-08</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-09</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.246</t>
+          <t>$1.212</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+98.3%</t>
+          <t>+56.5%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.229</t>
+          <t>$1.189</t>
         </is>
       </c>
     </row>
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.7763</v>
+        <v>0.6853166666666667</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6504666666666666</v>
+        <v>0.6208166666666667</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.5268</v>
+        <v>1.4955</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,10 +1787,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.2176375</v>
+        <v>1.19969375</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.23948125</v>
+        <v>1.2129125</v>
       </c>
       <c r="F13" s="32" t="n">
         <v>0.6521</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.4838</v>
+        <v>1.42908</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.42868</v>
+        <v>1.377906666666666</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.7476</v>
+        <v>0.6602</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1853,10 +1853,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1.241244444444445</v>
+        <v>1.219855555555555</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>1.292444444444445</v>
+        <v>1.208766666666667</v>
       </c>
       <c r="F16" s="27" t="n">
         <v>0.3272</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-08</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-09</t>
         </is>
       </c>
     </row>
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.5268</v>
+        <v>0.9809</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>1.1588</v>
+        <v>0.9809</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>918.4</v>
+        <v>590</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>697.034</v>
+        <v>590</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="71" t="inlineStr">
-        <is>
-          <t>▲ +45.8%</t>
+      <c r="J8" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="E17" s="66" t="n">
-        <v>1.4884</v>
+        <v>1.3146</v>
       </c>
       <c r="F17" s="66" t="n">
         <v>1.1589</v>
       </c>
       <c r="G17" s="67" t="n">
-        <v>899</v>
+        <v>794</v>
       </c>
       <c r="H17" s="67" t="n">
         <v>700</v>
@@ -2646,9 +2646,9 @@
       <c r="I17" s="68" t="n">
         <v>604</v>
       </c>
-      <c r="J17" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.0%</t>
+      <c r="J17" s="69" t="inlineStr">
+        <is>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="K17" s="70" t="inlineStr">
@@ -2726,23 +2726,23 @@
         </is>
       </c>
       <c r="E19" s="66" t="n">
-        <v>1.0772</v>
+        <v>0.9639</v>
       </c>
       <c r="F19" s="66" t="n">
-        <v>1.389</v>
+        <v>0.9639</v>
       </c>
       <c r="G19" s="67" t="n">
-        <v>208.97</v>
+        <v>187</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>269.46</v>
+        <v>187</v>
       </c>
       <c r="I19" s="68" t="n">
         <v>194</v>
       </c>
       <c r="J19" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="K19" s="70" t="inlineStr">
@@ -3680,23 +3680,23 @@
         </is>
       </c>
       <c r="E41" s="66" t="n">
-        <v>1.2786</v>
+        <v>1.009</v>
       </c>
       <c r="F41" s="66" t="n">
-        <v>1.245</v>
+        <v>1.0675</v>
       </c>
       <c r="G41" s="67" t="n">
-        <v>167.5</v>
+        <v>132.18</v>
       </c>
       <c r="H41" s="67" t="n">
-        <v>163.09</v>
+        <v>139.84</v>
       </c>
       <c r="I41" s="68" t="n">
         <v>131</v>
       </c>
       <c r="J41" s="71" t="inlineStr">
         <is>
-          <t>▲ +98.3%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="K41" s="70" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+      <c r="J49" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4150,23 +4150,23 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.421</v>
+        <v>1.464</v>
       </c>
       <c r="F51" s="66" t="n">
-        <v>1.4095</v>
+        <v>1.4196</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>5090</v>
+        <v>5244</v>
       </c>
       <c r="H51" s="67" t="n">
-        <v>5049</v>
+        <v>5085</v>
       </c>
       <c r="I51" s="68" t="n">
         <v>3582</v>
       </c>
       <c r="J51" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="K51" s="70" t="inlineStr">
@@ -4392,23 +4392,23 @@
         </is>
       </c>
       <c r="E57" s="66" t="n">
-        <v>1.4616</v>
+        <v>1.3037</v>
       </c>
       <c r="F57" s="66" t="n">
-        <v>1.8136</v>
+        <v>1.2462</v>
       </c>
       <c r="G57" s="67" t="n">
-        <v>93.69</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="H57" s="67" t="n">
-        <v>116.25</v>
+        <v>79.88</v>
       </c>
       <c r="I57" s="68" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="J57" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.6%</t>
+      <c r="J57" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="K57" s="70" t="inlineStr">
@@ -4486,23 +4486,23 @@
         </is>
       </c>
       <c r="E59" s="66" t="n">
-        <v>1.4632</v>
+        <v>1.4286</v>
       </c>
       <c r="F59" s="66" t="n">
-        <v>1.4632</v>
+        <v>1.2775</v>
       </c>
       <c r="G59" s="67" t="n">
-        <v>26.63</v>
+        <v>26</v>
       </c>
       <c r="H59" s="67" t="n">
-        <v>26.63</v>
+        <v>23.25</v>
       </c>
       <c r="I59" s="68" t="n">
         <v>18.2</v>
       </c>
       <c r="J59" s="71" t="inlineStr">
         <is>
-          <t>▲ +18.6%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="K59" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.246427777777778</v>
+        <v>1.212237037037037</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.228544444444444</v>
+        <v>1.189327777777778</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-08</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-09</t>
         </is>
       </c>
     </row>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.5268</v>
-      </c>
-      <c r="E9" s="71" t="inlineStr">
-        <is>
-          <t>▲ +45.8%</t>
+        <v>0.9809</v>
+      </c>
+      <c r="E9" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.1588</v>
-      </c>
-      <c r="H9" s="71" t="inlineStr">
-        <is>
-          <t>▲ +18.1%</t>
+        <v>0.9809</v>
+      </c>
+      <c r="H9" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>918.4</v>
+        <v>590</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>697.034</v>
+        <v>590</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5343,11 +5343,11 @@
         <v>1.3289</v>
       </c>
       <c r="D18" s="91" t="n">
-        <v>1.4884</v>
-      </c>
-      <c r="E18" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.0%</t>
+        <v>1.3146</v>
+      </c>
+      <c r="E18" s="69" t="inlineStr">
+        <is>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="F18" s="90" t="n">
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I18" s="58" t="n">
-        <v>899</v>
+        <v>794</v>
       </c>
       <c r="J18" s="58" t="n">
         <v>700</v>
@@ -5433,29 +5433,29 @@
         <v>0.8608</v>
       </c>
       <c r="D20" s="91" t="n">
-        <v>1.0772</v>
+        <v>0.9639</v>
       </c>
       <c r="E20" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="F20" s="90" t="n">
         <v>0.9124</v>
       </c>
       <c r="G20" s="91" t="n">
-        <v>1.389</v>
+        <v>0.9639</v>
       </c>
       <c r="H20" s="71" t="inlineStr">
         <is>
-          <t>▲ +52.2%</t>
+          <t>▲ +5.6%</t>
         </is>
       </c>
       <c r="I20" s="58" t="n">
-        <v>208.97</v>
+        <v>187</v>
       </c>
       <c r="J20" s="58" t="n">
-        <v>269.46</v>
+        <v>187</v>
       </c>
       <c r="K20" s="61" t="inlineStr">
         <is>
@@ -6347,29 +6347,29 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="D42" s="91" t="n">
-        <v>1.2786</v>
+        <v>1.009</v>
       </c>
       <c r="E42" s="71" t="inlineStr">
         <is>
-          <t>▲ +98.3%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="F42" s="90" t="n">
         <v>0.6288</v>
       </c>
       <c r="G42" s="91" t="n">
-        <v>1.245</v>
+        <v>1.0675</v>
       </c>
       <c r="H42" s="71" t="inlineStr">
         <is>
-          <t>▲ +98.0%</t>
+          <t>▲ +69.8%</t>
         </is>
       </c>
       <c r="I42" s="58" t="n">
-        <v>167.5</v>
+        <v>132.18</v>
       </c>
       <c r="J42" s="58" t="n">
-        <v>163.09</v>
+        <v>139.84</v>
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>1.2544</v>
-      </c>
-      <c r="E50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="E50" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>1.2544</v>
-      </c>
-      <c r="H50" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="H50" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -6797,29 +6797,29 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.421</v>
+        <v>1.464</v>
       </c>
       <c r="E52" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
         <v>1.2741</v>
       </c>
       <c r="G52" s="91" t="n">
-        <v>1.4095</v>
+        <v>1.4196</v>
       </c>
       <c r="H52" s="71" t="inlineStr">
         <is>
-          <t>▲ +10.6%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>5090</v>
+        <v>5244</v>
       </c>
       <c r="J52" s="58" t="n">
-        <v>5049</v>
+        <v>5085</v>
       </c>
       <c r="K52" s="61" t="inlineStr">
         <is>
@@ -7029,29 +7029,29 @@
         <v>1.31</v>
       </c>
       <c r="D58" s="91" t="n">
-        <v>1.4616</v>
-      </c>
-      <c r="E58" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.6%</t>
+        <v>1.3037</v>
+      </c>
+      <c r="E58" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="F58" s="90" t="n">
         <v>1.2499</v>
       </c>
       <c r="G58" s="91" t="n">
-        <v>1.8136</v>
-      </c>
-      <c r="H58" s="71" t="inlineStr">
-        <is>
-          <t>▲ +45.1%</t>
+        <v>1.2462</v>
+      </c>
+      <c r="H58" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.3%</t>
         </is>
       </c>
       <c r="I58" s="58" t="n">
-        <v>93.69</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J58" s="58" t="n">
-        <v>116.25</v>
+        <v>79.88</v>
       </c>
       <c r="K58" s="61" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
         <v>1.2332</v>
       </c>
       <c r="D60" s="91" t="n">
-        <v>1.4632</v>
+        <v>1.4286</v>
       </c>
       <c r="E60" s="71" t="inlineStr">
         <is>
-          <t>▲ +18.6%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="F60" s="90" t="n">
         <v>1.2885</v>
       </c>
       <c r="G60" s="91" t="n">
-        <v>1.4632</v>
-      </c>
-      <c r="H60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +13.6%</t>
+        <v>1.2775</v>
+      </c>
+      <c r="H60" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="I60" s="58" t="n">
-        <v>26.63</v>
+        <v>26</v>
       </c>
       <c r="J60" s="58" t="n">
-        <v>26.63</v>
+        <v>23.25</v>
       </c>
       <c r="K60" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G10" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  Tanzania</t>
+          <t xml:space="preserve">  6.  South Sudan</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
@@ -7615,14 +7615,14 @@
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.7476</v>
+        <v>0.6602</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>0.7476</v>
-      </c>
-      <c r="K10" s="106" t="inlineStr">
-        <is>
-          <t>▼ -29.6%</t>
+        <v>0.6602</v>
+      </c>
+      <c r="K10" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7650,23 +7650,23 @@
       </c>
       <c r="G11" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Niger</t>
+          <t xml:space="preserve">  7.  Tanzania</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.8262</v>
+        <v>0.7476</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>1.0232</v>
-      </c>
-      <c r="K11" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.7476</v>
+      </c>
+      <c r="K11" s="106" t="inlineStr">
+        <is>
+          <t>▼ -29.6%</t>
         </is>
       </c>
     </row>
@@ -7694,19 +7694,19 @@
       </c>
       <c r="G12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Tunisia</t>
+          <t xml:space="preserve">  8.  Niger</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8377</v>
+        <v>0.8262</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>0.7318</v>
+        <v>1.0232</v>
       </c>
       <c r="K12" s="99" t="inlineStr">
         <is>
@@ -7738,51 +7738,51 @@
       </c>
       <c r="G13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Ghana</t>
+          <t xml:space="preserve">  9.  Tunisia</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8439</v>
+        <v>0.8377</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.9108000000000001</v>
-      </c>
-      <c r="K13" s="106" t="inlineStr">
-        <is>
-          <t>▼ -7.7%</t>
+        <v>0.7318</v>
+      </c>
+      <c r="K13" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Sudan</t>
+          <t xml:space="preserve">  10.  Kenya</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.5268</v>
+        <v>1.5142</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.1588</v>
+        <v>1.5067</v>
       </c>
       <c r="E14" s="114" t="inlineStr">
         <is>
-          <t>▲ +45.8%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Burkina Faso</t>
+          <t xml:space="preserve">  10.  Ghana</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
@@ -7791,14 +7791,14 @@
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.8858</v>
+        <v>0.8439</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>1.6374</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="K14" s="106" t="inlineStr">
         <is>
-          <t>▼ -36.4%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
     </row>
@@ -7867,145 +7867,145 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.2786</v>
+        <v>1.009</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +98.3%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.6339</v>
+        <v>0.3643</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>0.6602</v>
+        <v>1.0882</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.2544</v>
+        <v>1.5342</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.5942</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.0474</v>
+        <v>1.15</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.5268</v>
+        <v>1.6</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +45.8%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.4794</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0882</v>
+        <v>1.0316</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.5342</v>
+        <v>1.3693</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +41.0%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.446</v>
+        <v>0.3377</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.15</v>
+        <v>1.2762</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.6</v>
+        <v>1.4955</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.45</v>
+        <v>0.2193</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
@@ -8015,121 +8015,121 @@
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.2332</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.3693</v>
+        <v>1.4286</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.3377</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.0722</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.0772</v>
+        <v>1.2049</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +12.4%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.2164</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>1.2332</v>
+        <v>0.8608</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.4632</v>
+        <v>0.9639</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +18.6%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.23</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.2762</v>
+        <v>0.5861</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.4955</v>
+        <v>0.6521</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.2193</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
@@ -8139,28 +8139,28 @@
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.1425</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.2049</v>
+        <v>1.2555</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.4%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1327</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,59 +8170,59 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.4222</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.4884</v>
+        <v>1.5556</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1595</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.31</v>
+        <v>1.3986</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.4616</v>
+        <v>1.5142</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.6%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1516</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
@@ -8232,59 +8232,59 @@
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.5244</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>0.6521</v>
+        <v>1.6391</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.066</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.3587</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.2555</v>
+        <v>1.4487</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +6.6%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.113</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,28 +8294,28 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.4222</v>
+        <v>1.2886</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.5556</v>
+        <v>1.3674</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,90 +8325,90 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.4106</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.5142</v>
+        <v>1.4968</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.3819</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.464</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.08210000000000001</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3587</v>
+        <v>1.3479</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.4487</v>
+        <v>1.3699</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.6%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.09</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,90 +8418,90 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.3681</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3674</v>
+        <v>1.3873</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0788</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.0555</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.4968</v>
+        <v>1.0582</v>
       </c>
       <c r="F38" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +0.3%</t>
         </is>
       </c>
       <c r="G38" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.31</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.421</v>
-      </c>
-      <c r="F39" s="71" t="inlineStr">
-        <is>
-          <t>▲ +2.8%</t>
-        </is>
-      </c>
-      <c r="G39" s="117" t="n">
-        <v>0.0391</v>
+        <v>1.3037</v>
+      </c>
+      <c r="F39" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
+        </is>
+      </c>
+      <c r="G39" s="119" t="n">
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
@@ -8511,121 +8511,121 @@
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3691</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3699</v>
-      </c>
-      <c r="F40" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.6%</t>
-        </is>
-      </c>
-      <c r="G40" s="117" t="n">
-        <v>0.022</v>
+        <v>1.3595</v>
+      </c>
+      <c r="F40" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.7%</t>
+        </is>
+      </c>
+      <c r="G40" s="119" t="n">
+        <v>-0.009599999999999999</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.2677</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.3873</v>
-      </c>
-      <c r="F41" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.4%</t>
-        </is>
-      </c>
-      <c r="G41" s="117" t="n">
-        <v>0.0192</v>
+        <v>1.257</v>
+      </c>
+      <c r="F41" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.8%</t>
+        </is>
+      </c>
+      <c r="G41" s="119" t="n">
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3289</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.0582</v>
-      </c>
-      <c r="F42" s="71" t="inlineStr">
-        <is>
-          <t>▲ +0.3%</t>
-        </is>
-      </c>
-      <c r="G42" s="117" t="n">
-        <v>0.0027</v>
+        <v>1.3146</v>
+      </c>
+      <c r="F42" s="69" t="inlineStr">
+        <is>
+          <t>▼ -1.1%</t>
+        </is>
+      </c>
+      <c r="G42" s="119" t="n">
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.2262</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.3595</v>
+        <v>1.2003</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.7%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
@@ -8635,169 +8635,169 @@
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.784</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.257</v>
+        <v>1.6851</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.0641</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>1.2003</v>
+        <v>0.9982</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.1%</t>
+          <t>▼ -6.2%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0259</v>
+        <v>-0.0659</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>ZWG</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>1.784</v>
+        <v>2.17</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>1.6851</v>
+        <v>2.0331</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.1369</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.0474</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.9982</v>
+        <v>0.9809</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C48" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>GHS</t>
         </is>
       </c>
       <c r="D48" s="88" t="n">
-        <v>2.17</v>
+        <v>0.914</v>
       </c>
       <c r="E48" s="89" t="n">
-        <v>2.0331</v>
+        <v>0.8439</v>
       </c>
       <c r="F48" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.3%</t>
+          <t>▼ -7.7%</t>
         </is>
       </c>
       <c r="G48" s="119" t="n">
-        <v>-0.1369</v>
+        <v>-0.0701</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="53" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Central Africa</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>GHS</t>
+          <t>XAF</t>
         </is>
       </c>
       <c r="D49" s="88" t="n">
-        <v>0.914</v>
+        <v>1.0671</v>
       </c>
       <c r="E49" s="91" t="n">
-        <v>0.8439</v>
+        <v>0.9851</v>
       </c>
       <c r="F49" s="69" t="inlineStr">
         <is>
@@ -8805,192 +8805,161 @@
         </is>
       </c>
       <c r="G49" s="119" t="n">
-        <v>-0.0701</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="62" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B50" s="63" t="inlineStr">
         <is>
-          <t>Central Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C50" s="118" t="inlineStr">
         <is>
-          <t>XAF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D50" s="88" t="n">
-        <v>1.0671</v>
+        <v>1.2212</v>
       </c>
       <c r="E50" s="89" t="n">
-        <v>0.9851</v>
+        <v>1.1258</v>
       </c>
       <c r="F50" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -7.8%</t>
         </is>
       </c>
       <c r="G50" s="119" t="n">
-        <v>-0.082</v>
+        <v>-0.0954</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.2212</v>
+        <v>1.1939</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>1.1258</v>
+        <v>1.0606</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -7.8%</t>
+          <t>▼ -11.2%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.0954</v>
+        <v>-0.1333</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>1.1939</v>
+        <v>0.4771</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>1.0606</v>
+        <v>0.4175</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.0596</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B53" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C53" s="116" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D53" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.0616</v>
       </c>
       <c r="E53" s="91" t="n">
-        <v>0.4175</v>
+        <v>0.7476</v>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.6%</t>
         </is>
       </c>
       <c r="G53" s="119" t="n">
-        <v>-0.0596</v>
+        <v>-0.314</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="62" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="B54" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C54" s="118" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D54" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.3919</v>
       </c>
       <c r="E54" s="89" t="n">
-        <v>0.7476</v>
+        <v>0.8858</v>
       </c>
       <c r="F54" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.6%</t>
+          <t>▼ -36.4%</t>
         </is>
       </c>
       <c r="G54" s="119" t="n">
-        <v>-0.314</v>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="53" t="inlineStr">
-        <is>
-          <t>Burkina Faso</t>
-        </is>
-      </c>
-      <c r="B55" s="54" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="C55" s="116" t="inlineStr">
-        <is>
-          <t>XOF</t>
-        </is>
-      </c>
-      <c r="D55" s="88" t="n">
-        <v>1.3919</v>
-      </c>
-      <c r="E55" s="91" t="n">
-        <v>0.8858</v>
-      </c>
-      <c r="F55" s="69" t="inlineStr">
-        <is>
-          <t>▼ -36.4%</t>
-        </is>
-      </c>
-      <c r="G55" s="119" t="n">
         <v>-0.5061</v>
       </c>
     </row>
@@ -9048,16 +9017,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.7763</v>
+        <v>0.6853166666666667</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6504666666666666</v>
+        <v>0.6208166666666667</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.5268</v>
+        <v>1.4955</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9252,20 +9221,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>1.5268</v>
+        <v>0.9809</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>1.1588</v>
+        <v>0.9809</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>918.4</v>
+        <v>590</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>697.034</v>
-      </c>
-      <c r="G10" s="71" t="inlineStr">
-        <is>
-          <t>▲ +45.8%</t>
+        <v>590</v>
+      </c>
+      <c r="G10" s="69" t="inlineStr">
+        <is>
+          <t>▼ -6.3%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9324,10 +9293,10 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.2176375</v>
+        <v>1.19969375</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.23948125</v>
+        <v>1.2129125</v>
       </c>
       <c r="E14" s="131" t="n">
         <v>0.6521</v>
@@ -9596,20 +9565,20 @@
         </is>
       </c>
       <c r="C22" s="57" t="n">
-        <v>1.4884</v>
+        <v>1.3146</v>
       </c>
       <c r="D22" s="57" t="n">
         <v>1.1589</v>
       </c>
       <c r="E22" s="58" t="n">
-        <v>899</v>
+        <v>794</v>
       </c>
       <c r="F22" s="58" t="n">
         <v>700</v>
       </c>
-      <c r="G22" s="71" t="inlineStr">
-        <is>
-          <t>▲ +12.0%</t>
+      <c r="G22" s="69" t="inlineStr">
+        <is>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="H22" s="61" t="inlineStr">
@@ -9664,20 +9633,20 @@
         </is>
       </c>
       <c r="C24" s="57" t="n">
-        <v>1.0772</v>
+        <v>0.9639</v>
       </c>
       <c r="D24" s="57" t="n">
-        <v>1.389</v>
+        <v>0.9639</v>
       </c>
       <c r="E24" s="58" t="n">
-        <v>208.97</v>
+        <v>187</v>
       </c>
       <c r="F24" s="58" t="n">
-        <v>269.46</v>
+        <v>187</v>
       </c>
       <c r="G24" s="71" t="inlineStr">
         <is>
-          <t>▲ +25.1%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="H24" s="61" t="inlineStr">
@@ -10284,13 +10253,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.4838</v>
+        <v>1.42908</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.42868</v>
+        <v>1.377906666666666</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.7476</v>
+        <v>0.6602</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10488,20 +10457,20 @@
         </is>
       </c>
       <c r="C52" s="57" t="n">
-        <v>1.2786</v>
+        <v>1.009</v>
       </c>
       <c r="D52" s="57" t="n">
-        <v>1.245</v>
+        <v>1.0675</v>
       </c>
       <c r="E52" s="58" t="n">
-        <v>167.5</v>
+        <v>132.18</v>
       </c>
       <c r="F52" s="58" t="n">
-        <v>163.09</v>
+        <v>139.84</v>
       </c>
       <c r="G52" s="71" t="inlineStr">
         <is>
-          <t>▲ +98.3%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="H52" s="61" t="inlineStr">
@@ -10760,20 +10729,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>1.2544</v>
+        <v>0.6602</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>5700</v>
+        <v>3000</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G60" s="71" t="inlineStr">
-        <is>
-          <t>▲ +90.0%</t>
+        <v>3000</v>
+      </c>
+      <c r="G60" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">
@@ -10828,20 +10797,20 @@
         </is>
       </c>
       <c r="C62" s="57" t="n">
-        <v>1.421</v>
+        <v>1.464</v>
       </c>
       <c r="D62" s="57" t="n">
-        <v>1.4095</v>
+        <v>1.4196</v>
       </c>
       <c r="E62" s="58" t="n">
-        <v>5090</v>
+        <v>5244</v>
       </c>
       <c r="F62" s="58" t="n">
-        <v>5049</v>
+        <v>5085</v>
       </c>
       <c r="G62" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="H62" s="61" t="inlineStr">
@@ -10866,10 +10835,10 @@
       </c>
       <c r="B65" s="150" t="n"/>
       <c r="C65" s="151" t="n">
-        <v>1.241244444444445</v>
+        <v>1.219855555555555</v>
       </c>
       <c r="D65" s="151" t="n">
-        <v>1.292444444444445</v>
+        <v>1.208766666666667</v>
       </c>
       <c r="E65" s="152" t="n">
         <v>0.3272</v>
@@ -11070,20 +11039,20 @@
         </is>
       </c>
       <c r="C71" s="57" t="n">
-        <v>1.4616</v>
+        <v>1.3037</v>
       </c>
       <c r="D71" s="57" t="n">
-        <v>1.8136</v>
+        <v>1.2462</v>
       </c>
       <c r="E71" s="58" t="n">
-        <v>93.69</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="F71" s="58" t="n">
-        <v>116.25</v>
-      </c>
-      <c r="G71" s="71" t="inlineStr">
-        <is>
-          <t>▲ +11.6%</t>
+        <v>79.88</v>
+      </c>
+      <c r="G71" s="69" t="inlineStr">
+        <is>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">
@@ -11138,20 +11107,20 @@
         </is>
       </c>
       <c r="C73" s="57" t="n">
-        <v>1.4632</v>
+        <v>1.4286</v>
       </c>
       <c r="D73" s="57" t="n">
-        <v>1.4632</v>
+        <v>1.2775</v>
       </c>
       <c r="E73" s="58" t="n">
-        <v>26.63</v>
+        <v>26</v>
       </c>
       <c r="F73" s="58" t="n">
-        <v>26.63</v>
+        <v>23.25</v>
       </c>
       <c r="G73" s="71" t="inlineStr">
         <is>
-          <t>▲ +18.6%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="H73" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-09</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-10</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.212</t>
+          <t>$1.221</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+56.5%</t>
+          <t>+90.0%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.189</t>
+          <t>$1.200</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.6853166666666667</v>
+        <v>0.7590833333333333</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6208166666666667</v>
+        <v>0.6987833333333334</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.4955</v>
+        <v>1.533</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,10 +1787,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.19969375</v>
+        <v>1.16504375</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.2129125</v>
+        <v>1.18040625</v>
       </c>
       <c r="F13" s="32" t="n">
         <v>0.6521</v>
@@ -1831,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.42908</v>
+        <v>1.468713333333333</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.377906666666666</v>
+        <v>1.419726666666666</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>0.6602</v>
+        <v>0.7476</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>2.8617</v>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-09</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-10</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.3678</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.2584</v>
+        <v>0.5964</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -22.9%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.4955</v>
+        <v>1.4357</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.4955</v>
+        <v>1.4457</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +12.5%</t>
         </is>
       </c>
       <c r="K7" s="70" t="inlineStr">
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.533</v>
       </c>
       <c r="F8" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.1605</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>590</v>
+        <v>922.1</v>
       </c>
       <c r="H8" s="58" t="n">
-        <v>590</v>
+        <v>698.026</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>601.5</v>
       </c>
-      <c r="J8" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+      <c r="J8" s="71" t="inlineStr">
+        <is>
+          <t>▲ +46.4%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2353,13 +2353,13 @@
         <v>1.2003</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>1.2417</v>
+        <v>1.1921</v>
       </c>
       <c r="G11" s="67" t="n">
         <v>725</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
@@ -2444,23 +2444,23 @@
         </is>
       </c>
       <c r="E13" s="66" t="n">
-        <v>1.3674</v>
+        <v>1.3665</v>
       </c>
       <c r="F13" s="66" t="n">
-        <v>1.1484</v>
+        <v>1.1403</v>
       </c>
       <c r="G13" s="67" t="n">
-        <v>151.1</v>
+        <v>151</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>126.9</v>
+        <v>126</v>
       </c>
       <c r="I13" s="68" t="n">
         <v>110.5</v>
       </c>
       <c r="J13" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +6.0%</t>
         </is>
       </c>
       <c r="K13" s="70" t="inlineStr">
@@ -2585,23 +2585,23 @@
         </is>
       </c>
       <c r="E16" s="57" t="n">
-        <v>1.3873</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="F16" s="57" t="n">
-        <v>1.3873</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="G16" s="58" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="H16" s="58" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="I16" s="59" t="n">
         <v>8650</v>
       </c>
-      <c r="J16" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.4%</t>
+      <c r="J16" s="69" t="inlineStr">
+        <is>
+          <t>▼ -32.4%</t>
         </is>
       </c>
       <c r="K16" s="61" t="inlineStr">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="E18" s="57" t="n">
-        <v>1.4487</v>
+        <v>1.3576</v>
       </c>
       <c r="F18" s="57" t="n">
         <v>1.1589</v>
       </c>
       <c r="G18" s="58" t="n">
-        <v>875</v>
+        <v>820</v>
       </c>
       <c r="H18" s="58" t="n">
         <v>700</v>
@@ -2693,9 +2693,9 @@
       <c r="I18" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J18" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+      <c r="J18" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K18" s="61" t="inlineStr">
@@ -3774,23 +3774,23 @@
         </is>
       </c>
       <c r="E43" s="66" t="n">
-        <v>1.0606</v>
+        <v>1.1039</v>
       </c>
       <c r="F43" s="66" t="n">
-        <v>1.0087</v>
+        <v>1.0519</v>
       </c>
       <c r="G43" s="67" t="n">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="H43" s="67" t="n">
-        <v>4660</v>
+        <v>4860</v>
       </c>
       <c r="I43" s="68" t="n">
         <v>4620</v>
       </c>
       <c r="J43" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="K43" s="70" t="inlineStr">
@@ -4056,23 +4056,23 @@
         </is>
       </c>
       <c r="E49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="F49" s="66" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="G49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="H49" s="67" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="I49" s="68" t="n">
         <v>4544</v>
       </c>
-      <c r="J49" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J49" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="K49" s="70" t="inlineStr">
@@ -4150,23 +4150,23 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.464</v>
+        <v>1.421</v>
       </c>
       <c r="F51" s="66" t="n">
-        <v>1.4196</v>
+        <v>1.4095</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>5244</v>
+        <v>5090</v>
       </c>
       <c r="H51" s="67" t="n">
-        <v>5085</v>
+        <v>5049</v>
       </c>
       <c r="I51" s="68" t="n">
         <v>3582</v>
       </c>
       <c r="J51" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.9%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="K51" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.212237037037037</v>
+        <v>1.221175925925926</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.189327777777778</v>
+        <v>1.199975925925926</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-09</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-10</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.4175</v>
+        <v>0.3678</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -22.9%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.2584</v>
-      </c>
-      <c r="H6" s="69" t="inlineStr">
-        <is>
-          <t>▼ -36.6%</t>
+        <v>0.5964</v>
+      </c>
+      <c r="H6" s="71" t="inlineStr">
+        <is>
+          <t>▲ +46.3%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.4955</v>
+        <v>1.4357</v>
       </c>
       <c r="E8" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +12.5%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.4955</v>
+        <v>1.4457</v>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>▲ +30.4%</t>
+          <t>▲ +26.1%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -4976,29 +4976,29 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="E9" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+        <v>1.533</v>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>▲ +46.4%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
         <v>0.9809</v>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="H9" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.1605</v>
+      </c>
+      <c r="H9" s="71" t="inlineStr">
+        <is>
+          <t>▲ +18.3%</t>
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>590</v>
+        <v>922.1</v>
       </c>
       <c r="J9" s="67" t="n">
-        <v>590</v>
+        <v>698.026</v>
       </c>
       <c r="K9" s="70" t="inlineStr">
         <is>
@@ -5084,18 +5084,18 @@
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>1.2417</v>
+        <v>1.1921</v>
       </c>
       <c r="H12" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.4%</t>
+          <t>▼ -5.3%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
         <v>725</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -5163,29 +5163,29 @@
         <v>1.2886</v>
       </c>
       <c r="D14" s="91" t="n">
-        <v>1.3674</v>
+        <v>1.3665</v>
       </c>
       <c r="E14" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +6.0%</t>
         </is>
       </c>
       <c r="F14" s="90" t="n">
         <v>1.0826</v>
       </c>
       <c r="G14" s="91" t="n">
-        <v>1.1484</v>
+        <v>1.1403</v>
       </c>
       <c r="H14" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +5.3%</t>
         </is>
       </c>
       <c r="I14" s="58" t="n">
-        <v>151.1</v>
+        <v>151</v>
       </c>
       <c r="J14" s="58" t="n">
-        <v>126.9</v>
+        <v>126</v>
       </c>
       <c r="K14" s="61" t="inlineStr">
         <is>
@@ -5298,29 +5298,29 @@
         <v>1.3681</v>
       </c>
       <c r="D17" s="89" t="n">
-        <v>1.3873</v>
-      </c>
-      <c r="E17" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.4%</t>
+        <v>0.9249000000000001</v>
+      </c>
+      <c r="E17" s="69" t="inlineStr">
+        <is>
+          <t>▼ -32.4%</t>
         </is>
       </c>
       <c r="F17" s="90" t="n">
         <v>1.341</v>
       </c>
       <c r="G17" s="89" t="n">
-        <v>1.3873</v>
-      </c>
-      <c r="H17" s="71" t="inlineStr">
-        <is>
-          <t>▲ +3.5%</t>
+        <v>0.9249000000000001</v>
+      </c>
+      <c r="H17" s="69" t="inlineStr">
+        <is>
+          <t>▼ -31.0%</t>
         </is>
       </c>
       <c r="I17" s="67" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="J17" s="67" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="K17" s="70" t="inlineStr">
         <is>
@@ -5388,11 +5388,11 @@
         <v>1.3587</v>
       </c>
       <c r="D19" s="89" t="n">
-        <v>1.4487</v>
-      </c>
-      <c r="E19" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+        <v>1.3576</v>
+      </c>
+      <c r="E19" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="90" t="n">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="I19" s="67" t="n">
-        <v>875</v>
+        <v>820</v>
       </c>
       <c r="J19" s="67" t="n">
         <v>700</v>
@@ -6437,29 +6437,29 @@
         <v>1.1939</v>
       </c>
       <c r="D44" s="91" t="n">
-        <v>1.0606</v>
+        <v>1.1039</v>
       </c>
       <c r="E44" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="F44" s="90" t="n">
         <v>1.1199</v>
       </c>
       <c r="G44" s="91" t="n">
-        <v>1.0087</v>
+        <v>1.0519</v>
       </c>
       <c r="H44" s="69" t="inlineStr">
         <is>
-          <t>▼ -9.9%</t>
+          <t>▼ -6.1%</t>
         </is>
       </c>
       <c r="I44" s="58" t="n">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="J44" s="58" t="n">
-        <v>4660</v>
+        <v>4860</v>
       </c>
       <c r="K44" s="61" t="inlineStr">
         <is>
@@ -6707,29 +6707,29 @@
         <v>0.6602</v>
       </c>
       <c r="D50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="E50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="E50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="F50" s="90" t="n">
         <v>0.6602</v>
       </c>
       <c r="G50" s="91" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="H50" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.2544</v>
+      </c>
+      <c r="H50" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="I50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="J50" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="K50" s="61" t="inlineStr">
         <is>
@@ -6797,29 +6797,29 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.464</v>
+        <v>1.421</v>
       </c>
       <c r="E52" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.9%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
         <v>1.2741</v>
       </c>
       <c r="G52" s="91" t="n">
-        <v>1.4196</v>
+        <v>1.4095</v>
       </c>
       <c r="H52" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.4%</t>
+          <t>▲ +10.6%</t>
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>5244</v>
+        <v>5090</v>
       </c>
       <c r="J52" s="58" t="n">
-        <v>5085</v>
+        <v>5049</v>
       </c>
       <c r="K52" s="61" t="inlineStr">
         <is>
@@ -7527,14 +7527,14 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.4175</v>
+        <v>0.3678</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.2584</v>
+        <v>0.5964</v>
       </c>
       <c r="K8" s="106" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -22.9%</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G10" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6.  South Sudan</t>
+          <t xml:space="preserve">  6.  Tanzania</t>
         </is>
       </c>
       <c r="H10" s="107" t="inlineStr">
@@ -7615,14 +7615,14 @@
         </is>
       </c>
       <c r="I10" s="108" t="n">
-        <v>0.6602</v>
+        <v>0.7476</v>
       </c>
       <c r="J10" s="109" t="n">
-        <v>0.6602</v>
-      </c>
-      <c r="K10" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.7476</v>
+      </c>
+      <c r="K10" s="106" t="inlineStr">
+        <is>
+          <t>▼ -29.6%</t>
         </is>
       </c>
     </row>
@@ -7650,23 +7650,23 @@
       </c>
       <c r="G11" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Tanzania</t>
+          <t xml:space="preserve">  7.  Niger</t>
         </is>
       </c>
       <c r="H11" s="100" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I11" s="101" t="n">
-        <v>0.7476</v>
+        <v>0.8262</v>
       </c>
       <c r="J11" s="102" t="n">
-        <v>0.7476</v>
-      </c>
-      <c r="K11" s="106" t="inlineStr">
-        <is>
-          <t>▼ -29.6%</t>
+        <v>1.0232</v>
+      </c>
+      <c r="K11" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7694,19 +7694,19 @@
       </c>
       <c r="G12" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Niger</t>
+          <t xml:space="preserve">  8.  Tunisia</t>
         </is>
       </c>
       <c r="H12" s="107" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="I12" s="108" t="n">
-        <v>0.8262</v>
+        <v>0.8377</v>
       </c>
       <c r="J12" s="109" t="n">
-        <v>1.0232</v>
+        <v>0.7318</v>
       </c>
       <c r="K12" s="99" t="inlineStr">
         <is>
@@ -7738,51 +7738,51 @@
       </c>
       <c r="G13" s="113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Tunisia</t>
+          <t xml:space="preserve">  9.  Ghana</t>
         </is>
       </c>
       <c r="H13" s="100" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="I13" s="101" t="n">
-        <v>0.8377</v>
+        <v>0.8439</v>
       </c>
       <c r="J13" s="102" t="n">
-        <v>0.7318</v>
-      </c>
-      <c r="K13" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="K13" s="106" t="inlineStr">
+        <is>
+          <t>▼ -7.7%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Kenya</t>
+          <t xml:space="preserve">  10.  Sudan</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.5142</v>
+        <v>1.533</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.5067</v>
+        <v>1.1605</v>
       </c>
       <c r="E14" s="114" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +46.4%</t>
         </is>
       </c>
       <c r="G14" s="111" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Ghana</t>
+          <t xml:space="preserve">  10.  Burkina Faso</t>
         </is>
       </c>
       <c r="H14" s="107" t="inlineStr">
@@ -7791,14 +7791,14 @@
         </is>
       </c>
       <c r="I14" s="108" t="n">
-        <v>0.8439</v>
+        <v>0.8858</v>
       </c>
       <c r="J14" s="109" t="n">
-        <v>0.9108000000000001</v>
+        <v>1.6374</v>
       </c>
       <c r="K14" s="106" t="inlineStr">
         <is>
-          <t>▼ -7.7%</t>
+          <t>▼ -36.4%</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,152 +7860,152 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.009</v>
+        <v>1.2544</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.3643</v>
+        <v>0.5942</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>1.0882</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.5342</v>
+        <v>1.009</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +41.0%</t>
+          <t>▲ +56.5%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.446</v>
+        <v>0.3643</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="53" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C21" s="116" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D21" s="88" t="n">
-        <v>1.15</v>
+        <v>1.0474</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.6</v>
+        <v>1.533</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +46.4%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.45</v>
+        <v>0.4856</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C22" s="118" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="D22" s="88" t="n">
-        <v>1.0316</v>
+        <v>1.0882</v>
       </c>
       <c r="E22" s="89" t="n">
-        <v>1.3693</v>
+        <v>1.5342</v>
       </c>
       <c r="F22" s="71" t="inlineStr">
         <is>
-          <t>▲ +32.7%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="G22" s="117" t="n">
-        <v>0.3377</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C23" s="116" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D23" s="88" t="n">
-        <v>1.2762</v>
+        <v>1.15</v>
       </c>
       <c r="E23" s="91" t="n">
-        <v>1.4955</v>
+        <v>1.6</v>
       </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G23" s="117" t="n">
-        <v>0.2193</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
@@ -8015,28 +8015,28 @@
       </c>
       <c r="C24" s="118" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="D24" s="88" t="n">
-        <v>1.2332</v>
+        <v>1.0316</v>
       </c>
       <c r="E24" s="89" t="n">
-        <v>1.4286</v>
+        <v>1.3693</v>
       </c>
       <c r="F24" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.8%</t>
+          <t>▲ +32.7%</t>
         </is>
       </c>
       <c r="G24" s="117" t="n">
-        <v>0.1954</v>
+        <v>0.3377</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
@@ -8046,121 +8046,121 @@
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.2332</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.2049</v>
+        <v>1.4286</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.4%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1327</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B26" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C26" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="D26" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.2762</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>0.9639</v>
+        <v>1.4357</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +12.5%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1595</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.0722</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>0.6521</v>
+        <v>1.2049</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +12.4%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.066</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>1.1425</v>
+        <v>0.8608</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>1.2555</v>
+        <v>0.9639</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +12.0%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,59 +8170,59 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>1.4222</v>
+        <v>0.5861</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>1.5556</v>
+        <v>0.6521</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +11.3%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.1425</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.5142</v>
+        <v>1.2555</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
@@ -8232,59 +8232,59 @@
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.4222</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.5556</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3587</v>
+        <v>1.3986</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.4487</v>
+        <v>1.5142</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.6%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.09</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,22 +8294,22 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.5244</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.3674</v>
+        <v>1.6391</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.0788</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -8346,38 +8346,38 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.2886</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.464</v>
+        <v>1.3665</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.9%</t>
+          <t>▲ +6.0%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0779</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
@@ -8387,53 +8387,53 @@
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3819</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.3699</v>
+        <v>1.421</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.022</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>GNF</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3681</v>
+        <v>1.3479</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3873</v>
+        <v>1.3699</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.4%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.0192</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -8718,32 +8718,32 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>MGA</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.0474</v>
+        <v>1.1939</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>0.9809</v>
+        <v>1.1039</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.3%</t>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="G47" s="119" t="n">
-        <v>-0.0665</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -8842,94 +8842,94 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>EGP</t>
         </is>
       </c>
       <c r="D51" s="88" t="n">
-        <v>1.1939</v>
+        <v>0.4771</v>
       </c>
       <c r="E51" s="91" t="n">
-        <v>1.0606</v>
+        <v>0.3678</v>
       </c>
       <c r="F51" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -22.9%</t>
         </is>
       </c>
       <c r="G51" s="119" t="n">
-        <v>-0.1333</v>
+        <v>-0.1093</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="B52" s="63" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C52" s="118" t="inlineStr">
         <is>
-          <t>EGP</t>
+          <t>TZS</t>
         </is>
       </c>
       <c r="D52" s="88" t="n">
-        <v>0.4771</v>
+        <v>1.0616</v>
       </c>
       <c r="E52" s="89" t="n">
-        <v>0.4175</v>
+        <v>0.7476</v>
       </c>
       <c r="F52" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -29.6%</t>
         </is>
       </c>
       <c r="G52" s="119" t="n">
-        <v>-0.0596</v>
+        <v>-0.314</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B53" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C53" s="116" t="inlineStr">
         <is>
-          <t>TZS</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D53" s="88" t="n">
-        <v>1.0616</v>
+        <v>1.3681</v>
       </c>
       <c r="E53" s="91" t="n">
-        <v>0.7476</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="F53" s="69" t="inlineStr">
         <is>
-          <t>▼ -29.6%</t>
+          <t>▼ -32.4%</t>
         </is>
       </c>
       <c r="G53" s="119" t="n">
-        <v>-0.314</v>
+        <v>-0.4432</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -9017,16 +9017,16 @@
       </c>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="123" t="n">
-        <v>0.6853166666666667</v>
+        <v>0.7590833333333333</v>
       </c>
       <c r="D4" s="123" t="n">
-        <v>0.6208166666666667</v>
+        <v>0.6987833333333334</v>
       </c>
       <c r="E4" s="124" t="n">
         <v>0.0309</v>
       </c>
       <c r="F4" s="125" t="n">
-        <v>1.4955</v>
+        <v>1.533</v>
       </c>
       <c r="G4" s="122" t="n"/>
       <c r="H4" s="122" t="n"/>
@@ -9119,20 +9119,20 @@
         </is>
       </c>
       <c r="C7" s="66" t="n">
-        <v>0.4175</v>
+        <v>0.3678</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>0.2584</v>
+        <v>0.5964</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="F7" s="67" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>▼ -12.5%</t>
+          <t>▼ -22.9%</t>
         </is>
       </c>
       <c r="H7" s="70" t="inlineStr">
@@ -9187,20 +9187,20 @@
         </is>
       </c>
       <c r="C9" s="66" t="n">
-        <v>1.4955</v>
+        <v>1.4357</v>
       </c>
       <c r="D9" s="66" t="n">
-        <v>1.4955</v>
+        <v>1.4457</v>
       </c>
       <c r="E9" s="67" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="F9" s="67" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.2%</t>
+          <t>▲ +12.5%</t>
         </is>
       </c>
       <c r="H9" s="70" t="inlineStr">
@@ -9221,20 +9221,20 @@
         </is>
       </c>
       <c r="C10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.533</v>
       </c>
       <c r="D10" s="57" t="n">
-        <v>0.9809</v>
+        <v>1.1605</v>
       </c>
       <c r="E10" s="58" t="n">
-        <v>590</v>
+        <v>922.1</v>
       </c>
       <c r="F10" s="58" t="n">
-        <v>590</v>
-      </c>
-      <c r="G10" s="69" t="inlineStr">
-        <is>
-          <t>▼ -6.3%</t>
+        <v>698.026</v>
+      </c>
+      <c r="G10" s="71" t="inlineStr">
+        <is>
+          <t>▲ +46.4%</t>
         </is>
       </c>
       <c r="H10" s="61" t="inlineStr">
@@ -9293,10 +9293,10 @@
       </c>
       <c r="B14" s="129" t="n"/>
       <c r="C14" s="130" t="n">
-        <v>1.19969375</v>
+        <v>1.16504375</v>
       </c>
       <c r="D14" s="130" t="n">
-        <v>1.2129125</v>
+        <v>1.18040625</v>
       </c>
       <c r="E14" s="131" t="n">
         <v>0.6521</v>
@@ -9364,13 +9364,13 @@
         <v>1.2003</v>
       </c>
       <c r="D16" s="57" t="n">
-        <v>1.2417</v>
+        <v>1.1921</v>
       </c>
       <c r="E16" s="58" t="n">
         <v>725</v>
       </c>
       <c r="F16" s="58" t="n">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="G16" s="69" t="inlineStr">
         <is>
@@ -9429,20 +9429,20 @@
         </is>
       </c>
       <c r="C18" s="57" t="n">
-        <v>1.3674</v>
+        <v>1.3665</v>
       </c>
       <c r="D18" s="57" t="n">
-        <v>1.1484</v>
+        <v>1.1403</v>
       </c>
       <c r="E18" s="58" t="n">
-        <v>151.1</v>
+        <v>151</v>
       </c>
       <c r="F18" s="58" t="n">
-        <v>126.9</v>
+        <v>126</v>
       </c>
       <c r="G18" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +6.0%</t>
         </is>
       </c>
       <c r="H18" s="61" t="inlineStr">
@@ -9531,20 +9531,20 @@
         </is>
       </c>
       <c r="C21" s="66" t="n">
-        <v>1.3873</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="D21" s="66" t="n">
-        <v>1.3873</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="E21" s="67" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="F21" s="67" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G21" s="71" t="inlineStr">
-        <is>
-          <t>▲ +1.4%</t>
+        <v>8000</v>
+      </c>
+      <c r="G21" s="69" t="inlineStr">
+        <is>
+          <t>▼ -32.4%</t>
         </is>
       </c>
       <c r="H21" s="70" t="inlineStr">
@@ -9599,20 +9599,20 @@
         </is>
       </c>
       <c r="C23" s="66" t="n">
-        <v>1.4487</v>
+        <v>1.3576</v>
       </c>
       <c r="D23" s="66" t="n">
         <v>1.1589</v>
       </c>
       <c r="E23" s="67" t="n">
-        <v>875</v>
+        <v>820</v>
       </c>
       <c r="F23" s="67" t="n">
         <v>700</v>
       </c>
-      <c r="G23" s="71" t="inlineStr">
-        <is>
-          <t>▲ +6.6%</t>
+      <c r="G23" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="70" t="inlineStr">
@@ -10253,13 +10253,13 @@
       </c>
       <c r="B46" s="143" t="n"/>
       <c r="C46" s="144" t="n">
-        <v>1.42908</v>
+        <v>1.468713333333333</v>
       </c>
       <c r="D46" s="144" t="n">
-        <v>1.377906666666666</v>
+        <v>1.419726666666666</v>
       </c>
       <c r="E46" s="145" t="n">
-        <v>0.6602</v>
+        <v>0.7476</v>
       </c>
       <c r="F46" s="146" t="n">
         <v>2.8617</v>
@@ -10525,20 +10525,20 @@
         </is>
       </c>
       <c r="C54" s="57" t="n">
-        <v>1.0606</v>
+        <v>1.1039</v>
       </c>
       <c r="D54" s="57" t="n">
-        <v>1.0087</v>
+        <v>1.0519</v>
       </c>
       <c r="E54" s="58" t="n">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="F54" s="58" t="n">
-        <v>4660</v>
+        <v>4860</v>
       </c>
       <c r="G54" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.2%</t>
+          <t>▼ -7.5%</t>
         </is>
       </c>
       <c r="H54" s="61" t="inlineStr">
@@ -10729,20 +10729,20 @@
         </is>
       </c>
       <c r="C60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="D60" s="57" t="n">
-        <v>0.6602</v>
+        <v>1.2544</v>
       </c>
       <c r="E60" s="58" t="n">
-        <v>3000</v>
+        <v>5700</v>
       </c>
       <c r="F60" s="58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G60" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5700</v>
+      </c>
+      <c r="G60" s="71" t="inlineStr">
+        <is>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="H60" s="61" t="inlineStr">
@@ -10797,20 +10797,20 @@
         </is>
       </c>
       <c r="C62" s="57" t="n">
-        <v>1.464</v>
+        <v>1.421</v>
       </c>
       <c r="D62" s="57" t="n">
-        <v>1.4196</v>
+        <v>1.4095</v>
       </c>
       <c r="E62" s="58" t="n">
-        <v>5244</v>
+        <v>5090</v>
       </c>
       <c r="F62" s="58" t="n">
-        <v>5085</v>
+        <v>5049</v>
       </c>
       <c r="G62" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.9%</t>
+          <t>▲ +2.8%</t>
         </is>
       </c>
       <c r="H62" s="61" t="inlineStr">

--- a/africa_fuel_tracker_latest.xlsx
+++ b/africa_fuel_tracker_latest.xlsx
@@ -1612,7 +1612,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-10</t>
+          <t>Official fuel price intelligence  ·  54 African nations  ·  Updated: 2026-05-11</t>
         </is>
       </c>
       <c r="H3" s="1" t="n"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$1.221</t>
+          <t>$1.245</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>+90.0%</t>
+          <t>+98.3%</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>$1.200</t>
+          <t>$1.225</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1765,16 +1765,16 @@
         <v>6</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>0.7590833333333333</v>
+        <v>0.7771333333333333</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0.6987833333333334</v>
+        <v>0.6507499999999999</v>
       </c>
       <c r="F12" s="27" t="n">
         <v>0.0309</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>1.533</v>
+        <v>1.5318</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1787,13 +1787,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>1.16504375</v>
+        <v>1.21135</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1.18040625</v>
+        <v>1.2590625</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>0.6521</v>
+        <v>0.6508</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>1.6391</v>
@@ -1831,10 +1831,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>1.468713333333333</v>
+        <v>1.49662</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>1.419726666666666</v>
+        <v>1.445786666666666</v>
       </c>
       <c r="F15" s="32" t="n">
         <v>0.7476</v>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1"/>
@@ -1971,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-10</t>
+          <t>⛽  ALL COUNTRIES — CURRENT FUEL PRICES  ·  2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
         </is>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.3678</v>
+        <v>0.4175</v>
       </c>
       <c r="F5" s="66" t="n">
-        <v>0.5964</v>
+        <v>0.2584</v>
       </c>
       <c r="G5" s="67" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I5" s="68" t="n">
         <v>50.3</v>
       </c>
       <c r="J5" s="69" t="inlineStr">
         <is>
-          <t>▼ -22.9%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="K5" s="70" t="inlineStr">
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="E7" s="66" t="n">
-        <v>1.4357</v>
+        <v>1.4955</v>
       </c>
       <c r="F7" s="66" t="n">
-        <v>1.4457</v>
+        <v>1.4955</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="I7" s="68" t="n">
         <v>10.03</v>
       </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.5%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="K7" s="70" t="inlineStr">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="E8" s="57" t="n">
-        <v>1.533</v>
+        <v>1.5318</v>
       </c>
       <c r="F8" s="57" t="n">
         <v>1.1605</v>
       </c>
       <c r="G8" s="58" t="n">
-        <v>922.1</v>
+        <v>921.4</v>
       </c>
       <c r="H8" s="58" t="n">
         <v>698.026</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="J8" s="71" t="inlineStr">
         <is>
-          <t>▲ +46.4%</t>
+          <t>▲ +46.2%</t>
         </is>
       </c>
       <c r="K8" s="61" t="inlineStr">
@@ -2353,13 +2353,13 @@
         <v>1.2003</v>
       </c>
       <c r="F11" s="66" t="n">
-        <v>1.1921</v>
+        <v>1.2417</v>
       </c>
       <c r="G11" s="67" t="n">
         <v>725</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="I11" s="68" t="n">
         <v>604</v>
@@ -2444,23 +2444,23 @@
         </is>
       </c>
       <c r="E13" s="66" t="n">
-        <v>1.3665</v>
+        <v>1.3674</v>
       </c>
       <c r="F13" s="66" t="n">
-        <v>1.1403</v>
+        <v>1.1484</v>
       </c>
       <c r="G13" s="67" t="n">
-        <v>151</v>
+        <v>151.1</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>126</v>
+        <v>126.9</v>
       </c>
       <c r="I13" s="68" t="n">
         <v>110.5</v>
       </c>
       <c r="J13" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.0%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="K13" s="70" t="inlineStr">
@@ -2585,23 +2585,23 @@
         </is>
       </c>
       <c r="E16" s="57" t="n">
-        <v>0.9249000000000001</v>
+        <v>1.3873</v>
       </c>
       <c r="F16" s="57" t="n">
-        <v>0.9249000000000001</v>
+        <v>1.3873</v>
       </c>
       <c r="G16" s="58" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="H16" s="58" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="I16" s="59" t="n">
         <v>8650</v>
       </c>
-      <c r="J16" s="69" t="inlineStr">
-        <is>
-          <t>▼ -32.4%</t>
+      <c r="J16" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="K16" s="61" t="inlineStr">
@@ -2682,13 +2682,13 @@
         <v>1.3576</v>
       </c>
       <c r="F18" s="57" t="n">
-        <v>1.1589</v>
+        <v>1.1175</v>
       </c>
       <c r="G18" s="58" t="n">
         <v>820</v>
       </c>
       <c r="H18" s="58" t="n">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="I18" s="59" t="n">
         <v>604</v>
@@ -2726,23 +2726,23 @@
         </is>
       </c>
       <c r="E19" s="66" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="F19" s="66" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="G19" s="67" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="I19" s="68" t="n">
         <v>194</v>
       </c>
       <c r="J19" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="K19" s="70" t="inlineStr">
@@ -2773,23 +2773,23 @@
         </is>
       </c>
       <c r="E20" s="57" t="n">
-        <v>1.2831</v>
+        <v>1.4487</v>
       </c>
       <c r="F20" s="57" t="n">
-        <v>1.2003</v>
+        <v>1.5563</v>
       </c>
       <c r="G20" s="58" t="n">
-        <v>775</v>
+        <v>875</v>
       </c>
       <c r="H20" s="58" t="n">
-        <v>725</v>
+        <v>940</v>
       </c>
       <c r="I20" s="59" t="n">
         <v>604</v>
       </c>
-      <c r="J20" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J20" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="K20" s="61" t="inlineStr">
@@ -2914,23 +2914,23 @@
         </is>
       </c>
       <c r="E23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.6508</v>
       </c>
       <c r="F23" s="66" t="n">
-        <v>0.6521</v>
+        <v>0.6508</v>
       </c>
       <c r="G23" s="67" t="n">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="H23" s="67" t="n">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="I23" s="68" t="n">
         <v>1621</v>
       </c>
       <c r="J23" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="K23" s="70" t="inlineStr">
@@ -3680,23 +3680,23 @@
         </is>
       </c>
       <c r="E41" s="66" t="n">
-        <v>1.009</v>
+        <v>1.2786</v>
       </c>
       <c r="F41" s="66" t="n">
-        <v>1.0675</v>
+        <v>1.3776</v>
       </c>
       <c r="G41" s="67" t="n">
-        <v>132.18</v>
+        <v>167.5</v>
       </c>
       <c r="H41" s="67" t="n">
-        <v>139.84</v>
+        <v>180.46</v>
       </c>
       <c r="I41" s="68" t="n">
         <v>131</v>
       </c>
       <c r="J41" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +98.3%</t>
         </is>
       </c>
       <c r="K41" s="70" t="inlineStr">
@@ -3962,23 +3962,23 @@
         </is>
       </c>
       <c r="E47" s="66" t="n">
-        <v>1.4968</v>
+        <v>1.6028</v>
       </c>
       <c r="F47" s="66" t="n">
-        <v>1.5682</v>
+        <v>1.6389</v>
       </c>
       <c r="G47" s="67" t="n">
-        <v>21.18</v>
+        <v>22.68</v>
       </c>
       <c r="H47" s="67" t="n">
-        <v>22.19</v>
+        <v>23.19</v>
       </c>
       <c r="I47" s="68" t="n">
         <v>14.15</v>
       </c>
       <c r="J47" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +13.6%</t>
         </is>
       </c>
       <c r="K47" s="70" t="inlineStr">
@@ -4150,23 +4150,23 @@
         </is>
       </c>
       <c r="E51" s="66" t="n">
-        <v>1.421</v>
+        <v>1.464</v>
       </c>
       <c r="F51" s="66" t="n">
-        <v>1.4095</v>
+        <v>1.4196</v>
       </c>
       <c r="G51" s="67" t="n">
-        <v>5090</v>
+        <v>5244</v>
       </c>
       <c r="H51" s="67" t="n">
-        <v>5049</v>
+        <v>5085</v>
       </c>
       <c r="I51" s="68" t="n">
         <v>3582</v>
       </c>
       <c r="J51" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="K51" s="70" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E63" s="77" t="n">
-        <v>1.221175925925926</v>
+        <v>1.244653703703704</v>
       </c>
       <c r="F63" s="77" t="n">
-        <v>1.199975925925926</v>
+        <v>1.225183333333334</v>
       </c>
       <c r="G63" s="78" t="n"/>
       <c r="H63" s="78" t="n"/>
@@ -4694,7 +4694,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="50" t="inlineStr">
         <is>
-          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-10</t>
+          <t>⛽  PRICE HISTORY  ·  JAN 2026 → 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4841,29 +4841,29 @@
         <v>0.4771</v>
       </c>
       <c r="D6" s="91" t="n">
-        <v>0.3678</v>
+        <v>0.4175</v>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>▼ -22.9%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
       <c r="F6" s="90" t="n">
         <v>0.4076</v>
       </c>
       <c r="G6" s="91" t="n">
-        <v>0.5964</v>
-      </c>
-      <c r="H6" s="71" t="inlineStr">
-        <is>
-          <t>▲ +46.3%</t>
+        <v>0.2584</v>
+      </c>
+      <c r="H6" s="69" t="inlineStr">
+        <is>
+          <t>▼ -36.6%</t>
         </is>
       </c>
       <c r="I6" s="58" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="J6" s="58" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K6" s="61" t="inlineStr">
         <is>
@@ -4931,29 +4931,29 @@
         <v>1.2762</v>
       </c>
       <c r="D8" s="91" t="n">
-        <v>1.4357</v>
+        <v>1.4955</v>
       </c>
       <c r="E8" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.5%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="F8" s="90" t="n">
         <v>1.1466</v>
       </c>
       <c r="G8" s="91" t="n">
-        <v>1.4457</v>
+        <v>1.4955</v>
       </c>
       <c r="H8" s="71" t="inlineStr">
         <is>
-          <t>▲ +26.1%</t>
+          <t>▲ +30.4%</t>
         </is>
       </c>
       <c r="I8" s="58" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="K8" s="61" t="inlineStr">
         <is>
@@ -4976,11 +4976,11 @@
         <v>1.0474</v>
       </c>
       <c r="D9" s="89" t="n">
-        <v>1.533</v>
+        <v>1.5318</v>
       </c>
       <c r="E9" s="71" t="inlineStr">
         <is>
-          <t>▲ +46.4%</t>
+          <t>▲ +46.2%</t>
         </is>
       </c>
       <c r="F9" s="90" t="n">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="I9" s="67" t="n">
-        <v>922.1</v>
+        <v>921.4</v>
       </c>
       <c r="J9" s="67" t="n">
         <v>698.026</v>
@@ -5084,18 +5084,18 @@
         <v>1.2593</v>
       </c>
       <c r="G12" s="91" t="n">
-        <v>1.1921</v>
+        <v>1.2417</v>
       </c>
       <c r="H12" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.3%</t>
+          <t>▼ -1.4%</t>
         </is>
       </c>
       <c r="I12" s="58" t="n">
         <v>725</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="K12" s="61" t="inlineStr">
         <is>
@@ -5163,29 +5163,29 @@
         <v>1.2886</v>
       </c>
       <c r="D14" s="91" t="n">
-        <v>1.3665</v>
+        <v>1.3674</v>
       </c>
       <c r="E14" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.0%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="F14" s="90" t="n">
         <v>1.0826</v>
       </c>
       <c r="G14" s="91" t="n">
-        <v>1.1403</v>
+        <v>1.1484</v>
       </c>
       <c r="H14" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.3%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="I14" s="58" t="n">
-        <v>151</v>
+        <v>151.1</v>
       </c>
       <c r="J14" s="58" t="n">
-        <v>126</v>
+        <v>126.9</v>
       </c>
       <c r="K14" s="61" t="inlineStr">
         <is>
@@ -5298,29 +5298,29 @@
         <v>1.3681</v>
       </c>
       <c r="D17" s="89" t="n">
-        <v>0.9249000000000001</v>
-      </c>
-      <c r="E17" s="69" t="inlineStr">
-        <is>
-          <t>▼ -32.4%</t>
+        <v>1.3873</v>
+      </c>
+      <c r="E17" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.4%</t>
         </is>
       </c>
       <c r="F17" s="90" t="n">
         <v>1.341</v>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.9249000000000001</v>
-      </c>
-      <c r="H17" s="69" t="inlineStr">
-        <is>
-          <t>▼ -31.0%</t>
+        <v>1.3873</v>
+      </c>
+      <c r="H17" s="71" t="inlineStr">
+        <is>
+          <t>▲ +3.5%</t>
         </is>
       </c>
       <c r="I17" s="67" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="J17" s="67" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="K17" s="70" t="inlineStr">
         <is>
@@ -5399,18 +5399,18 @@
         <v>1.1185</v>
       </c>
       <c r="G19" s="89" t="n">
-        <v>1.1589</v>
-      </c>
-      <c r="H19" s="71" t="inlineStr">
-        <is>
-          <t>▲ +3.6%</t>
+        <v>1.1175</v>
+      </c>
+      <c r="H19" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I19" s="67" t="n">
         <v>820</v>
       </c>
       <c r="J19" s="67" t="n">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="K19" s="70" t="inlineStr">
         <is>
@@ -5433,29 +5433,29 @@
         <v>0.8608</v>
       </c>
       <c r="D20" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.0772</v>
       </c>
       <c r="E20" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="F20" s="90" t="n">
         <v>0.9124</v>
       </c>
       <c r="G20" s="91" t="n">
-        <v>0.9639</v>
+        <v>1.389</v>
       </c>
       <c r="H20" s="71" t="inlineStr">
         <is>
-          <t>▲ +5.6%</t>
+          <t>▲ +52.2%</t>
         </is>
       </c>
       <c r="I20" s="58" t="n">
-        <v>187</v>
+        <v>208.97</v>
       </c>
       <c r="J20" s="58" t="n">
-        <v>187</v>
+        <v>269.46</v>
       </c>
       <c r="K20" s="61" t="inlineStr">
         <is>
@@ -5478,29 +5478,29 @@
         <v>1.2831</v>
       </c>
       <c r="D21" s="89" t="n">
-        <v>1.2831</v>
-      </c>
-      <c r="E21" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.4487</v>
+      </c>
+      <c r="E21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="F21" s="90" t="n">
         <v>1.2003</v>
       </c>
       <c r="G21" s="89" t="n">
-        <v>1.2003</v>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.5563</v>
+      </c>
+      <c r="H21" s="71" t="inlineStr">
+        <is>
+          <t>▲ +29.7%</t>
         </is>
       </c>
       <c r="I21" s="67" t="n">
-        <v>775</v>
+        <v>875</v>
       </c>
       <c r="J21" s="67" t="n">
-        <v>725</v>
+        <v>940</v>
       </c>
       <c r="K21" s="70" t="inlineStr">
         <is>
@@ -5613,29 +5613,29 @@
         <v>0.5861</v>
       </c>
       <c r="D24" s="91" t="n">
-        <v>0.6521</v>
+        <v>0.6508</v>
       </c>
       <c r="E24" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="F24" s="90" t="n">
         <v>0.7403</v>
       </c>
       <c r="G24" s="91" t="n">
-        <v>0.6521</v>
+        <v>0.6508</v>
       </c>
       <c r="H24" s="69" t="inlineStr">
         <is>
-          <t>▼ -11.9%</t>
+          <t>▼ -12.1%</t>
         </is>
       </c>
       <c r="I24" s="58" t="n">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="J24" s="58" t="n">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="K24" s="61" t="inlineStr">
         <is>
@@ -6347,29 +6347,29 @@
         <v>0.6447000000000001</v>
       </c>
       <c r="D42" s="91" t="n">
-        <v>1.009</v>
+        <v>1.2786</v>
       </c>
       <c r="E42" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +98.3%</t>
         </is>
       </c>
       <c r="F42" s="90" t="n">
         <v>0.6288</v>
       </c>
       <c r="G42" s="91" t="n">
-        <v>1.0675</v>
+        <v>1.3776</v>
       </c>
       <c r="H42" s="71" t="inlineStr">
         <is>
-          <t>▲ +69.8%</t>
+          <t>▲ +119.1%</t>
         </is>
       </c>
       <c r="I42" s="58" t="n">
-        <v>132.18</v>
+        <v>167.5</v>
       </c>
       <c r="J42" s="58" t="n">
-        <v>139.84</v>
+        <v>180.46</v>
       </c>
       <c r="K42" s="61" t="inlineStr">
         <is>
@@ -6617,29 +6617,29 @@
         <v>1.4106</v>
       </c>
       <c r="D48" s="91" t="n">
-        <v>1.4968</v>
+        <v>1.6028</v>
       </c>
       <c r="E48" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +13.6%</t>
         </is>
       </c>
       <c r="F48" s="90" t="n">
         <v>1.33</v>
       </c>
       <c r="G48" s="91" t="n">
-        <v>1.5682</v>
+        <v>1.6389</v>
       </c>
       <c r="H48" s="71" t="inlineStr">
         <is>
-          <t>▲ +17.9%</t>
+          <t>▲ +23.2%</t>
         </is>
       </c>
       <c r="I48" s="58" t="n">
-        <v>21.18</v>
+        <v>22.68</v>
       </c>
       <c r="J48" s="58" t="n">
-        <v>22.19</v>
+        <v>23.19</v>
       </c>
       <c r="K48" s="61" t="inlineStr">
         <is>
@@ -6797,29 +6797,29 @@
         <v>1.3819</v>
       </c>
       <c r="D52" s="91" t="n">
-        <v>1.421</v>
+        <v>1.464</v>
       </c>
       <c r="E52" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="F52" s="90" t="n">
         <v>1.2741</v>
       </c>
       <c r="G52" s="91" t="n">
-        <v>1.4095</v>
+        <v>1.4196</v>
       </c>
       <c r="H52" s="71" t="inlineStr">
         <is>
-          <t>▲ +10.6%</t>
+          <t>▲ +11.4%</t>
         </is>
       </c>
       <c r="I52" s="58" t="n">
-        <v>5090</v>
+        <v>5244</v>
       </c>
       <c r="J52" s="58" t="n">
-        <v>5049</v>
+        <v>5085</v>
       </c>
       <c r="K52" s="61" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7527,14 +7527,14 @@
         </is>
       </c>
       <c r="I8" s="108" t="n">
-        <v>0.3678</v>
+        <v>0.4175</v>
       </c>
       <c r="J8" s="109" t="n">
-        <v>0.5964</v>
+        <v>0.2584</v>
       </c>
       <c r="K8" s="106" t="inlineStr">
         <is>
-          <t>▼ -22.9%</t>
+          <t>▼ -12.5%</t>
         </is>
       </c>
     </row>
@@ -7571,14 +7571,14 @@
         </is>
       </c>
       <c r="I9" s="101" t="n">
-        <v>0.6521</v>
+        <v>0.6508</v>
       </c>
       <c r="J9" s="102" t="n">
-        <v>0.6521</v>
+        <v>0.6508</v>
       </c>
       <c r="K9" s="114" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7.  Somalia</t>
+          <t xml:space="preserve">  7.  Seychelles</t>
         </is>
       </c>
       <c r="B11" s="96" t="inlineStr">
@@ -7638,14 +7638,14 @@
         </is>
       </c>
       <c r="C11" s="97" t="n">
-        <v>1.6</v>
+        <v>1.6028</v>
       </c>
       <c r="D11" s="98" t="n">
-        <v>1.4</v>
+        <v>1.6389</v>
       </c>
       <c r="E11" s="114" t="inlineStr">
         <is>
-          <t>▲ +39.1%</t>
+          <t>▲ +13.6%</t>
         </is>
       </c>
       <c r="G11" s="113" t="inlineStr">
@@ -7673,23 +7673,23 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8.  Sierra Leone</t>
+          <t xml:space="preserve">  8.  Somalia</t>
         </is>
       </c>
       <c r="B12" s="103" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C12" s="104" t="n">
-        <v>1.5556</v>
+        <v>1.6</v>
       </c>
       <c r="D12" s="105" t="n">
-        <v>1.7778</v>
+        <v>1.4</v>
       </c>
       <c r="E12" s="114" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +39.1%</t>
         </is>
       </c>
       <c r="G12" s="111" t="inlineStr">
@@ -7717,7 +7717,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9.  Gambia</t>
+          <t xml:space="preserve">  9.  Sierra Leone</t>
         </is>
       </c>
       <c r="B13" s="96" t="inlineStr">
@@ -7726,14 +7726,14 @@
         </is>
       </c>
       <c r="C13" s="97" t="n">
-        <v>1.5342</v>
+        <v>1.5556</v>
       </c>
       <c r="D13" s="98" t="n">
-        <v>1.6438</v>
+        <v>1.7778</v>
       </c>
       <c r="E13" s="114" t="inlineStr">
         <is>
-          <t>▲ +41.0%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G13" s="113" t="inlineStr">
@@ -7761,23 +7761,23 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.  Sudan</t>
+          <t xml:space="preserve">  10.  Gambia</t>
         </is>
       </c>
       <c r="B14" s="103" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C14" s="104" t="n">
-        <v>1.533</v>
+        <v>1.5342</v>
       </c>
       <c r="D14" s="105" t="n">
-        <v>1.1605</v>
+        <v>1.6438</v>
       </c>
       <c r="E14" s="114" t="inlineStr">
         <is>
-          <t>▲ +46.4%</t>
+          <t>▲ +41.0%</t>
         </is>
       </c>
       <c r="G14" s="111" t="inlineStr">
@@ -7850,7 +7850,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -7860,28 +7860,28 @@
       </c>
       <c r="C19" s="116" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>ETB</t>
         </is>
       </c>
       <c r="D19" s="88" t="n">
-        <v>0.6602</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="E19" s="91" t="n">
-        <v>1.2544</v>
+        <v>1.2786</v>
       </c>
       <c r="F19" s="71" t="inlineStr">
         <is>
-          <t>▲ +90.0%</t>
+          <t>▲ +98.3%</t>
         </is>
       </c>
       <c r="G19" s="117" t="n">
-        <v>0.5942</v>
+        <v>0.6339</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
@@ -7891,22 +7891,22 @@
       </c>
       <c r="C20" s="118" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D20" s="88" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="E20" s="89" t="n">
-        <v>1.009</v>
+        <v>1.2544</v>
       </c>
       <c r="F20" s="71" t="inlineStr">
         <is>
-          <t>▲ +56.5%</t>
+          <t>▲ +90.0%</t>
         </is>
       </c>
       <c r="G20" s="117" t="n">
-        <v>0.3643</v>
+        <v>0.5942</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -7929,15 +7929,15 @@
         <v>1.0474</v>
       </c>
       <c r="E21" s="91" t="n">
-        <v>1.533</v>
+        <v>1.5318</v>
       </c>
       <c r="F21" s="71" t="inlineStr">
         <is>
-          <t>▲ +46.4%</t>
+          <t>▲ +46.2%</t>
         </is>
       </c>
       <c r="G21" s="117" t="n">
-        <v>0.4856</v>
+        <v>0.4844</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -8036,32 +8036,32 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="53" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C25" s="116" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>LRD</t>
         </is>
       </c>
       <c r="D25" s="88" t="n">
-        <v>1.2332</v>
+        <v>0.8608</v>
       </c>
       <c r="E25" s="91" t="n">
-        <v>1.4286</v>
+        <v>1.0772</v>
       </c>
       <c r="F25" s="71" t="inlineStr">
         <is>
-          <t>▲ +15.8%</t>
+          <t>▲ +25.1%</t>
         </is>
       </c>
       <c r="G25" s="117" t="n">
-        <v>0.1954</v>
+        <v>0.2164</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -8084,21 +8084,21 @@
         <v>1.2762</v>
       </c>
       <c r="E26" s="89" t="n">
-        <v>1.4357</v>
+        <v>1.4955</v>
       </c>
       <c r="F26" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.5%</t>
+          <t>▲ +17.2%</t>
         </is>
       </c>
       <c r="G26" s="117" t="n">
-        <v>0.1595</v>
+        <v>0.2193</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B27" s="54" t="inlineStr">
@@ -8108,59 +8108,59 @@
       </c>
       <c r="C27" s="116" t="inlineStr">
         <is>
-          <t>SZL</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="D27" s="88" t="n">
-        <v>1.0722</v>
+        <v>1.2332</v>
       </c>
       <c r="E27" s="91" t="n">
-        <v>1.2049</v>
+        <v>1.4286</v>
       </c>
       <c r="F27" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.4%</t>
+          <t>▲ +15.8%</t>
         </is>
       </c>
       <c r="G27" s="117" t="n">
-        <v>0.1327</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C28" s="118" t="inlineStr">
         <is>
-          <t>LRD</t>
+          <t>SCR</t>
         </is>
       </c>
       <c r="D28" s="88" t="n">
-        <v>0.8608</v>
+        <v>1.4106</v>
       </c>
       <c r="E28" s="89" t="n">
-        <v>0.9639</v>
+        <v>1.6028</v>
       </c>
       <c r="F28" s="71" t="inlineStr">
         <is>
-          <t>▲ +12.0%</t>
+          <t>▲ +13.6%</t>
         </is>
       </c>
       <c r="G28" s="117" t="n">
-        <v>0.1031</v>
+        <v>0.1922</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="B29" s="54" t="inlineStr">
@@ -8170,28 +8170,28 @@
       </c>
       <c r="C29" s="116" t="inlineStr">
         <is>
-          <t>NGN</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D29" s="88" t="n">
-        <v>0.5861</v>
+        <v>1.2831</v>
       </c>
       <c r="E29" s="91" t="n">
-        <v>0.6521</v>
+        <v>1.4487</v>
       </c>
       <c r="F29" s="71" t="inlineStr">
         <is>
-          <t>▲ +11.3%</t>
+          <t>▲ +12.9%</t>
         </is>
       </c>
       <c r="G29" s="117" t="n">
-        <v>0.066</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
@@ -8201,28 +8201,28 @@
       </c>
       <c r="C30" s="118" t="inlineStr">
         <is>
-          <t>BWP</t>
+          <t>SZL</t>
         </is>
       </c>
       <c r="D30" s="88" t="n">
-        <v>1.1425</v>
+        <v>1.0722</v>
       </c>
       <c r="E30" s="89" t="n">
-        <v>1.2555</v>
+        <v>1.2049</v>
       </c>
       <c r="F30" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.9%</t>
+          <t>▲ +12.4%</t>
         </is>
       </c>
       <c r="G30" s="117" t="n">
-        <v>0.113</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B31" s="54" t="inlineStr">
@@ -8232,59 +8232,59 @@
       </c>
       <c r="C31" s="116" t="inlineStr">
         <is>
-          <t>SLL</t>
+          <t>NGN</t>
         </is>
       </c>
       <c r="D31" s="88" t="n">
-        <v>1.4222</v>
+        <v>0.5861</v>
       </c>
       <c r="E31" s="91" t="n">
-        <v>1.5556</v>
+        <v>0.6508</v>
       </c>
       <c r="F31" s="71" t="inlineStr">
         <is>
-          <t>▲ +9.4%</t>
+          <t>▲ +11.0%</t>
         </is>
       </c>
       <c r="G31" s="117" t="n">
-        <v>0.1334</v>
+        <v>0.06469999999999999</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C32" s="118" t="inlineStr">
         <is>
-          <t>KES</t>
+          <t>BWP</t>
         </is>
       </c>
       <c r="D32" s="88" t="n">
-        <v>1.3986</v>
+        <v>1.1425</v>
       </c>
       <c r="E32" s="89" t="n">
-        <v>1.5142</v>
+        <v>1.2555</v>
       </c>
       <c r="F32" s="71" t="inlineStr">
         <is>
-          <t>▲ +8.3%</t>
+          <t>▲ +9.9%</t>
         </is>
       </c>
       <c r="G32" s="117" t="n">
-        <v>0.1156</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="53" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B33" s="54" t="inlineStr">
@@ -8294,28 +8294,28 @@
       </c>
       <c r="C33" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="D33" s="88" t="n">
-        <v>1.5244</v>
+        <v>1.4222</v>
       </c>
       <c r="E33" s="91" t="n">
-        <v>1.6391</v>
+        <v>1.5556</v>
       </c>
       <c r="F33" s="71" t="inlineStr">
         <is>
-          <t>▲ +7.5%</t>
+          <t>▲ +9.4%</t>
         </is>
       </c>
       <c r="G33" s="117" t="n">
-        <v>0.1147</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -8325,28 +8325,28 @@
       </c>
       <c r="C34" s="118" t="inlineStr">
         <is>
-          <t>SCR</t>
+          <t>KES</t>
         </is>
       </c>
       <c r="D34" s="88" t="n">
-        <v>1.4106</v>
+        <v>1.3986</v>
       </c>
       <c r="E34" s="89" t="n">
-        <v>1.4968</v>
+        <v>1.5142</v>
       </c>
       <c r="F34" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.1%</t>
+          <t>▲ +8.3%</t>
         </is>
       </c>
       <c r="G34" s="117" t="n">
-        <v>0.0862</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="53" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr">
@@ -8356,59 +8356,59 @@
       </c>
       <c r="C35" s="116" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D35" s="88" t="n">
-        <v>1.2886</v>
+        <v>1.5244</v>
       </c>
       <c r="E35" s="91" t="n">
-        <v>1.3665</v>
+        <v>1.6391</v>
       </c>
       <c r="F35" s="71" t="inlineStr">
         <is>
-          <t>▲ +6.0%</t>
+          <t>▲ +7.5%</t>
         </is>
       </c>
       <c r="G35" s="117" t="n">
-        <v>0.0779</v>
+        <v>0.1147</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C36" s="118" t="inlineStr">
         <is>
-          <t>UGX</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D36" s="88" t="n">
-        <v>1.3819</v>
+        <v>1.2886</v>
       </c>
       <c r="E36" s="89" t="n">
-        <v>1.421</v>
+        <v>1.3674</v>
       </c>
       <c r="F36" s="71" t="inlineStr">
         <is>
-          <t>▲ +2.8%</t>
+          <t>▲ +6.1%</t>
         </is>
       </c>
       <c r="G36" s="117" t="n">
-        <v>0.0391</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr">
@@ -8418,400 +8418,400 @@
       </c>
       <c r="C37" s="116" t="inlineStr">
         <is>
-          <t>BIF</t>
+          <t>UGX</t>
         </is>
       </c>
       <c r="D37" s="88" t="n">
-        <v>1.3479</v>
+        <v>1.3819</v>
       </c>
       <c r="E37" s="91" t="n">
-        <v>1.3699</v>
+        <v>1.464</v>
       </c>
       <c r="F37" s="71" t="inlineStr">
         <is>
-          <t>▲ +1.6%</t>
+          <t>▲ +5.9%</t>
         </is>
       </c>
       <c r="G37" s="117" t="n">
-        <v>0.022</v>
+        <v>0.08210000000000001</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C38" s="118" t="inlineStr">
         <is>
-          <t>NAD</t>
+          <t>BIF</t>
         </is>
       </c>
       <c r="D38" s="88" t="n">
-        <v>1.0555</v>
+        <v>1.3479</v>
       </c>
       <c r="E38" s="89" t="n">
-        <v>1.0582</v>
+        <v>1.3699</v>
       </c>
       <c r="F38" s="71" t="inlineStr">
         <is>
-          <t>▲ +0.3%</t>
+          <t>▲ +1.6%</t>
         </is>
       </c>
       <c r="G38" s="117" t="n">
-        <v>0.0027</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="53" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B39" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C39" s="116" t="inlineStr">
         <is>
-          <t>MZN</t>
+          <t>GNF</t>
         </is>
       </c>
       <c r="D39" s="88" t="n">
-        <v>1.31</v>
+        <v>1.3681</v>
       </c>
       <c r="E39" s="91" t="n">
-        <v>1.3037</v>
-      </c>
-      <c r="F39" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.5%</t>
-        </is>
-      </c>
-      <c r="G39" s="119" t="n">
-        <v>-0.0063</v>
+        <v>1.3873</v>
+      </c>
+      <c r="F39" s="71" t="inlineStr">
+        <is>
+          <t>▲ +1.4%</t>
+        </is>
+      </c>
+      <c r="G39" s="117" t="n">
+        <v>0.0192</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C40" s="118" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>NAD</t>
         </is>
       </c>
       <c r="D40" s="88" t="n">
-        <v>1.3691</v>
+        <v>1.0555</v>
       </c>
       <c r="E40" s="89" t="n">
-        <v>1.3595</v>
-      </c>
-      <c r="F40" s="69" t="inlineStr">
-        <is>
-          <t>▼ -0.7%</t>
-        </is>
-      </c>
-      <c r="G40" s="119" t="n">
-        <v>-0.009599999999999999</v>
+        <v>1.0582</v>
+      </c>
+      <c r="F40" s="71" t="inlineStr">
+        <is>
+          <t>▲ +0.3%</t>
+        </is>
+      </c>
+      <c r="G40" s="117" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="53" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C41" s="116" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MZN</t>
         </is>
       </c>
       <c r="D41" s="88" t="n">
-        <v>1.2677</v>
+        <v>1.31</v>
       </c>
       <c r="E41" s="91" t="n">
-        <v>1.257</v>
+        <v>1.3037</v>
       </c>
       <c r="F41" s="69" t="inlineStr">
         <is>
-          <t>▼ -0.8%</t>
+          <t>▼ -0.5%</t>
         </is>
       </c>
       <c r="G41" s="119" t="n">
-        <v>-0.0107</v>
+        <v>-0.0063</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C42" s="118" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="D42" s="88" t="n">
-        <v>1.3289</v>
+        <v>1.3691</v>
       </c>
       <c r="E42" s="89" t="n">
-        <v>1.3146</v>
+        <v>1.3595</v>
       </c>
       <c r="F42" s="69" t="inlineStr">
         <is>
-          <t>▼ -1.1%</t>
+          <t>▼ -0.7%</t>
         </is>
       </c>
       <c r="G42" s="119" t="n">
-        <v>-0.0143</v>
+        <v>-0.009599999999999999</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="53" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C43" s="116" t="inlineStr">
         <is>
-          <t>XOF</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="D43" s="88" t="n">
-        <v>1.2262</v>
+        <v>1.2677</v>
       </c>
       <c r="E43" s="91" t="n">
-        <v>1.2003</v>
+        <v>1.257</v>
       </c>
       <c r="F43" s="69" t="inlineStr">
         <is>
-          <t>▼ -2.1%</t>
+          <t>▼ -0.8%</t>
         </is>
       </c>
       <c r="G43" s="119" t="n">
-        <v>-0.0259</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C44" s="118" t="inlineStr">
         <is>
-          <t>KMF</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D44" s="88" t="n">
-        <v>1.784</v>
+        <v>1.3289</v>
       </c>
       <c r="E44" s="89" t="n">
-        <v>1.6851</v>
+        <v>1.3146</v>
       </c>
       <c r="F44" s="69" t="inlineStr">
         <is>
-          <t>▼ -5.5%</t>
+          <t>▼ -1.1%</t>
         </is>
       </c>
       <c r="G44" s="119" t="n">
-        <v>-0.0989</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="53" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>ZMW</t>
+          <t>XOF</t>
         </is>
       </c>
       <c r="D45" s="88" t="n">
-        <v>1.0641</v>
+        <v>1.2262</v>
       </c>
       <c r="E45" s="91" t="n">
-        <v>0.9982</v>
+        <v>1.2003</v>
       </c>
       <c r="F45" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.2%</t>
+          <t>▼ -2.1%</t>
         </is>
       </c>
       <c r="G45" s="119" t="n">
-        <v>-0.0659</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="62" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="B46" s="63" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>East Africa</t>
         </is>
       </c>
       <c r="C46" s="118" t="inlineStr">
         <is>
-          <t>ZWG</t>
+          <t>KMF</t>
         </is>
       </c>
       <c r="D46" s="88" t="n">
-        <v>2.17</v>
+        <v>1.784</v>
       </c>
       <c r="E46" s="89" t="n">
-        <v>2.0331</v>
+        <v>1.6851</v>
       </c>
       <c r="F46" s="69" t="inlineStr">
         <is>
-          <t>▼ -6.3%</t>
+          <t>▼ -5.5%</t>
         </is>
       </c>
       <c r="G46" s="119" t="n">
-        <v>-0.1369</v>
+        <v>-0.0989</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="53" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="B47" s="54" t="inlineStr">
         <is>
-          <t>East Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>ZMW</t>
         </is>
       </c>
       <c r="D47" s="88" t="n">
-        <v>1.1939</v>
+        <v>1.0641</v>
       </c>
       <c r="E47" s="91" t="n">
-        <v>1.1039</v>
+        <v>0.9982</v>
       </c>
       <c r="F47" s="69" t="inlineStr">
         <is>
-         